--- a/Financial Analysis/INTC.xlsx
+++ b/Financial Analysis/INTC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C3D2F1-496E-4049-9CB1-DDCA05D92818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3ACCBFA-C7C4-45AA-B6EE-0606E93A7EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{99FD0C39-1228-4528-9306-B2D51C30197E}"/>
   </bookViews>
@@ -897,14 +897,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="9">
-        <v>20.14</v>
+        <v>20.5</v>
       </c>
       <c r="E3" s="4">
-        <v>45771</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45772</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="4">
         <v>45862</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>87468.02</v>
+        <v>89031.5</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -969,7 +969,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>111544.02</v>
+        <v>113107.5</v>
       </c>
     </row>
   </sheetData>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AS43" s="9">
         <f>Main!D3</f>
-        <v>20.14</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="44" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="AS44" s="10">
         <f>AS42/AS43-1</f>
-        <v>-0.37659448511523141</v>
+        <v>-0.38754209415711027</v>
       </c>
     </row>
     <row r="45" spans="2:45" x14ac:dyDescent="0.3">
@@ -8440,7 +8440,7 @@
         <v>21000</v>
       </c>
       <c r="AG85" s="2">
-        <f t="shared" ref="AG85:AP85" si="110">AF85*0.94</f>
+        <f t="shared" ref="AG85:AH85" si="110">AF85*0.94</f>
         <v>19740</v>
       </c>
       <c r="AH85" s="2">
@@ -8452,7 +8452,7 @@
         <v>17627.819999999996</v>
       </c>
       <c r="AJ85" s="2">
-        <f t="shared" ref="AJ85:AP85" si="111">AI85*0.95</f>
+        <f t="shared" ref="AJ85" si="111">AI85*0.95</f>
         <v>16746.428999999996</v>
       </c>
       <c r="AK85" s="2">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="AS94" s="9">
         <f>Main!D3</f>
-        <v>20.14</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="95" spans="2:144" x14ac:dyDescent="0.3">

--- a/Financial Analysis/INTC.xlsx
+++ b/Financial Analysis/INTC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3ACCBFA-C7C4-45AA-B6EE-0606E93A7EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6316778D-0ADD-44D8-ABD6-DB7C7C3B3C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{99FD0C39-1228-4528-9306-B2D51C30197E}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="108">
   <si>
     <t>INTC</t>
   </si>
@@ -349,10 +349,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Overvalued</t>
-  </si>
-  <si>
-    <t>Q125 8K</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -474,16 +471,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>91</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -498,7 +495,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13243560" y="7620"/>
+          <a:off x="13822680" y="0"/>
           <a:ext cx="0" cy="16733520"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -897,17 +894,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="9">
-        <v>20.5</v>
+        <v>32.020000000000003</v>
       </c>
       <c r="E3" s="4">
-        <v>45804</v>
+        <v>45918</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45927</v>
       </c>
       <c r="G3" s="4">
-        <v>45862</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -915,10 +912,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>4343</v>
+        <f>4369</f>
+        <v>4369</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -927,7 +925,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>89031.5</v>
+        <v>139895.38</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -935,11 +933,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>8947+12101+5027</f>
-        <v>26075</v>
+        <f>9643+11563+5383</f>
+        <v>26589</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -947,11 +945,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="2">
-        <f>5240+44911</f>
-        <v>50151</v>
+        <f>6731+44026</f>
+        <v>50757</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -960,7 +958,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>-24076</v>
+        <v>-24168</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -969,7 +967,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>113107.5</v>
+        <v>164063.38</v>
       </c>
     </row>
   </sheetData>
@@ -988,7 +986,7 @@
     <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="8.88671875" customWidth="1"/>
     <col min="44" max="44" width="13.21875" customWidth="1"/>
-    <col min="45" max="45" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:42" x14ac:dyDescent="0.3">
@@ -1327,10 +1325,12 @@
       <c r="S5" s="16">
         <v>8017</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="16">
         <v>7629</v>
       </c>
-      <c r="U5" s="11"/>
+      <c r="U5" s="16">
+        <v>7871</v>
+      </c>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
       <c r="AD5" s="12">
@@ -1426,7 +1426,9 @@
       <c r="T6" s="11">
         <v>4126</v>
       </c>
-      <c r="U6" s="11"/>
+      <c r="U6" s="11">
+        <v>3939</v>
+      </c>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
       <c r="AD6" s="12">
@@ -1923,12 +1925,11 @@
         <v>12667</v>
       </c>
       <c r="U11" s="7">
-        <f>Q11*0.94</f>
-        <v>12063.019999999999</v>
+        <v>12859</v>
       </c>
       <c r="V11" s="7">
-        <f>R11*0.96</f>
-        <v>12752.64</v>
+        <f>R11*0.98</f>
+        <v>13018.32</v>
       </c>
       <c r="W11" s="7">
         <f>S11*0.97</f>
@@ -1961,47 +1962,47 @@
       </c>
       <c r="AF11" s="7">
         <f>SUM(T11:W11)</f>
-        <v>51314.859999999993</v>
+        <v>52376.52</v>
       </c>
       <c r="AG11" s="7">
         <f>AF11*1.1</f>
-        <v>56446.345999999998</v>
+        <v>57614.171999999999</v>
       </c>
       <c r="AH11" s="7">
         <f>AG11*1.07</f>
-        <v>60397.590219999998</v>
+        <v>61647.164040000003</v>
       </c>
       <c r="AI11" s="7">
         <f>AH11*1.05</f>
-        <v>63417.469730999997</v>
+        <v>64729.522242000006</v>
       </c>
       <c r="AJ11" s="7">
         <f>AI11*1.04</f>
-        <v>65954.168520239997</v>
+        <v>67318.703131680013</v>
       </c>
       <c r="AK11" s="7">
         <f>AJ11*1.03</f>
-        <v>67932.793575847201</v>
+        <v>69338.26422563041</v>
       </c>
       <c r="AL11" s="7">
         <f t="shared" ref="AL11:AP11" si="11">AK11*1.03</f>
-        <v>69970.777383122622</v>
+        <v>71418.412152399324</v>
       </c>
       <c r="AM11" s="7">
         <f t="shared" si="11"/>
-        <v>72069.900704616302</v>
+        <v>73560.964516971304</v>
       </c>
       <c r="AN11" s="7">
         <f t="shared" si="11"/>
-        <v>74231.997725754787</v>
+        <v>75767.793452480444</v>
       </c>
       <c r="AO11" s="7">
         <f t="shared" si="11"/>
-        <v>76458.957657527426</v>
+        <v>78040.827256054865</v>
       </c>
       <c r="AP11" s="7">
         <f t="shared" si="11"/>
-        <v>78752.726387253249</v>
+        <v>80382.052073736515</v>
       </c>
     </row>
     <row r="12" spans="2:42" x14ac:dyDescent="0.3">
@@ -2063,16 +2064,15 @@
         <v>7995</v>
       </c>
       <c r="U12" s="2">
-        <f>U11-U13</f>
-        <v>7660.0176999999994</v>
+        <v>9317</v>
       </c>
       <c r="V12" s="2">
         <f t="shared" ref="V12:W12" si="12">V11-V13</f>
-        <v>8034.1632</v>
+        <v>8579.0728799999997</v>
       </c>
       <c r="W12" s="2">
         <f t="shared" si="12"/>
-        <v>8575.9639999999999</v>
+        <v>8714.2860000000001</v>
       </c>
       <c r="Y12" s="2">
         <v>27111</v>
@@ -2101,47 +2101,47 @@
       </c>
       <c r="AF12" s="2">
         <f>SUM(T12:W12)</f>
-        <v>32265.144899999999</v>
+        <v>34605.35888</v>
       </c>
       <c r="AG12" s="2">
         <f t="shared" ref="AG12:AP12" si="13">AG11-AG13</f>
-        <v>33867.8076</v>
+        <v>34568.503199999999</v>
       </c>
       <c r="AH12" s="2">
         <f t="shared" si="13"/>
-        <v>35030.602327600005</v>
+        <v>35755.355143200002</v>
       </c>
       <c r="AI12" s="2">
         <f t="shared" si="13"/>
-        <v>36782.132443980001</v>
+        <v>37543.122900360002</v>
       </c>
       <c r="AJ12" s="2">
         <f t="shared" si="13"/>
-        <v>38253.417741739198</v>
+        <v>39044.847816374408</v>
       </c>
       <c r="AK12" s="2">
         <f t="shared" si="13"/>
-        <v>39401.02027399138</v>
+        <v>40216.193250865639</v>
       </c>
       <c r="AL12" s="2">
         <f t="shared" si="13"/>
-        <v>40583.050882211122</v>
+        <v>41422.679048391612</v>
       </c>
       <c r="AM12" s="2">
         <f t="shared" si="13"/>
-        <v>41800.542408677458</v>
+        <v>42665.359419843357</v>
       </c>
       <c r="AN12" s="2">
         <f t="shared" si="13"/>
-        <v>43054.558680937778</v>
+        <v>43945.320202438656</v>
       </c>
       <c r="AO12" s="2">
         <f t="shared" si="13"/>
-        <v>44346.195441365911</v>
+        <v>45263.679808511821</v>
       </c>
       <c r="AP12" s="2">
         <f t="shared" si="13"/>
-        <v>45676.581304606887</v>
+        <v>46621.590202767176</v>
       </c>
     </row>
     <row r="13" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2149,7 +2149,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:T13" si="14">C11-C12</f>
+        <f t="shared" ref="C13:U13" si="14">C11-C12</f>
         <v>11348</v>
       </c>
       <c r="D13" s="7">
@@ -2221,16 +2221,16 @@
         <v>4672</v>
       </c>
       <c r="U13" s="7">
-        <f>U11*0.365</f>
-        <v>4403.0022999999992</v>
+        <f t="shared" si="14"/>
+        <v>3542</v>
       </c>
       <c r="V13" s="7">
-        <f>V11*0.37</f>
-        <v>4718.4767999999995</v>
+        <f>V11*0.341</f>
+        <v>4439.24712</v>
       </c>
       <c r="W13" s="7">
-        <f>W11*0.38</f>
-        <v>5256.2359999999999</v>
+        <f>W11*0.37</f>
+        <v>5117.9139999999998</v>
       </c>
       <c r="Y13" s="7">
         <f t="shared" ref="Y13:AF13" si="15">Y11-Y12</f>
@@ -2262,47 +2262,47 @@
       </c>
       <c r="AF13" s="7">
         <f t="shared" si="15"/>
-        <v>19049.715099999994</v>
+        <v>17771.161119999997</v>
       </c>
       <c r="AG13" s="7">
         <f>AG11*0.4</f>
-        <v>22578.538400000001</v>
+        <v>23045.668799999999</v>
       </c>
       <c r="AH13" s="7">
         <f>AH11*0.42</f>
-        <v>25366.987892399997</v>
+        <v>25891.808896800001</v>
       </c>
       <c r="AI13" s="7">
         <f t="shared" ref="AI13:AP13" si="16">AI11*0.42</f>
-        <v>26635.337287019996</v>
+        <v>27186.399341640001</v>
       </c>
       <c r="AJ13" s="7">
         <f t="shared" si="16"/>
-        <v>27700.750778500798</v>
+        <v>28273.855315305605</v>
       </c>
       <c r="AK13" s="7">
         <f t="shared" si="16"/>
-        <v>28531.773301855825</v>
+        <v>29122.070974764771</v>
       </c>
       <c r="AL13" s="7">
         <f t="shared" si="16"/>
-        <v>29387.7265009115</v>
+        <v>29995.733104007715</v>
       </c>
       <c r="AM13" s="7">
         <f t="shared" si="16"/>
-        <v>30269.358295938844</v>
+        <v>30895.605097127947</v>
       </c>
       <c r="AN13" s="7">
         <f t="shared" si="16"/>
-        <v>31177.439044817009</v>
+        <v>31822.473250041785</v>
       </c>
       <c r="AO13" s="7">
         <f t="shared" si="16"/>
-        <v>32112.762216161518</v>
+        <v>32777.147447543044</v>
       </c>
       <c r="AP13" s="7">
         <f t="shared" si="16"/>
-        <v>33076.145082646362</v>
+        <v>33760.461870969339</v>
       </c>
     </row>
     <row r="14" spans="2:42" x14ac:dyDescent="0.3">
@@ -2364,16 +2364,15 @@
         <v>3640</v>
       </c>
       <c r="U14" s="2">
-        <f t="shared" ref="U14" si="17">Q14*0.98</f>
-        <v>4154.22</v>
+        <v>3684</v>
       </c>
       <c r="V14" s="2">
-        <f>R14*0.98</f>
-        <v>3968.02</v>
+        <f>R14*0.93</f>
+        <v>3765.57</v>
       </c>
       <c r="W14" s="2">
-        <f>S14*1.05</f>
-        <v>4069.8</v>
+        <f>S14*1.01</f>
+        <v>3914.76</v>
       </c>
       <c r="Y14" s="2">
         <v>13543</v>
@@ -2402,47 +2401,47 @@
       </c>
       <c r="AF14" s="2">
         <f>SUM(T14:W14)</f>
-        <v>15832.04</v>
+        <v>15004.33</v>
       </c>
       <c r="AG14" s="2">
-        <f>AF14*1.02</f>
-        <v>16148.680800000002</v>
+        <f>AF14*0.98</f>
+        <v>14704.243399999999</v>
       </c>
       <c r="AH14" s="2">
         <f>AG14*1.01</f>
-        <v>16310.167608000002</v>
+        <v>14851.285834</v>
       </c>
       <c r="AI14" s="2">
         <f>AH14*1.01</f>
-        <v>16473.269284080001</v>
+        <v>14999.79869234</v>
       </c>
       <c r="AJ14" s="2">
-        <f t="shared" ref="AJ14:AP15" si="18">AI14*1.01</f>
-        <v>16638.001976920801</v>
+        <f t="shared" ref="AJ14:AP15" si="17">AI14*1.01</f>
+        <v>15149.7966792634</v>
       </c>
       <c r="AK14" s="2">
-        <f t="shared" si="18"/>
-        <v>16804.381996690008</v>
+        <f t="shared" si="17"/>
+        <v>15301.294646056034</v>
       </c>
       <c r="AL14" s="2">
-        <f t="shared" si="18"/>
-        <v>16972.425816656909</v>
+        <f t="shared" si="17"/>
+        <v>15454.307592516594</v>
       </c>
       <c r="AM14" s="2">
-        <f t="shared" si="18"/>
-        <v>17142.150074823479</v>
+        <f t="shared" si="17"/>
+        <v>15608.850668441761</v>
       </c>
       <c r="AN14" s="2">
-        <f t="shared" si="18"/>
-        <v>17313.571575571714</v>
+        <f t="shared" si="17"/>
+        <v>15764.939175126179</v>
       </c>
       <c r="AO14" s="2">
-        <f t="shared" si="18"/>
-        <v>17486.707291327431</v>
+        <f t="shared" si="17"/>
+        <v>15922.588566877441</v>
       </c>
       <c r="AP14" s="2">
-        <f t="shared" si="18"/>
-        <v>17661.574364240707</v>
+        <f t="shared" si="17"/>
+        <v>16081.814452546216</v>
       </c>
     </row>
     <row r="15" spans="2:42" x14ac:dyDescent="0.3">
@@ -2504,12 +2503,11 @@
         <v>1177</v>
       </c>
       <c r="U15" s="2">
-        <f t="shared" ref="U15:V15" si="19">Q15*0.85</f>
-        <v>1129.6499999999999</v>
+        <v>1144</v>
       </c>
       <c r="V15" s="2">
-        <f t="shared" si="19"/>
-        <v>1175.55</v>
+        <f>R15*0.86</f>
+        <v>1189.3799999999999</v>
       </c>
       <c r="W15" s="2">
         <f>S15*1.03</f>
@@ -2542,47 +2540,47 @@
       </c>
       <c r="AF15" s="2">
         <f>SUM(T15:W15)</f>
-        <v>4758.37</v>
+        <v>4786.55</v>
       </c>
       <c r="AG15" s="2">
-        <f>AF15*1.02</f>
-        <v>4853.5374000000002</v>
+        <f>AF15*0.97</f>
+        <v>4642.9534999999996</v>
       </c>
       <c r="AH15" s="2">
-        <f t="shared" ref="AH15:AK15" si="20">AG15*1.02</f>
-        <v>4950.6081480000003</v>
+        <f t="shared" ref="AH15:AK15" si="18">AG15*1.02</f>
+        <v>4735.8125700000001</v>
       </c>
       <c r="AI15" s="2">
-        <f t="shared" si="20"/>
-        <v>5049.6203109600001</v>
+        <f t="shared" si="18"/>
+        <v>4830.5288214000002</v>
       </c>
       <c r="AJ15" s="2">
-        <f t="shared" si="20"/>
-        <v>5150.6127171792004</v>
+        <f t="shared" si="18"/>
+        <v>4927.1393978280003</v>
       </c>
       <c r="AK15" s="2">
-        <f t="shared" si="20"/>
-        <v>5253.6249715227841</v>
+        <f t="shared" si="18"/>
+        <v>5025.6821857845607</v>
       </c>
       <c r="AL15" s="2">
         <f>AK15*1.01</f>
-        <v>5306.1612212380123</v>
+        <v>5075.9390076424061</v>
       </c>
       <c r="AM15" s="2">
-        <f t="shared" si="18"/>
-        <v>5359.2228334503925</v>
+        <f t="shared" si="17"/>
+        <v>5126.6983977188302</v>
       </c>
       <c r="AN15" s="2">
-        <f t="shared" si="18"/>
-        <v>5412.8150617848969</v>
+        <f t="shared" si="17"/>
+        <v>5177.9653816960181</v>
       </c>
       <c r="AO15" s="2">
-        <f t="shared" si="18"/>
-        <v>5466.9432124027462</v>
+        <f t="shared" si="17"/>
+        <v>5229.7450355129786</v>
       </c>
       <c r="AP15" s="2">
-        <f t="shared" si="18"/>
-        <v>5521.6126445267737</v>
+        <f t="shared" si="17"/>
+        <v>5282.0424858681081</v>
       </c>
     </row>
     <row r="16" spans="2:42" x14ac:dyDescent="0.3">
@@ -2644,10 +2642,10 @@
         <v>156</v>
       </c>
       <c r="U16" s="2">
-        <v>100</v>
+        <v>1890</v>
       </c>
       <c r="V16" s="2">
-        <v>100</v>
+        <v>650</v>
       </c>
       <c r="W16" s="2">
         <v>50</v>
@@ -2679,47 +2677,47 @@
       </c>
       <c r="AF16" s="2">
         <f>SUM(T16:W16)</f>
-        <v>406</v>
+        <v>2746</v>
       </c>
       <c r="AG16" s="2">
         <f>AF16*0.7</f>
-        <v>284.2</v>
+        <v>1922.1999999999998</v>
       </c>
       <c r="AH16" s="2">
-        <f t="shared" ref="AH16:AP16" si="21">AG16*0.7</f>
-        <v>198.93999999999997</v>
+        <f t="shared" ref="AH16:AP16" si="19">AG16*0.7</f>
+        <v>1345.5399999999997</v>
       </c>
       <c r="AI16" s="2">
-        <f t="shared" si="21"/>
-        <v>139.25799999999998</v>
+        <f t="shared" si="19"/>
+        <v>941.8779999999997</v>
       </c>
       <c r="AJ16" s="2">
-        <f t="shared" si="21"/>
-        <v>97.480599999999981</v>
+        <f t="shared" si="19"/>
+        <v>659.3145999999997</v>
       </c>
       <c r="AK16" s="2">
-        <f t="shared" si="21"/>
-        <v>68.236419999999981</v>
+        <f t="shared" si="19"/>
+        <v>461.52021999999977</v>
       </c>
       <c r="AL16" s="2">
-        <f t="shared" si="21"/>
-        <v>47.765493999999983</v>
+        <f t="shared" si="19"/>
+        <v>323.0641539999998</v>
       </c>
       <c r="AM16" s="2">
-        <f t="shared" si="21"/>
-        <v>33.435845799999989</v>
+        <f t="shared" si="19"/>
+        <v>226.14490779999986</v>
       </c>
       <c r="AN16" s="2">
-        <f t="shared" si="21"/>
-        <v>23.405092059999991</v>
+        <f t="shared" si="19"/>
+        <v>158.30143545999988</v>
       </c>
       <c r="AO16" s="2">
-        <f t="shared" si="21"/>
-        <v>16.383564441999994</v>
+        <f t="shared" si="19"/>
+        <v>110.81100482199992</v>
       </c>
       <c r="AP16" s="2">
-        <f t="shared" si="21"/>
-        <v>11.468495109399996</v>
+        <f t="shared" si="19"/>
+        <v>77.56770337539993</v>
       </c>
     </row>
     <row r="17" spans="2:152" x14ac:dyDescent="0.3">
@@ -2727,160 +2725,160 @@
         <v>26</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" ref="C17:S17" si="22">SUM(C14:C16)</f>
+        <f t="shared" ref="C17:S17" si="20">SUM(C14:C16)</f>
         <v>5464</v>
       </c>
       <c r="D17" s="2">
+        <f t="shared" si="20"/>
+        <v>7160</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="20"/>
+        <v>5660</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="20"/>
+        <v>5519</v>
+      </c>
+      <c r="G17" s="2">
+        <f t="shared" si="20"/>
+        <v>6020</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="20"/>
+        <v>4903</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="20"/>
+        <v>6287</v>
+      </c>
+      <c r="J17" s="2">
+        <f t="shared" si="20"/>
+        <v>6710</v>
+      </c>
+      <c r="K17" s="2">
+        <f t="shared" si="20"/>
+        <v>6632</v>
+      </c>
+      <c r="L17" s="2">
+        <f t="shared" si="20"/>
+        <v>5476</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="20"/>
+        <v>5654</v>
+      </c>
+      <c r="N17" s="2">
+        <f t="shared" si="20"/>
+        <v>6026</v>
+      </c>
+      <c r="O17" s="2">
+        <f t="shared" si="20"/>
+        <v>4192</v>
+      </c>
+      <c r="P17" s="2">
+        <f t="shared" si="20"/>
+        <v>6286</v>
+      </c>
+      <c r="Q17" s="2">
+        <f t="shared" si="20"/>
+        <v>6511</v>
+      </c>
+      <c r="R17" s="2">
+        <f t="shared" si="20"/>
+        <v>11054</v>
+      </c>
+      <c r="S17" s="2">
+        <f t="shared" si="20"/>
+        <v>5172</v>
+      </c>
+      <c r="T17" s="2">
+        <f t="shared" ref="T17:W17" si="21">SUM(T14:T16)</f>
+        <v>4973</v>
+      </c>
+      <c r="U17" s="2">
+        <f t="shared" si="21"/>
+        <v>6718</v>
+      </c>
+      <c r="V17" s="2">
+        <f t="shared" si="21"/>
+        <v>5604.95</v>
+      </c>
+      <c r="W17" s="2">
+        <f t="shared" si="21"/>
+        <v>5240.93</v>
+      </c>
+      <c r="Y17" s="2">
+        <f t="shared" ref="Y17:AE17" si="22">SUM(Y14:Y16)</f>
+        <v>20421</v>
+      </c>
+      <c r="Z17" s="2">
         <f t="shared" si="22"/>
-        <v>7160</v>
-      </c>
-      <c r="E17" s="2">
+        <v>20105</v>
+      </c>
+      <c r="AA17" s="2">
         <f t="shared" si="22"/>
-        <v>5660</v>
-      </c>
-      <c r="F17" s="2">
+        <v>19934</v>
+      </c>
+      <c r="AB17" s="2">
         <f t="shared" si="22"/>
-        <v>5519</v>
-      </c>
-      <c r="G17" s="2">
+        <v>24359</v>
+      </c>
+      <c r="AC17" s="2">
         <f t="shared" si="22"/>
-        <v>6020</v>
-      </c>
-      <c r="H17" s="2">
+        <v>24532</v>
+      </c>
+      <c r="AD17" s="2">
         <f t="shared" si="22"/>
-        <v>4903</v>
-      </c>
-      <c r="I17" s="2">
+        <v>21348</v>
+      </c>
+      <c r="AE17" s="2">
         <f t="shared" si="22"/>
-        <v>6287</v>
-      </c>
-      <c r="J17" s="2">
-        <f t="shared" si="22"/>
-        <v>6710</v>
-      </c>
-      <c r="K17" s="2">
-        <f t="shared" si="22"/>
-        <v>6632</v>
-      </c>
-      <c r="L17" s="2">
-        <f t="shared" si="22"/>
-        <v>5476</v>
-      </c>
-      <c r="M17" s="2">
-        <f t="shared" si="22"/>
-        <v>5654</v>
-      </c>
-      <c r="N17" s="2">
-        <f t="shared" si="22"/>
-        <v>6026</v>
-      </c>
-      <c r="O17" s="2">
-        <f t="shared" si="22"/>
-        <v>4192</v>
-      </c>
-      <c r="P17" s="2">
-        <f t="shared" si="22"/>
-        <v>6286</v>
-      </c>
-      <c r="Q17" s="2">
-        <f t="shared" si="22"/>
-        <v>6511</v>
-      </c>
-      <c r="R17" s="2">
-        <f t="shared" si="22"/>
-        <v>11054</v>
-      </c>
-      <c r="S17" s="2">
-        <f t="shared" si="22"/>
-        <v>5172</v>
-      </c>
-      <c r="T17" s="2">
-        <f t="shared" ref="T17:W17" si="23">SUM(T14:T16)</f>
-        <v>4973</v>
-      </c>
-      <c r="U17" s="2">
+        <v>29023</v>
+      </c>
+      <c r="AF17" s="2">
+        <f t="shared" ref="AF17:AP17" si="23">SUM(AF14:AF16)</f>
+        <v>22536.880000000001</v>
+      </c>
+      <c r="AG17" s="2">
         <f t="shared" si="23"/>
-        <v>5383.87</v>
-      </c>
-      <c r="V17" s="2">
+        <v>21269.3969</v>
+      </c>
+      <c r="AH17" s="2">
         <f t="shared" si="23"/>
-        <v>5243.57</v>
-      </c>
-      <c r="W17" s="2">
+        <v>20932.638404000001</v>
+      </c>
+      <c r="AI17" s="2">
         <f t="shared" si="23"/>
-        <v>5395.97</v>
-      </c>
-      <c r="Y17" s="2">
-        <f t="shared" ref="Y17:AE17" si="24">SUM(Y14:Y16)</f>
-        <v>20421</v>
-      </c>
-      <c r="Z17" s="2">
-        <f t="shared" si="24"/>
-        <v>20105</v>
-      </c>
-      <c r="AA17" s="2">
-        <f t="shared" si="24"/>
-        <v>19934</v>
-      </c>
-      <c r="AB17" s="2">
-        <f t="shared" si="24"/>
-        <v>24359</v>
-      </c>
-      <c r="AC17" s="2">
-        <f t="shared" si="24"/>
-        <v>24532</v>
-      </c>
-      <c r="AD17" s="2">
-        <f t="shared" si="24"/>
-        <v>21348</v>
-      </c>
-      <c r="AE17" s="2">
-        <f t="shared" si="24"/>
-        <v>29023</v>
-      </c>
-      <c r="AF17" s="2">
-        <f t="shared" ref="AF17:AP17" si="25">SUM(AF14:AF16)</f>
-        <v>20996.41</v>
-      </c>
-      <c r="AG17" s="2">
-        <f t="shared" si="25"/>
-        <v>21286.418200000004</v>
-      </c>
-      <c r="AH17" s="2">
-        <f t="shared" si="25"/>
-        <v>21459.715756000001</v>
-      </c>
-      <c r="AI17" s="2">
-        <f t="shared" si="25"/>
-        <v>21662.147595040002</v>
+        <v>20772.205513740002</v>
       </c>
       <c r="AJ17" s="2">
-        <f t="shared" si="25"/>
-        <v>21886.0952941</v>
+        <f t="shared" si="23"/>
+        <v>20736.250677091397</v>
       </c>
       <c r="AK17" s="2">
-        <f t="shared" si="25"/>
-        <v>22126.243388212795</v>
+        <f t="shared" si="23"/>
+        <v>20788.497051840593</v>
       </c>
       <c r="AL17" s="2">
-        <f t="shared" si="25"/>
-        <v>22326.352531894921</v>
+        <f t="shared" si="23"/>
+        <v>20853.310754159</v>
       </c>
       <c r="AM17" s="2">
-        <f t="shared" si="25"/>
-        <v>22534.808754073871</v>
+        <f t="shared" si="23"/>
+        <v>20961.693973960591</v>
       </c>
       <c r="AN17" s="2">
-        <f t="shared" si="25"/>
-        <v>22749.791729416611</v>
+        <f t="shared" si="23"/>
+        <v>21101.205992282197</v>
       </c>
       <c r="AO17" s="2">
-        <f t="shared" si="25"/>
-        <v>22970.034068172175</v>
+        <f t="shared" si="23"/>
+        <v>21263.14460721242</v>
       </c>
       <c r="AP17" s="2">
-        <f t="shared" si="25"/>
-        <v>23194.655503876878</v>
+        <f t="shared" si="23"/>
+        <v>21441.424641789723</v>
       </c>
     </row>
     <row r="18" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2888,160 +2886,160 @@
         <v>25</v>
       </c>
       <c r="C18" s="7">
-        <f t="shared" ref="C18:S18" si="26">C13-C17</f>
+        <f t="shared" ref="C18:S18" si="24">C13-C17</f>
         <v>5884</v>
       </c>
       <c r="D18" s="7">
+        <f t="shared" si="24"/>
+        <v>3694</v>
+      </c>
+      <c r="E18" s="7">
+        <f t="shared" si="24"/>
+        <v>5546</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="24"/>
+        <v>5227</v>
+      </c>
+      <c r="G18" s="7">
+        <f t="shared" si="24"/>
+        <v>4989</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="24"/>
+        <v>4341</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="24"/>
+        <v>-700</v>
+      </c>
+      <c r="J18" s="7">
+        <f t="shared" si="24"/>
+        <v>-175</v>
+      </c>
+      <c r="K18" s="7">
+        <f t="shared" si="24"/>
+        <v>-1132</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="24"/>
+        <v>-1468</v>
+      </c>
+      <c r="M18" s="7">
+        <f t="shared" si="24"/>
+        <v>-1016</v>
+      </c>
+      <c r="N18" s="7">
+        <f t="shared" si="24"/>
+        <v>-8</v>
+      </c>
+      <c r="O18" s="7">
+        <f t="shared" si="24"/>
+        <v>2855</v>
+      </c>
+      <c r="P18" s="7">
+        <f t="shared" si="24"/>
+        <v>-1069</v>
+      </c>
+      <c r="Q18" s="7">
+        <f t="shared" si="24"/>
+        <v>-1964</v>
+      </c>
+      <c r="R18" s="7">
+        <f t="shared" si="24"/>
+        <v>-9057</v>
+      </c>
+      <c r="S18" s="7">
+        <f t="shared" si="24"/>
+        <v>412</v>
+      </c>
+      <c r="T18" s="7">
+        <f t="shared" ref="T18:W18" si="25">T13-T17</f>
+        <v>-301</v>
+      </c>
+      <c r="U18" s="7">
+        <f t="shared" si="25"/>
+        <v>-3176</v>
+      </c>
+      <c r="V18" s="7">
+        <f t="shared" si="25"/>
+        <v>-1165.7028799999998</v>
+      </c>
+      <c r="W18" s="7">
+        <f t="shared" si="25"/>
+        <v>-123.01600000000053</v>
+      </c>
+      <c r="Y18" s="7">
+        <f t="shared" ref="Y18:AE18" si="26">Y13-Y17</f>
+        <v>23316</v>
+      </c>
+      <c r="Z18" s="7">
         <f t="shared" si="26"/>
-        <v>3694</v>
-      </c>
-      <c r="E18" s="7">
+        <v>22035</v>
+      </c>
+      <c r="AA18" s="7">
         <f t="shared" si="26"/>
-        <v>5546</v>
-      </c>
-      <c r="F18" s="7">
+        <v>23678</v>
+      </c>
+      <c r="AB18" s="7">
         <f t="shared" si="26"/>
-        <v>5227</v>
-      </c>
-      <c r="G18" s="7">
+        <v>19456</v>
+      </c>
+      <c r="AC18" s="7">
         <f t="shared" si="26"/>
-        <v>4989</v>
-      </c>
-      <c r="H18" s="7">
+        <v>2334</v>
+      </c>
+      <c r="AD18" s="7">
         <f t="shared" si="26"/>
-        <v>4341</v>
-      </c>
-      <c r="I18" s="7">
+        <v>363</v>
+      </c>
+      <c r="AE18" s="7">
         <f t="shared" si="26"/>
-        <v>-700</v>
-      </c>
-      <c r="J18" s="7">
-        <f t="shared" si="26"/>
-        <v>-175</v>
-      </c>
-      <c r="K18" s="7">
-        <f t="shared" si="26"/>
-        <v>-1132</v>
-      </c>
-      <c r="L18" s="7">
-        <f t="shared" si="26"/>
-        <v>-1468</v>
-      </c>
-      <c r="M18" s="7">
-        <f t="shared" si="26"/>
-        <v>-1016</v>
-      </c>
-      <c r="N18" s="7">
-        <f t="shared" si="26"/>
-        <v>-8</v>
-      </c>
-      <c r="O18" s="7">
-        <f t="shared" si="26"/>
-        <v>2855</v>
-      </c>
-      <c r="P18" s="7">
-        <f t="shared" si="26"/>
-        <v>-1069</v>
-      </c>
-      <c r="Q18" s="7">
-        <f t="shared" si="26"/>
-        <v>-1964</v>
-      </c>
-      <c r="R18" s="7">
-        <f t="shared" si="26"/>
-        <v>-9057</v>
-      </c>
-      <c r="S18" s="7">
-        <f t="shared" si="26"/>
-        <v>412</v>
-      </c>
-      <c r="T18" s="7">
-        <f t="shared" ref="T18:W18" si="27">T13-T17</f>
-        <v>-301</v>
-      </c>
-      <c r="U18" s="7">
+        <v>-11678</v>
+      </c>
+      <c r="AF18" s="7">
+        <f t="shared" ref="AF18:AP18" si="27">AF13-AF17</f>
+        <v>-4765.718880000004</v>
+      </c>
+      <c r="AG18" s="7">
         <f t="shared" si="27"/>
-        <v>-980.8677000000007</v>
-      </c>
-      <c r="V18" s="7">
+        <v>1776.2718999999997</v>
+      </c>
+      <c r="AH18" s="7">
         <f t="shared" si="27"/>
-        <v>-525.09320000000025</v>
-      </c>
-      <c r="W18" s="7">
+        <v>4959.1704927999999</v>
+      </c>
+      <c r="AI18" s="7">
         <f t="shared" si="27"/>
-        <v>-139.73400000000038</v>
-      </c>
-      <c r="Y18" s="7">
-        <f t="shared" ref="Y18:AE18" si="28">Y13-Y17</f>
-        <v>23316</v>
-      </c>
-      <c r="Z18" s="7">
-        <f t="shared" si="28"/>
-        <v>22035</v>
-      </c>
-      <c r="AA18" s="7">
-        <f t="shared" si="28"/>
-        <v>23678</v>
-      </c>
-      <c r="AB18" s="7">
-        <f t="shared" si="28"/>
-        <v>19456</v>
-      </c>
-      <c r="AC18" s="7">
-        <f t="shared" si="28"/>
-        <v>2334</v>
-      </c>
-      <c r="AD18" s="7">
-        <f t="shared" si="28"/>
-        <v>363</v>
-      </c>
-      <c r="AE18" s="7">
-        <f t="shared" si="28"/>
-        <v>-11678</v>
-      </c>
-      <c r="AF18" s="7">
-        <f t="shared" ref="AF18:AP18" si="29">AF13-AF17</f>
-        <v>-1946.6949000000059</v>
-      </c>
-      <c r="AG18" s="7">
-        <f t="shared" si="29"/>
-        <v>1292.1201999999976</v>
-      </c>
-      <c r="AH18" s="7">
-        <f t="shared" si="29"/>
-        <v>3907.2721363999954</v>
-      </c>
-      <c r="AI18" s="7">
-        <f t="shared" si="29"/>
-        <v>4973.1896919799947</v>
+        <v>6414.1938278999987</v>
       </c>
       <c r="AJ18" s="7">
-        <f t="shared" si="29"/>
-        <v>5814.6554844007987</v>
+        <f t="shared" si="27"/>
+        <v>7537.6046382142085</v>
       </c>
       <c r="AK18" s="7">
-        <f t="shared" si="29"/>
-        <v>6405.5299136430294</v>
+        <f t="shared" si="27"/>
+        <v>8333.5739229241772</v>
       </c>
       <c r="AL18" s="7">
-        <f t="shared" si="29"/>
-        <v>7061.3739690165785</v>
+        <f t="shared" si="27"/>
+        <v>9142.4223498487154</v>
       </c>
       <c r="AM18" s="7">
-        <f t="shared" si="29"/>
-        <v>7734.5495418649734</v>
+        <f t="shared" si="27"/>
+        <v>9933.911123167356</v>
       </c>
       <c r="AN18" s="7">
-        <f t="shared" si="29"/>
-        <v>8427.6473154003979</v>
+        <f t="shared" si="27"/>
+        <v>10721.267257759588</v>
       </c>
       <c r="AO18" s="7">
-        <f t="shared" si="29"/>
-        <v>9142.7281479893427</v>
+        <f t="shared" si="27"/>
+        <v>11514.002840330624</v>
       </c>
       <c r="AP18" s="7">
-        <f t="shared" si="29"/>
-        <v>9881.4895787694841</v>
+        <f t="shared" si="27"/>
+        <v>12319.037229179616</v>
       </c>
     </row>
     <row r="19" spans="2:152" x14ac:dyDescent="0.3">
@@ -3103,7 +3101,7 @@
         <v>112</v>
       </c>
       <c r="U19" s="2">
-        <v>0</v>
+        <v>-502</v>
       </c>
       <c r="V19" s="2">
         <v>0</v>
@@ -3138,47 +3136,47 @@
       </c>
       <c r="AF19" s="2">
         <f>SUM(T19:W19)</f>
-        <v>112</v>
+        <v>-390</v>
       </c>
       <c r="AG19" s="2">
-        <f t="shared" ref="AG19:AP19" si="30">AF19*0.95</f>
-        <v>106.39999999999999</v>
+        <f t="shared" ref="AG19:AP19" si="28">AF19*0.95</f>
+        <v>-370.5</v>
       </c>
       <c r="AH19" s="2">
-        <f t="shared" si="30"/>
-        <v>101.07999999999998</v>
+        <f t="shared" si="28"/>
+        <v>-351.97499999999997</v>
       </c>
       <c r="AI19" s="2">
-        <f t="shared" si="30"/>
-        <v>96.025999999999982</v>
+        <f t="shared" si="28"/>
+        <v>-334.37624999999997</v>
       </c>
       <c r="AJ19" s="2">
-        <f t="shared" si="30"/>
-        <v>91.224699999999984</v>
+        <f t="shared" si="28"/>
+        <v>-317.65743749999996</v>
       </c>
       <c r="AK19" s="2">
-        <f t="shared" si="30"/>
-        <v>86.663464999999988</v>
+        <f t="shared" si="28"/>
+        <v>-301.77456562499992</v>
       </c>
       <c r="AL19" s="2">
-        <f t="shared" si="30"/>
-        <v>82.330291749999986</v>
+        <f t="shared" si="28"/>
+        <v>-286.68583734374994</v>
       </c>
       <c r="AM19" s="2">
-        <f t="shared" si="30"/>
-        <v>78.21377716249998</v>
+        <f t="shared" si="28"/>
+        <v>-272.35154547656242</v>
       </c>
       <c r="AN19" s="2">
-        <f t="shared" si="30"/>
-        <v>74.303088304374981</v>
+        <f t="shared" si="28"/>
+        <v>-258.73396820273427</v>
       </c>
       <c r="AO19" s="2">
-        <f t="shared" si="30"/>
-        <v>70.587933889156233</v>
+        <f t="shared" si="28"/>
+        <v>-245.79726979259755</v>
       </c>
       <c r="AP19" s="2">
-        <f t="shared" si="30"/>
-        <v>67.058537194698417</v>
+        <f t="shared" si="28"/>
+        <v>-233.50740630296767</v>
       </c>
     </row>
     <row r="20" spans="2:152" x14ac:dyDescent="0.3">
@@ -3240,7 +3238,7 @@
         <v>173</v>
       </c>
       <c r="U20" s="2">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="V20" s="2">
         <v>0</v>
@@ -3275,47 +3273,47 @@
       </c>
       <c r="AF20" s="2">
         <f>SUM(T20:W20)</f>
-        <v>173</v>
+        <v>268</v>
       </c>
       <c r="AG20" s="2">
-        <f t="shared" ref="AG20:AP20" si="31">AF20*1.01</f>
-        <v>174.73</v>
+        <f t="shared" ref="AG20:AP20" si="29">AF20*1.01</f>
+        <v>270.68</v>
       </c>
       <c r="AH20" s="2">
-        <f t="shared" si="31"/>
-        <v>176.47729999999999</v>
+        <f t="shared" si="29"/>
+        <v>273.38679999999999</v>
       </c>
       <c r="AI20" s="2">
-        <f t="shared" si="31"/>
-        <v>178.24207299999998</v>
+        <f t="shared" si="29"/>
+        <v>276.12066800000002</v>
       </c>
       <c r="AJ20" s="2">
-        <f t="shared" si="31"/>
-        <v>180.02449372999999</v>
+        <f t="shared" si="29"/>
+        <v>278.88187468000001</v>
       </c>
       <c r="AK20" s="2">
-        <f t="shared" si="31"/>
-        <v>181.82473866729998</v>
+        <f t="shared" si="29"/>
+        <v>281.67069342680003</v>
       </c>
       <c r="AL20" s="2">
-        <f t="shared" si="31"/>
-        <v>183.64298605397298</v>
+        <f t="shared" si="29"/>
+        <v>284.48740036106801</v>
       </c>
       <c r="AM20" s="2">
-        <f t="shared" si="31"/>
-        <v>185.47941591451271</v>
+        <f t="shared" si="29"/>
+        <v>287.33227436467871</v>
       </c>
       <c r="AN20" s="2">
-        <f t="shared" si="31"/>
-        <v>187.33421007365783</v>
+        <f t="shared" si="29"/>
+        <v>290.20559710832549</v>
       </c>
       <c r="AO20" s="2">
-        <f t="shared" si="31"/>
-        <v>189.20755217439441</v>
+        <f t="shared" si="29"/>
+        <v>293.10765307940875</v>
       </c>
       <c r="AP20" s="2">
-        <f t="shared" si="31"/>
-        <v>191.09962769613836</v>
+        <f t="shared" si="29"/>
+        <v>296.03872961020284</v>
       </c>
     </row>
     <row r="21" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3323,160 +3321,160 @@
         <v>28</v>
       </c>
       <c r="C21" s="7">
-        <f t="shared" ref="C21:W21" si="32">C18-C19-C20</f>
+        <f t="shared" ref="C21:W21" si="30">C18-C19-C20</f>
         <v>7488</v>
       </c>
       <c r="D21" s="7">
+        <f t="shared" si="30"/>
+        <v>3906</v>
+      </c>
+      <c r="E21" s="7">
+        <f t="shared" si="30"/>
+        <v>5745</v>
+      </c>
+      <c r="F21" s="7">
+        <f t="shared" si="30"/>
+        <v>6858</v>
+      </c>
+      <c r="G21" s="7">
+        <f t="shared" si="30"/>
+        <v>5194</v>
+      </c>
+      <c r="H21" s="7">
+        <f t="shared" si="30"/>
+        <v>9661</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" si="30"/>
+        <v>-909</v>
+      </c>
+      <c r="J21" s="7">
+        <f t="shared" si="30"/>
+        <v>-188</v>
+      </c>
+      <c r="K21" s="7">
+        <f t="shared" si="30"/>
+        <v>-796</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="30"/>
+        <v>-1158</v>
+      </c>
+      <c r="M21" s="7">
+        <f t="shared" si="30"/>
+        <v>-816</v>
+      </c>
+      <c r="N21" s="7">
+        <f t="shared" si="30"/>
+        <v>-52</v>
+      </c>
+      <c r="O21" s="7">
+        <f t="shared" si="30"/>
+        <v>3058</v>
+      </c>
+      <c r="P21" s="7">
+        <f t="shared" si="30"/>
+        <v>-719</v>
+      </c>
+      <c r="Q21" s="7">
+        <f t="shared" si="30"/>
+        <v>-2004</v>
+      </c>
+      <c r="R21" s="7">
+        <f t="shared" si="30"/>
+        <v>-9086</v>
+      </c>
+      <c r="S21" s="7">
+        <f t="shared" si="30"/>
+        <v>599</v>
+      </c>
+      <c r="T21" s="7">
+        <f t="shared" si="30"/>
+        <v>-586</v>
+      </c>
+      <c r="U21" s="7">
+        <f t="shared" si="30"/>
+        <v>-2769</v>
+      </c>
+      <c r="V21" s="7">
+        <f t="shared" si="30"/>
+        <v>-1165.7028799999998</v>
+      </c>
+      <c r="W21" s="7">
+        <f t="shared" si="30"/>
+        <v>-123.01600000000053</v>
+      </c>
+      <c r="Y21" s="7">
+        <f t="shared" ref="Y21:AE21" si="31">Y18-Y19-Y20</f>
+        <v>23317</v>
+      </c>
+      <c r="Z21" s="7">
+        <f t="shared" si="31"/>
+        <v>24058</v>
+      </c>
+      <c r="AA21" s="7">
+        <f t="shared" si="31"/>
+        <v>25078</v>
+      </c>
+      <c r="AB21" s="7">
+        <f t="shared" si="31"/>
+        <v>21703</v>
+      </c>
+      <c r="AC21" s="7">
+        <f t="shared" si="31"/>
+        <v>7768</v>
+      </c>
+      <c r="AD21" s="7">
+        <f t="shared" si="31"/>
+        <v>1032</v>
+      </c>
+      <c r="AE21" s="7">
+        <f t="shared" si="31"/>
+        <v>-11210</v>
+      </c>
+      <c r="AF21" s="7">
+        <f t="shared" ref="AF21:AP21" si="32">AF18-AF19-AF20</f>
+        <v>-4643.718880000004</v>
+      </c>
+      <c r="AG21" s="7">
         <f t="shared" si="32"/>
-        <v>3906</v>
-      </c>
-      <c r="E21" s="7">
+        <v>1876.0918999999997</v>
+      </c>
+      <c r="AH21" s="7">
         <f t="shared" si="32"/>
-        <v>5745</v>
-      </c>
-      <c r="F21" s="7">
+        <v>5037.7586928000001</v>
+      </c>
+      <c r="AI21" s="7">
         <f t="shared" si="32"/>
-        <v>6858</v>
-      </c>
-      <c r="G21" s="7">
+        <v>6472.4494098999985</v>
+      </c>
+      <c r="AJ21" s="7">
         <f t="shared" si="32"/>
-        <v>5194</v>
-      </c>
-      <c r="H21" s="7">
+        <v>7576.3802010342088</v>
+      </c>
+      <c r="AK21" s="7">
         <f t="shared" si="32"/>
-        <v>9661</v>
-      </c>
-      <c r="I21" s="7">
+        <v>8353.6777951223776</v>
+      </c>
+      <c r="AL21" s="7">
         <f t="shared" si="32"/>
-        <v>-909</v>
-      </c>
-      <c r="J21" s="7">
+        <v>9144.6207868313977</v>
+      </c>
+      <c r="AM21" s="7">
         <f t="shared" si="32"/>
-        <v>-188</v>
-      </c>
-      <c r="K21" s="7">
+        <v>9918.9303942792394</v>
+      </c>
+      <c r="AN21" s="7">
         <f t="shared" si="32"/>
-        <v>-796</v>
-      </c>
-      <c r="L21" s="7">
+        <v>10689.795628853997</v>
+      </c>
+      <c r="AO21" s="7">
         <f t="shared" si="32"/>
-        <v>-1158</v>
-      </c>
-      <c r="M21" s="7">
+        <v>11466.692457043813</v>
+      </c>
+      <c r="AP21" s="7">
         <f t="shared" si="32"/>
-        <v>-816</v>
-      </c>
-      <c r="N21" s="7">
-        <f t="shared" si="32"/>
-        <v>-52</v>
-      </c>
-      <c r="O21" s="7">
-        <f t="shared" si="32"/>
-        <v>3058</v>
-      </c>
-      <c r="P21" s="7">
-        <f t="shared" si="32"/>
-        <v>-719</v>
-      </c>
-      <c r="Q21" s="7">
-        <f t="shared" si="32"/>
-        <v>-2004</v>
-      </c>
-      <c r="R21" s="7">
-        <f t="shared" si="32"/>
-        <v>-9086</v>
-      </c>
-      <c r="S21" s="7">
-        <f t="shared" si="32"/>
-        <v>599</v>
-      </c>
-      <c r="T21" s="7">
-        <f t="shared" si="32"/>
-        <v>-586</v>
-      </c>
-      <c r="U21" s="7">
-        <f t="shared" si="32"/>
-        <v>-980.8677000000007</v>
-      </c>
-      <c r="V21" s="7">
-        <f t="shared" si="32"/>
-        <v>-525.09320000000025</v>
-      </c>
-      <c r="W21" s="7">
-        <f t="shared" si="32"/>
-        <v>-139.73400000000038</v>
-      </c>
-      <c r="Y21" s="7">
-        <f t="shared" ref="Y21:AE21" si="33">Y18-Y19-Y20</f>
-        <v>23317</v>
-      </c>
-      <c r="Z21" s="7">
-        <f t="shared" si="33"/>
-        <v>24058</v>
-      </c>
-      <c r="AA21" s="7">
-        <f t="shared" si="33"/>
-        <v>25078</v>
-      </c>
-      <c r="AB21" s="7">
-        <f t="shared" si="33"/>
-        <v>21703</v>
-      </c>
-      <c r="AC21" s="7">
-        <f t="shared" si="33"/>
-        <v>7768</v>
-      </c>
-      <c r="AD21" s="7">
-        <f t="shared" si="33"/>
-        <v>1032</v>
-      </c>
-      <c r="AE21" s="7">
-        <f t="shared" si="33"/>
-        <v>-11210</v>
-      </c>
-      <c r="AF21" s="7">
-        <f t="shared" ref="AF21:AP21" si="34">AF18-AF19-AF20</f>
-        <v>-2231.6949000000059</v>
-      </c>
-      <c r="AG21" s="7">
-        <f t="shared" si="34"/>
-        <v>1010.9901999999975</v>
-      </c>
-      <c r="AH21" s="7">
-        <f t="shared" si="34"/>
-        <v>3629.7148363999954</v>
-      </c>
-      <c r="AI21" s="7">
-        <f t="shared" si="34"/>
-        <v>4698.9216189799945</v>
-      </c>
-      <c r="AJ21" s="7">
-        <f t="shared" si="34"/>
-        <v>5543.4062906707986</v>
-      </c>
-      <c r="AK21" s="7">
-        <f t="shared" si="34"/>
-        <v>6137.0417099757296</v>
-      </c>
-      <c r="AL21" s="7">
-        <f t="shared" si="34"/>
-        <v>6795.400691212606</v>
-      </c>
-      <c r="AM21" s="7">
-        <f t="shared" si="34"/>
-        <v>7470.8563487879601</v>
-      </c>
-      <c r="AN21" s="7">
-        <f t="shared" si="34"/>
-        <v>8166.0100170223641</v>
-      </c>
-      <c r="AO21" s="7">
-        <f t="shared" si="34"/>
-        <v>8882.9326619257936</v>
-      </c>
-      <c r="AP21" s="7">
-        <f t="shared" si="34"/>
-        <v>9623.3314138786482</v>
+        <v>12256.50590587238</v>
       </c>
     </row>
     <row r="22" spans="2:152" x14ac:dyDescent="0.3">
@@ -3538,16 +3536,15 @@
         <v>301</v>
       </c>
       <c r="U22" s="2">
-        <f>U21*0.2</f>
-        <v>-196.17354000000014</v>
+        <v>255</v>
       </c>
       <c r="V22" s="2">
-        <f t="shared" ref="V22:W22" si="35">V21*0.2</f>
-        <v>-105.01864000000006</v>
+        <f t="shared" ref="V22:W22" si="33">V21*0.2</f>
+        <v>-233.14057599999998</v>
       </c>
       <c r="W22" s="2">
-        <f t="shared" si="35"/>
-        <v>-27.946800000000078</v>
+        <f t="shared" si="33"/>
+        <v>-24.603200000000108</v>
       </c>
       <c r="Y22" s="2">
         <v>2264</v>
@@ -3576,47 +3573,47 @@
       </c>
       <c r="AF22" s="2">
         <f>SUM(T22:W22)</f>
-        <v>-28.138980000000284</v>
+        <v>298.25622399999986</v>
       </c>
       <c r="AG22" s="2">
-        <f t="shared" ref="AG22:AP22" si="36">AG21*0.25</f>
-        <v>252.74754999999936</v>
+        <f>AG21*0.2</f>
+        <v>375.21837999999997</v>
       </c>
       <c r="AH22" s="2">
-        <f t="shared" si="36"/>
-        <v>907.42870909999885</v>
+        <f t="shared" ref="AH22:AP22" si="34">AH21*0.2</f>
+        <v>1007.5517385600001</v>
       </c>
       <c r="AI22" s="2">
-        <f t="shared" si="36"/>
-        <v>1174.7304047449986</v>
+        <f t="shared" si="34"/>
+        <v>1294.4898819799998</v>
       </c>
       <c r="AJ22" s="2">
-        <f t="shared" si="36"/>
-        <v>1385.8515726676997</v>
+        <f t="shared" si="34"/>
+        <v>1515.2760402068418</v>
       </c>
       <c r="AK22" s="2">
-        <f t="shared" si="36"/>
-        <v>1534.2604274939324</v>
+        <f t="shared" si="34"/>
+        <v>1670.7355590244756</v>
       </c>
       <c r="AL22" s="2">
-        <f t="shared" si="36"/>
-        <v>1698.8501728031515</v>
+        <f t="shared" si="34"/>
+        <v>1828.9241573662796</v>
       </c>
       <c r="AM22" s="2">
-        <f t="shared" si="36"/>
-        <v>1867.71408719699</v>
+        <f t="shared" si="34"/>
+        <v>1983.786078855848</v>
       </c>
       <c r="AN22" s="2">
-        <f t="shared" si="36"/>
-        <v>2041.502504255591</v>
+        <f t="shared" si="34"/>
+        <v>2137.9591257707993</v>
       </c>
       <c r="AO22" s="2">
-        <f t="shared" si="36"/>
-        <v>2220.7331654814484</v>
+        <f t="shared" si="34"/>
+        <v>2293.3384914087628</v>
       </c>
       <c r="AP22" s="2">
-        <f t="shared" si="36"/>
-        <v>2405.832853469662</v>
+        <f t="shared" si="34"/>
+        <v>2451.3011811744759</v>
       </c>
     </row>
     <row r="23" spans="2:152" x14ac:dyDescent="0.3">
@@ -3678,16 +3675,15 @@
         <v>-66</v>
       </c>
       <c r="U23" s="2">
-        <f>U21*0.05</f>
-        <v>-49.043385000000036</v>
+        <v>-106</v>
       </c>
       <c r="V23" s="2">
-        <f t="shared" ref="V23:W23" si="37">V21*0.05</f>
-        <v>-26.254660000000015</v>
+        <f t="shared" ref="V23:W23" si="35">V21*0.05</f>
+        <v>-58.285143999999995</v>
       </c>
       <c r="W23" s="2">
-        <f t="shared" si="37"/>
-        <v>-6.9867000000000195</v>
+        <f t="shared" si="35"/>
+        <v>-6.1508000000000269</v>
       </c>
       <c r="Y23" s="2">
         <v>0</v>
@@ -3716,47 +3712,47 @@
       </c>
       <c r="AF23" s="2">
         <f>SUM(T23:W23)</f>
-        <v>-148.28474500000007</v>
+        <v>-236.43594400000003</v>
       </c>
       <c r="AG23" s="2">
-        <f t="shared" ref="AG23:AP23" si="38">AG21*0.03</f>
-        <v>30.329705999999923</v>
+        <f t="shared" ref="AG23:AP23" si="36">AG21*0.03</f>
+        <v>56.282756999999989</v>
       </c>
       <c r="AH23" s="2">
-        <f t="shared" si="38"/>
-        <v>108.89144509199986</v>
+        <f t="shared" si="36"/>
+        <v>151.132760784</v>
       </c>
       <c r="AI23" s="2">
-        <f t="shared" si="38"/>
-        <v>140.96764856939984</v>
+        <f t="shared" si="36"/>
+        <v>194.17348229699994</v>
       </c>
       <c r="AJ23" s="2">
-        <f t="shared" si="38"/>
-        <v>166.30218872012395</v>
+        <f t="shared" si="36"/>
+        <v>227.29140603102624</v>
       </c>
       <c r="AK23" s="2">
-        <f t="shared" si="38"/>
-        <v>184.11125129927188</v>
+        <f t="shared" si="36"/>
+        <v>250.61033385367131</v>
       </c>
       <c r="AL23" s="2">
-        <f t="shared" si="38"/>
-        <v>203.86202073637818</v>
+        <f t="shared" si="36"/>
+        <v>274.33862360494192</v>
       </c>
       <c r="AM23" s="2">
-        <f t="shared" si="38"/>
-        <v>224.12569046363879</v>
+        <f t="shared" si="36"/>
+        <v>297.56791182837719</v>
       </c>
       <c r="AN23" s="2">
-        <f t="shared" si="38"/>
-        <v>244.9803005106709</v>
+        <f t="shared" si="36"/>
+        <v>320.69386886561989</v>
       </c>
       <c r="AO23" s="2">
-        <f t="shared" si="38"/>
-        <v>266.48797985777378</v>
+        <f t="shared" si="36"/>
+        <v>344.00077371131437</v>
       </c>
       <c r="AP23" s="2">
-        <f t="shared" si="38"/>
-        <v>288.69994241635942</v>
+        <f t="shared" si="36"/>
+        <v>367.6951771761714</v>
       </c>
     </row>
     <row r="24" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3764,600 +3760,600 @@
         <v>31</v>
       </c>
       <c r="C24" s="7">
-        <f t="shared" ref="C24:S24" si="39">C21-C22-C23</f>
+        <f t="shared" ref="C24:S24" si="37">C21-C22-C23</f>
         <v>5857</v>
       </c>
       <c r="D24" s="7">
+        <f t="shared" si="37"/>
+        <v>3361</v>
+      </c>
+      <c r="E24" s="7">
+        <f t="shared" si="37"/>
+        <v>5061</v>
+      </c>
+      <c r="F24" s="7">
+        <f t="shared" si="37"/>
+        <v>6823</v>
+      </c>
+      <c r="G24" s="7">
+        <f t="shared" si="37"/>
+        <v>4623</v>
+      </c>
+      <c r="H24" s="7">
+        <f t="shared" si="37"/>
+        <v>8113</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="37"/>
+        <v>-454</v>
+      </c>
+      <c r="J24" s="7">
+        <f t="shared" si="37"/>
+        <v>1019</v>
+      </c>
+      <c r="K24" s="7">
+        <f t="shared" si="37"/>
+        <v>-664</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="37"/>
+        <v>-2758</v>
+      </c>
+      <c r="M24" s="7">
+        <f t="shared" si="37"/>
+        <v>1481</v>
+      </c>
+      <c r="N24" s="7">
+        <f t="shared" si="37"/>
+        <v>297</v>
+      </c>
+      <c r="O24" s="7">
+        <f t="shared" si="37"/>
+        <v>2939</v>
+      </c>
+      <c r="P24" s="7">
+        <f t="shared" si="37"/>
+        <v>-381</v>
+      </c>
+      <c r="Q24" s="7">
+        <f t="shared" si="37"/>
+        <v>-1610</v>
+      </c>
+      <c r="R24" s="7">
+        <f t="shared" si="37"/>
+        <v>-16639</v>
+      </c>
+      <c r="S24" s="7">
+        <f t="shared" si="37"/>
+        <v>-126</v>
+      </c>
+      <c r="T24" s="7">
+        <f t="shared" ref="T24:W24" si="38">T21-T22-T23</f>
+        <v>-821</v>
+      </c>
+      <c r="U24" s="7">
+        <f t="shared" si="38"/>
+        <v>-2918</v>
+      </c>
+      <c r="V24" s="7">
+        <f t="shared" si="38"/>
+        <v>-874.27715999999987</v>
+      </c>
+      <c r="W24" s="7">
+        <f t="shared" si="38"/>
+        <v>-92.262000000000398</v>
+      </c>
+      <c r="Y24" s="7">
+        <f t="shared" ref="Y24:AE24" si="39">Y21-Y22-Y23</f>
+        <v>21053</v>
+      </c>
+      <c r="Z24" s="7">
         <f t="shared" si="39"/>
-        <v>3361</v>
-      </c>
-      <c r="E24" s="7">
+        <v>21048</v>
+      </c>
+      <c r="AA24" s="7">
         <f t="shared" si="39"/>
-        <v>5061</v>
-      </c>
-      <c r="F24" s="7">
+        <v>20899</v>
+      </c>
+      <c r="AB24" s="7">
         <f t="shared" si="39"/>
-        <v>6823</v>
-      </c>
-      <c r="G24" s="7">
+        <v>19868</v>
+      </c>
+      <c r="AC24" s="7">
         <f t="shared" si="39"/>
-        <v>4623</v>
-      </c>
-      <c r="H24" s="7">
+        <v>8014</v>
+      </c>
+      <c r="AD24" s="7">
         <f t="shared" si="39"/>
-        <v>8113</v>
-      </c>
-      <c r="I24" s="7">
+        <v>1959</v>
+      </c>
+      <c r="AE24" s="7">
         <f t="shared" si="39"/>
-        <v>-454</v>
-      </c>
-      <c r="J24" s="7">
-        <f t="shared" si="39"/>
-        <v>1019</v>
-      </c>
-      <c r="K24" s="7">
-        <f t="shared" si="39"/>
-        <v>-664</v>
-      </c>
-      <c r="L24" s="7">
-        <f t="shared" si="39"/>
-        <v>-2758</v>
-      </c>
-      <c r="M24" s="7">
-        <f t="shared" si="39"/>
-        <v>1481</v>
-      </c>
-      <c r="N24" s="7">
-        <f t="shared" si="39"/>
-        <v>297</v>
-      </c>
-      <c r="O24" s="7">
-        <f t="shared" si="39"/>
-        <v>2939</v>
-      </c>
-      <c r="P24" s="7">
-        <f t="shared" si="39"/>
-        <v>-381</v>
-      </c>
-      <c r="Q24" s="7">
-        <f t="shared" si="39"/>
-        <v>-1610</v>
-      </c>
-      <c r="R24" s="7">
-        <f t="shared" si="39"/>
-        <v>-16639</v>
-      </c>
-      <c r="S24" s="7">
-        <f t="shared" si="39"/>
-        <v>-126</v>
-      </c>
-      <c r="T24" s="7">
-        <f t="shared" ref="T24:W24" si="40">T21-T22-T23</f>
-        <v>-821</v>
-      </c>
-      <c r="U24" s="7">
+        <v>-18756</v>
+      </c>
+      <c r="AF24" s="7">
+        <f t="shared" ref="AF24:AP24" si="40">AF21-AF22-AF23</f>
+        <v>-4705.5391600000039</v>
+      </c>
+      <c r="AG24" s="7">
         <f t="shared" si="40"/>
-        <v>-735.65077500000052</v>
-      </c>
-      <c r="V24" s="7">
+        <v>1444.5907629999997</v>
+      </c>
+      <c r="AH24" s="7">
         <f t="shared" si="40"/>
-        <v>-393.81990000000019</v>
-      </c>
-      <c r="W24" s="7">
+        <v>3879.0741934560001</v>
+      </c>
+      <c r="AI24" s="7">
         <f t="shared" si="40"/>
-        <v>-104.80050000000028</v>
-      </c>
-      <c r="Y24" s="7">
-        <f t="shared" ref="Y24:AE24" si="41">Y21-Y22-Y23</f>
-        <v>21053</v>
-      </c>
-      <c r="Z24" s="7">
-        <f t="shared" si="41"/>
-        <v>21048</v>
-      </c>
-      <c r="AA24" s="7">
-        <f t="shared" si="41"/>
-        <v>20899</v>
-      </c>
-      <c r="AB24" s="7">
-        <f t="shared" si="41"/>
-        <v>19868</v>
-      </c>
-      <c r="AC24" s="7">
-        <f t="shared" si="41"/>
-        <v>8014</v>
-      </c>
-      <c r="AD24" s="7">
-        <f t="shared" si="41"/>
-        <v>1959</v>
-      </c>
-      <c r="AE24" s="7">
-        <f t="shared" si="41"/>
-        <v>-18756</v>
-      </c>
-      <c r="AF24" s="7">
-        <f t="shared" ref="AF24:AP24" si="42">AF21-AF22-AF23</f>
-        <v>-2055.2711750000058</v>
-      </c>
-      <c r="AG24" s="7">
-        <f t="shared" si="42"/>
-        <v>727.91294399999822</v>
-      </c>
-      <c r="AH24" s="7">
-        <f t="shared" si="42"/>
-        <v>2613.394682207997</v>
-      </c>
-      <c r="AI24" s="7">
-        <f t="shared" si="42"/>
-        <v>3383.2235656655957</v>
+        <v>4983.7860456229982</v>
       </c>
       <c r="AJ24" s="7">
-        <f t="shared" si="42"/>
-        <v>3991.252529282975</v>
+        <f t="shared" si="40"/>
+        <v>5833.8127547963413</v>
       </c>
       <c r="AK24" s="7">
-        <f t="shared" si="42"/>
-        <v>4418.6700311825252</v>
+        <f t="shared" si="40"/>
+        <v>6432.3319022442311</v>
       </c>
       <c r="AL24" s="7">
-        <f t="shared" si="42"/>
-        <v>4892.6884976730762</v>
+        <f t="shared" si="40"/>
+        <v>7041.3580058601765</v>
       </c>
       <c r="AM24" s="7">
-        <f t="shared" si="42"/>
-        <v>5379.0165711273321</v>
+        <f t="shared" si="40"/>
+        <v>7637.5764035950142</v>
       </c>
       <c r="AN24" s="7">
-        <f t="shared" si="42"/>
-        <v>5879.5272122561028</v>
+        <f t="shared" si="40"/>
+        <v>8231.1426342175782</v>
       </c>
       <c r="AO24" s="7">
-        <f t="shared" si="42"/>
-        <v>6395.7115165865716</v>
+        <f t="shared" si="40"/>
+        <v>8829.3531919237375</v>
       </c>
       <c r="AP24" s="7">
-        <f t="shared" si="42"/>
-        <v>6928.7986179926265</v>
+        <f t="shared" si="40"/>
+        <v>9437.5095475217331</v>
       </c>
       <c r="AQ24" s="1">
         <f>AP24*(1+$AS$37)</f>
-        <v>6859.5106318127</v>
+        <v>9343.1344520465154</v>
       </c>
       <c r="AR24" s="1">
-        <f t="shared" ref="AR24:DC24" si="43">AQ24*(1+$AS$37)</f>
-        <v>6790.9155254945726</v>
+        <f t="shared" ref="AR24:DC24" si="41">AQ24*(1+$AS$37)</f>
+        <v>9249.7031075260511</v>
       </c>
       <c r="AS24" s="1">
-        <f t="shared" si="43"/>
-        <v>6723.0063702396264</v>
+        <f t="shared" si="41"/>
+        <v>9157.2060764507896</v>
       </c>
       <c r="AT24" s="1">
-        <f t="shared" si="43"/>
-        <v>6655.7763065372301</v>
+        <f t="shared" si="41"/>
+        <v>9065.6340156862825</v>
       </c>
       <c r="AU24" s="1">
-        <f t="shared" si="43"/>
-        <v>6589.2185434718576</v>
+        <f t="shared" si="41"/>
+        <v>8974.9776755294188</v>
       </c>
       <c r="AV24" s="1">
-        <f t="shared" si="43"/>
-        <v>6523.3263580371386</v>
+        <f t="shared" si="41"/>
+        <v>8885.2278987741247</v>
       </c>
       <c r="AW24" s="1">
-        <f t="shared" si="43"/>
-        <v>6458.0930944567672</v>
+        <f t="shared" si="41"/>
+        <v>8796.375619786384</v>
       </c>
       <c r="AX24" s="1">
-        <f t="shared" si="43"/>
-        <v>6393.5121635121995</v>
+        <f t="shared" si="41"/>
+        <v>8708.4118635885206</v>
       </c>
       <c r="AY24" s="1">
-        <f t="shared" si="43"/>
-        <v>6329.5770418770771</v>
+        <f t="shared" si="41"/>
+        <v>8621.3277449526358</v>
       </c>
       <c r="AZ24" s="1">
-        <f t="shared" si="43"/>
-        <v>6266.281271458306</v>
+        <f t="shared" si="41"/>
+        <v>8535.1144675031101</v>
       </c>
       <c r="BA24" s="1">
-        <f t="shared" si="43"/>
-        <v>6203.6184587437228</v>
+        <f t="shared" si="41"/>
+        <v>8449.7633228280793</v>
       </c>
       <c r="BB24" s="1">
-        <f t="shared" si="43"/>
-        <v>6141.5822741562852</v>
+        <f t="shared" si="41"/>
+        <v>8365.2656895997989</v>
       </c>
       <c r="BC24" s="1">
-        <f t="shared" si="43"/>
-        <v>6080.1664514147224</v>
+        <f t="shared" si="41"/>
+        <v>8281.6130327038009</v>
       </c>
       <c r="BD24" s="1">
-        <f t="shared" si="43"/>
-        <v>6019.3647869005754</v>
+        <f t="shared" si="41"/>
+        <v>8198.7969023767619</v>
       </c>
       <c r="BE24" s="1">
-        <f t="shared" si="43"/>
-        <v>5959.1711390315695</v>
+        <f t="shared" si="41"/>
+        <v>8116.8089333529942</v>
       </c>
       <c r="BF24" s="1">
-        <f t="shared" si="43"/>
-        <v>5899.5794276412535</v>
+        <f t="shared" si="41"/>
+        <v>8035.6408440194646</v>
       </c>
       <c r="BG24" s="1">
-        <f t="shared" si="43"/>
-        <v>5840.5836333648413</v>
+        <f t="shared" si="41"/>
+        <v>7955.2844355792695</v>
       </c>
       <c r="BH24" s="1">
-        <f t="shared" si="43"/>
-        <v>5782.1777970311932</v>
+        <f t="shared" si="41"/>
+        <v>7875.7315912234772</v>
       </c>
       <c r="BI24" s="1">
-        <f t="shared" si="43"/>
-        <v>5724.3560190608814</v>
+        <f t="shared" si="41"/>
+        <v>7796.9742753112423</v>
       </c>
       <c r="BJ24" s="1">
-        <f t="shared" si="43"/>
-        <v>5667.1124588702723</v>
+        <f t="shared" si="41"/>
+        <v>7719.0045325581295</v>
       </c>
       <c r="BK24" s="1">
-        <f t="shared" si="43"/>
-        <v>5610.4413342815697</v>
+        <f t="shared" si="41"/>
+        <v>7641.8144872325483</v>
       </c>
       <c r="BL24" s="1">
-        <f t="shared" si="43"/>
-        <v>5554.3369209387538</v>
+        <f t="shared" si="41"/>
+        <v>7565.3963423602227</v>
       </c>
       <c r="BM24" s="1">
-        <f t="shared" si="43"/>
-        <v>5498.7935517293663</v>
+        <f t="shared" si="41"/>
+        <v>7489.7423789366203</v>
       </c>
       <c r="BN24" s="1">
-        <f t="shared" si="43"/>
-        <v>5443.8056162120729</v>
+        <f t="shared" si="41"/>
+        <v>7414.844955147254</v>
       </c>
       <c r="BO24" s="1">
-        <f t="shared" si="43"/>
-        <v>5389.3675600499519</v>
+        <f t="shared" si="41"/>
+        <v>7340.6965055957817</v>
       </c>
       <c r="BP24" s="1">
-        <f t="shared" si="43"/>
-        <v>5335.4738844494523</v>
+        <f t="shared" si="41"/>
+        <v>7267.289540539824</v>
       </c>
       <c r="BQ24" s="1">
-        <f t="shared" si="43"/>
-        <v>5282.1191456049573</v>
+        <f t="shared" si="41"/>
+        <v>7194.6166451344261</v>
       </c>
       <c r="BR24" s="1">
-        <f t="shared" si="43"/>
-        <v>5229.2979541489076</v>
+        <f t="shared" si="41"/>
+        <v>7122.6704786830815</v>
       </c>
       <c r="BS24" s="1">
-        <f t="shared" si="43"/>
-        <v>5177.0049746074183</v>
+        <f t="shared" si="41"/>
+        <v>7051.4437738962506</v>
       </c>
       <c r="BT24" s="1">
-        <f t="shared" si="43"/>
-        <v>5125.2349248613436</v>
+        <f t="shared" si="41"/>
+        <v>6980.9293361572882</v>
       </c>
       <c r="BU24" s="1">
-        <f t="shared" si="43"/>
-        <v>5073.9825756127302</v>
+        <f t="shared" si="41"/>
+        <v>6911.1200427957156</v>
       </c>
       <c r="BV24" s="1">
-        <f t="shared" si="43"/>
-        <v>5023.242749856603</v>
+        <f t="shared" si="41"/>
+        <v>6842.008842367758</v>
       </c>
       <c r="BW24" s="1">
-        <f t="shared" si="43"/>
-        <v>4973.0103223580372</v>
+        <f t="shared" si="41"/>
+        <v>6773.5887539440801</v>
       </c>
       <c r="BX24" s="1">
-        <f t="shared" si="43"/>
-        <v>4923.2802191344572</v>
+        <f t="shared" si="41"/>
+        <v>6705.8528664046389</v>
       </c>
       <c r="BY24" s="1">
-        <f t="shared" si="43"/>
-        <v>4874.0474169431127</v>
+        <f t="shared" si="41"/>
+        <v>6638.7943377405927</v>
       </c>
       <c r="BZ24" s="1">
-        <f t="shared" si="43"/>
-        <v>4825.3069427736818</v>
+        <f t="shared" si="41"/>
+        <v>6572.4063943631863</v>
       </c>
       <c r="CA24" s="1">
-        <f t="shared" si="43"/>
-        <v>4777.0538733459452</v>
+        <f t="shared" si="41"/>
+        <v>6506.6823304195541</v>
       </c>
       <c r="CB24" s="1">
-        <f t="shared" si="43"/>
-        <v>4729.2833346124853</v>
+        <f t="shared" si="41"/>
+        <v>6441.6155071153589</v>
       </c>
       <c r="CC24" s="1">
-        <f t="shared" si="43"/>
-        <v>4681.9905012663603</v>
+        <f t="shared" si="41"/>
+        <v>6377.1993520442056</v>
       </c>
       <c r="CD24" s="1">
-        <f t="shared" si="43"/>
-        <v>4635.1705962536962</v>
+        <f t="shared" si="41"/>
+        <v>6313.4273585237634</v>
       </c>
       <c r="CE24" s="1">
-        <f t="shared" si="43"/>
-        <v>4588.8188902911588</v>
+        <f t="shared" si="41"/>
+        <v>6250.2930849385257</v>
       </c>
       <c r="CF24" s="1">
-        <f t="shared" si="43"/>
-        <v>4542.9307013882471</v>
+        <f t="shared" si="41"/>
+        <v>6187.7901540891407</v>
       </c>
       <c r="CG24" s="1">
-        <f t="shared" si="43"/>
-        <v>4497.5013943743643</v>
+        <f t="shared" si="41"/>
+        <v>6125.9122525482489</v>
       </c>
       <c r="CH24" s="1">
-        <f t="shared" si="43"/>
-        <v>4452.5263804306205</v>
+        <f t="shared" si="41"/>
+        <v>6064.6531300227662</v>
       </c>
       <c r="CI24" s="1">
-        <f t="shared" si="43"/>
-        <v>4408.0011166263139</v>
+        <f t="shared" si="41"/>
+        <v>6004.006598722538</v>
       </c>
       <c r="CJ24" s="1">
-        <f t="shared" si="43"/>
-        <v>4363.921105460051</v>
+        <f t="shared" si="41"/>
+        <v>5943.9665327353123</v>
       </c>
       <c r="CK24" s="1">
-        <f t="shared" si="43"/>
-        <v>4320.2818944054507</v>
+        <f t="shared" si="41"/>
+        <v>5884.5268674079589</v>
       </c>
       <c r="CL24" s="1">
-        <f t="shared" si="43"/>
-        <v>4277.0790754613963</v>
+        <f t="shared" si="41"/>
+        <v>5825.6815987338796</v>
       </c>
       <c r="CM24" s="1">
-        <f t="shared" si="43"/>
-        <v>4234.3082847067826</v>
+        <f t="shared" si="41"/>
+        <v>5767.4247827465406</v>
       </c>
       <c r="CN24" s="1">
-        <f t="shared" si="43"/>
-        <v>4191.9652018597144</v>
+        <f t="shared" si="41"/>
+        <v>5709.7505349190751</v>
       </c>
       <c r="CO24" s="1">
-        <f t="shared" si="43"/>
-        <v>4150.0455498411175</v>
+        <f t="shared" si="41"/>
+        <v>5652.653029569884</v>
       </c>
       <c r="CP24" s="1">
-        <f t="shared" si="43"/>
-        <v>4108.5450943427059</v>
+        <f t="shared" si="41"/>
+        <v>5596.1264992741853</v>
       </c>
       <c r="CQ24" s="1">
-        <f t="shared" si="43"/>
-        <v>4067.4596433992788</v>
+        <f t="shared" si="41"/>
+        <v>5540.1652342814432</v>
       </c>
       <c r="CR24" s="1">
-        <f t="shared" si="43"/>
-        <v>4026.7850469652858</v>
+        <f t="shared" si="41"/>
+        <v>5484.7635819386287</v>
       </c>
       <c r="CS24" s="1">
-        <f t="shared" si="43"/>
-        <v>3986.517196495633</v>
+        <f t="shared" si="41"/>
+        <v>5429.9159461192421</v>
       </c>
       <c r="CT24" s="1">
-        <f t="shared" si="43"/>
-        <v>3946.6520245306765</v>
+        <f t="shared" si="41"/>
+        <v>5375.6167866580499</v>
       </c>
       <c r="CU24" s="1">
-        <f t="shared" si="43"/>
-        <v>3907.1855042853699</v>
+        <f t="shared" si="41"/>
+        <v>5321.8606187914693</v>
       </c>
       <c r="CV24" s="1">
-        <f t="shared" si="43"/>
-        <v>3868.1136492425162</v>
+        <f t="shared" si="41"/>
+        <v>5268.6420126035546</v>
       </c>
       <c r="CW24" s="1">
-        <f t="shared" si="43"/>
-        <v>3829.4325127500911</v>
+        <f t="shared" si="41"/>
+        <v>5215.9555924775186</v>
       </c>
       <c r="CX24" s="1">
-        <f t="shared" si="43"/>
-        <v>3791.1381876225901</v>
+        <f t="shared" si="41"/>
+        <v>5163.7960365527433</v>
       </c>
       <c r="CY24" s="1">
-        <f t="shared" si="43"/>
-        <v>3753.2268057463643</v>
+        <f t="shared" si="41"/>
+        <v>5112.1580761872156</v>
       </c>
       <c r="CZ24" s="1">
-        <f t="shared" si="43"/>
-        <v>3715.6945376889007</v>
+        <f t="shared" si="41"/>
+        <v>5061.0364954253437</v>
       </c>
       <c r="DA24" s="1">
-        <f t="shared" si="43"/>
-        <v>3678.5375923120118</v>
+        <f t="shared" si="41"/>
+        <v>5010.4261304710899</v>
       </c>
       <c r="DB24" s="1">
-        <f t="shared" si="43"/>
-        <v>3641.7522163888916</v>
+        <f t="shared" si="41"/>
+        <v>4960.3218691663787</v>
       </c>
       <c r="DC24" s="1">
-        <f t="shared" si="43"/>
-        <v>3605.3346942250027</v>
+        <f t="shared" si="41"/>
+        <v>4910.7186504747151</v>
       </c>
       <c r="DD24" s="1">
-        <f t="shared" ref="DD24:EV24" si="44">DC24*(1+$AS$37)</f>
-        <v>3569.2813472827529</v>
+        <f t="shared" ref="DD24:EV24" si="42">DC24*(1+$AS$37)</f>
+        <v>4861.6114639699681</v>
       </c>
       <c r="DE24" s="1">
-        <f t="shared" si="44"/>
-        <v>3533.5885338099251</v>
+        <f t="shared" si="42"/>
+        <v>4812.9953493302683</v>
       </c>
       <c r="DF24" s="1">
-        <f t="shared" si="44"/>
-        <v>3498.252648471826</v>
+        <f t="shared" si="42"/>
+        <v>4764.8653958369659</v>
       </c>
       <c r="DG24" s="1">
-        <f t="shared" si="44"/>
-        <v>3463.2701219871078</v>
+        <f t="shared" si="42"/>
+        <v>4717.2167418785966</v>
       </c>
       <c r="DH24" s="1">
-        <f t="shared" si="44"/>
-        <v>3428.6374207672366</v>
+        <f t="shared" si="42"/>
+        <v>4670.044574459811</v>
       </c>
       <c r="DI24" s="1">
-        <f t="shared" si="44"/>
-        <v>3394.3510465595641</v>
+        <f t="shared" si="42"/>
+        <v>4623.3441287152127</v>
       </c>
       <c r="DJ24" s="1">
-        <f t="shared" si="44"/>
-        <v>3360.4075360939682</v>
+        <f t="shared" si="42"/>
+        <v>4577.1106874280604</v>
       </c>
       <c r="DK24" s="1">
-        <f t="shared" si="44"/>
-        <v>3326.8034607330287</v>
+        <f t="shared" si="42"/>
+        <v>4531.3395805537793</v>
       </c>
       <c r="DL24" s="1">
-        <f t="shared" si="44"/>
-        <v>3293.5354261256985</v>
+        <f t="shared" si="42"/>
+        <v>4486.0261847482416</v>
       </c>
       <c r="DM24" s="1">
-        <f t="shared" si="44"/>
-        <v>3260.6000718644414</v>
+        <f t="shared" si="42"/>
+        <v>4441.1659229007591</v>
       </c>
       <c r="DN24" s="1">
-        <f t="shared" si="44"/>
-        <v>3227.9940711457971</v>
+        <f t="shared" si="42"/>
+        <v>4396.7542636717517</v>
       </c>
       <c r="DO24" s="1">
-        <f t="shared" si="44"/>
-        <v>3195.714130434339</v>
+        <f t="shared" si="42"/>
+        <v>4352.7867210350341</v>
       </c>
       <c r="DP24" s="1">
-        <f t="shared" si="44"/>
-        <v>3163.7569891299954</v>
+        <f t="shared" si="42"/>
+        <v>4309.2588538246837</v>
       </c>
       <c r="DQ24" s="1">
-        <f t="shared" si="44"/>
-        <v>3132.1194192386956</v>
+        <f t="shared" si="42"/>
+        <v>4266.166265286437</v>
       </c>
       <c r="DR24" s="1">
-        <f t="shared" si="44"/>
-        <v>3100.7982250463087</v>
+        <f t="shared" si="42"/>
+        <v>4223.5046026335722</v>
       </c>
       <c r="DS24" s="1">
-        <f t="shared" si="44"/>
-        <v>3069.7902427958456</v>
+        <f t="shared" si="42"/>
+        <v>4181.2695566072362</v>
       </c>
       <c r="DT24" s="1">
-        <f t="shared" si="44"/>
-        <v>3039.0923403678871</v>
+        <f t="shared" si="42"/>
+        <v>4139.4568610411634</v>
       </c>
       <c r="DU24" s="1">
-        <f t="shared" si="44"/>
-        <v>3008.7014169642084</v>
+        <f t="shared" si="42"/>
+        <v>4098.0622924307518</v>
       </c>
       <c r="DV24" s="1">
-        <f t="shared" si="44"/>
-        <v>2978.6144027945661</v>
+        <f t="shared" si="42"/>
+        <v>4057.0816695064441</v>
       </c>
       <c r="DW24" s="1">
-        <f t="shared" si="44"/>
-        <v>2948.8282587666204</v>
+        <f t="shared" si="42"/>
+        <v>4016.5108528113797</v>
       </c>
       <c r="DX24" s="1">
-        <f t="shared" si="44"/>
-        <v>2919.3399761789542</v>
+        <f t="shared" si="42"/>
+        <v>3976.345744283266</v>
       </c>
       <c r="DY24" s="1">
-        <f t="shared" si="44"/>
-        <v>2890.1465764171649</v>
+        <f t="shared" si="42"/>
+        <v>3936.5822868404334</v>
       </c>
       <c r="DZ24" s="1">
-        <f t="shared" si="44"/>
-        <v>2861.2451106529934</v>
+        <f t="shared" si="42"/>
+        <v>3897.216463972029</v>
       </c>
       <c r="EA24" s="1">
-        <f t="shared" si="44"/>
-        <v>2832.6326595464634</v>
+        <f t="shared" si="42"/>
+        <v>3858.2442993323089</v>
       </c>
       <c r="EB24" s="1">
-        <f t="shared" si="44"/>
-        <v>2804.3063329509987</v>
+        <f t="shared" si="42"/>
+        <v>3819.6618563389857</v>
       </c>
       <c r="EC24" s="1">
-        <f t="shared" si="44"/>
-        <v>2776.2632696214887</v>
+        <f t="shared" si="42"/>
+        <v>3781.4652377755956</v>
       </c>
       <c r="ED24" s="1">
-        <f t="shared" si="44"/>
-        <v>2748.5006369252737</v>
+        <f t="shared" si="42"/>
+        <v>3743.6505853978397</v>
       </c>
       <c r="EE24" s="1">
-        <f t="shared" si="44"/>
-        <v>2721.0156305560208</v>
+        <f t="shared" si="42"/>
+        <v>3706.2140795438613</v>
       </c>
       <c r="EF24" s="1">
-        <f t="shared" si="44"/>
-        <v>2693.8054742504605</v>
+        <f t="shared" si="42"/>
+        <v>3669.1519387484227</v>
       </c>
       <c r="EG24" s="1">
-        <f t="shared" si="44"/>
-        <v>2666.8674195079557</v>
+        <f t="shared" si="42"/>
+        <v>3632.4604193609384</v>
       </c>
       <c r="EH24" s="1">
-        <f t="shared" si="44"/>
-        <v>2640.1987453128759</v>
+        <f t="shared" si="42"/>
+        <v>3596.1358151673289</v>
       </c>
       <c r="EI24" s="1">
-        <f t="shared" si="44"/>
-        <v>2613.7967578597472</v>
+        <f t="shared" si="42"/>
+        <v>3560.1744570156557</v>
       </c>
       <c r="EJ24" s="1">
-        <f t="shared" si="44"/>
-        <v>2587.6587902811498</v>
+        <f t="shared" si="42"/>
+        <v>3524.5727124454993</v>
       </c>
       <c r="EK24" s="1">
-        <f t="shared" si="44"/>
-        <v>2561.7822023783383</v>
+        <f t="shared" si="42"/>
+        <v>3489.326985321044</v>
       </c>
       <c r="EL24" s="1">
-        <f t="shared" si="44"/>
-        <v>2536.1643803545549</v>
+        <f t="shared" si="42"/>
+        <v>3454.4337154678337</v>
       </c>
       <c r="EM24" s="1">
-        <f t="shared" si="44"/>
-        <v>2510.8027365510093</v>
+        <f t="shared" si="42"/>
+        <v>3419.8893783131552</v>
       </c>
       <c r="EN24" s="1">
-        <f t="shared" si="44"/>
-        <v>2485.6947091854991</v>
+        <f t="shared" si="42"/>
+        <v>3385.6904845300237</v>
       </c>
       <c r="EO24" s="1">
-        <f t="shared" si="44"/>
-        <v>2460.837762093644</v>
+        <f t="shared" si="42"/>
+        <v>3351.8335796847236</v>
       </c>
       <c r="EP24" s="1">
-        <f t="shared" si="44"/>
-        <v>2436.2293844727074</v>
+        <f t="shared" si="42"/>
+        <v>3318.3152438878765</v>
       </c>
       <c r="EQ24" s="1">
-        <f t="shared" si="44"/>
-        <v>2411.8670906279804</v>
+        <f t="shared" si="42"/>
+        <v>3285.1320914489975</v>
       </c>
       <c r="ER24" s="1">
-        <f t="shared" si="44"/>
-        <v>2387.7484197217004</v>
+        <f t="shared" si="42"/>
+        <v>3252.2807705345076</v>
       </c>
       <c r="ES24" s="1">
-        <f t="shared" si="44"/>
-        <v>2363.8709355244832</v>
+        <f t="shared" si="42"/>
+        <v>3219.7579628291624</v>
       </c>
       <c r="ET24" s="1">
-        <f t="shared" si="44"/>
-        <v>2340.2322261692384</v>
+        <f t="shared" si="42"/>
+        <v>3187.5603832008705</v>
       </c>
       <c r="EU24" s="1">
-        <f t="shared" si="44"/>
-        <v>2316.8299039075459</v>
+        <f t="shared" si="42"/>
+        <v>3155.6847793688617</v>
       </c>
       <c r="EV24" s="1">
-        <f t="shared" si="44"/>
-        <v>2293.6616048684705</v>
+        <f t="shared" si="42"/>
+        <v>3124.1279315751731</v>
       </c>
     </row>
     <row r="25" spans="2:152" x14ac:dyDescent="0.3">
@@ -4419,13 +4415,16 @@
         <v>4343</v>
       </c>
       <c r="U25" s="2">
-        <v>4343</v>
+        <f>4369</f>
+        <v>4369</v>
       </c>
       <c r="V25" s="2">
-        <v>4343</v>
+        <f>4369</f>
+        <v>4369</v>
       </c>
       <c r="W25" s="2">
-        <v>4343</v>
+        <f>4369</f>
+        <v>4369</v>
       </c>
       <c r="Y25" s="2">
         <v>4313</v>
@@ -4487,160 +4486,160 @@
         <v>32</v>
       </c>
       <c r="C26" s="6">
-        <f t="shared" ref="C26:S26" si="45">C24/C25</f>
+        <f t="shared" ref="C26:S26" si="43">C24/C25</f>
         <v>1.3579874797124971</v>
       </c>
       <c r="D26" s="6">
+        <f t="shared" si="43"/>
+        <v>0.77927196846742408</v>
+      </c>
+      <c r="E26" s="6">
+        <f t="shared" si="43"/>
+        <v>1.1734291676327382</v>
+      </c>
+      <c r="F26" s="6">
+        <f t="shared" si="43"/>
+        <v>1.5819615117087873</v>
+      </c>
+      <c r="G26" s="6">
+        <f t="shared" si="43"/>
+        <v>1.071875724553675</v>
+      </c>
+      <c r="H26" s="6">
+        <f t="shared" si="43"/>
+        <v>1.8810572687224669</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="43"/>
+        <v>-0.10526315789473684</v>
+      </c>
+      <c r="J26" s="6">
+        <f t="shared" si="43"/>
+        <v>0.23626246232320891</v>
+      </c>
+      <c r="K26" s="6">
+        <f t="shared" si="43"/>
+        <v>-0.15395316485045213</v>
+      </c>
+      <c r="L26" s="6">
+        <f t="shared" si="43"/>
+        <v>-0.63946209135172738</v>
+      </c>
+      <c r="M26" s="6">
+        <f t="shared" si="43"/>
+        <v>0.3433804776257825</v>
+      </c>
+      <c r="N26" s="6">
+        <f t="shared" si="43"/>
+        <v>6.8861581265940178E-2</v>
+      </c>
+      <c r="O26" s="6">
+        <f t="shared" si="43"/>
+        <v>0.68142824020403436</v>
+      </c>
+      <c r="P26" s="6">
+        <f t="shared" si="43"/>
+        <v>-8.8337584048226295E-2</v>
+      </c>
+      <c r="Q26" s="6">
+        <f t="shared" si="43"/>
+        <v>-0.37329005332715048</v>
+      </c>
+      <c r="R26" s="6">
+        <f t="shared" si="43"/>
+        <v>-3.8578715511245072</v>
+      </c>
+      <c r="S26" s="6">
+        <f t="shared" si="43"/>
+        <v>-2.9173419773095625E-2</v>
+      </c>
+      <c r="T26" s="6">
+        <f t="shared" ref="T26:W26" si="44">T24/T25</f>
+        <v>-0.18903983421597972</v>
+      </c>
+      <c r="U26" s="6">
+        <f t="shared" si="44"/>
+        <v>-0.66788738841840234</v>
+      </c>
+      <c r="V26" s="6">
+        <f t="shared" si="44"/>
+        <v>-0.2001092149233234</v>
+      </c>
+      <c r="W26" s="6">
+        <f t="shared" si="44"/>
+        <v>-2.1117418173495169E-2</v>
+      </c>
+      <c r="Y26" s="6">
+        <f t="shared" ref="Y26:AE26" si="45">Y24/Y25</f>
+        <v>4.881289125898447</v>
+      </c>
+      <c r="Z26" s="6">
         <f t="shared" si="45"/>
-        <v>0.77927196846742408</v>
-      </c>
-      <c r="E26" s="6">
+        <v>4.8801298400185482</v>
+      </c>
+      <c r="AA26" s="6">
         <f t="shared" si="45"/>
-        <v>1.1734291676327382</v>
-      </c>
-      <c r="F26" s="6">
+        <v>4.8455831207975884</v>
+      </c>
+      <c r="AB26" s="6">
         <f t="shared" si="45"/>
-        <v>1.5819615117087873</v>
-      </c>
-      <c r="G26" s="6">
+        <v>4.6065383723626248</v>
+      </c>
+      <c r="AC26" s="6">
         <f t="shared" si="45"/>
-        <v>1.071875724553675</v>
-      </c>
-      <c r="H26" s="6">
+        <v>1.8581034083004868</v>
+      </c>
+      <c r="AD26" s="6">
         <f t="shared" si="45"/>
-        <v>1.8810572687224669</v>
-      </c>
-      <c r="I26" s="6">
+        <v>0.4542082077440297</v>
+      </c>
+      <c r="AE26" s="6">
         <f t="shared" si="45"/>
-        <v>-0.10526315789473684</v>
-      </c>
-      <c r="J26" s="6">
-        <f t="shared" si="45"/>
-        <v>0.23626246232320891</v>
-      </c>
-      <c r="K26" s="6">
-        <f t="shared" si="45"/>
-        <v>-0.15395316485045213</v>
-      </c>
-      <c r="L26" s="6">
-        <f t="shared" si="45"/>
-        <v>-0.63946209135172738</v>
-      </c>
-      <c r="M26" s="6">
-        <f t="shared" si="45"/>
-        <v>0.3433804776257825</v>
-      </c>
-      <c r="N26" s="6">
-        <f t="shared" si="45"/>
-        <v>6.8861581265940178E-2</v>
-      </c>
-      <c r="O26" s="6">
-        <f t="shared" si="45"/>
-        <v>0.68142824020403436</v>
-      </c>
-      <c r="P26" s="6">
-        <f t="shared" si="45"/>
-        <v>-8.8337584048226295E-2</v>
-      </c>
-      <c r="Q26" s="6">
-        <f t="shared" si="45"/>
-        <v>-0.37329005332715048</v>
-      </c>
-      <c r="R26" s="6">
-        <f t="shared" si="45"/>
-        <v>-3.8578715511245072</v>
-      </c>
-      <c r="S26" s="6">
-        <f t="shared" si="45"/>
-        <v>-2.9173419773095625E-2</v>
-      </c>
-      <c r="T26" s="6">
-        <f t="shared" ref="T26:W26" si="46">T24/T25</f>
-        <v>-0.18903983421597972</v>
-      </c>
-      <c r="U26" s="6">
+        <v>-4.3426719147950914</v>
+      </c>
+      <c r="AF26" s="6">
+        <f t="shared" ref="AF26:AP26" si="46">AF24/AF25</f>
+        <v>-1.083476665899149</v>
+      </c>
+      <c r="AG26" s="6">
         <f t="shared" si="46"/>
-        <v>-0.16938769859544106</v>
-      </c>
-      <c r="V26" s="6">
+        <v>0.3326250893391664</v>
+      </c>
+      <c r="AH26" s="6">
         <f t="shared" si="46"/>
-        <v>-9.0679230946350498E-2</v>
-      </c>
-      <c r="W26" s="6">
+        <v>0.89317849262169013</v>
+      </c>
+      <c r="AI26" s="6">
         <f t="shared" si="46"/>
-        <v>-2.4130900299332323E-2</v>
-      </c>
-      <c r="Y26" s="6">
-        <f t="shared" ref="Y26:AE26" si="47">Y24/Y25</f>
-        <v>4.881289125898447</v>
-      </c>
-      <c r="Z26" s="6">
-        <f t="shared" si="47"/>
-        <v>4.8801298400185482</v>
-      </c>
-      <c r="AA26" s="6">
-        <f t="shared" si="47"/>
-        <v>4.8455831207975884</v>
-      </c>
-      <c r="AB26" s="6">
-        <f t="shared" si="47"/>
-        <v>4.6065383723626248</v>
-      </c>
-      <c r="AC26" s="6">
-        <f t="shared" si="47"/>
-        <v>1.8581034083004868</v>
-      </c>
-      <c r="AD26" s="6">
-        <f t="shared" si="47"/>
-        <v>0.4542082077440297</v>
-      </c>
-      <c r="AE26" s="6">
-        <f t="shared" si="47"/>
-        <v>-4.3426719147950914</v>
-      </c>
-      <c r="AF26" s="6">
-        <f t="shared" ref="AF26:AP26" si="48">AF24/AF25</f>
-        <v>-0.47323766405710471</v>
-      </c>
-      <c r="AG26" s="6">
-        <f t="shared" si="48"/>
-        <v>0.16760601980197978</v>
-      </c>
-      <c r="AH26" s="6">
-        <f t="shared" si="48"/>
-        <v>0.60174871798480245</v>
-      </c>
-      <c r="AI26" s="6">
-        <f t="shared" si="48"/>
-        <v>0.77900611689283805</v>
+        <v>1.1475445649603957</v>
       </c>
       <c r="AJ26" s="6">
-        <f t="shared" si="48"/>
-        <v>0.91900818081578983</v>
+        <f t="shared" si="46"/>
+        <v>1.3432679610399128</v>
       </c>
       <c r="AK26" s="6">
-        <f t="shared" si="48"/>
-        <v>1.017423447198371</v>
+        <f t="shared" si="46"/>
+        <v>1.481080336689899</v>
       </c>
       <c r="AL26" s="6">
-        <f t="shared" si="48"/>
-        <v>1.1265688458837384</v>
+        <f t="shared" si="46"/>
+        <v>1.621311997665249</v>
       </c>
       <c r="AM26" s="6">
-        <f t="shared" si="48"/>
-        <v>1.2385486003056256</v>
+        <f t="shared" si="46"/>
+        <v>1.7585946128471135</v>
       </c>
       <c r="AN26" s="6">
-        <f t="shared" si="48"/>
-        <v>1.3537939701257433</v>
+        <f t="shared" si="46"/>
+        <v>1.8952665517424772</v>
       </c>
       <c r="AO26" s="6">
-        <f t="shared" si="48"/>
-        <v>1.4726482884150522</v>
+        <f t="shared" si="46"/>
+        <v>2.0330078728813579</v>
       </c>
       <c r="AP26" s="6">
-        <f t="shared" si="48"/>
-        <v>1.5953945701111274</v>
+        <f t="shared" si="46"/>
+        <v>2.1730392695191649</v>
       </c>
     </row>
     <row r="27" spans="2:152" x14ac:dyDescent="0.3">
@@ -4651,11 +4650,11 @@
         <v>96</v>
       </c>
       <c r="P28" s="8">
-        <f t="shared" ref="P28:Q34" si="49">P3/L3-1</f>
+        <f t="shared" ref="P28:Q34" si="47">P3/L3-1</f>
         <v>0.30973922299095258</v>
       </c>
       <c r="Q28" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>6.6244725738396681E-2</v>
       </c>
       <c r="R28" s="8">
@@ -4713,19 +4712,19 @@
         <v>97</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>0.37393601408864097</v>
       </c>
       <c r="Q29" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>0.14989733059548249</v>
       </c>
       <c r="R29" s="8">
-        <f t="shared" ref="R29:S34" si="50">R4/N4-1</f>
+        <f t="shared" ref="R29:S34" si="48">R4/N4-1</f>
         <v>8.5498556517876967E-2</v>
       </c>
       <c r="S29" s="14" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T29" s="14"/>
@@ -4733,7 +4732,7 @@
       <c r="V29" s="14"/>
       <c r="W29" s="14"/>
       <c r="AE29" s="14">
-        <f t="shared" ref="AE29:AE34" si="51">AE4/AD4-1</f>
+        <f t="shared" ref="AE29:AE34" si="49">AE4/AD4-1</f>
         <v>0.18998814162290367</v>
       </c>
       <c r="AF29" s="8">
@@ -4775,19 +4774,19 @@
         <v>98</v>
       </c>
       <c r="P30" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>-0.18711018711018712</v>
       </c>
       <c r="Q30" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>-0.21595330739299612</v>
       </c>
       <c r="R30" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-0.39116202945990175</v>
       </c>
       <c r="S30" s="14">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>-9.3509724106739078E-2</v>
       </c>
       <c r="T30" s="14"/>
@@ -4795,7 +4794,7 @@
       <c r="V30" s="14"/>
       <c r="W30" s="14"/>
       <c r="AE30" s="14">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>-0.12124401913875593</v>
       </c>
       <c r="AF30" s="8">
@@ -4837,39 +4836,39 @@
         <v>99</v>
       </c>
       <c r="P31" s="8">
+        <f t="shared" si="47"/>
+        <v>4.6535677352637084E-2</v>
+      </c>
+      <c r="Q31" s="8">
+        <f t="shared" si="47"/>
+        <v>-3.4865293185419977E-2</v>
+      </c>
+      <c r="R31" s="8">
+        <f t="shared" si="48"/>
+        <v>8.8751625487646368E-2</v>
+      </c>
+      <c r="S31" s="8">
+        <f t="shared" si="48"/>
+        <v>-3.3114473308592629E-2</v>
+      </c>
+      <c r="T31" s="8">
+        <f t="shared" ref="T31:W34" si="50">T6/P6-1</f>
+        <v>0.35902503293807642</v>
+      </c>
+      <c r="U31" s="8">
+        <f t="shared" si="50"/>
+        <v>0.29359605911330044</v>
+      </c>
+      <c r="V31" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="W31" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="AE31" s="14">
         <f t="shared" si="49"/>
-        <v>4.6535677352637084E-2</v>
-      </c>
-      <c r="Q31" s="8">
-        <f t="shared" si="49"/>
-        <v>-3.4865293185419977E-2</v>
-      </c>
-      <c r="R31" s="8">
-        <f t="shared" si="50"/>
-        <v>8.8751625487646368E-2</v>
-      </c>
-      <c r="S31" s="8">
-        <f t="shared" si="50"/>
-        <v>-3.3114473308592629E-2</v>
-      </c>
-      <c r="T31" s="8">
-        <f t="shared" ref="T31:W34" si="52">T6/P6-1</f>
-        <v>0.35902503293807642</v>
-      </c>
-      <c r="U31" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="V31" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="W31" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="AE31" s="14">
-        <f t="shared" si="51"/>
         <v>1.440443213296394E-2</v>
       </c>
       <c r="AF31" s="8">
@@ -4911,39 +4910,39 @@
         <v>100</v>
       </c>
       <c r="P32" s="8">
+        <f t="shared" si="47"/>
+        <v>-8.3948959032907999E-2</v>
+      </c>
+      <c r="Q32" s="8">
+        <f t="shared" si="47"/>
+        <v>-1.4662756598240456E-2</v>
+      </c>
+      <c r="R32" s="8">
+        <f t="shared" si="48"/>
+        <v>4.2068965517241486E-2</v>
+      </c>
+      <c r="S32" s="8">
+        <f t="shared" si="48"/>
+        <v>0.1033310673011556</v>
+      </c>
+      <c r="T32" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="U32" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="V32" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="W32" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="AE32" s="14">
         <f t="shared" si="49"/>
-        <v>-8.3948959032907999E-2</v>
-      </c>
-      <c r="Q32" s="8">
-        <f t="shared" si="49"/>
-        <v>-1.4662756598240456E-2</v>
-      </c>
-      <c r="R32" s="8">
-        <f t="shared" si="50"/>
-        <v>4.2068965517241486E-2</v>
-      </c>
-      <c r="S32" s="8">
-        <f t="shared" si="50"/>
-        <v>0.1033310673011556</v>
-      </c>
-      <c r="T32" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="U32" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="V32" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="W32" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="AE32" s="14">
-        <f t="shared" si="51"/>
         <v>1.17769310703153E-2</v>
       </c>
       <c r="AF32" s="8">
@@ -4985,39 +4984,39 @@
         <v>101</v>
       </c>
       <c r="P33" s="8">
+        <f t="shared" si="47"/>
+        <v>-9.5632374249637775E-2</v>
+      </c>
+      <c r="Q33" s="8">
+        <f t="shared" si="47"/>
+        <v>3.5474592521572479E-2</v>
+      </c>
+      <c r="R33" s="8">
+        <f t="shared" si="48"/>
+        <v>-8.0304311073541856E-2</v>
+      </c>
+      <c r="S33" s="8">
+        <f t="shared" si="48"/>
+        <v>-0.13004830917874399</v>
+      </c>
+      <c r="T33" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="U33" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="V33" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="W33" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="AE33" s="14">
         <f t="shared" si="49"/>
-        <v>-9.5632374249637775E-2</v>
-      </c>
-      <c r="Q33" s="8">
-        <f t="shared" si="49"/>
-        <v>3.5474592521572479E-2</v>
-      </c>
-      <c r="R33" s="8">
-        <f t="shared" si="50"/>
-        <v>-8.0304311073541856E-2</v>
-      </c>
-      <c r="S33" s="8">
-        <f t="shared" si="50"/>
-        <v>-0.13004830917874399</v>
-      </c>
-      <c r="T33" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="U33" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="V33" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="W33" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="AE33" s="14">
-        <f t="shared" si="51"/>
         <v>-7.2289793759915399E-2</v>
       </c>
       <c r="AF33" s="8">
@@ -5059,39 +5058,39 @@
         <v>102</v>
       </c>
       <c r="P34" s="8">
+        <f t="shared" si="47"/>
+        <v>-0.46180555555555558</v>
+      </c>
+      <c r="Q34" s="8">
+        <f t="shared" si="47"/>
+        <v>-0.31782945736434109</v>
+      </c>
+      <c r="R34" s="8">
+        <f t="shared" si="48"/>
+        <v>-0.28443526170798894</v>
+      </c>
+      <c r="S34" s="8">
+        <f t="shared" si="48"/>
+        <v>-0.19660755589822665</v>
+      </c>
+      <c r="T34" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="U34" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="V34" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="W34" s="8">
+        <f t="shared" si="50"/>
+        <v>-1</v>
+      </c>
+      <c r="AE34" s="14">
         <f t="shared" si="49"/>
-        <v>-0.46180555555555558</v>
-      </c>
-      <c r="Q34" s="8">
-        <f t="shared" si="49"/>
-        <v>-0.31782945736434109</v>
-      </c>
-      <c r="R34" s="8">
-        <f t="shared" si="50"/>
-        <v>-0.28443526170798894</v>
-      </c>
-      <c r="S34" s="8">
-        <f t="shared" si="50"/>
-        <v>-0.19660755589822665</v>
-      </c>
-      <c r="T34" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="U34" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="V34" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="W34" s="8">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
-      <c r="AE34" s="14">
-        <f t="shared" si="51"/>
         <v>-0.31811697574893005</v>
       </c>
       <c r="AF34" s="8">
@@ -5137,67 +5136,67 @@
         <v>2.7530283311642867E-2</v>
       </c>
       <c r="H35" s="10">
-        <f t="shared" ref="H35:S35" si="53">H11/D11-1</f>
+        <f t="shared" ref="H35:S35" si="51">H11/D11-1</f>
         <v>-6.7097036547552502E-2</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-0.2195507106107687</v>
       </c>
       <c r="J35" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-0.20081283868278454</v>
       </c>
       <c r="K35" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-0.31595869056897896</v>
       </c>
       <c r="L35" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-0.36168473818994173</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-0.15482018145029697</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-7.6933107315164895E-2</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>9.7137159948725182E-2</v>
       </c>
       <c r="P35" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>8.6128894579598825E-2</v>
       </c>
       <c r="Q35" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-8.9582207120241231E-3</v>
       </c>
       <c r="R35" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-6.1731883034326862E-2</v>
       </c>
       <c r="S35" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>-7.4386602622354969E-2</v>
       </c>
       <c r="T35" s="10">
-        <f t="shared" ref="T35" si="54">T11/P11-1</f>
+        <f t="shared" ref="T35" si="52">T11/P11-1</f>
         <v>-4.4797233574347395E-3</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" ref="U35" si="55">U11/Q11-1</f>
-        <v>-6.0000000000000053E-2</v>
+        <f t="shared" ref="U35" si="53">U11/Q11-1</f>
+        <v>2.0260266500429225E-3</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" ref="V35" si="56">V11/R11-1</f>
-        <v>-4.0000000000000036E-2</v>
+        <f t="shared" ref="V35" si="54">V11/R11-1</f>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="W35" s="10">
-        <f t="shared" ref="W35" si="57">W11/S11-1</f>
+        <f t="shared" ref="W35" si="55">W11/S11-1</f>
         <v>-3.0000000000000027E-2</v>
       </c>
       <c r="Z35" s="10">
@@ -5205,67 +5204,67 @@
         <v>1.576614724480585E-2</v>
       </c>
       <c r="AA35" s="10">
-        <f t="shared" ref="AA35:AP35" si="58">AA11/Z11-1</f>
+        <f t="shared" ref="AA35:AP35" si="56">AA11/Z11-1</f>
         <v>8.2012089210032668E-2</v>
       </c>
       <c r="AB35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>1.4858669269395275E-2</v>
       </c>
       <c r="AC35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>-0.20209050415063778</v>
       </c>
       <c r="AD35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>-0.13997525930155108</v>
       </c>
       <c r="AE35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>-2.0782621523935951E-2</v>
       </c>
       <c r="AF35" s="10">
-        <f t="shared" si="58"/>
-        <v>-3.363665467693655E-2</v>
+        <f t="shared" si="56"/>
+        <v>-1.3643434210278582E-2</v>
       </c>
       <c r="AG35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AI35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AK35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AP35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -5274,19 +5273,19 @@
         <v>43</v>
       </c>
       <c r="C36" s="8">
-        <f t="shared" ref="C36:F36" si="59">C13/C11</f>
+        <f t="shared" ref="C36:F36" si="57">C13/C11</f>
         <v>0.568024827310041</v>
       </c>
       <c r="D36" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>0.55172063233873836</v>
       </c>
       <c r="E36" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>0.57083184758799854</v>
       </c>
       <c r="F36" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>0.55992080033347225</v>
       </c>
       <c r="G36" s="8">
@@ -5294,140 +5293,140 @@
         <v>0.53629189399844113</v>
       </c>
       <c r="H36" s="8">
-        <f t="shared" ref="H36:S36" si="60">H13/H11</f>
+        <f t="shared" ref="H36:S36" si="58">H13/H11</f>
         <v>0.50367787282733067</v>
       </c>
       <c r="I36" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.36466288101298872</v>
       </c>
       <c r="J36" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.42606597991915501</v>
       </c>
       <c r="K36" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.39168209656744052</v>
       </c>
       <c r="L36" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.34212548015364919</v>
       </c>
       <c r="M36" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.35817437639972199</v>
       </c>
       <c r="N36" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.42506003672835146</v>
       </c>
       <c r="O36" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.45741918732961184</v>
       </c>
       <c r="P36" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.41001257466205598</v>
       </c>
       <c r="Q36" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.35432089145172602</v>
       </c>
       <c r="R36" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.15033122553447756</v>
       </c>
       <c r="S36" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.39158485273492288</v>
       </c>
       <c r="T36" s="8">
-        <f t="shared" ref="T36:W36" si="61">T13/T11</f>
+        <f t="shared" ref="T36:W36" si="59">T13/T11</f>
         <v>0.36883239914739085</v>
       </c>
       <c r="U36" s="8">
+        <f t="shared" si="59"/>
+        <v>0.27544910179640719</v>
+      </c>
+      <c r="V36" s="8">
+        <f t="shared" si="59"/>
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="W36" s="8">
+        <f t="shared" si="59"/>
+        <v>0.37</v>
+      </c>
+      <c r="Y36" s="8">
+        <f t="shared" ref="Y36" si="60">Y13/Y11</f>
+        <v>0.61733570460704612</v>
+      </c>
+      <c r="Z36" s="8">
+        <f t="shared" ref="Z36:AP36" si="61">Z13/Z11</f>
+        <v>0.5855624261793928</v>
+      </c>
+      <c r="AA36" s="8">
         <f t="shared" si="61"/>
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="V36" s="8">
+        <v>0.5600832188218372</v>
+      </c>
+      <c r="AB36" s="8">
         <f t="shared" si="61"/>
-        <v>0.37</v>
-      </c>
-      <c r="W36" s="8">
+        <v>0.5544518121077141</v>
+      </c>
+      <c r="AC36" s="8">
         <f t="shared" si="61"/>
-        <v>0.38</v>
-      </c>
-      <c r="Y36" s="8">
-        <f t="shared" ref="Y36" si="62">Y13/Y11</f>
-        <v>0.61733570460704612</v>
-      </c>
-      <c r="Z36" s="8">
-        <f t="shared" ref="Z36:AP36" si="63">Z13/Z11</f>
-        <v>0.5855624261793928</v>
-      </c>
-      <c r="AA36" s="8">
-        <f t="shared" si="63"/>
-        <v>0.5600832188218372</v>
-      </c>
-      <c r="AB36" s="8">
-        <f t="shared" si="63"/>
-        <v>0.5544518121077141</v>
-      </c>
-      <c r="AC36" s="8">
-        <f t="shared" si="63"/>
         <v>0.42607923367272499</v>
       </c>
       <c r="AD36" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.40036512502766097</v>
       </c>
       <c r="AE36" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.32664168283083184</v>
       </c>
       <c r="AF36" s="8">
-        <f t="shared" si="63"/>
-        <v>0.3712319413908563</v>
+        <f t="shared" si="61"/>
+        <v>0.33929633202053128</v>
       </c>
       <c r="AG36" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.4</v>
       </c>
       <c r="AH36" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.42</v>
       </c>
       <c r="AI36" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.42</v>
       </c>
       <c r="AJ36" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.42</v>
       </c>
       <c r="AK36" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.42</v>
       </c>
       <c r="AL36" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.42</v>
       </c>
       <c r="AM36" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.42</v>
       </c>
       <c r="AN36" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.42</v>
       </c>
       <c r="AO36" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.42</v>
       </c>
       <c r="AP36" s="8">
-        <f t="shared" si="63"/>
-        <v>0.42</v>
+        <f t="shared" si="61"/>
+        <v>0.42000000000000004</v>
       </c>
     </row>
     <row r="37" spans="2:45" x14ac:dyDescent="0.3">
@@ -5443,68 +5442,68 @@
         <v>0.10779753761969912</v>
       </c>
       <c r="H37" s="8">
-        <f t="shared" ref="H37:S37" si="64">H14/D14-1</f>
+        <f t="shared" ref="H37:S37" si="62">H14/D14-1</f>
         <v>0.20397460667954737</v>
       </c>
       <c r="I37" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>0.18438761776581436</v>
       </c>
       <c r="J37" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>0.13121220089403107</v>
       </c>
       <c r="K37" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>0.10249444307236355</v>
       </c>
       <c r="L37" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>-5.8000917010545661E-2</v>
       </c>
       <c r="M37" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>-7.2727272727272751E-2</v>
       </c>
       <c r="N37" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>-0.10041841004184104</v>
       </c>
       <c r="O37" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>-0.10685483870967738</v>
       </c>
       <c r="P37" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>6.6439522998296363E-2</v>
       </c>
       <c r="Q37" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>3.8970588235294201E-2</v>
       </c>
       <c r="R37" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>4.6253229974160259E-2</v>
       </c>
       <c r="S37" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>-2.7840481565086561E-2</v>
       </c>
       <c r="T37" s="8">
-        <f t="shared" ref="T37:T38" si="65">T14/P14-1</f>
+        <f t="shared" ref="T37:T38" si="63">T14/P14-1</f>
         <v>-0.16932907348242809</v>
       </c>
       <c r="U37" s="8">
-        <f t="shared" ref="U37:U38" si="66">U14/Q14-1</f>
-        <v>-1.9999999999999907E-2</v>
+        <f t="shared" ref="U37:U38" si="64">U14/Q14-1</f>
+        <v>-0.13092710544939845</v>
       </c>
       <c r="V37" s="8">
-        <f t="shared" ref="V37:V38" si="67">V14/R14-1</f>
-        <v>-2.0000000000000018E-2</v>
+        <f t="shared" ref="V37:V38" si="65">V14/R14-1</f>
+        <v>-6.9999999999999951E-2</v>
       </c>
       <c r="W37" s="8">
-        <f t="shared" ref="W37:W38" si="68">W14/S14-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="W37:W38" si="66">W14/S14-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="Y37" s="8"/>
       <c r="Z37" s="8">
@@ -5512,67 +5511,67 @@
         <v>-1.3364837923650619E-2</v>
       </c>
       <c r="AA37" s="8">
-        <f t="shared" ref="AA37:AP37" si="69">AA14/Z14-1</f>
+        <f t="shared" ref="AA37:AP37" si="67">AA14/Z14-1</f>
         <v>1.451878461308187E-2</v>
       </c>
       <c r="AB37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.12053703157273521</v>
       </c>
       <c r="AC37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.15391705069124417</v>
       </c>
       <c r="AD37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>-8.4550433591967122E-2</v>
       </c>
       <c r="AE37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>3.116041381029544E-2</v>
       </c>
       <c r="AF37" s="8">
-        <f t="shared" si="69"/>
-        <v>-4.3150006043756739E-2</v>
+        <f t="shared" si="67"/>
+        <v>-9.3174785446633601E-2</v>
       </c>
       <c r="AG37" s="8">
-        <f t="shared" si="69"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="67"/>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AH37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP37" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR37" t="s">
@@ -5595,67 +5594,67 @@
         <v>0.10529311326124069</v>
       </c>
       <c r="H38" s="8">
-        <f t="shared" ref="H38:S38" si="70">H15/D15-1</f>
+        <f t="shared" ref="H38:S38" si="68">H15/D15-1</f>
         <v>0.31927710843373491</v>
       </c>
       <c r="I38" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>0.12570356472795496</v>
       </c>
       <c r="J38" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>4.1816009557944955E-2</v>
       </c>
       <c r="K38" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>-0.12152420185375901</v>
       </c>
       <c r="L38" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>-0.25627853881278539</v>
       </c>
       <c r="M38" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>-0.23666666666666669</v>
       </c>
       <c r="N38" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>-0.23165137614678899</v>
       </c>
       <c r="O38" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>-5.216881594372802E-2</v>
       </c>
       <c r="P38" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>0.19416730621642353</v>
       </c>
       <c r="Q38" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>-3.2751091703056789E-2</v>
       </c>
       <c r="R38" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>3.2089552238806052E-2</v>
       </c>
       <c r="S38" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>-0.23376623376623373</v>
       </c>
       <c r="T38" s="8">
+        <f t="shared" si="63"/>
+        <v>-0.24357326478149099</v>
+      </c>
+      <c r="U38" s="8">
+        <f t="shared" si="64"/>
+        <v>-0.13920240782543269</v>
+      </c>
+      <c r="V38" s="8">
         <f t="shared" si="65"/>
-        <v>-0.24357326478149099</v>
-      </c>
-      <c r="U38" s="8">
+        <v>-0.14000000000000012</v>
+      </c>
+      <c r="W38" s="8">
         <f t="shared" si="66"/>
-        <v>-0.15000000000000013</v>
-      </c>
-      <c r="V38" s="8">
-        <f t="shared" si="67"/>
-        <v>-0.15000000000000002</v>
-      </c>
-      <c r="W38" s="8">
-        <f t="shared" si="68"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Y38" s="8"/>
@@ -5664,74 +5663,74 @@
         <v>-8.633093525179858E-2</v>
       </c>
       <c r="AA38" s="8">
-        <f t="shared" ref="AA38:AP38" si="71">AA15/Z15-1</f>
+        <f t="shared" ref="AA38:AP38" si="69">AA15/Z15-1</f>
         <v>-2.6771653543307128E-2</v>
       </c>
       <c r="AB38" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>5.8737864077669899E-2</v>
       </c>
       <c r="AC38" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>7.0151306740027453E-2</v>
       </c>
       <c r="AD38" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>-0.19537275064267356</v>
       </c>
       <c r="AE38" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>-2.2541711040113599E-2</v>
       </c>
       <c r="AF38" s="8">
-        <f t="shared" si="71"/>
-        <v>-0.13594152896313783</v>
+        <f t="shared" si="69"/>
+        <v>-0.13082440530234241</v>
       </c>
       <c r="AG38" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
+        <v>-3.0000000000000138E-2</v>
+      </c>
+      <c r="AH38" s="8">
+        <f t="shared" si="69"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH38" s="8">
-        <f t="shared" si="71"/>
+      <c r="AI38" s="8">
+        <f t="shared" si="69"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI38" s="8">
-        <f t="shared" si="71"/>
+      <c r="AJ38" s="8">
+        <f t="shared" si="69"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AJ38" s="8">
-        <f t="shared" si="71"/>
+      <c r="AK38" s="8">
+        <f t="shared" si="69"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AK38" s="8">
-        <f t="shared" si="71"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AL38" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM38" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN38" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO38" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP38" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR38" t="s">
         <v>50</v>
       </c>
       <c r="AS38" s="8">
-        <v>0.06</v>
+        <v>4.4999999999999998E-2</v>
       </c>
     </row>
     <row r="39" spans="2:45" x14ac:dyDescent="0.3">
@@ -5739,19 +5738,19 @@
         <v>47</v>
       </c>
       <c r="C39" s="8">
-        <f t="shared" ref="C39:F39" si="72">C18/C11</f>
+        <f t="shared" ref="C39:F39" si="70">C18/C11</f>
         <v>0.2945239763740114</v>
       </c>
       <c r="D39" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>0.18777004015655976</v>
       </c>
       <c r="E39" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>0.28251235291121185</v>
       </c>
       <c r="F39" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>0.27235306377657359</v>
       </c>
       <c r="G39" s="8">
@@ -5759,147 +5758,147 @@
         <v>0.24303390491036633</v>
       </c>
       <c r="H39" s="8">
-        <f t="shared" ref="H39:S39" si="73">H18/H11</f>
+        <f t="shared" ref="H39:S39" si="71">H18/H11</f>
         <v>0.23652808805099984</v>
       </c>
       <c r="I39" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-4.5688923699497425E-2</v>
       </c>
       <c r="J39" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-1.1409571000130394E-2</v>
       </c>
       <c r="K39" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-8.0615296966244129E-2</v>
       </c>
       <c r="L39" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-0.12530943235168587</v>
       </c>
       <c r="M39" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-7.8461657270831722E-2</v>
       </c>
       <c r="N39" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-5.6505156095493713E-4</v>
       </c>
       <c r="O39" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.18531740880176556</v>
       </c>
       <c r="P39" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-8.4014460861364354E-2</v>
       </c>
       <c r="Q39" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-0.15304293618016052</v>
       </c>
       <c r="R39" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-0.68179765130984649</v>
       </c>
       <c r="S39" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>2.8892005610098175E-2</v>
       </c>
       <c r="T39" s="8">
-        <f t="shared" ref="T39:W39" si="74">T18/T11</f>
+        <f t="shared" ref="T39:W39" si="72">T18/T11</f>
         <v>-2.3762532564932503E-2</v>
       </c>
       <c r="U39" s="8">
+        <f t="shared" si="72"/>
+        <v>-0.246986546387744</v>
+      </c>
+      <c r="V39" s="8">
+        <f t="shared" si="72"/>
+        <v>-8.9543265183218715E-2</v>
+      </c>
+      <c r="W39" s="8">
+        <f t="shared" si="72"/>
+        <v>-8.8934515116901539E-3</v>
+      </c>
+      <c r="Y39" s="8">
+        <f t="shared" ref="Y39" si="73">Y18/Y11</f>
+        <v>0.32909891598915991</v>
+      </c>
+      <c r="Z39" s="8">
+        <f t="shared" ref="Z39:AP39" si="74">Z18/Z11</f>
+        <v>0.30619050927534219</v>
+      </c>
+      <c r="AA39" s="8">
         <f t="shared" si="74"/>
-        <v>-8.1311951733479743E-2</v>
-      </c>
-      <c r="V39" s="8">
+        <v>0.30408260238611995</v>
+      </c>
+      <c r="AB39" s="8">
         <f t="shared" si="74"/>
-        <v>-4.117525469236176E-2</v>
-      </c>
-      <c r="W39" s="8">
+        <v>0.24620368495646891</v>
+      </c>
+      <c r="AC39" s="8">
         <f t="shared" si="74"/>
-        <v>-1.0102080652390827E-2</v>
-      </c>
-      <c r="Y39" s="8">
-        <f t="shared" ref="Y39" si="75">Y18/Y11</f>
-        <v>0.32909891598915991</v>
-      </c>
-      <c r="Z39" s="8">
-        <f t="shared" ref="Z39:AP39" si="76">Z18/Z11</f>
-        <v>0.30619050927534219</v>
-      </c>
-      <c r="AA39" s="8">
-        <f t="shared" si="76"/>
-        <v>0.30408260238611995</v>
-      </c>
-      <c r="AB39" s="8">
-        <f t="shared" si="76"/>
-        <v>0.24620368495646891</v>
-      </c>
-      <c r="AC39" s="8">
-        <f t="shared" si="76"/>
         <v>3.7015891140926828E-2</v>
       </c>
       <c r="AD39" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>6.6939588404514271E-3</v>
       </c>
       <c r="AE39" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>-0.21992052880360069</v>
       </c>
       <c r="AF39" s="8">
-        <f t="shared" si="76"/>
-        <v>-3.7936280056108621E-2</v>
+        <f t="shared" si="74"/>
+        <v>-9.0989605265871118E-2</v>
       </c>
       <c r="AG39" s="8">
-        <f t="shared" si="76"/>
-        <v>2.2891122128613918E-2</v>
+        <f t="shared" si="74"/>
+        <v>3.0830468239654643E-2</v>
       </c>
       <c r="AH39" s="8">
-        <f t="shared" si="76"/>
-        <v>6.4692517071751401E-2</v>
+        <f t="shared" si="74"/>
+        <v>8.0444422221632492E-2</v>
       </c>
       <c r="AI39" s="8">
-        <f t="shared" si="76"/>
-        <v>7.8419869368408099E-2</v>
+        <f t="shared" si="74"/>
+        <v>9.9092247335298936E-2</v>
       </c>
       <c r="AJ39" s="8">
-        <f t="shared" si="76"/>
-        <v>8.8162061850819914E-2</v>
+        <f t="shared" si="74"/>
+        <v>0.11196895197862228</v>
       </c>
       <c r="AK39" s="8">
-        <f t="shared" si="76"/>
-        <v>9.4292161067853528E-2</v>
+        <f t="shared" si="74"/>
+        <v>0.12018723018225959</v>
       </c>
       <c r="AL39" s="8">
-        <f t="shared" si="76"/>
-        <v>0.10091890119145404</v>
+        <f t="shared" si="74"/>
+        <v>0.12801212004461476</v>
       </c>
       <c r="AM39" s="8">
-        <f t="shared" si="76"/>
-        <v>0.10732010820391696</v>
+        <f t="shared" si="74"/>
+        <v>0.13504324186607825</v>
       </c>
       <c r="AN39" s="8">
-        <f t="shared" si="76"/>
-        <v>0.11353119373852479</v>
+        <f t="shared" si="74"/>
+        <v>0.1415016429702903</v>
       </c>
       <c r="AO39" s="8">
-        <f t="shared" si="76"/>
-        <v>0.11957693942076957</v>
+        <f t="shared" si="74"/>
+        <v>0.14753819564921769</v>
       </c>
       <c r="AP39" s="8">
-        <f t="shared" si="76"/>
-        <v>0.12547488870644205</v>
+        <f t="shared" si="74"/>
+        <v>0.15325606788290311</v>
       </c>
       <c r="AR39" t="s">
         <v>51</v>
       </c>
       <c r="AS39" s="2">
         <f>NPV(AS38,AF24:EV24)</f>
-        <v>78604.04604405124</v>
+        <v>146006.90887939278</v>
       </c>
     </row>
     <row r="40" spans="2:45" x14ac:dyDescent="0.3">
@@ -5907,19 +5906,19 @@
         <v>29</v>
       </c>
       <c r="C40" s="8">
-        <f t="shared" ref="C40:F40" si="77">C22/C21</f>
+        <f t="shared" ref="C40:F40" si="75">C22/C21</f>
         <v>0.21781517094017094</v>
       </c>
       <c r="D40" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>0.1395289298515105</v>
       </c>
       <c r="E40" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>0.11906005221932114</v>
       </c>
       <c r="F40" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>5.1035287255759695E-3</v>
       </c>
       <c r="G40" s="8">
@@ -5927,147 +5926,147 @@
         <v>0.10993453985367732</v>
       </c>
       <c r="H40" s="8">
-        <f t="shared" ref="H40:S40" si="78">H22/H21</f>
+        <f t="shared" ref="H40:S40" si="76">H22/H21</f>
         <v>0.16023186005589485</v>
       </c>
       <c r="I40" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.50055005500550054</v>
       </c>
       <c r="J40" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>6.4202127659574471</v>
       </c>
       <c r="K40" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.16959798994974876</v>
       </c>
       <c r="L40" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>-1.390328151986183</v>
       </c>
       <c r="M40" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>2.8051470588235294</v>
       </c>
       <c r="N40" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>6.9615384615384617</v>
       </c>
       <c r="O40" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>4.1857423152387184E-2</v>
       </c>
       <c r="P40" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.39221140472878996</v>
       </c>
       <c r="Q40" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.17465069860279442</v>
       </c>
       <c r="R40" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>-0.86979969183359018</v>
       </c>
       <c r="S40" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>1.2554257095158599</v>
       </c>
       <c r="T40" s="8">
-        <f t="shared" ref="T40:W40" si="79">T22/T21</f>
+        <f t="shared" ref="T40:W40" si="77">T22/T21</f>
         <v>-0.51365187713310578</v>
       </c>
       <c r="U40" s="8">
+        <f t="shared" si="77"/>
+        <v>-9.2091007583965337E-2</v>
+      </c>
+      <c r="V40" s="8">
+        <f t="shared" si="77"/>
+        <v>0.2</v>
+      </c>
+      <c r="W40" s="8">
+        <f t="shared" si="77"/>
+        <v>0.2</v>
+      </c>
+      <c r="Y40" s="8">
+        <f t="shared" ref="Y40" si="78">Y22/Y21</f>
+        <v>9.7096539005875546E-2</v>
+      </c>
+      <c r="Z40" s="8">
+        <f t="shared" ref="Z40:AP40" si="79">Z22/Z21</f>
+        <v>0.12511430709119628</v>
+      </c>
+      <c r="AA40" s="8">
+        <f t="shared" si="79"/>
+        <v>0.16664008294122337</v>
+      </c>
+      <c r="AB40" s="8">
+        <f t="shared" si="79"/>
+        <v>8.4550522969174771E-2</v>
+      </c>
+      <c r="AC40" s="8">
+        <f t="shared" si="79"/>
+        <v>-3.2054582904222452E-2</v>
+      </c>
+      <c r="AD40" s="8">
+        <f t="shared" si="79"/>
+        <v>-0.88468992248062017</v>
+      </c>
+      <c r="AE40" s="8">
+        <f t="shared" si="79"/>
+        <v>-0.71570026761819805</v>
+      </c>
+      <c r="AF40" s="8">
+        <f t="shared" si="79"/>
+        <v>-6.4227881081380098E-2</v>
+      </c>
+      <c r="AG40" s="8">
         <f t="shared" si="79"/>
         <v>0.2</v>
       </c>
-      <c r="V40" s="8">
+      <c r="AH40" s="8">
         <f t="shared" si="79"/>
         <v>0.2</v>
       </c>
-      <c r="W40" s="8">
+      <c r="AI40" s="8">
         <f t="shared" si="79"/>
         <v>0.2</v>
       </c>
-      <c r="Y40" s="8">
-        <f t="shared" ref="Y40" si="80">Y22/Y21</f>
-        <v>9.7096539005875546E-2</v>
-      </c>
-      <c r="Z40" s="8">
-        <f t="shared" ref="Z40:AP40" si="81">Z22/Z21</f>
-        <v>0.12511430709119628</v>
-      </c>
-      <c r="AA40" s="8">
-        <f t="shared" si="81"/>
-        <v>0.16664008294122337</v>
-      </c>
-      <c r="AB40" s="8">
-        <f t="shared" si="81"/>
-        <v>8.4550522969174771E-2</v>
-      </c>
-      <c r="AC40" s="8">
-        <f t="shared" si="81"/>
-        <v>-3.2054582904222452E-2</v>
-      </c>
-      <c r="AD40" s="8">
-        <f t="shared" si="81"/>
-        <v>-0.88468992248062017</v>
-      </c>
-      <c r="AE40" s="8">
-        <f t="shared" si="81"/>
-        <v>-0.71570026761819805</v>
-      </c>
-      <c r="AF40" s="8">
-        <f t="shared" si="81"/>
-        <v>1.2608793433188475E-2</v>
-      </c>
-      <c r="AG40" s="8">
-        <f t="shared" si="81"/>
-        <v>0.25</v>
-      </c>
-      <c r="AH40" s="8">
-        <f t="shared" si="81"/>
-        <v>0.25</v>
-      </c>
-      <c r="AI40" s="8">
-        <f t="shared" si="81"/>
-        <v>0.25</v>
-      </c>
       <c r="AJ40" s="8">
-        <f t="shared" si="81"/>
-        <v>0.25</v>
+        <f t="shared" si="79"/>
+        <v>0.2</v>
       </c>
       <c r="AK40" s="8">
-        <f t="shared" si="81"/>
-        <v>0.25</v>
+        <f t="shared" si="79"/>
+        <v>0.2</v>
       </c>
       <c r="AL40" s="8">
-        <f t="shared" si="81"/>
-        <v>0.25</v>
+        <f t="shared" si="79"/>
+        <v>0.2</v>
       </c>
       <c r="AM40" s="8">
-        <f t="shared" si="81"/>
-        <v>0.25</v>
+        <f t="shared" si="79"/>
+        <v>0.2</v>
       </c>
       <c r="AN40" s="8">
-        <f t="shared" si="81"/>
-        <v>0.25</v>
+        <f t="shared" si="79"/>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AO40" s="8">
-        <f t="shared" si="81"/>
-        <v>0.25</v>
+        <f t="shared" si="79"/>
+        <v>0.2</v>
       </c>
       <c r="AP40" s="8">
-        <f t="shared" si="81"/>
-        <v>0.25</v>
+        <f t="shared" si="79"/>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AR40" t="s">
         <v>52</v>
       </c>
       <c r="AS40" s="2">
         <f>Main!D8</f>
-        <v>-24076</v>
+        <v>-24168</v>
       </c>
     </row>
     <row r="41" spans="2:45" x14ac:dyDescent="0.3">
@@ -6075,19 +6074,19 @@
         <v>30</v>
       </c>
       <c r="C41" s="8">
-        <f t="shared" ref="C41:F41" si="82">C23/C21</f>
+        <f t="shared" ref="C41:F41" si="80">C23/C21</f>
         <v>0</v>
       </c>
       <c r="D41" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="E41" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="F41" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="G41" s="8">
@@ -6095,139 +6094,139 @@
         <v>0</v>
       </c>
       <c r="H41" s="8">
-        <f t="shared" ref="H41:S41" si="83">H23/H21</f>
+        <f t="shared" ref="H41:S41" si="81">H23/H21</f>
         <v>0</v>
       </c>
       <c r="I41" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="J41" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="K41" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-3.7688442211055275E-3</v>
       </c>
       <c r="L41" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>8.6355785837651123E-3</v>
       </c>
       <c r="M41" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>9.8039215686274508E-3</v>
       </c>
       <c r="N41" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-0.25</v>
       </c>
       <c r="O41" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-2.9431000654022237E-3</v>
       </c>
       <c r="P41" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>7.7885952712100137E-2</v>
       </c>
       <c r="Q41" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>2.1956087824351298E-2</v>
       </c>
       <c r="R41" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>3.8520801232665637E-2</v>
       </c>
       <c r="S41" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-4.5075125208681135E-2</v>
       </c>
       <c r="T41" s="8">
-        <f t="shared" ref="T41:W41" si="84">T23/T21</f>
+        <f t="shared" ref="T41:W41" si="82">T23/T21</f>
         <v>0.11262798634812286</v>
       </c>
       <c r="U41" s="8">
+        <f t="shared" si="82"/>
+        <v>3.828096785843265E-2</v>
+      </c>
+      <c r="V41" s="8">
+        <f t="shared" si="82"/>
+        <v>0.05</v>
+      </c>
+      <c r="W41" s="8">
+        <f t="shared" si="82"/>
+        <v>0.05</v>
+      </c>
+      <c r="Y41" s="8">
+        <f t="shared" ref="Y41" si="83">Y23/Y21</f>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="8">
+        <f t="shared" ref="Z41:AP41" si="84">Z23/Z21</f>
+        <v>0</v>
+      </c>
+      <c r="AA41" s="8">
         <f t="shared" si="84"/>
-        <v>0.05</v>
-      </c>
-      <c r="V41" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="8">
         <f t="shared" si="84"/>
-        <v>0.05</v>
-      </c>
-      <c r="W41" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="8">
         <f t="shared" si="84"/>
-        <v>0.05</v>
-      </c>
-      <c r="Y41" s="8">
-        <f t="shared" ref="Y41" si="85">Y23/Y21</f>
-        <v>0</v>
-      </c>
-      <c r="Z41" s="8">
-        <f t="shared" ref="Z41:AP41" si="86">Z23/Z21</f>
-        <v>0</v>
-      </c>
-      <c r="AA41" s="8">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-      <c r="AB41" s="8">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-      <c r="AC41" s="8">
-        <f t="shared" si="86"/>
         <v>3.8619979402677651E-4</v>
       </c>
       <c r="AD41" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>-1.3565891472868217E-2</v>
       </c>
       <c r="AE41" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>4.2551293487957179E-2</v>
       </c>
       <c r="AF41" s="8">
-        <f t="shared" si="86"/>
-        <v>6.644490024151585E-2</v>
+        <f t="shared" si="84"/>
+        <v>5.0915214747021861E-2</v>
       </c>
       <c r="AG41" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>0.03</v>
       </c>
       <c r="AH41" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>0.03</v>
       </c>
       <c r="AI41" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
+        <v>2.9999999999999995E-2</v>
+      </c>
+      <c r="AJ41" s="8">
+        <f t="shared" si="84"/>
+        <v>2.9999999999999995E-2</v>
+      </c>
+      <c r="AK41" s="8">
+        <f t="shared" si="84"/>
+        <v>0.03</v>
+      </c>
+      <c r="AL41" s="8">
+        <f t="shared" si="84"/>
+        <v>0.03</v>
+      </c>
+      <c r="AM41" s="8">
+        <f t="shared" si="84"/>
         <v>3.0000000000000002E-2</v>
       </c>
-      <c r="AJ41" s="8">
-        <f t="shared" si="86"/>
+      <c r="AN41" s="8">
+        <f t="shared" si="84"/>
         <v>0.03</v>
       </c>
-      <c r="AK41" s="8">
-        <f t="shared" si="86"/>
+      <c r="AO41" s="8">
+        <f t="shared" si="84"/>
         <v>0.03</v>
       </c>
-      <c r="AL41" s="8">
-        <f t="shared" si="86"/>
-        <v>0.03</v>
-      </c>
-      <c r="AM41" s="8">
-        <f t="shared" si="86"/>
-        <v>0.03</v>
-      </c>
-      <c r="AN41" s="8">
-        <f t="shared" si="86"/>
-        <v>0.03</v>
-      </c>
-      <c r="AO41" s="8">
-        <f t="shared" si="86"/>
-        <v>2.9999999999999995E-2</v>
-      </c>
       <c r="AP41" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>0.03</v>
       </c>
       <c r="AR41" t="s">
@@ -6235,7 +6234,7 @@
       </c>
       <c r="AS41" s="2">
         <f>AS39+AS40</f>
-        <v>54528.04604405124</v>
+        <v>121838.90887939278</v>
       </c>
     </row>
     <row r="42" spans="2:45" x14ac:dyDescent="0.3">
@@ -6243,19 +6242,19 @@
         <v>48</v>
       </c>
       <c r="C42" s="8">
-        <f t="shared" ref="C42:F42" si="87">C24/C11</f>
+        <f t="shared" ref="C42:F42" si="85">C24/C11</f>
         <v>0.29317248973871257</v>
       </c>
       <c r="D42" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>0.17084328775479082</v>
       </c>
       <c r="E42" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>0.25780653048749425</v>
       </c>
       <c r="F42" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>0.35551271363067943</v>
       </c>
       <c r="G42" s="8">
@@ -6263,147 +6262,147 @@
         <v>0.2252045985970382</v>
       </c>
       <c r="H42" s="8">
-        <f t="shared" ref="H42:S42" si="88">H24/H11</f>
+        <f t="shared" ref="H42:S42" si="86">H24/H11</f>
         <v>0.44205307034272329</v>
       </c>
       <c r="I42" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>-2.9632530513674041E-2</v>
       </c>
       <c r="J42" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>6.643630199504498E-2</v>
       </c>
       <c r="K42" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>-4.7286711294687367E-2</v>
       </c>
       <c r="L42" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>-0.23542466922748612</v>
       </c>
       <c r="M42" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>0.114371766159549</v>
       </c>
       <c r="N42" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>2.097753920045204E-2</v>
       </c>
       <c r="O42" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>0.19076982993638841</v>
       </c>
       <c r="P42" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>-2.9943414020748193E-2</v>
       </c>
       <c r="Q42" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>-0.12545780409880777</v>
       </c>
       <c r="R42" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>-1.2525594700391449</v>
       </c>
       <c r="S42" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>-8.8359046283309952E-3</v>
       </c>
       <c r="T42" s="8">
-        <f t="shared" ref="T42:W42" si="89">T24/T11</f>
+        <f t="shared" ref="T42:W42" si="87">T24/T11</f>
         <v>-6.4814083839898951E-2</v>
       </c>
       <c r="U42" s="8">
+        <f t="shared" si="87"/>
+        <v>-0.22692277782098141</v>
+      </c>
+      <c r="V42" s="8">
+        <f t="shared" si="87"/>
+        <v>-6.715744888741404E-2</v>
+      </c>
+      <c r="W42" s="8">
+        <f t="shared" si="87"/>
+        <v>-6.670088633767615E-3</v>
+      </c>
+      <c r="Y42" s="8">
+        <f t="shared" ref="Y42" si="88">Y24/Y11</f>
+        <v>0.29715729448961159</v>
+      </c>
+      <c r="Z42" s="8">
+        <f t="shared" ref="Z42:AP42" si="89">Z24/Z11</f>
+        <v>0.2924755089279511</v>
+      </c>
+      <c r="AA42" s="8">
         <f t="shared" si="89"/>
-        <v>-6.0983963800109807E-2</v>
-      </c>
-      <c r="V42" s="8">
+        <v>0.26839354283586114</v>
+      </c>
+      <c r="AB42" s="8">
         <f t="shared" si="89"/>
-        <v>-3.088144101927132E-2</v>
-      </c>
-      <c r="W42" s="8">
+        <v>0.25141729094958493</v>
+      </c>
+      <c r="AC42" s="8">
         <f t="shared" si="89"/>
-        <v>-7.5765604892931195E-3</v>
-      </c>
-      <c r="Y42" s="8">
-        <f t="shared" ref="Y42" si="90">Y24/Y11</f>
-        <v>0.29715729448961159</v>
-      </c>
-      <c r="Z42" s="8">
-        <f t="shared" ref="Z42:AP42" si="91">Z24/Z11</f>
-        <v>0.2924755089279511</v>
-      </c>
-      <c r="AA42" s="8">
-        <f t="shared" si="91"/>
-        <v>0.26839354283586114</v>
-      </c>
-      <c r="AB42" s="8">
-        <f t="shared" si="91"/>
-        <v>0.25141729094958493</v>
-      </c>
-      <c r="AC42" s="8">
-        <f t="shared" si="91"/>
         <v>0.1270974085704317</v>
       </c>
       <c r="AD42" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="89"/>
         <v>3.6125248948882499E-2</v>
       </c>
       <c r="AE42" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="89"/>
         <v>-0.35321368712453627</v>
       </c>
       <c r="AF42" s="8">
-        <f t="shared" si="91"/>
-        <v>-4.0052163739704369E-2</v>
+        <f t="shared" si="89"/>
+        <v>-8.9840622477400253E-2</v>
       </c>
       <c r="AG42" s="8">
-        <f t="shared" si="91"/>
-        <v>1.2895661022947319E-2</v>
+        <f t="shared" si="89"/>
+        <v>2.5073531613020485E-2</v>
       </c>
       <c r="AH42" s="8">
-        <f t="shared" si="91"/>
-        <v>4.3269850215689569E-2</v>
+        <f t="shared" si="89"/>
+        <v>6.2923806047899419E-2</v>
       </c>
       <c r="AI42" s="8">
-        <f t="shared" si="91"/>
-        <v>5.3348447675637775E-2</v>
+        <f t="shared" si="89"/>
+        <v>7.6994018695062283E-2</v>
       </c>
       <c r="AJ42" s="8">
-        <f t="shared" si="91"/>
-        <v>6.05155461562394E-2</v>
+        <f t="shared" si="89"/>
+        <v>8.6659612907054998E-2</v>
       </c>
       <c r="AK42" s="8">
-        <f t="shared" si="91"/>
-        <v>6.5044727275186537E-2</v>
+        <f t="shared" si="89"/>
+        <v>9.2767420328162237E-2</v>
       </c>
       <c r="AL42" s="8">
-        <f t="shared" si="91"/>
-        <v>6.9924741165634421E-2</v>
+        <f t="shared" si="89"/>
+        <v>9.85930349562332E-2</v>
       </c>
       <c r="AM42" s="8">
-        <f t="shared" si="91"/>
-        <v>7.4636103540278484E-2</v>
+        <f t="shared" si="89"/>
+        <v>0.10382648533425555</v>
       </c>
       <c r="AN42" s="8">
-        <f t="shared" si="91"/>
-        <v>7.9204755259014145E-2</v>
+        <f t="shared" si="89"/>
+        <v>0.10863643058814869</v>
       </c>
       <c r="AO42" s="8">
-        <f t="shared" si="91"/>
-        <v>8.3648949874964851E-2</v>
+        <f t="shared" si="89"/>
+        <v>0.11313761658310335</v>
       </c>
       <c r="AP42" s="8">
-        <f t="shared" si="91"/>
-        <v>8.7981698359513652E-2</v>
+        <f t="shared" si="89"/>
+        <v>0.11740816891393198</v>
       </c>
       <c r="AR42" t="s">
         <v>54</v>
       </c>
       <c r="AS42" s="9">
         <f>AS41/AP25</f>
-        <v>12.55538706977924</v>
+        <v>28.054089081140404</v>
       </c>
     </row>
     <row r="43" spans="2:45" x14ac:dyDescent="0.3">
@@ -6412,7 +6411,7 @@
       </c>
       <c r="AS43" s="9">
         <f>Main!D3</f>
-        <v>20.5</v>
+        <v>32.020000000000003</v>
       </c>
     </row>
     <row r="44" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6448,7 +6447,7 @@
       </c>
       <c r="AS44" s="10">
         <f>AS42/AS43-1</f>
-        <v>-0.38754209415711027</v>
+        <v>-0.12385730539848838</v>
       </c>
     </row>
     <row r="45" spans="2:45" x14ac:dyDescent="0.3">
@@ -6549,7 +6548,7 @@
         <v>11127</v>
       </c>
     </row>
-    <row r="49" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>61</v>
       </c>
@@ -6572,7 +6571,7 @@
         <v>3706</v>
       </c>
     </row>
-    <row r="50" spans="2:30" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>62</v>
       </c>
@@ -6601,7 +6600,7 @@
         <v>43269</v>
       </c>
     </row>
-    <row r="51" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>63</v>
       </c>
@@ -6624,7 +6623,7 @@
         <v>96647</v>
       </c>
     </row>
-    <row r="52" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>58</v>
       </c>
@@ -6647,7 +6646,7 @@
         <v>5829</v>
       </c>
     </row>
-    <row r="53" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>64</v>
       </c>
@@ -6670,7 +6669,7 @@
         <v>27591</v>
       </c>
     </row>
-    <row r="54" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>65</v>
       </c>
@@ -6693,7 +6692,7 @@
         <v>4589</v>
       </c>
     </row>
-    <row r="55" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>66</v>
       </c>
@@ -6716,7 +6715,7 @@
         <v>13647</v>
       </c>
     </row>
-    <row r="56" spans="2:30" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
         <v>67</v>
       </c>
@@ -6745,7 +6744,7 @@
         <v>148303</v>
       </c>
     </row>
-    <row r="57" spans="2:30" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
         <v>68</v>
       </c>
@@ -6765,6 +6764,7 @@
         <f>R50+R56</f>
         <v>193542</v>
       </c>
+      <c r="U57" s="7"/>
       <c r="AC57" s="7">
         <f>AC50+AC56</f>
         <v>182103</v>
@@ -6773,8 +6773,11 @@
         <f>AD50+AD56</f>
         <v>191572</v>
       </c>
-    </row>
-    <row r="58" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="AF57" s="7">
+        <v>192520</v>
+      </c>
+    </row>
+    <row r="58" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>69</v>
       </c>
@@ -6797,7 +6800,7 @@
         <v>8578</v>
       </c>
     </row>
-    <row r="59" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>70</v>
       </c>
@@ -6820,7 +6823,7 @@
         <v>3655</v>
       </c>
     </row>
-    <row r="60" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>5</v>
       </c>
@@ -6843,7 +6846,7 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="61" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>29</v>
       </c>
@@ -6866,7 +6869,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="62" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>71</v>
       </c>
@@ -6889,7 +6892,7 @@
         <v>12425</v>
       </c>
     </row>
-    <row r="63" spans="2:30" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
         <v>72</v>
       </c>
@@ -6918,7 +6921,7 @@
         <v>28053</v>
       </c>
     </row>
-    <row r="64" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>5</v>
       </c>
@@ -7056,42 +7059,45 @@
         <v>31</v>
       </c>
       <c r="L70" s="7">
-        <f t="shared" ref="L70:T70" si="92">L24</f>
+        <f t="shared" ref="L70:T70" si="90">L24</f>
         <v>-2758</v>
       </c>
       <c r="M70" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>1481</v>
       </c>
       <c r="N70" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>297</v>
       </c>
       <c r="O70" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>2939</v>
       </c>
       <c r="P70" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-381</v>
       </c>
       <c r="Q70" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-1610</v>
       </c>
       <c r="R70" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-16639</v>
       </c>
       <c r="S70" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-126</v>
       </c>
       <c r="T70" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-821</v>
       </c>
-      <c r="U70" s="7"/>
+      <c r="U70" s="7">
+        <f t="shared" ref="U70" si="91">U24</f>
+        <v>-2918</v>
+      </c>
       <c r="V70" s="7"/>
       <c r="W70" s="7"/>
       <c r="AC70" s="7">
@@ -7108,47 +7114,47 @@
       </c>
       <c r="AF70" s="7">
         <f>AF24</f>
-        <v>-2055.2711750000058</v>
+        <v>-4705.5391600000039</v>
       </c>
       <c r="AG70" s="7">
-        <f t="shared" ref="AG70:AP70" si="93">AG24</f>
-        <v>727.91294399999822</v>
+        <f t="shared" ref="AG70:AP70" si="92">AG24</f>
+        <v>1444.5907629999997</v>
       </c>
       <c r="AH70" s="7">
-        <f t="shared" si="93"/>
-        <v>2613.394682207997</v>
+        <f t="shared" si="92"/>
+        <v>3879.0741934560001</v>
       </c>
       <c r="AI70" s="7">
-        <f t="shared" si="93"/>
-        <v>3383.2235656655957</v>
+        <f t="shared" si="92"/>
+        <v>4983.7860456229982</v>
       </c>
       <c r="AJ70" s="7">
-        <f t="shared" si="93"/>
-        <v>3991.252529282975</v>
+        <f t="shared" si="92"/>
+        <v>5833.8127547963413</v>
       </c>
       <c r="AK70" s="7">
-        <f t="shared" si="93"/>
-        <v>4418.6700311825252</v>
+        <f t="shared" si="92"/>
+        <v>6432.3319022442311</v>
       </c>
       <c r="AL70" s="7">
-        <f t="shared" si="93"/>
-        <v>4892.6884976730762</v>
+        <f t="shared" si="92"/>
+        <v>7041.3580058601765</v>
       </c>
       <c r="AM70" s="7">
-        <f t="shared" si="93"/>
-        <v>5379.0165711273321</v>
+        <f t="shared" si="92"/>
+        <v>7637.5764035950142</v>
       </c>
       <c r="AN70" s="7">
-        <f t="shared" si="93"/>
-        <v>5879.5272122561028</v>
+        <f t="shared" si="92"/>
+        <v>8231.1426342175782</v>
       </c>
       <c r="AO70" s="7">
-        <f t="shared" si="93"/>
-        <v>6395.7115165865716</v>
+        <f t="shared" si="92"/>
+        <v>8829.3531919237375</v>
       </c>
       <c r="AP70" s="7">
-        <f t="shared" si="93"/>
-        <v>6928.7986179926265</v>
+        <f t="shared" si="92"/>
+        <v>9437.5095475217331</v>
       </c>
     </row>
     <row r="71" spans="2:42" x14ac:dyDescent="0.3">
@@ -7159,11 +7165,11 @@
         <v>1901</v>
       </c>
       <c r="M71" s="2">
-        <f t="shared" ref="M71:M83" si="94">M91-L71</f>
+        <f t="shared" ref="M71:M83" si="93">M91-L71</f>
         <v>1832</v>
       </c>
       <c r="N71" s="2">
-        <f t="shared" ref="N71:N83" si="95">N91-M71-L71</f>
+        <f t="shared" ref="N71:N83" si="94">N91-M71-L71</f>
         <v>2020</v>
       </c>
       <c r="O71" s="2">
@@ -7174,11 +7180,11 @@
         <v>2200</v>
       </c>
       <c r="Q71" s="2">
-        <f t="shared" ref="Q71:Q83" si="96">Q91-P71</f>
+        <f t="shared" ref="Q71:Q83" si="95">Q91-P71</f>
         <v>2203</v>
       </c>
       <c r="R71" s="2">
-        <f t="shared" ref="R71:R83" si="97">R91-Q71-P71</f>
+        <f t="shared" ref="R71:R83" si="96">R91-Q71-P71</f>
         <v>3248</v>
       </c>
       <c r="S71" s="2">
@@ -7188,7 +7194,10 @@
       <c r="T71" s="2">
         <v>2425</v>
       </c>
-      <c r="U71" s="2"/>
+      <c r="U71" s="2">
+        <f t="shared" ref="U71:U75" si="97">U91-T71</f>
+        <v>2788</v>
+      </c>
       <c r="V71" s="2"/>
       <c r="W71" s="2"/>
       <c r="AC71" s="2">
@@ -7201,47 +7210,47 @@
         <v>9951</v>
       </c>
       <c r="AF71" s="2">
-        <v>9200</v>
+        <v>9500</v>
       </c>
       <c r="AG71" s="2">
         <f>AF71*1.01</f>
-        <v>9292</v>
+        <v>9595</v>
       </c>
       <c r="AH71" s="2">
         <f t="shared" ref="AH71:AP71" si="98">AG71*1.01</f>
-        <v>9384.92</v>
+        <v>9690.9500000000007</v>
       </c>
       <c r="AI71" s="2">
         <f t="shared" si="98"/>
-        <v>9478.7692000000006</v>
+        <v>9787.8595000000005</v>
       </c>
       <c r="AJ71" s="2">
         <f t="shared" si="98"/>
-        <v>9573.5568920000005</v>
+        <v>9885.7380950000006</v>
       </c>
       <c r="AK71" s="2">
         <f t="shared" si="98"/>
-        <v>9669.2924609199999</v>
+        <v>9984.59547595</v>
       </c>
       <c r="AL71" s="2">
         <f t="shared" si="98"/>
-        <v>9765.9853855292004</v>
+        <v>10084.441430709499</v>
       </c>
       <c r="AM71" s="2">
         <f t="shared" si="98"/>
-        <v>9863.645239384492</v>
+        <v>10185.285845016595</v>
       </c>
       <c r="AN71" s="2">
         <f t="shared" si="98"/>
-        <v>9962.2816917783366</v>
+        <v>10287.13870346676</v>
       </c>
       <c r="AO71" s="2">
         <f t="shared" si="98"/>
-        <v>10061.90450869612</v>
+        <v>10390.010090501428</v>
       </c>
       <c r="AP71" s="2">
         <f t="shared" si="98"/>
-        <v>10162.523553783081</v>
+        <v>10493.910191406443</v>
       </c>
     </row>
     <row r="72" spans="2:42" x14ac:dyDescent="0.3">
@@ -7252,11 +7261,11 @@
         <v>739</v>
       </c>
       <c r="M72" s="2">
+        <f t="shared" si="93"/>
+        <v>922</v>
+      </c>
+      <c r="N72" s="2">
         <f t="shared" si="94"/>
-        <v>922</v>
-      </c>
-      <c r="N72" s="2">
-        <f t="shared" si="95"/>
         <v>772</v>
       </c>
       <c r="O72" s="2">
@@ -7267,11 +7276,11 @@
         <v>1179</v>
       </c>
       <c r="Q72" s="2">
+        <f t="shared" si="95"/>
+        <v>780</v>
+      </c>
+      <c r="R72" s="2">
         <f t="shared" si="96"/>
-        <v>780</v>
-      </c>
-      <c r="R72" s="2">
-        <f t="shared" si="97"/>
         <v>800</v>
       </c>
       <c r="S72" s="2">
@@ -7281,7 +7290,10 @@
       <c r="T72" s="2">
         <v>684</v>
       </c>
-      <c r="U72" s="2"/>
+      <c r="U72" s="2">
+        <f t="shared" si="97"/>
+        <v>664</v>
+      </c>
       <c r="V72" s="2"/>
       <c r="W72" s="2"/>
       <c r="AC72" s="2">
@@ -7345,11 +7357,11 @@
         <v>55</v>
       </c>
       <c r="M73" s="2">
+        <f t="shared" si="93"/>
+        <v>200</v>
+      </c>
+      <c r="N73" s="2">
         <f t="shared" si="94"/>
-        <v>200</v>
-      </c>
-      <c r="N73" s="2">
-        <f t="shared" si="95"/>
         <v>463</v>
       </c>
       <c r="O73" s="2">
@@ -7360,11 +7372,11 @@
         <v>348</v>
       </c>
       <c r="Q73" s="2">
+        <f t="shared" si="95"/>
+        <v>943</v>
+      </c>
+      <c r="R73" s="2">
         <f t="shared" si="96"/>
-        <v>943</v>
-      </c>
-      <c r="R73" s="2">
-        <f t="shared" si="97"/>
         <v>2335</v>
       </c>
       <c r="S73" s="2">
@@ -7374,7 +7386,10 @@
       <c r="T73" s="2">
         <v>0</v>
       </c>
-      <c r="U73" s="2"/>
+      <c r="U73" s="2">
+        <f t="shared" si="97"/>
+        <v>382</v>
+      </c>
       <c r="V73" s="2"/>
       <c r="W73" s="2"/>
       <c r="AC73" s="2">
@@ -7388,47 +7403,47 @@
       </c>
       <c r="AF73" s="2">
         <f>AF16</f>
-        <v>406</v>
+        <v>2746</v>
       </c>
       <c r="AG73" s="2">
         <f t="shared" ref="AG73:AP73" si="102">AG16</f>
-        <v>284.2</v>
+        <v>1922.1999999999998</v>
       </c>
       <c r="AH73" s="2">
         <f t="shared" si="102"/>
-        <v>198.93999999999997</v>
+        <v>1345.5399999999997</v>
       </c>
       <c r="AI73" s="2">
         <f t="shared" si="102"/>
-        <v>139.25799999999998</v>
+        <v>941.8779999999997</v>
       </c>
       <c r="AJ73" s="2">
         <f t="shared" si="102"/>
-        <v>97.480599999999981</v>
+        <v>659.3145999999997</v>
       </c>
       <c r="AK73" s="2">
         <f t="shared" si="102"/>
-        <v>68.236419999999981</v>
+        <v>461.52021999999977</v>
       </c>
       <c r="AL73" s="2">
         <f t="shared" si="102"/>
-        <v>47.765493999999983</v>
+        <v>323.0641539999998</v>
       </c>
       <c r="AM73" s="2">
         <f t="shared" si="102"/>
-        <v>33.435845799999989</v>
+        <v>226.14490779999986</v>
       </c>
       <c r="AN73" s="2">
         <f t="shared" si="102"/>
-        <v>23.405092059999991</v>
+        <v>158.30143545999988</v>
       </c>
       <c r="AO73" s="2">
         <f t="shared" si="102"/>
-        <v>16.383564441999994</v>
+        <v>110.81100482199992</v>
       </c>
       <c r="AP73" s="2">
         <f t="shared" si="102"/>
-        <v>11.468495109399996</v>
+        <v>77.56770337539993</v>
       </c>
     </row>
     <row r="74" spans="2:42" x14ac:dyDescent="0.3">
@@ -7439,11 +7454,11 @@
         <v>465</v>
       </c>
       <c r="M74" s="2">
+        <f t="shared" si="93"/>
+        <v>444</v>
+      </c>
+      <c r="N74" s="2">
         <f t="shared" si="94"/>
-        <v>444</v>
-      </c>
-      <c r="N74" s="2">
-        <f t="shared" si="95"/>
         <v>427</v>
       </c>
       <c r="O74" s="2">
@@ -7454,11 +7469,11 @@
         <v>351</v>
       </c>
       <c r="Q74" s="2">
+        <f t="shared" si="95"/>
+        <v>366</v>
+      </c>
+      <c r="R74" s="2">
         <f t="shared" si="96"/>
-        <v>366</v>
-      </c>
-      <c r="R74" s="2">
-        <f t="shared" si="97"/>
         <v>364</v>
       </c>
       <c r="S74" s="2">
@@ -7468,7 +7483,10 @@
       <c r="T74" s="2">
         <v>249</v>
       </c>
-      <c r="U74" s="2"/>
+      <c r="U74" s="2">
+        <f t="shared" si="97"/>
+        <v>225</v>
+      </c>
       <c r="V74" s="2"/>
       <c r="W74" s="2"/>
       <c r="AC74" s="2">
@@ -7533,11 +7551,11 @@
         <v>-167</v>
       </c>
       <c r="M75" s="2">
+        <f t="shared" si="93"/>
+        <v>21</v>
+      </c>
+      <c r="N75" s="2">
         <f t="shared" si="94"/>
-        <v>21</v>
-      </c>
-      <c r="N75" s="2">
-        <f t="shared" si="95"/>
         <v>193</v>
       </c>
       <c r="O75" s="2">
@@ -7548,11 +7566,11 @@
         <v>-208</v>
       </c>
       <c r="Q75" s="2">
+        <f t="shared" si="95"/>
+        <v>124</v>
+      </c>
+      <c r="R75" s="2">
         <f t="shared" si="96"/>
-        <v>124</v>
-      </c>
-      <c r="R75" s="2">
-        <f t="shared" si="97"/>
         <v>159</v>
       </c>
       <c r="S75" s="2">
@@ -7562,7 +7580,10 @@
       <c r="T75" s="2">
         <v>112</v>
       </c>
-      <c r="U75" s="2"/>
+      <c r="U75" s="2">
+        <f t="shared" si="97"/>
+        <v>-502</v>
+      </c>
       <c r="V75" s="2"/>
       <c r="W75" s="2"/>
       <c r="AC75" s="2">
@@ -7618,11 +7639,11 @@
         <v>0</v>
       </c>
       <c r="M76" s="2">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="N76" s="2">
         <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="N76" s="2">
-        <f t="shared" si="95"/>
         <v>-1376</v>
       </c>
       <c r="O76" s="2">
@@ -7633,11 +7654,11 @@
         <v>0</v>
       </c>
       <c r="Q76" s="2">
+        <f t="shared" si="95"/>
+        <v>0</v>
+      </c>
+      <c r="R76" s="2">
         <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="R76" s="2">
-        <f t="shared" si="97"/>
         <v>6368</v>
       </c>
       <c r="S76" s="2">
@@ -7647,7 +7668,10 @@
       <c r="T76" s="2">
         <v>19</v>
       </c>
-      <c r="U76" s="2"/>
+      <c r="U76" s="2">
+        <f t="shared" ref="U76:U83" si="105">U96-T76</f>
+        <v>87</v>
+      </c>
       <c r="V76" s="2"/>
       <c r="W76" s="2"/>
       <c r="AC76" s="2">
@@ -7698,15 +7722,15 @@
         <v>81</v>
       </c>
       <c r="L77" s="2">
-        <f t="shared" ref="L77" si="105">L97-K77</f>
+        <f t="shared" ref="L77" si="106">L97-K77</f>
         <v>0</v>
       </c>
       <c r="M77" s="2">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="N77" s="2">
         <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="2">
-        <f t="shared" si="95"/>
         <v>-87</v>
       </c>
       <c r="O77" s="2">
@@ -7717,11 +7741,11 @@
         <v>0</v>
       </c>
       <c r="Q77" s="2">
+        <f t="shared" si="95"/>
+        <v>0</v>
+      </c>
+      <c r="R77" s="2">
         <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="R77" s="2">
-        <f t="shared" si="97"/>
         <v>2290</v>
       </c>
       <c r="S77" s="2">
@@ -7731,7 +7755,10 @@
       <c r="T77" s="2">
         <v>0</v>
       </c>
-      <c r="U77" s="2"/>
+      <c r="U77" s="2">
+        <f t="shared" si="105"/>
+        <v>482</v>
+      </c>
       <c r="V77" s="2"/>
       <c r="W77" s="2"/>
       <c r="AC77" s="2">
@@ -7748,43 +7775,43 @@
         <v>1126</v>
       </c>
       <c r="AG77" s="2">
-        <f t="shared" ref="AG77:AP77" si="106">AF77*0.5</f>
+        <f t="shared" ref="AG77:AP77" si="107">AF77*0.5</f>
         <v>563</v>
       </c>
       <c r="AH77" s="2">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>281.5</v>
       </c>
       <c r="AI77" s="2">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>140.75</v>
       </c>
       <c r="AJ77" s="2">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>70.375</v>
       </c>
       <c r="AK77" s="2">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>35.1875</v>
       </c>
       <c r="AL77" s="2">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>17.59375</v>
       </c>
       <c r="AM77" s="2">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>8.796875</v>
       </c>
       <c r="AN77" s="2">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>4.3984375</v>
       </c>
       <c r="AO77" s="2">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>2.19921875</v>
       </c>
       <c r="AP77" s="2">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>1.099609375</v>
       </c>
     </row>
@@ -7796,11 +7823,11 @@
         <v>286</v>
       </c>
       <c r="M78" s="2">
+        <f t="shared" si="93"/>
+        <v>851</v>
+      </c>
+      <c r="N78" s="2">
         <f t="shared" si="94"/>
-        <v>851</v>
-      </c>
-      <c r="N78" s="2">
-        <f t="shared" si="95"/>
         <v>153</v>
       </c>
       <c r="O78" s="2">
@@ -7811,11 +7838,11 @@
         <v>80</v>
       </c>
       <c r="Q78" s="2">
+        <f t="shared" si="95"/>
+        <v>192</v>
+      </c>
+      <c r="R78" s="2">
         <f t="shared" si="96"/>
-        <v>192</v>
-      </c>
-      <c r="R78" s="2">
-        <f t="shared" si="97"/>
         <v>10</v>
       </c>
       <c r="S78" s="2">
@@ -7825,7 +7852,10 @@
       <c r="T78" s="2">
         <v>414</v>
       </c>
-      <c r="U78" s="2"/>
+      <c r="U78" s="2">
+        <f t="shared" si="105"/>
+        <v>590</v>
+      </c>
       <c r="V78" s="2"/>
       <c r="W78" s="2"/>
       <c r="AC78" s="2">
@@ -7879,11 +7909,11 @@
         <v>231</v>
       </c>
       <c r="M79" s="2">
+        <f t="shared" si="93"/>
+        <v>1009</v>
+      </c>
+      <c r="N79" s="2">
         <f t="shared" si="94"/>
-        <v>1009</v>
-      </c>
-      <c r="N79" s="2">
-        <f t="shared" si="95"/>
         <v>518</v>
       </c>
       <c r="O79" s="2">
@@ -7894,11 +7924,11 @@
         <v>-366</v>
       </c>
       <c r="Q79" s="2">
+        <f t="shared" si="95"/>
+        <v>250</v>
+      </c>
+      <c r="R79" s="2">
         <f t="shared" si="96"/>
-        <v>250</v>
-      </c>
-      <c r="R79" s="2">
-        <f t="shared" si="97"/>
         <v>-853</v>
       </c>
       <c r="S79" s="2">
@@ -7908,7 +7938,10 @@
       <c r="T79" s="2">
         <v>-83</v>
       </c>
-      <c r="U79" s="2"/>
+      <c r="U79" s="2">
+        <f t="shared" si="105"/>
+        <v>182</v>
+      </c>
       <c r="V79" s="2"/>
       <c r="W79" s="2"/>
       <c r="AC79" s="2">
@@ -7962,11 +7995,11 @@
         <v>-771</v>
       </c>
       <c r="M80" s="2">
+        <f t="shared" si="93"/>
+        <v>-331</v>
+      </c>
+      <c r="N80" s="2">
         <f t="shared" si="94"/>
-        <v>-331</v>
-      </c>
-      <c r="N80" s="2">
-        <f t="shared" si="95"/>
         <v>20</v>
       </c>
       <c r="O80" s="2">
@@ -7977,11 +8010,11 @@
         <v>-386</v>
       </c>
       <c r="Q80" s="2">
+        <f t="shared" si="95"/>
+        <v>570</v>
+      </c>
+      <c r="R80" s="2">
         <f t="shared" si="96"/>
-        <v>570</v>
-      </c>
-      <c r="R80" s="2">
-        <f t="shared" si="97"/>
         <v>382</v>
       </c>
       <c r="S80" s="2">
@@ -7991,7 +8024,10 @@
       <c r="T80" s="2">
         <v>-240</v>
       </c>
-      <c r="U80" s="2"/>
+      <c r="U80" s="2">
+        <f t="shared" si="105"/>
+        <v>354</v>
+      </c>
       <c r="V80" s="2"/>
       <c r="W80" s="2"/>
       <c r="AC80" s="2">
@@ -8045,11 +8081,11 @@
         <v>-1560</v>
       </c>
       <c r="M81" s="2">
+        <f t="shared" si="93"/>
+        <v>220</v>
+      </c>
+      <c r="N81" s="2">
         <f t="shared" si="94"/>
-        <v>220</v>
-      </c>
-      <c r="N81" s="2">
-        <f t="shared" si="95"/>
         <v>169</v>
       </c>
       <c r="O81" s="2">
@@ -8060,11 +8096,11 @@
         <v>-1289</v>
       </c>
       <c r="Q81" s="2">
+        <f t="shared" si="95"/>
+        <v>-20</v>
+      </c>
+      <c r="R81" s="2">
         <f t="shared" si="96"/>
-        <v>-20</v>
-      </c>
-      <c r="R81" s="2">
-        <f t="shared" si="97"/>
         <v>2693</v>
       </c>
       <c r="S81" s="2">
@@ -8074,7 +8110,10 @@
       <c r="T81" s="2">
         <v>-741</v>
       </c>
-      <c r="U81" s="2"/>
+      <c r="U81" s="2">
+        <f t="shared" si="105"/>
+        <v>1763</v>
+      </c>
       <c r="V81" s="2"/>
       <c r="W81" s="2"/>
       <c r="AC81" s="2">
@@ -8128,11 +8167,11 @@
         <v>1344</v>
       </c>
       <c r="M82" s="2">
+        <f t="shared" si="93"/>
+        <v>-3530</v>
+      </c>
+      <c r="N82" s="2">
         <f t="shared" si="94"/>
-        <v>-3530</v>
-      </c>
-      <c r="N82" s="2">
-        <f t="shared" si="95"/>
         <v>886</v>
       </c>
       <c r="O82" s="2">
@@ -8143,11 +8182,11 @@
         <v>-591</v>
       </c>
       <c r="Q82" s="2">
+        <f t="shared" si="95"/>
+        <v>-1583</v>
+      </c>
+      <c r="R82" s="2">
         <f t="shared" si="96"/>
-        <v>-1583</v>
-      </c>
-      <c r="R82" s="2">
-        <f t="shared" si="97"/>
         <v>1244</v>
       </c>
       <c r="S82" s="2">
@@ -8157,7 +8196,10 @@
       <c r="T82" s="2">
         <v>67</v>
       </c>
-      <c r="U82" s="2"/>
+      <c r="U82" s="2">
+        <f t="shared" si="105"/>
+        <v>-1405</v>
+      </c>
       <c r="V82" s="2"/>
       <c r="W82" s="2"/>
       <c r="AC82" s="2">
@@ -8211,11 +8253,11 @@
         <v>-1540</v>
       </c>
       <c r="M83" s="2">
+        <f t="shared" si="93"/>
+        <v>-303</v>
+      </c>
+      <c r="N83" s="2">
         <f t="shared" si="94"/>
-        <v>-303</v>
-      </c>
-      <c r="N83" s="2">
-        <f t="shared" si="95"/>
         <v>1356</v>
       </c>
       <c r="O83" s="2">
@@ -8226,11 +8268,11 @@
         <v>-2104</v>
       </c>
       <c r="Q83" s="2">
+        <f t="shared" si="95"/>
+        <v>121</v>
+      </c>
+      <c r="R83" s="2">
         <f t="shared" si="96"/>
-        <v>121</v>
-      </c>
-      <c r="R83" s="2">
-        <f t="shared" si="97"/>
         <v>2003</v>
       </c>
       <c r="S83" s="2">
@@ -8240,7 +8282,10 @@
       <c r="T83" s="2">
         <v>-1206</v>
       </c>
-      <c r="U83" s="2"/>
+      <c r="U83" s="2">
+        <f t="shared" si="105"/>
+        <v>-536</v>
+      </c>
       <c r="V83" s="2"/>
       <c r="W83" s="2"/>
       <c r="AC83" s="2">
@@ -8292,42 +8337,45 @@
         <v>83</v>
       </c>
       <c r="L84" s="7">
-        <f t="shared" ref="L84:S84" si="107">L70+SUM(L71:L83)</f>
+        <f t="shared" ref="L84:S84" si="108">L70+SUM(L71:L83)</f>
         <v>-1775</v>
       </c>
       <c r="M84" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>2816</v>
       </c>
       <c r="N84" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>5811</v>
       </c>
       <c r="O84" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>4903</v>
       </c>
       <c r="P84" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-1167</v>
       </c>
       <c r="Q84" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>2336</v>
       </c>
       <c r="R84" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>4404</v>
       </c>
       <c r="S84" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>3192</v>
       </c>
       <c r="T84" s="7">
-        <f t="shared" ref="T84" si="108">T70+SUM(T71:T83)</f>
+        <f t="shared" ref="T84" si="109">T70+SUM(T71:T83)</f>
         <v>879</v>
       </c>
-      <c r="U84" s="7"/>
+      <c r="U84" s="7">
+        <f t="shared" ref="U84" si="110">U70+SUM(U71:U83)</f>
+        <v>2156</v>
+      </c>
       <c r="V84" s="7"/>
       <c r="W84" s="7"/>
       <c r="AC84" s="7">
@@ -8344,47 +8392,47 @@
       </c>
       <c r="AF84" s="7">
         <f>AF70+SUM(AF71:AF83)</f>
-        <v>12933.288824999994</v>
+        <v>12923.020839999997</v>
       </c>
       <c r="AG84" s="7">
-        <f t="shared" ref="AG84:AP84" si="109">AG70+SUM(AG71:AG83)</f>
-        <v>15180.804143999998</v>
+        <f t="shared" ref="AG84:AP84" si="111">AG70+SUM(AG71:AG83)</f>
+        <v>17838.481962999998</v>
       </c>
       <c r="AH84" s="7">
-        <f t="shared" si="109"/>
-        <v>16850.439706207999</v>
+        <f t="shared" si="111"/>
+        <v>19568.749217455999</v>
       </c>
       <c r="AI84" s="7">
-        <f t="shared" si="109"/>
-        <v>17572.556690145597</v>
+        <f t="shared" si="111"/>
+        <v>20284.829470102999</v>
       </c>
       <c r="AJ84" s="7">
-        <f t="shared" si="109"/>
-        <v>18222.983636252575</v>
+        <f t="shared" si="111"/>
+        <v>20939.559064765941</v>
       </c>
       <c r="AK84" s="7">
-        <f t="shared" si="109"/>
-        <v>18742.374487091518</v>
+        <f t="shared" si="111"/>
+        <v>21464.623173183223</v>
       </c>
       <c r="AL84" s="7">
-        <f t="shared" si="109"/>
-        <v>19336.612682288251</v>
+        <f t="shared" si="111"/>
+        <v>22079.036895655649</v>
       </c>
       <c r="AM84" s="7">
-        <f t="shared" si="109"/>
-        <v>19960.003113282692</v>
+        <f t="shared" si="111"/>
+        <v>22732.912613382476</v>
       </c>
       <c r="AN84" s="7">
-        <f t="shared" si="109"/>
-        <v>20608.203397345726</v>
+        <f t="shared" si="111"/>
+        <v>23419.572174395624</v>
       </c>
       <c r="AO84" s="7">
-        <f t="shared" si="109"/>
-        <v>21279.241603743416</v>
+        <f t="shared" si="111"/>
+        <v>24135.41630126589</v>
       </c>
       <c r="AP84" s="7">
-        <f t="shared" si="109"/>
-        <v>21972.370739799044</v>
+        <f t="shared" si="111"/>
+        <v>24878.567515217514</v>
       </c>
     </row>
     <row r="85" spans="2:144" x14ac:dyDescent="0.3">
@@ -8424,7 +8472,10 @@
       <c r="T85" s="2">
         <v>5183</v>
       </c>
-      <c r="U85" s="2"/>
+      <c r="U85" s="2">
+        <f>U105-T85</f>
+        <v>3550</v>
+      </c>
       <c r="V85" s="2"/>
       <c r="W85" s="2"/>
       <c r="AC85" s="2">
@@ -8437,47 +8488,47 @@
         <v>23944</v>
       </c>
       <c r="AF85" s="2">
-        <v>21000</v>
+        <v>18000</v>
       </c>
       <c r="AG85" s="2">
-        <f t="shared" ref="AG85:AH85" si="110">AF85*0.94</f>
-        <v>19740</v>
+        <f>AF85*0.98</f>
+        <v>17640</v>
       </c>
       <c r="AH85" s="2">
-        <f t="shared" si="110"/>
-        <v>18555.599999999999</v>
+        <f t="shared" ref="AH85:AI85" si="112">AG85*0.98</f>
+        <v>17287.2</v>
       </c>
       <c r="AI85" s="2">
-        <f>AH85*0.95</f>
-        <v>17627.819999999996</v>
+        <f t="shared" si="112"/>
+        <v>16941.456000000002</v>
       </c>
       <c r="AJ85" s="2">
-        <f t="shared" ref="AJ85" si="111">AI85*0.95</f>
-        <v>16746.428999999996</v>
+        <f t="shared" ref="AJ85:AP85" si="113">AI85*0.99</f>
+        <v>16772.041440000001</v>
       </c>
       <c r="AK85" s="2">
-        <f>AJ85*0.98</f>
-        <v>16411.500419999997</v>
+        <f t="shared" si="113"/>
+        <v>16604.321025600002</v>
       </c>
       <c r="AL85" s="2">
-        <f t="shared" ref="AL85:AP85" si="112">AK85*0.98</f>
-        <v>16083.270411599997</v>
+        <f t="shared" si="113"/>
+        <v>16438.277815344001</v>
       </c>
       <c r="AM85" s="2">
-        <f t="shared" si="112"/>
-        <v>15761.605003367997</v>
+        <f t="shared" si="113"/>
+        <v>16273.895037190561</v>
       </c>
       <c r="AN85" s="2">
-        <f t="shared" si="112"/>
-        <v>15446.372903300637</v>
+        <f t="shared" si="113"/>
+        <v>16111.156086818655</v>
       </c>
       <c r="AO85" s="2">
-        <f t="shared" si="112"/>
-        <v>15137.445445234624</v>
+        <f t="shared" si="113"/>
+        <v>15950.044525950469</v>
       </c>
       <c r="AP85" s="2">
-        <f t="shared" si="112"/>
-        <v>14834.696536329931</v>
+        <f t="shared" si="113"/>
+        <v>15790.544080690965</v>
       </c>
     </row>
     <row r="86" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -8489,503 +8540,506 @@
         <v>-9188</v>
       </c>
       <c r="M86" s="7">
-        <f t="shared" ref="M86:S86" si="113">M84-M85</f>
+        <f t="shared" ref="M86:S86" si="114">M84-M85</f>
         <v>-3072</v>
       </c>
       <c r="N86" s="7">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>58</v>
       </c>
       <c r="O86" s="7">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-1793</v>
       </c>
       <c r="P86" s="7">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-7137</v>
       </c>
       <c r="Q86" s="7">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-3346</v>
       </c>
       <c r="R86" s="7">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-2054</v>
       </c>
       <c r="S86" s="7">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-2642</v>
       </c>
       <c r="T86" s="7">
-        <f t="shared" ref="T86" si="114">T84-T85</f>
+        <f t="shared" ref="T86:U86" si="115">T84-T85</f>
         <v>-4304</v>
       </c>
-      <c r="U86" s="7"/>
+      <c r="U86" s="7">
+        <f t="shared" si="115"/>
+        <v>-1394</v>
+      </c>
       <c r="V86" s="7"/>
       <c r="W86" s="7"/>
       <c r="AC86" s="7">
-        <f t="shared" ref="AC86" si="115">AC84-AC85</f>
+        <f t="shared" ref="AC86" si="116">AC84-AC85</f>
         <v>-9414</v>
       </c>
       <c r="AD86" s="7">
-        <f t="shared" ref="AD86" si="116">AD84-AD85</f>
+        <f t="shared" ref="AD86" si="117">AD84-AD85</f>
         <v>-13995</v>
       </c>
       <c r="AE86" s="7">
-        <f t="shared" ref="AE86" si="117">AE84-AE85</f>
+        <f t="shared" ref="AE86" si="118">AE84-AE85</f>
         <v>-15179</v>
       </c>
       <c r="AF86" s="7">
-        <f t="shared" ref="AF86" si="118">AF84-AF85</f>
-        <v>-8066.7111750000058</v>
+        <f t="shared" ref="AF86" si="119">AF84-AF85</f>
+        <v>-5076.9791600000026</v>
       </c>
       <c r="AG86" s="7">
-        <f t="shared" ref="AG86" si="119">AG84-AG85</f>
-        <v>-4559.1958560000021</v>
+        <f t="shared" ref="AG86" si="120">AG84-AG85</f>
+        <v>198.48196299999836</v>
       </c>
       <c r="AH86" s="7">
-        <f t="shared" ref="AH86" si="120">AH84-AH85</f>
-        <v>-1705.1602937919997</v>
+        <f t="shared" ref="AH86" si="121">AH84-AH85</f>
+        <v>2281.5492174559986</v>
       </c>
       <c r="AI86" s="7">
-        <f t="shared" ref="AI86" si="121">AI84-AI85</f>
-        <v>-55.263309854399267</v>
+        <f t="shared" ref="AI86" si="122">AI84-AI85</f>
+        <v>3343.3734701029971</v>
       </c>
       <c r="AJ86" s="7">
-        <f t="shared" ref="AJ86" si="122">AJ84-AJ85</f>
-        <v>1476.5546362525783</v>
+        <f t="shared" ref="AJ86" si="123">AJ84-AJ85</f>
+        <v>4167.5176247659401</v>
       </c>
       <c r="AK86" s="7">
-        <f t="shared" ref="AK86" si="123">AK84-AK85</f>
-        <v>2330.8740670915213</v>
+        <f t="shared" ref="AK86" si="124">AK84-AK85</f>
+        <v>4860.3021475832211</v>
       </c>
       <c r="AL86" s="7">
-        <f t="shared" ref="AL86" si="124">AL84-AL85</f>
-        <v>3253.3422706882538</v>
+        <f t="shared" ref="AL86" si="125">AL84-AL85</f>
+        <v>5640.7590803116473</v>
       </c>
       <c r="AM86" s="7">
-        <f t="shared" ref="AM86" si="125">AM84-AM85</f>
-        <v>4198.3981099146949</v>
+        <f t="shared" ref="AM86" si="126">AM84-AM85</f>
+        <v>6459.0175761919145</v>
       </c>
       <c r="AN86" s="7">
-        <f t="shared" ref="AN86" si="126">AN84-AN85</f>
-        <v>5161.8304940450889</v>
+        <f t="shared" ref="AN86" si="127">AN84-AN85</f>
+        <v>7308.4160875769685</v>
       </c>
       <c r="AO86" s="7">
-        <f t="shared" ref="AO86" si="127">AO84-AO85</f>
-        <v>6141.7961585087924</v>
+        <f t="shared" ref="AO86" si="128">AO84-AO85</f>
+        <v>8185.3717753154215</v>
       </c>
       <c r="AP86" s="7">
-        <f t="shared" ref="AP86" si="128">AP84-AP85</f>
-        <v>7137.6742034691124</v>
+        <f t="shared" ref="AP86" si="129">AP84-AP85</f>
+        <v>9088.023434526549</v>
       </c>
       <c r="AQ86" s="1">
         <f>AP86*(1+$AS$88)</f>
-        <v>7066.2974614344212</v>
+        <v>8997.1432001812827</v>
       </c>
       <c r="AR86" s="1">
-        <f t="shared" ref="AR86:DC86" si="129">AQ86*(1+$AS$88)</f>
-        <v>6995.6344868200767</v>
+        <f t="shared" ref="AR86:DC86" si="130">AQ86*(1+$AS$88)</f>
+        <v>8907.1717681794689</v>
       </c>
       <c r="AS86" s="1">
-        <f t="shared" si="129"/>
-        <v>6925.6781419518757</v>
+        <f t="shared" si="130"/>
+        <v>8818.1000504976746</v>
       </c>
       <c r="AT86" s="1">
-        <f t="shared" si="129"/>
-        <v>6856.4213605323566</v>
+        <f t="shared" si="130"/>
+        <v>8729.9190499926972</v>
       </c>
       <c r="AU86" s="1">
-        <f t="shared" si="129"/>
-        <v>6787.8571469270328</v>
+        <f t="shared" si="130"/>
+        <v>8642.61985949277</v>
       </c>
       <c r="AV86" s="1">
-        <f t="shared" si="129"/>
-        <v>6719.9785754577624</v>
+        <f t="shared" si="130"/>
+        <v>8556.1936608978431</v>
       </c>
       <c r="AW86" s="1">
-        <f t="shared" si="129"/>
-        <v>6652.7787897031849</v>
+        <f t="shared" si="130"/>
+        <v>8470.6317242888654</v>
       </c>
       <c r="AX86" s="1">
-        <f t="shared" si="129"/>
-        <v>6586.251001806153</v>
+        <f t="shared" si="130"/>
+        <v>8385.9254070459774</v>
       </c>
       <c r="AY86" s="1">
-        <f t="shared" si="129"/>
-        <v>6520.3884917880914</v>
+        <f t="shared" si="130"/>
+        <v>8302.066152975518</v>
       </c>
       <c r="AZ86" s="1">
-        <f t="shared" si="129"/>
-        <v>6455.1846068702107</v>
+        <f t="shared" si="130"/>
+        <v>8219.0454914457623</v>
       </c>
       <c r="BA86" s="1">
-        <f t="shared" si="129"/>
-        <v>6390.6327608015081</v>
+        <f t="shared" si="130"/>
+        <v>8136.8550365313049</v>
       </c>
       <c r="BB86" s="1">
-        <f t="shared" si="129"/>
-        <v>6326.726433193493</v>
+        <f t="shared" si="130"/>
+        <v>8055.4864861659917</v>
       </c>
       <c r="BC86" s="1">
-        <f t="shared" si="129"/>
-        <v>6263.4591688615583</v>
+        <f t="shared" si="130"/>
+        <v>7974.9316213043321</v>
       </c>
       <c r="BD86" s="1">
-        <f t="shared" si="129"/>
-        <v>6200.8245771729426</v>
+        <f t="shared" si="130"/>
+        <v>7895.182305091289</v>
       </c>
       <c r="BE86" s="1">
-        <f t="shared" si="129"/>
-        <v>6138.8163314012127</v>
+        <f t="shared" si="130"/>
+        <v>7816.230482040376</v>
       </c>
       <c r="BF86" s="1">
-        <f t="shared" si="129"/>
-        <v>6077.4281680872009</v>
+        <f t="shared" si="130"/>
+        <v>7738.0681772199723</v>
       </c>
       <c r="BG86" s="1">
-        <f t="shared" si="129"/>
-        <v>6016.6538864063286</v>
+        <f t="shared" si="130"/>
+        <v>7660.6874954477726</v>
       </c>
       <c r="BH86" s="1">
-        <f t="shared" si="129"/>
-        <v>5956.4873475422655</v>
+        <f t="shared" si="130"/>
+        <v>7584.0806204932951</v>
       </c>
       <c r="BI86" s="1">
-        <f t="shared" si="129"/>
-        <v>5896.9224740668424</v>
+        <f t="shared" si="130"/>
+        <v>7508.2398142883621</v>
       </c>
       <c r="BJ86" s="1">
-        <f t="shared" si="129"/>
-        <v>5837.953249326174</v>
+        <f t="shared" si="130"/>
+        <v>7433.1574161454782</v>
       </c>
       <c r="BK86" s="1">
-        <f t="shared" si="129"/>
-        <v>5779.5737168329124</v>
+        <f t="shared" si="130"/>
+        <v>7358.8258419840231</v>
       </c>
       <c r="BL86" s="1">
-        <f t="shared" si="129"/>
-        <v>5721.7779796645837</v>
+        <f t="shared" si="130"/>
+        <v>7285.2375835641824</v>
       </c>
       <c r="BM86" s="1">
-        <f t="shared" si="129"/>
-        <v>5664.5601998679376</v>
+        <f t="shared" si="130"/>
+        <v>7212.3852077285401</v>
       </c>
       <c r="BN86" s="1">
-        <f t="shared" si="129"/>
-        <v>5607.9145978692586</v>
+        <f t="shared" si="130"/>
+        <v>7140.2613556512542</v>
       </c>
       <c r="BO86" s="1">
-        <f t="shared" si="129"/>
-        <v>5551.8354518905662</v>
+        <f t="shared" si="130"/>
+        <v>7068.8587420947415</v>
       </c>
       <c r="BP86" s="1">
-        <f t="shared" si="129"/>
-        <v>5496.3170973716606</v>
+        <f t="shared" si="130"/>
+        <v>6998.1701546737941</v>
       </c>
       <c r="BQ86" s="1">
-        <f t="shared" si="129"/>
-        <v>5441.3539263979437</v>
+        <f t="shared" si="130"/>
+        <v>6928.1884531270562</v>
       </c>
       <c r="BR86" s="1">
-        <f t="shared" si="129"/>
-        <v>5386.9403871339646</v>
+        <f t="shared" si="130"/>
+        <v>6858.9065685957858</v>
       </c>
       <c r="BS86" s="1">
-        <f t="shared" si="129"/>
-        <v>5333.0709832626253</v>
+        <f t="shared" si="130"/>
+        <v>6790.3175029098275</v>
       </c>
       <c r="BT86" s="1">
-        <f t="shared" si="129"/>
-        <v>5279.7402734299994</v>
+        <f t="shared" si="130"/>
+        <v>6722.4143278807287</v>
       </c>
       <c r="BU86" s="1">
-        <f t="shared" si="129"/>
-        <v>5226.9428706956996</v>
+        <f t="shared" si="130"/>
+        <v>6655.1901846019209</v>
       </c>
       <c r="BV86" s="1">
-        <f t="shared" si="129"/>
-        <v>5174.6734419887425</v>
+        <f t="shared" si="130"/>
+        <v>6588.6382827559019</v>
       </c>
       <c r="BW86" s="1">
-        <f t="shared" si="129"/>
-        <v>5122.9267075688549</v>
+        <f t="shared" si="130"/>
+        <v>6522.7518999283429</v>
       </c>
       <c r="BX86" s="1">
-        <f t="shared" si="129"/>
-        <v>5071.6974404931661</v>
+        <f t="shared" si="130"/>
+        <v>6457.5243809290596</v>
       </c>
       <c r="BY86" s="1">
-        <f t="shared" si="129"/>
-        <v>5020.9804660882346</v>
+        <f t="shared" si="130"/>
+        <v>6392.9491371197691</v>
       </c>
       <c r="BZ86" s="1">
-        <f t="shared" si="129"/>
-        <v>4970.770661427352</v>
+        <f t="shared" si="130"/>
+        <v>6329.0196457485717</v>
       </c>
       <c r="CA86" s="1">
-        <f t="shared" si="129"/>
-        <v>4921.0629548130782</v>
+        <f t="shared" si="130"/>
+        <v>6265.729449291086</v>
       </c>
       <c r="CB86" s="1">
-        <f t="shared" si="129"/>
-        <v>4871.8523252649475</v>
+        <f t="shared" si="130"/>
+        <v>6203.0721547981748</v>
       </c>
       <c r="CC86" s="1">
-        <f t="shared" si="129"/>
-        <v>4823.1338020122976</v>
+        <f t="shared" si="130"/>
+        <v>6141.0414332501932</v>
       </c>
       <c r="CD86" s="1">
-        <f t="shared" si="129"/>
-        <v>4774.9024639921745</v>
+        <f t="shared" si="130"/>
+        <v>6079.6310189176911</v>
       </c>
       <c r="CE86" s="1">
-        <f t="shared" si="129"/>
-        <v>4727.1534393522525</v>
+        <f t="shared" si="130"/>
+        <v>6018.8347087285138</v>
       </c>
       <c r="CF86" s="1">
-        <f t="shared" si="129"/>
-        <v>4679.88190495873</v>
+        <f t="shared" si="130"/>
+        <v>5958.6463616412284</v>
       </c>
       <c r="CG86" s="1">
-        <f t="shared" si="129"/>
-        <v>4633.0830859091429</v>
+        <f t="shared" si="130"/>
+        <v>5899.059898024816</v>
       </c>
       <c r="CH86" s="1">
-        <f t="shared" si="129"/>
-        <v>4586.7522550500516</v>
+        <f t="shared" si="130"/>
+        <v>5840.0692990445677</v>
       </c>
       <c r="CI86" s="1">
-        <f t="shared" si="129"/>
-        <v>4540.8847324995513</v>
+        <f t="shared" si="130"/>
+        <v>5781.6686060541224</v>
       </c>
       <c r="CJ86" s="1">
-        <f t="shared" si="129"/>
-        <v>4495.4758851745555</v>
+        <f t="shared" si="130"/>
+        <v>5723.8519199935809</v>
       </c>
       <c r="CK86" s="1">
-        <f t="shared" si="129"/>
-        <v>4450.5211263228102</v>
+        <f t="shared" si="130"/>
+        <v>5666.6134007936453</v>
       </c>
       <c r="CL86" s="1">
-        <f t="shared" si="129"/>
-        <v>4406.0159150595819</v>
+        <f t="shared" si="130"/>
+        <v>5609.947266785709</v>
       </c>
       <c r="CM86" s="1">
-        <f t="shared" si="129"/>
-        <v>4361.9557559089862</v>
+        <f t="shared" si="130"/>
+        <v>5553.8477941178517</v>
       </c>
       <c r="CN86" s="1">
-        <f t="shared" si="129"/>
-        <v>4318.3361983498962</v>
+        <f t="shared" si="130"/>
+        <v>5498.3093161766728</v>
       </c>
       <c r="CO86" s="1">
-        <f t="shared" si="129"/>
-        <v>4275.1528363663974</v>
+        <f t="shared" si="130"/>
+        <v>5443.3262230149057</v>
       </c>
       <c r="CP86" s="1">
-        <f t="shared" si="129"/>
-        <v>4232.4013080027335</v>
+        <f t="shared" si="130"/>
+        <v>5388.8929607847567</v>
       </c>
       <c r="CQ86" s="1">
-        <f t="shared" si="129"/>
-        <v>4190.0772949227057</v>
+        <f t="shared" si="130"/>
+        <v>5335.0040311769089</v>
       </c>
       <c r="CR86" s="1">
-        <f t="shared" si="129"/>
-        <v>4148.1765219734789</v>
+        <f t="shared" si="130"/>
+        <v>5281.6539908651393</v>
       </c>
       <c r="CS86" s="1">
-        <f t="shared" si="129"/>
-        <v>4106.6947567537436</v>
+        <f t="shared" si="130"/>
+        <v>5228.8374509564883</v>
       </c>
       <c r="CT86" s="1">
-        <f t="shared" si="129"/>
-        <v>4065.6278091862059</v>
+        <f t="shared" si="130"/>
+        <v>5176.5490764469232</v>
       </c>
       <c r="CU86" s="1">
-        <f t="shared" si="129"/>
-        <v>4024.9715310943438</v>
+        <f t="shared" si="130"/>
+        <v>5124.783585682454</v>
       </c>
       <c r="CV86" s="1">
-        <f t="shared" si="129"/>
-        <v>3984.7218157834004</v>
+        <f t="shared" si="130"/>
+        <v>5073.5357498256299</v>
       </c>
       <c r="CW86" s="1">
-        <f t="shared" si="129"/>
-        <v>3944.8745976255664</v>
+        <f t="shared" si="130"/>
+        <v>5022.8003923273736</v>
       </c>
       <c r="CX86" s="1">
-        <f t="shared" si="129"/>
-        <v>3905.4258516493105</v>
+        <f t="shared" si="130"/>
+        <v>4972.5723884040999</v>
       </c>
       <c r="CY86" s="1">
-        <f t="shared" si="129"/>
-        <v>3866.3715931328175</v>
+        <f t="shared" si="130"/>
+        <v>4922.8466645200588</v>
       </c>
       <c r="CZ86" s="1">
-        <f t="shared" si="129"/>
-        <v>3827.7078772014893</v>
+        <f t="shared" si="130"/>
+        <v>4873.6181978748582</v>
       </c>
       <c r="DA86" s="1">
-        <f t="shared" si="129"/>
-        <v>3789.4307984294742</v>
+        <f t="shared" si="130"/>
+        <v>4824.8820158961098</v>
       </c>
       <c r="DB86" s="1">
-        <f t="shared" si="129"/>
-        <v>3751.5364904451794</v>
+        <f t="shared" si="130"/>
+        <v>4776.6331957371485</v>
       </c>
       <c r="DC86" s="1">
-        <f t="shared" si="129"/>
-        <v>3714.0211255407276</v>
+        <f t="shared" si="130"/>
+        <v>4728.8668637797773</v>
       </c>
       <c r="DD86" s="1">
-        <f t="shared" ref="DD86:EN86" si="130">DC86*(1+$AS$88)</f>
-        <v>3676.8809142853202</v>
+        <f t="shared" ref="DD86:EN86" si="131">DC86*(1+$AS$88)</f>
+        <v>4681.5781951419794</v>
       </c>
       <c r="DE86" s="1">
-        <f t="shared" si="130"/>
-        <v>3640.112105142467</v>
+        <f t="shared" si="131"/>
+        <v>4634.7624131905595</v>
       </c>
       <c r="DF86" s="1">
-        <f t="shared" si="130"/>
-        <v>3603.7109840910425</v>
+        <f t="shared" si="131"/>
+        <v>4588.4147890586537</v>
       </c>
       <c r="DG86" s="1">
-        <f t="shared" si="130"/>
-        <v>3567.673874250132</v>
+        <f t="shared" si="131"/>
+        <v>4542.5306411680667</v>
       </c>
       <c r="DH86" s="1">
-        <f t="shared" si="130"/>
-        <v>3531.9971355076309</v>
+        <f t="shared" si="131"/>
+        <v>4497.1053347563857</v>
       </c>
       <c r="DI86" s="1">
-        <f t="shared" si="130"/>
-        <v>3496.6771641525547</v>
+        <f t="shared" si="131"/>
+        <v>4452.1342814088221</v>
       </c>
       <c r="DJ86" s="1">
-        <f t="shared" si="130"/>
-        <v>3461.7103925110291</v>
+        <f t="shared" si="131"/>
+        <v>4407.6129385947334</v>
       </c>
       <c r="DK86" s="1">
-        <f t="shared" si="130"/>
-        <v>3427.0932885859188</v>
+        <f t="shared" si="131"/>
+        <v>4363.5368092087856</v>
       </c>
       <c r="DL86" s="1">
-        <f t="shared" si="130"/>
-        <v>3392.8223557000597</v>
+        <f t="shared" si="131"/>
+        <v>4319.9014411166982</v>
       </c>
       <c r="DM86" s="1">
-        <f t="shared" si="130"/>
-        <v>3358.8941321430589</v>
+        <f t="shared" si="131"/>
+        <v>4276.7024267055313</v>
       </c>
       <c r="DN86" s="1">
-        <f t="shared" si="130"/>
-        <v>3325.3051908216285</v>
+        <f t="shared" si="131"/>
+        <v>4233.9354024384756</v>
       </c>
       <c r="DO86" s="1">
-        <f t="shared" si="130"/>
-        <v>3292.0521389134124</v>
+        <f t="shared" si="131"/>
+        <v>4191.5960484140905</v>
       </c>
       <c r="DP86" s="1">
-        <f t="shared" si="130"/>
-        <v>3259.1316175242782</v>
+        <f t="shared" si="131"/>
+        <v>4149.6800879299499</v>
       </c>
       <c r="DQ86" s="1">
-        <f t="shared" si="130"/>
-        <v>3226.5403013490354</v>
+        <f t="shared" si="131"/>
+        <v>4108.1832870506505</v>
       </c>
       <c r="DR86" s="1">
-        <f t="shared" si="130"/>
-        <v>3194.274898335545</v>
+        <f t="shared" si="131"/>
+        <v>4067.1014541801442</v>
       </c>
       <c r="DS86" s="1">
-        <f t="shared" si="130"/>
-        <v>3162.3321493521894</v>
+        <f t="shared" si="131"/>
+        <v>4026.4304396383427</v>
       </c>
       <c r="DT86" s="1">
-        <f t="shared" si="130"/>
-        <v>3130.7088278586675</v>
+        <f t="shared" si="131"/>
+        <v>3986.1661352419592</v>
       </c>
       <c r="DU86" s="1">
-        <f t="shared" si="130"/>
-        <v>3099.4017395800806</v>
+        <f t="shared" si="131"/>
+        <v>3946.3044738895396</v>
       </c>
       <c r="DV86" s="1">
-        <f t="shared" si="130"/>
-        <v>3068.4077221842799</v>
+        <f t="shared" si="131"/>
+        <v>3906.8414291506442</v>
       </c>
       <c r="DW86" s="1">
-        <f t="shared" si="130"/>
-        <v>3037.723644962437</v>
+        <f t="shared" si="131"/>
+        <v>3867.7730148591377</v>
       </c>
       <c r="DX86" s="1">
-        <f t="shared" si="130"/>
-        <v>3007.3464085128126</v>
+        <f t="shared" si="131"/>
+        <v>3829.0952847105464</v>
       </c>
       <c r="DY86" s="1">
-        <f t="shared" si="130"/>
-        <v>2977.2729444276843</v>
+        <f t="shared" si="131"/>
+        <v>3790.8043318634409</v>
       </c>
       <c r="DZ86" s="1">
-        <f t="shared" si="130"/>
-        <v>2947.5002149834072</v>
+        <f t="shared" si="131"/>
+        <v>3752.8962885448063</v>
       </c>
       <c r="EA86" s="1">
-        <f t="shared" si="130"/>
-        <v>2918.0252128335733</v>
+        <f t="shared" si="131"/>
+        <v>3715.3673256593584</v>
       </c>
       <c r="EB86" s="1">
-        <f t="shared" si="130"/>
-        <v>2888.8449607052376</v>
+        <f t="shared" si="131"/>
+        <v>3678.2136524027646</v>
       </c>
       <c r="EC86" s="1">
-        <f t="shared" si="130"/>
-        <v>2859.9565110981853</v>
+        <f t="shared" si="131"/>
+        <v>3641.4315158787372</v>
       </c>
       <c r="ED86" s="1">
-        <f t="shared" si="130"/>
-        <v>2831.3569459872033</v>
+        <f t="shared" si="131"/>
+        <v>3605.0172007199499</v>
       </c>
       <c r="EE86" s="1">
-        <f t="shared" si="130"/>
-        <v>2803.043376527331</v>
+        <f t="shared" si="131"/>
+        <v>3568.9670287127506</v>
       </c>
       <c r="EF86" s="1">
-        <f t="shared" si="130"/>
-        <v>2775.0129427620577</v>
+        <f t="shared" si="131"/>
+        <v>3533.2773584256229</v>
       </c>
       <c r="EG86" s="1">
-        <f t="shared" si="130"/>
-        <v>2747.2628133344369</v>
+        <f t="shared" si="131"/>
+        <v>3497.9445848413666</v>
       </c>
       <c r="EH86" s="1">
-        <f t="shared" si="130"/>
-        <v>2719.7901852010928</v>
+        <f t="shared" si="131"/>
+        <v>3462.9651389929527</v>
       </c>
       <c r="EI86" s="1">
-        <f t="shared" si="130"/>
-        <v>2692.5922833490818</v>
+        <f t="shared" si="131"/>
+        <v>3428.335487603023</v>
       </c>
       <c r="EJ86" s="1">
-        <f t="shared" si="130"/>
-        <v>2665.6663605155909</v>
+        <f t="shared" si="131"/>
+        <v>3394.0521327269926</v>
       </c>
       <c r="EK86" s="1">
-        <f t="shared" si="130"/>
-        <v>2639.0096969104347</v>
+        <f t="shared" si="131"/>
+        <v>3360.1116113997227</v>
       </c>
       <c r="EL86" s="1">
-        <f t="shared" si="130"/>
-        <v>2612.6195999413303</v>
+        <f t="shared" si="131"/>
+        <v>3326.5104952857255</v>
       </c>
       <c r="EM86" s="1">
-        <f t="shared" si="130"/>
-        <v>2586.4934039419168</v>
+        <f t="shared" si="131"/>
+        <v>3293.2453903328683</v>
       </c>
       <c r="EN86" s="1">
-        <f t="shared" si="130"/>
-        <v>2560.6284699024977</v>
+        <f t="shared" si="131"/>
+        <v>3260.3129364295396</v>
       </c>
     </row>
     <row r="87" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -9014,28 +9068,34 @@
       <c r="N88" s="7"/>
       <c r="O88" s="7"/>
       <c r="P88" s="8">
-        <f t="shared" ref="P88:R88" si="131">P85/L85-1</f>
+        <f t="shared" ref="P88:R88" si="132">P85/L85-1</f>
         <v>-0.19465803318494534</v>
       </c>
       <c r="Q88" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>-3.4986413043478271E-2</v>
       </c>
       <c r="R88" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.12254475925604025</v>
       </c>
       <c r="S88" s="8">
         <f>S85/O85-1</f>
         <v>-0.12873357228195936</v>
       </c>
-      <c r="T88" s="8"/>
-      <c r="U88" s="8"/>
+      <c r="T88" s="8">
+        <f t="shared" ref="T88:U88" si="133">T85/P85-1</f>
+        <v>-0.13182579564489116</v>
+      </c>
+      <c r="U88" s="8">
+        <f t="shared" si="133"/>
+        <v>-0.37521999296022523</v>
+      </c>
       <c r="V88" s="8"/>
       <c r="W88" s="8"/>
       <c r="AC88" s="7"/>
       <c r="AD88" s="8">
-        <f t="shared" ref="AD88" si="132">AD85/AC85-1</f>
+        <f t="shared" ref="AD88" si="134">AD85/AC85-1</f>
         <v>3.6467557559169306E-2</v>
       </c>
       <c r="AE88" s="8">
@@ -9054,7 +9114,7 @@
         <v>50</v>
       </c>
       <c r="AS89" s="8">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="90" spans="2:144" x14ac:dyDescent="0.3">
@@ -9077,12 +9137,16 @@
         <f>R24+Q24+P24</f>
         <v>-18630</v>
       </c>
+      <c r="U90" s="2">
+        <f>U24+T24</f>
+        <v>-3739</v>
+      </c>
       <c r="AR90" t="s">
         <v>95</v>
       </c>
       <c r="AS90" s="2">
         <f>NPV(AS89,AF86:EN86)</f>
-        <v>57773.595173221482</v>
+        <v>117845.85718643072</v>
       </c>
     </row>
     <row r="91" spans="2:144" x14ac:dyDescent="0.3">
@@ -9101,12 +9165,15 @@
       <c r="R91">
         <v>7651</v>
       </c>
+      <c r="U91">
+        <v>5213</v>
+      </c>
       <c r="AR91" t="s">
         <v>52</v>
       </c>
       <c r="AS91" s="2">
         <f>Main!D8</f>
-        <v>-24076</v>
+        <v>-24168</v>
       </c>
     </row>
     <row r="92" spans="2:144" x14ac:dyDescent="0.3">
@@ -9125,12 +9192,15 @@
       <c r="R92">
         <v>2759</v>
       </c>
+      <c r="U92">
+        <v>1348</v>
+      </c>
       <c r="AR92" t="s">
         <v>53</v>
       </c>
       <c r="AS92" s="2">
         <f>AS90+AS91</f>
-        <v>33697.595173221482</v>
+        <v>93677.857186430716</v>
       </c>
     </row>
     <row r="93" spans="2:144" x14ac:dyDescent="0.3">
@@ -9149,12 +9219,15 @@
       <c r="R93">
         <v>3626</v>
       </c>
+      <c r="U93">
+        <v>382</v>
+      </c>
       <c r="AR93" t="s">
         <v>54</v>
       </c>
       <c r="AS93" s="9">
         <f>AS92/AP25</f>
-        <v>7.7590594458258071</v>
+        <v>21.569849686030558</v>
       </c>
     </row>
     <row r="94" spans="2:144" x14ac:dyDescent="0.3">
@@ -9173,12 +9246,15 @@
       <c r="R94">
         <v>1081</v>
       </c>
+      <c r="U94">
+        <v>474</v>
+      </c>
       <c r="AR94" t="s">
         <v>55</v>
       </c>
       <c r="AS94" s="9">
         <f>Main!D3</f>
-        <v>20.5</v>
+        <v>32.020000000000003</v>
       </c>
     </row>
     <row r="95" spans="2:144" x14ac:dyDescent="0.3">
@@ -9197,6 +9273,9 @@
       <c r="R95">
         <v>75</v>
       </c>
+      <c r="U95">
+        <v>-390</v>
+      </c>
     </row>
     <row r="96" spans="2:144" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
@@ -9208,8 +9287,11 @@
       <c r="R96">
         <v>6368</v>
       </c>
-    </row>
-    <row r="97" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="U96">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="97" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>81</v>
       </c>
@@ -9219,8 +9301,11 @@
       <c r="R97">
         <v>2290</v>
       </c>
-    </row>
-    <row r="98" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="U97">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="98" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>59</v>
       </c>
@@ -9236,8 +9321,11 @@
       <c r="R98">
         <v>282</v>
       </c>
-    </row>
-    <row r="99" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="U98">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="99" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>60</v>
       </c>
@@ -9253,8 +9341,11 @@
       <c r="R99">
         <v>-969</v>
       </c>
-    </row>
-    <row r="100" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="U99">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>69</v>
       </c>
@@ -9270,8 +9361,11 @@
       <c r="R100">
         <v>566</v>
       </c>
-    </row>
-    <row r="101" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="U100">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="101" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>70</v>
       </c>
@@ -9287,8 +9381,11 @@
       <c r="R101">
         <v>1384</v>
       </c>
-    </row>
-    <row r="102" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="U101">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="102" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>29</v>
       </c>
@@ -9304,8 +9401,11 @@
       <c r="R102">
         <v>-930</v>
       </c>
-    </row>
-    <row r="103" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="U102">
+        <v>-1338</v>
+      </c>
+    </row>
+    <row r="103" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>82</v>
       </c>
@@ -9321,8 +9421,11 @@
       <c r="R103">
         <v>20</v>
       </c>
-    </row>
-    <row r="104" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="U103">
+        <v>-1742</v>
+      </c>
+    </row>
+    <row r="104" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>83</v>
       </c>
@@ -9342,8 +9445,12 @@
         <f>R90+SUM(R91:R103)</f>
         <v>5573</v>
       </c>
-    </row>
-    <row r="105" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="U104" s="2">
+        <f>U90+SUM(U91:U103)</f>
+        <v>3035</v>
+      </c>
+    </row>
+    <row r="105" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>63</v>
       </c>
@@ -9358,6 +9465,9 @@
       </c>
       <c r="R105">
         <v>18110</v>
+      </c>
+      <c r="U105">
+        <v>8733</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/INTC.xlsx
+++ b/Financial Analysis/INTC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6316778D-0ADD-44D8-ABD6-DB7C7C3B3C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28055210-8756-4829-AABF-8B6EE460EC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{99FD0C39-1228-4528-9306-B2D51C30197E}"/>
   </bookViews>
@@ -894,14 +894,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="9">
-        <v>32.020000000000003</v>
+        <v>36.729999999999997</v>
       </c>
       <c r="E3" s="4">
-        <v>45918</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45927</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="4">
         <v>45953</v>
@@ -925,7 +925,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>139895.38</v>
+        <v>160473.37</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -967,7 +967,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>164063.38</v>
+        <v>184641.37</v>
       </c>
     </row>
   </sheetData>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AS43" s="9">
         <f>Main!D3</f>
-        <v>32.020000000000003</v>
+        <v>36.729999999999997</v>
       </c>
     </row>
     <row r="44" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="AS44" s="10">
         <f>AS42/AS43-1</f>
-        <v>-0.12385730539848838</v>
+        <v>-0.23620775711569819</v>
       </c>
     </row>
     <row r="45" spans="2:45" x14ac:dyDescent="0.3">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AS94" s="9">
         <f>Main!D3</f>
-        <v>32.020000000000003</v>
+        <v>36.729999999999997</v>
       </c>
     </row>
     <row r="95" spans="2:144" x14ac:dyDescent="0.3">

--- a/Financial Analysis/INTC.xlsx
+++ b/Financial Analysis/INTC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28055210-8756-4829-AABF-8B6EE460EC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231DF6D5-D2D9-470B-8E10-2BD8B8C56EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{99FD0C39-1228-4528-9306-B2D51C30197E}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="117">
   <si>
     <t>INTC</t>
   </si>
@@ -349,7 +349,34 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Intel</t>
+  </si>
+  <si>
+    <t>Mobileye &amp; subsidiaries</t>
+  </si>
+  <si>
+    <t>NAND</t>
+  </si>
+  <si>
+    <t>Total employees</t>
+  </si>
+  <si>
+    <t>Escrow</t>
+  </si>
+  <si>
+    <t>Divestitures</t>
+  </si>
+  <si>
+    <t>Raw materials</t>
+  </si>
+  <si>
+    <t>WIP</t>
+  </si>
+  <si>
+    <t>Finished goods</t>
+  </si>
+  <si>
+    <t>Slightly undervalued</t>
   </si>
 </sst>
 </file>
@@ -359,7 +386,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -397,6 +424,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -418,7 +454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -450,6 +486,9 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,15 +510,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -495,8 +534,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13822680" y="0"/>
-          <a:ext cx="0" cy="16733520"/>
+          <a:off x="14447520" y="0"/>
+          <a:ext cx="0" cy="17647920"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -529,7 +568,7 @@
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -894,17 +933,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="9">
-        <v>36.729999999999997</v>
+        <v>38.28</v>
       </c>
       <c r="E3" s="4">
-        <v>45937</v>
+        <v>45956</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45956</v>
       </c>
       <c r="G3" s="4">
-        <v>45953</v>
+        <v>46044</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -912,11 +951,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <f>4369</f>
-        <v>4369</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -925,7 +964,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>160473.37</v>
+        <v>172795.92</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -933,11 +972,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>9643+11563+5383</f>
-        <v>26589</v>
+        <f>11141+19794+8667</f>
+        <v>39602</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -945,11 +984,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="2">
-        <f>6731+44026</f>
-        <v>50757</v>
+        <f>2496+44057</f>
+        <v>46553</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -958,7 +997,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>-24168</v>
+        <v>-6951</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -967,7 +1006,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>184641.37</v>
+        <v>179746.92</v>
       </c>
     </row>
   </sheetData>
@@ -980,7 +1019,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="B2:EV105"/>
+  <dimension ref="B2:EV117"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
@@ -1331,8 +1370,12 @@
       <c r="U5" s="16">
         <v>7871</v>
       </c>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
+      <c r="V5" s="16">
+        <v>8500</v>
+      </c>
+      <c r="W5" s="15">
+        <v>8800</v>
+      </c>
       <c r="AD5" s="12">
         <f t="shared" si="1"/>
         <v>10450</v>
@@ -1429,8 +1472,12 @@
       <c r="U6" s="11">
         <v>3939</v>
       </c>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
+      <c r="V6" s="11">
+        <v>4100</v>
+      </c>
+      <c r="W6" s="15">
+        <v>4200</v>
+      </c>
       <c r="AD6" s="12">
         <f t="shared" si="1"/>
         <v>12635</v>
@@ -1524,7 +1571,7 @@
       <c r="T7" s="11"/>
       <c r="U7" s="11"/>
       <c r="V7" s="11"/>
-      <c r="W7" s="11"/>
+      <c r="W7" s="15"/>
       <c r="AD7" s="12">
         <f t="shared" si="1"/>
         <v>5774</v>
@@ -1617,8 +1664,12 @@
       </c>
       <c r="T8" s="11"/>
       <c r="U8" s="11"/>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11"/>
+      <c r="V8" s="11">
+        <v>4200</v>
+      </c>
+      <c r="W8" s="15">
+        <v>4300</v>
+      </c>
       <c r="AD8" s="12">
         <f t="shared" si="1"/>
         <v>18910</v>
@@ -1711,8 +1762,12 @@
       </c>
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
-      <c r="V9" s="11"/>
-      <c r="W9" s="11"/>
+      <c r="V9" s="11">
+        <v>1000</v>
+      </c>
+      <c r="W9" s="15">
+        <v>1000</v>
+      </c>
       <c r="AD9" s="12">
         <f t="shared" si="1"/>
         <v>5608</v>
@@ -1805,8 +1860,12 @@
       </c>
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
+      <c r="V10" s="11">
+        <v>-4200</v>
+      </c>
+      <c r="W10" s="15">
+        <v>-4300</v>
+      </c>
       <c r="AD10" s="12">
         <f t="shared" si="1"/>
         <v>-17957</v>
@@ -1928,12 +1987,11 @@
         <v>12859</v>
       </c>
       <c r="V11" s="7">
-        <f>R11*0.98</f>
-        <v>13018.32</v>
+        <v>13653</v>
       </c>
       <c r="W11" s="7">
-        <f>S11*0.97</f>
-        <v>13832.199999999999</v>
+        <f>S11*0.96</f>
+        <v>13689.6</v>
       </c>
       <c r="Y11" s="7">
         <v>70848</v>
@@ -1962,47 +2020,47 @@
       </c>
       <c r="AF11" s="7">
         <f>SUM(T11:W11)</f>
-        <v>52376.52</v>
+        <v>52868.6</v>
       </c>
       <c r="AG11" s="7">
         <f>AF11*1.1</f>
-        <v>57614.171999999999</v>
+        <v>58155.460000000006</v>
       </c>
       <c r="AH11" s="7">
         <f>AG11*1.07</f>
-        <v>61647.164040000003</v>
+        <v>62226.342200000014</v>
       </c>
       <c r="AI11" s="7">
         <f>AH11*1.05</f>
-        <v>64729.522242000006</v>
+        <v>65337.659310000017</v>
       </c>
       <c r="AJ11" s="7">
         <f>AI11*1.04</f>
-        <v>67318.703131680013</v>
+        <v>67951.165682400024</v>
       </c>
       <c r="AK11" s="7">
         <f>AJ11*1.03</f>
-        <v>69338.26422563041</v>
+        <v>69989.700652872023</v>
       </c>
       <c r="AL11" s="7">
         <f t="shared" ref="AL11:AP11" si="11">AK11*1.03</f>
-        <v>71418.412152399324</v>
+        <v>72089.39167245818</v>
       </c>
       <c r="AM11" s="7">
         <f t="shared" si="11"/>
-        <v>73560.964516971304</v>
+        <v>74252.073422631933</v>
       </c>
       <c r="AN11" s="7">
         <f t="shared" si="11"/>
-        <v>75767.793452480444</v>
+        <v>76479.635625310897</v>
       </c>
       <c r="AO11" s="7">
         <f t="shared" si="11"/>
-        <v>78040.827256054865</v>
+        <v>78774.02469407022</v>
       </c>
       <c r="AP11" s="7">
         <f t="shared" si="11"/>
-        <v>80382.052073736515</v>
+        <v>81137.245434892335</v>
       </c>
     </row>
     <row r="12" spans="2:42" x14ac:dyDescent="0.3">
@@ -2067,12 +2125,11 @@
         <v>9317</v>
       </c>
       <c r="V12" s="2">
-        <f t="shared" ref="V12:W12" si="12">V11-V13</f>
-        <v>8579.0728799999997</v>
+        <v>8435</v>
       </c>
       <c r="W12" s="2">
-        <f t="shared" si="12"/>
-        <v>8714.2860000000001</v>
+        <f t="shared" ref="W12" si="12">W11-W13</f>
+        <v>8966.6880000000019</v>
       </c>
       <c r="Y12" s="2">
         <v>27111</v>
@@ -2101,47 +2158,47 @@
       </c>
       <c r="AF12" s="2">
         <f>SUM(T12:W12)</f>
-        <v>34605.35888</v>
+        <v>34713.688000000002</v>
       </c>
       <c r="AG12" s="2">
         <f t="shared" ref="AG12:AP12" si="13">AG11-AG13</f>
-        <v>34568.503199999999</v>
+        <v>34893.275999999998</v>
       </c>
       <c r="AH12" s="2">
         <f t="shared" si="13"/>
-        <v>35755.355143200002</v>
+        <v>36091.278476000007</v>
       </c>
       <c r="AI12" s="2">
         <f t="shared" si="13"/>
-        <v>37543.122900360002</v>
+        <v>37895.842399800007</v>
       </c>
       <c r="AJ12" s="2">
         <f t="shared" si="13"/>
-        <v>39044.847816374408</v>
+        <v>39411.67609579202</v>
       </c>
       <c r="AK12" s="2">
         <f t="shared" si="13"/>
-        <v>40216.193250865639</v>
+        <v>40594.026378665774</v>
       </c>
       <c r="AL12" s="2">
         <f t="shared" si="13"/>
-        <v>41422.679048391612</v>
+        <v>41811.847170025751</v>
       </c>
       <c r="AM12" s="2">
         <f t="shared" si="13"/>
-        <v>42665.359419843357</v>
+        <v>43066.202585126521</v>
       </c>
       <c r="AN12" s="2">
         <f t="shared" si="13"/>
-        <v>43945.320202438656</v>
+        <v>44358.188662680317</v>
       </c>
       <c r="AO12" s="2">
         <f t="shared" si="13"/>
-        <v>45263.679808511821</v>
+        <v>45688.93432256073</v>
       </c>
       <c r="AP12" s="2">
         <f t="shared" si="13"/>
-        <v>46621.590202767176</v>
+        <v>47059.602352237554</v>
       </c>
     </row>
     <row r="13" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2149,7 +2206,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:U13" si="14">C11-C12</f>
+        <f t="shared" ref="C13:V13" si="14">C11-C12</f>
         <v>11348</v>
       </c>
       <c r="D13" s="7">
@@ -2225,12 +2282,12 @@
         <v>3542</v>
       </c>
       <c r="V13" s="7">
-        <f>V11*0.341</f>
-        <v>4439.24712</v>
+        <f t="shared" si="14"/>
+        <v>5218</v>
       </c>
       <c r="W13" s="7">
-        <f>W11*0.37</f>
-        <v>5117.9139999999998</v>
+        <f>W11*0.345</f>
+        <v>4722.9119999999994</v>
       </c>
       <c r="Y13" s="7">
         <f t="shared" ref="Y13:AF13" si="15">Y11-Y12</f>
@@ -2262,47 +2319,47 @@
       </c>
       <c r="AF13" s="7">
         <f t="shared" si="15"/>
-        <v>17771.161119999997</v>
+        <v>18154.911999999997</v>
       </c>
       <c r="AG13" s="7">
         <f>AG11*0.4</f>
-        <v>23045.668799999999</v>
+        <v>23262.184000000005</v>
       </c>
       <c r="AH13" s="7">
         <f>AH11*0.42</f>
-        <v>25891.808896800001</v>
+        <v>26135.063724000003</v>
       </c>
       <c r="AI13" s="7">
         <f t="shared" ref="AI13:AP13" si="16">AI11*0.42</f>
-        <v>27186.399341640001</v>
+        <v>27441.816910200007</v>
       </c>
       <c r="AJ13" s="7">
         <f t="shared" si="16"/>
-        <v>28273.855315305605</v>
+        <v>28539.489586608008</v>
       </c>
       <c r="AK13" s="7">
         <f t="shared" si="16"/>
-        <v>29122.070974764771</v>
+        <v>29395.674274206249</v>
       </c>
       <c r="AL13" s="7">
         <f t="shared" si="16"/>
-        <v>29995.733104007715</v>
+        <v>30277.544502432433</v>
       </c>
       <c r="AM13" s="7">
         <f t="shared" si="16"/>
-        <v>30895.605097127947</v>
+        <v>31185.870837505412</v>
       </c>
       <c r="AN13" s="7">
         <f t="shared" si="16"/>
-        <v>31822.473250041785</v>
+        <v>32121.446962630576</v>
       </c>
       <c r="AO13" s="7">
         <f t="shared" si="16"/>
-        <v>32777.147447543044</v>
+        <v>33085.09037150949</v>
       </c>
       <c r="AP13" s="7">
         <f t="shared" si="16"/>
-        <v>33760.461870969339</v>
+        <v>34077.64308265478</v>
       </c>
     </row>
     <row r="14" spans="2:42" x14ac:dyDescent="0.3">
@@ -2367,12 +2424,11 @@
         <v>3684</v>
       </c>
       <c r="V14" s="2">
-        <f>R14*0.93</f>
-        <v>3765.57</v>
+        <v>3231</v>
       </c>
       <c r="W14" s="2">
-        <f>S14*1.01</f>
-        <v>3914.76</v>
+        <f>S14*0.85</f>
+        <v>3294.6</v>
       </c>
       <c r="Y14" s="2">
         <v>13543</v>
@@ -2401,47 +2457,47 @@
       </c>
       <c r="AF14" s="2">
         <f>SUM(T14:W14)</f>
-        <v>15004.33</v>
+        <v>13849.6</v>
       </c>
       <c r="AG14" s="2">
         <f>AF14*0.98</f>
-        <v>14704.243399999999</v>
+        <v>13572.608</v>
       </c>
       <c r="AH14" s="2">
-        <f>AG14*1.01</f>
-        <v>14851.285834</v>
+        <f>AG14*1.02</f>
+        <v>13844.060160000001</v>
       </c>
       <c r="AI14" s="2">
-        <f>AH14*1.01</f>
-        <v>14999.79869234</v>
+        <f>AH14*1.02</f>
+        <v>14120.941363200001</v>
       </c>
       <c r="AJ14" s="2">
-        <f t="shared" ref="AJ14:AP15" si="17">AI14*1.01</f>
-        <v>15149.7966792634</v>
+        <f>AI14*1.02</f>
+        <v>14403.360190464002</v>
       </c>
       <c r="AK14" s="2">
-        <f t="shared" si="17"/>
-        <v>15301.294646056034</v>
+        <f t="shared" ref="AJ14:AP15" si="17">AJ14*1.01</f>
+        <v>14547.393792368643</v>
       </c>
       <c r="AL14" s="2">
         <f t="shared" si="17"/>
-        <v>15454.307592516594</v>
+        <v>14692.86773029233</v>
       </c>
       <c r="AM14" s="2">
         <f t="shared" si="17"/>
-        <v>15608.850668441761</v>
+        <v>14839.796407595253</v>
       </c>
       <c r="AN14" s="2">
         <f t="shared" si="17"/>
-        <v>15764.939175126179</v>
+        <v>14988.194371671207</v>
       </c>
       <c r="AO14" s="2">
         <f t="shared" si="17"/>
-        <v>15922.588566877441</v>
+        <v>15138.07631538792</v>
       </c>
       <c r="AP14" s="2">
         <f t="shared" si="17"/>
-        <v>16081.814452546216</v>
+        <v>15289.457078541798</v>
       </c>
     </row>
     <row r="15" spans="2:42" x14ac:dyDescent="0.3">
@@ -2506,12 +2562,11 @@
         <v>1144</v>
       </c>
       <c r="V15" s="2">
-        <f>R15*0.86</f>
-        <v>1189.3799999999999</v>
+        <v>1129</v>
       </c>
       <c r="W15" s="2">
-        <f>S15*1.03</f>
-        <v>1276.17</v>
+        <f>S15*0.96</f>
+        <v>1189.44</v>
       </c>
       <c r="Y15" s="2">
         <v>6950</v>
@@ -2540,47 +2595,47 @@
       </c>
       <c r="AF15" s="2">
         <f>SUM(T15:W15)</f>
-        <v>4786.55</v>
+        <v>4639.4400000000005</v>
       </c>
       <c r="AG15" s="2">
         <f>AF15*0.97</f>
-        <v>4642.9534999999996</v>
+        <v>4500.2568000000001</v>
       </c>
       <c r="AH15" s="2">
         <f t="shared" ref="AH15:AK15" si="18">AG15*1.02</f>
-        <v>4735.8125700000001</v>
+        <v>4590.2619359999999</v>
       </c>
       <c r="AI15" s="2">
         <f t="shared" si="18"/>
-        <v>4830.5288214000002</v>
+        <v>4682.0671747200004</v>
       </c>
       <c r="AJ15" s="2">
         <f t="shared" si="18"/>
-        <v>4927.1393978280003</v>
+        <v>4775.7085182144001</v>
       </c>
       <c r="AK15" s="2">
         <f t="shared" si="18"/>
-        <v>5025.6821857845607</v>
+        <v>4871.2226885786886</v>
       </c>
       <c r="AL15" s="2">
         <f>AK15*1.01</f>
-        <v>5075.9390076424061</v>
+        <v>4919.9349154644751</v>
       </c>
       <c r="AM15" s="2">
         <f t="shared" si="17"/>
-        <v>5126.6983977188302</v>
+        <v>4969.1342646191197</v>
       </c>
       <c r="AN15" s="2">
         <f t="shared" si="17"/>
-        <v>5177.9653816960181</v>
+        <v>5018.8256072653112</v>
       </c>
       <c r="AO15" s="2">
         <f t="shared" si="17"/>
-        <v>5229.7450355129786</v>
+        <v>5069.0138633379647</v>
       </c>
       <c r="AP15" s="2">
         <f t="shared" si="17"/>
-        <v>5282.0424858681081</v>
+        <v>5119.704001971344</v>
       </c>
     </row>
     <row r="16" spans="2:42" x14ac:dyDescent="0.3">
@@ -2645,10 +2700,10 @@
         <v>1890</v>
       </c>
       <c r="V16" s="2">
-        <v>650</v>
+        <v>175</v>
       </c>
       <c r="W16" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Y16" s="2">
         <v>-72</v>
@@ -2677,47 +2732,47 @@
       </c>
       <c r="AF16" s="2">
         <f>SUM(T16:W16)</f>
-        <v>2746</v>
+        <v>2321</v>
       </c>
       <c r="AG16" s="2">
         <f>AF16*0.7</f>
-        <v>1922.1999999999998</v>
+        <v>1624.6999999999998</v>
       </c>
       <c r="AH16" s="2">
         <f t="shared" ref="AH16:AP16" si="19">AG16*0.7</f>
-        <v>1345.5399999999997</v>
+        <v>1137.2899999999997</v>
       </c>
       <c r="AI16" s="2">
         <f t="shared" si="19"/>
-        <v>941.8779999999997</v>
+        <v>796.10299999999972</v>
       </c>
       <c r="AJ16" s="2">
         <f t="shared" si="19"/>
-        <v>659.3145999999997</v>
+        <v>557.2720999999998</v>
       </c>
       <c r="AK16" s="2">
         <f t="shared" si="19"/>
-        <v>461.52021999999977</v>
+        <v>390.09046999999981</v>
       </c>
       <c r="AL16" s="2">
         <f t="shared" si="19"/>
-        <v>323.0641539999998</v>
+        <v>273.06332899999984</v>
       </c>
       <c r="AM16" s="2">
         <f t="shared" si="19"/>
-        <v>226.14490779999986</v>
+        <v>191.14433029999987</v>
       </c>
       <c r="AN16" s="2">
         <f t="shared" si="19"/>
-        <v>158.30143545999988</v>
+        <v>133.80103120999991</v>
       </c>
       <c r="AO16" s="2">
         <f t="shared" si="19"/>
-        <v>110.81100482199992</v>
+        <v>93.660721846999934</v>
       </c>
       <c r="AP16" s="2">
         <f t="shared" si="19"/>
-        <v>77.56770337539993</v>
+        <v>65.562505292899957</v>
       </c>
     </row>
     <row r="17" spans="2:152" x14ac:dyDescent="0.3">
@@ -2802,11 +2857,11 @@
       </c>
       <c r="V17" s="2">
         <f t="shared" si="21"/>
-        <v>5604.95</v>
+        <v>4535</v>
       </c>
       <c r="W17" s="2">
         <f t="shared" si="21"/>
-        <v>5240.93</v>
+        <v>4584.04</v>
       </c>
       <c r="Y17" s="2">
         <f t="shared" ref="Y17:AE17" si="22">SUM(Y14:Y16)</f>
@@ -2838,47 +2893,47 @@
       </c>
       <c r="AF17" s="2">
         <f t="shared" ref="AF17:AP17" si="23">SUM(AF14:AF16)</f>
-        <v>22536.880000000001</v>
+        <v>20810.04</v>
       </c>
       <c r="AG17" s="2">
         <f t="shared" si="23"/>
-        <v>21269.3969</v>
+        <v>19697.5648</v>
       </c>
       <c r="AH17" s="2">
         <f t="shared" si="23"/>
-        <v>20932.638404000001</v>
+        <v>19571.612096000001</v>
       </c>
       <c r="AI17" s="2">
         <f t="shared" si="23"/>
-        <v>20772.205513740002</v>
+        <v>19599.111537920002</v>
       </c>
       <c r="AJ17" s="2">
         <f t="shared" si="23"/>
-        <v>20736.250677091397</v>
+        <v>19736.3408086784</v>
       </c>
       <c r="AK17" s="2">
         <f t="shared" si="23"/>
-        <v>20788.497051840593</v>
+        <v>19808.706950947329</v>
       </c>
       <c r="AL17" s="2">
         <f t="shared" si="23"/>
-        <v>20853.310754159</v>
+        <v>19885.865974756805</v>
       </c>
       <c r="AM17" s="2">
         <f t="shared" si="23"/>
-        <v>20961.693973960591</v>
+        <v>20000.075002514375</v>
       </c>
       <c r="AN17" s="2">
         <f t="shared" si="23"/>
-        <v>21101.205992282197</v>
+        <v>20140.821010146519</v>
       </c>
       <c r="AO17" s="2">
         <f t="shared" si="23"/>
-        <v>21263.14460721242</v>
+        <v>20300.750900572886</v>
       </c>
       <c r="AP17" s="2">
         <f t="shared" si="23"/>
-        <v>21441.424641789723</v>
+        <v>20474.723585806041</v>
       </c>
     </row>
     <row r="18" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2963,11 +3018,11 @@
       </c>
       <c r="V18" s="7">
         <f t="shared" si="25"/>
-        <v>-1165.7028799999998</v>
+        <v>683</v>
       </c>
       <c r="W18" s="7">
         <f t="shared" si="25"/>
-        <v>-123.01600000000053</v>
+        <v>138.87199999999939</v>
       </c>
       <c r="Y18" s="7">
         <f t="shared" ref="Y18:AE18" si="26">Y13-Y17</f>
@@ -2999,47 +3054,47 @@
       </c>
       <c r="AF18" s="7">
         <f t="shared" ref="AF18:AP18" si="27">AF13-AF17</f>
-        <v>-4765.718880000004</v>
+        <v>-2655.1280000000042</v>
       </c>
       <c r="AG18" s="7">
         <f t="shared" si="27"/>
-        <v>1776.2718999999997</v>
+        <v>3564.6192000000046</v>
       </c>
       <c r="AH18" s="7">
         <f t="shared" si="27"/>
-        <v>4959.1704927999999</v>
+        <v>6563.4516280000025</v>
       </c>
       <c r="AI18" s="7">
         <f t="shared" si="27"/>
-        <v>6414.1938278999987</v>
+        <v>7842.7053722800047</v>
       </c>
       <c r="AJ18" s="7">
         <f t="shared" si="27"/>
-        <v>7537.6046382142085</v>
+        <v>8803.1487779296076</v>
       </c>
       <c r="AK18" s="7">
         <f t="shared" si="27"/>
-        <v>8333.5739229241772</v>
+        <v>9586.9673232589194</v>
       </c>
       <c r="AL18" s="7">
         <f t="shared" si="27"/>
-        <v>9142.4223498487154</v>
+        <v>10391.678527675627</v>
       </c>
       <c r="AM18" s="7">
         <f t="shared" si="27"/>
-        <v>9933.911123167356</v>
+        <v>11185.795834991037</v>
       </c>
       <c r="AN18" s="7">
         <f t="shared" si="27"/>
-        <v>10721.267257759588</v>
+        <v>11980.625952484057</v>
       </c>
       <c r="AO18" s="7">
         <f t="shared" si="27"/>
-        <v>11514.002840330624</v>
+        <v>12784.339470936604</v>
       </c>
       <c r="AP18" s="7">
         <f t="shared" si="27"/>
-        <v>12319.037229179616</v>
+        <v>13602.919496848739</v>
       </c>
     </row>
     <row r="19" spans="2:152" x14ac:dyDescent="0.3">
@@ -3104,7 +3159,7 @@
         <v>-502</v>
       </c>
       <c r="V19" s="2">
-        <v>0</v>
+        <v>-221</v>
       </c>
       <c r="W19" s="2">
         <v>0</v>
@@ -3136,47 +3191,47 @@
       </c>
       <c r="AF19" s="2">
         <f>SUM(T19:W19)</f>
-        <v>-390</v>
+        <v>-611</v>
       </c>
       <c r="AG19" s="2">
         <f t="shared" ref="AG19:AP19" si="28">AF19*0.95</f>
-        <v>-370.5</v>
+        <v>-580.44999999999993</v>
       </c>
       <c r="AH19" s="2">
         <f t="shared" si="28"/>
-        <v>-351.97499999999997</v>
+        <v>-551.4274999999999</v>
       </c>
       <c r="AI19" s="2">
         <f t="shared" si="28"/>
-        <v>-334.37624999999997</v>
+        <v>-523.85612499999991</v>
       </c>
       <c r="AJ19" s="2">
         <f t="shared" si="28"/>
-        <v>-317.65743749999996</v>
+        <v>-497.66331874999986</v>
       </c>
       <c r="AK19" s="2">
         <f t="shared" si="28"/>
-        <v>-301.77456562499992</v>
+        <v>-472.78015281249986</v>
       </c>
       <c r="AL19" s="2">
         <f t="shared" si="28"/>
-        <v>-286.68583734374994</v>
+        <v>-449.14114517187483</v>
       </c>
       <c r="AM19" s="2">
         <f t="shared" si="28"/>
-        <v>-272.35154547656242</v>
+        <v>-426.68408791328108</v>
       </c>
       <c r="AN19" s="2">
         <f t="shared" si="28"/>
-        <v>-258.73396820273427</v>
+        <v>-405.349883517617</v>
       </c>
       <c r="AO19" s="2">
         <f t="shared" si="28"/>
-        <v>-245.79726979259755</v>
+        <v>-385.08238934173613</v>
       </c>
       <c r="AP19" s="2">
         <f t="shared" si="28"/>
-        <v>-233.50740630296767</v>
+        <v>-365.82826987464932</v>
       </c>
     </row>
     <row r="20" spans="2:152" x14ac:dyDescent="0.3">
@@ -3241,7 +3296,7 @@
         <v>95</v>
       </c>
       <c r="V20" s="2">
-        <v>0</v>
+        <v>-3670</v>
       </c>
       <c r="W20" s="2">
         <v>0</v>
@@ -3273,47 +3328,47 @@
       </c>
       <c r="AF20" s="2">
         <f>SUM(T20:W20)</f>
-        <v>268</v>
+        <v>-3402</v>
       </c>
       <c r="AG20" s="2">
         <f t="shared" ref="AG20:AP20" si="29">AF20*1.01</f>
-        <v>270.68</v>
+        <v>-3436.02</v>
       </c>
       <c r="AH20" s="2">
         <f t="shared" si="29"/>
-        <v>273.38679999999999</v>
+        <v>-3470.3802000000001</v>
       </c>
       <c r="AI20" s="2">
         <f t="shared" si="29"/>
-        <v>276.12066800000002</v>
+        <v>-3505.0840020000001</v>
       </c>
       <c r="AJ20" s="2">
         <f t="shared" si="29"/>
-        <v>278.88187468000001</v>
+        <v>-3540.1348420200002</v>
       </c>
       <c r="AK20" s="2">
         <f t="shared" si="29"/>
-        <v>281.67069342680003</v>
+        <v>-3575.5361904402002</v>
       </c>
       <c r="AL20" s="2">
         <f t="shared" si="29"/>
-        <v>284.48740036106801</v>
+        <v>-3611.2915523446022</v>
       </c>
       <c r="AM20" s="2">
         <f t="shared" si="29"/>
-        <v>287.33227436467871</v>
+        <v>-3647.4044678680484</v>
       </c>
       <c r="AN20" s="2">
         <f t="shared" si="29"/>
-        <v>290.20559710832549</v>
+        <v>-3683.8785125467289</v>
       </c>
       <c r="AO20" s="2">
         <f t="shared" si="29"/>
-        <v>293.10765307940875</v>
+        <v>-3720.7172976721963</v>
       </c>
       <c r="AP20" s="2">
         <f t="shared" si="29"/>
-        <v>296.03872961020284</v>
+        <v>-3757.9244706489185</v>
       </c>
     </row>
     <row r="21" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3398,11 +3453,11 @@
       </c>
       <c r="V21" s="7">
         <f t="shared" si="30"/>
-        <v>-1165.7028799999998</v>
+        <v>4574</v>
       </c>
       <c r="W21" s="7">
         <f t="shared" si="30"/>
-        <v>-123.01600000000053</v>
+        <v>138.87199999999939</v>
       </c>
       <c r="Y21" s="7">
         <f t="shared" ref="Y21:AE21" si="31">Y18-Y19-Y20</f>
@@ -3434,47 +3489,47 @@
       </c>
       <c r="AF21" s="7">
         <f t="shared" ref="AF21:AP21" si="32">AF18-AF19-AF20</f>
-        <v>-4643.718880000004</v>
+        <v>1357.8719999999958</v>
       </c>
       <c r="AG21" s="7">
         <f t="shared" si="32"/>
-        <v>1876.0918999999997</v>
+        <v>7581.089200000004</v>
       </c>
       <c r="AH21" s="7">
         <f t="shared" si="32"/>
-        <v>5037.7586928000001</v>
+        <v>10585.259328000002</v>
       </c>
       <c r="AI21" s="7">
         <f t="shared" si="32"/>
-        <v>6472.4494098999985</v>
+        <v>11871.645499280005</v>
       </c>
       <c r="AJ21" s="7">
         <f t="shared" si="32"/>
-        <v>7576.3802010342088</v>
+        <v>12840.946938699606</v>
       </c>
       <c r="AK21" s="7">
         <f t="shared" si="32"/>
-        <v>8353.6777951223776</v>
+        <v>13635.283666511619</v>
       </c>
       <c r="AL21" s="7">
         <f t="shared" si="32"/>
-        <v>9144.6207868313977</v>
+        <v>14452.111225192104</v>
       </c>
       <c r="AM21" s="7">
         <f t="shared" si="32"/>
-        <v>9918.9303942792394</v>
+        <v>15259.884390772368</v>
       </c>
       <c r="AN21" s="7">
         <f t="shared" si="32"/>
-        <v>10689.795628853997</v>
+        <v>16069.854348548404</v>
       </c>
       <c r="AO21" s="7">
         <f t="shared" si="32"/>
-        <v>11466.692457043813</v>
+        <v>16890.139157950536</v>
       </c>
       <c r="AP21" s="7">
         <f t="shared" si="32"/>
-        <v>12256.50590587238</v>
+        <v>17726.672237372306</v>
       </c>
     </row>
     <row r="22" spans="2:152" x14ac:dyDescent="0.3">
@@ -3539,12 +3594,11 @@
         <v>255</v>
       </c>
       <c r="V22" s="2">
-        <f t="shared" ref="V22:W22" si="33">V21*0.2</f>
-        <v>-233.14057599999998</v>
+        <v>304</v>
       </c>
       <c r="W22" s="2">
-        <f t="shared" si="33"/>
-        <v>-24.603200000000108</v>
+        <f>W21*4.76</f>
+        <v>661.03071999999702</v>
       </c>
       <c r="Y22" s="2">
         <v>2264</v>
@@ -3573,47 +3627,47 @@
       </c>
       <c r="AF22" s="2">
         <f>SUM(T22:W22)</f>
-        <v>298.25622399999986</v>
+        <v>1521.030719999997</v>
       </c>
       <c r="AG22" s="2">
         <f>AG21*0.2</f>
-        <v>375.21837999999997</v>
+        <v>1516.2178400000009</v>
       </c>
       <c r="AH22" s="2">
-        <f t="shared" ref="AH22:AP22" si="34">AH21*0.2</f>
-        <v>1007.5517385600001</v>
+        <f t="shared" ref="AH22:AP22" si="33">AH21*0.2</f>
+        <v>2117.0518656000004</v>
       </c>
       <c r="AI22" s="2">
-        <f t="shared" si="34"/>
-        <v>1294.4898819799998</v>
+        <f t="shared" si="33"/>
+        <v>2374.329099856001</v>
       </c>
       <c r="AJ22" s="2">
-        <f t="shared" si="34"/>
-        <v>1515.2760402068418</v>
+        <f t="shared" si="33"/>
+        <v>2568.1893877399216</v>
       </c>
       <c r="AK22" s="2">
-        <f t="shared" si="34"/>
-        <v>1670.7355590244756</v>
+        <f t="shared" si="33"/>
+        <v>2727.0567333023241</v>
       </c>
       <c r="AL22" s="2">
-        <f t="shared" si="34"/>
-        <v>1828.9241573662796</v>
+        <f t="shared" si="33"/>
+        <v>2890.4222450384209</v>
       </c>
       <c r="AM22" s="2">
-        <f t="shared" si="34"/>
-        <v>1983.786078855848</v>
+        <f t="shared" si="33"/>
+        <v>3051.9768781544735</v>
       </c>
       <c r="AN22" s="2">
-        <f t="shared" si="34"/>
-        <v>2137.9591257707993</v>
+        <f t="shared" si="33"/>
+        <v>3213.9708697096812</v>
       </c>
       <c r="AO22" s="2">
-        <f t="shared" si="34"/>
-        <v>2293.3384914087628</v>
+        <f t="shared" si="33"/>
+        <v>3378.0278315901073</v>
       </c>
       <c r="AP22" s="2">
-        <f t="shared" si="34"/>
-        <v>2451.3011811744759</v>
+        <f t="shared" si="33"/>
+        <v>3545.3344474744613</v>
       </c>
     </row>
     <row r="23" spans="2:152" x14ac:dyDescent="0.3">
@@ -3678,12 +3732,11 @@
         <v>-106</v>
       </c>
       <c r="V23" s="2">
-        <f t="shared" ref="V23:W23" si="35">V21*0.05</f>
-        <v>-58.285143999999995</v>
+        <v>207</v>
       </c>
       <c r="W23" s="2">
-        <f t="shared" si="35"/>
-        <v>-6.1508000000000269</v>
+        <f t="shared" ref="W23" si="34">W21*0.05</f>
+        <v>6.9435999999999698</v>
       </c>
       <c r="Y23" s="2">
         <v>0</v>
@@ -3712,47 +3765,47 @@
       </c>
       <c r="AF23" s="2">
         <f>SUM(T23:W23)</f>
-        <v>-236.43594400000003</v>
+        <v>41.943599999999968</v>
       </c>
       <c r="AG23" s="2">
-        <f t="shared" ref="AG23:AP23" si="36">AG21*0.03</f>
-        <v>56.282756999999989</v>
+        <f t="shared" ref="AG23:AP23" si="35">AG21*0.03</f>
+        <v>227.4326760000001</v>
       </c>
       <c r="AH23" s="2">
-        <f t="shared" si="36"/>
-        <v>151.132760784</v>
+        <f t="shared" si="35"/>
+        <v>317.55777984000002</v>
       </c>
       <c r="AI23" s="2">
-        <f t="shared" si="36"/>
-        <v>194.17348229699994</v>
+        <f t="shared" si="35"/>
+        <v>356.14936497840011</v>
       </c>
       <c r="AJ23" s="2">
-        <f t="shared" si="36"/>
-        <v>227.29140603102624</v>
+        <f t="shared" si="35"/>
+        <v>385.22840816098818</v>
       </c>
       <c r="AK23" s="2">
-        <f t="shared" si="36"/>
-        <v>250.61033385367131</v>
+        <f t="shared" si="35"/>
+        <v>409.05850999534857</v>
       </c>
       <c r="AL23" s="2">
-        <f t="shared" si="36"/>
-        <v>274.33862360494192</v>
+        <f t="shared" si="35"/>
+        <v>433.56333675576309</v>
       </c>
       <c r="AM23" s="2">
-        <f t="shared" si="36"/>
-        <v>297.56791182837719</v>
+        <f t="shared" si="35"/>
+        <v>457.79653172317103</v>
       </c>
       <c r="AN23" s="2">
-        <f t="shared" si="36"/>
-        <v>320.69386886561989</v>
+        <f t="shared" si="35"/>
+        <v>482.09563045645211</v>
       </c>
       <c r="AO23" s="2">
-        <f t="shared" si="36"/>
-        <v>344.00077371131437</v>
+        <f t="shared" si="35"/>
+        <v>506.70417473851609</v>
       </c>
       <c r="AP23" s="2">
-        <f t="shared" si="36"/>
-        <v>367.6951771761714</v>
+        <f t="shared" si="35"/>
+        <v>531.80016712116912</v>
       </c>
     </row>
     <row r="24" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3760,600 +3813,600 @@
         <v>31</v>
       </c>
       <c r="C24" s="7">
-        <f t="shared" ref="C24:S24" si="37">C21-C22-C23</f>
+        <f t="shared" ref="C24:S24" si="36">C21-C22-C23</f>
         <v>5857</v>
       </c>
       <c r="D24" s="7">
+        <f t="shared" si="36"/>
+        <v>3361</v>
+      </c>
+      <c r="E24" s="7">
+        <f t="shared" si="36"/>
+        <v>5061</v>
+      </c>
+      <c r="F24" s="7">
+        <f t="shared" si="36"/>
+        <v>6823</v>
+      </c>
+      <c r="G24" s="7">
+        <f t="shared" si="36"/>
+        <v>4623</v>
+      </c>
+      <c r="H24" s="7">
+        <f t="shared" si="36"/>
+        <v>8113</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="36"/>
+        <v>-454</v>
+      </c>
+      <c r="J24" s="7">
+        <f t="shared" si="36"/>
+        <v>1019</v>
+      </c>
+      <c r="K24" s="7">
+        <f t="shared" si="36"/>
+        <v>-664</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="36"/>
+        <v>-2758</v>
+      </c>
+      <c r="M24" s="7">
+        <f t="shared" si="36"/>
+        <v>1481</v>
+      </c>
+      <c r="N24" s="7">
+        <f t="shared" si="36"/>
+        <v>297</v>
+      </c>
+      <c r="O24" s="7">
+        <f t="shared" si="36"/>
+        <v>2939</v>
+      </c>
+      <c r="P24" s="7">
+        <f t="shared" si="36"/>
+        <v>-381</v>
+      </c>
+      <c r="Q24" s="7">
+        <f t="shared" si="36"/>
+        <v>-1610</v>
+      </c>
+      <c r="R24" s="7">
+        <f t="shared" si="36"/>
+        <v>-16639</v>
+      </c>
+      <c r="S24" s="7">
+        <f t="shared" si="36"/>
+        <v>-126</v>
+      </c>
+      <c r="T24" s="7">
+        <f t="shared" ref="T24:W24" si="37">T21-T22-T23</f>
+        <v>-821</v>
+      </c>
+      <c r="U24" s="7">
         <f t="shared" si="37"/>
-        <v>3361</v>
-      </c>
-      <c r="E24" s="7">
+        <v>-2918</v>
+      </c>
+      <c r="V24" s="7">
         <f t="shared" si="37"/>
-        <v>5061</v>
-      </c>
-      <c r="F24" s="7">
+        <v>4063</v>
+      </c>
+      <c r="W24" s="7">
         <f t="shared" si="37"/>
-        <v>6823</v>
-      </c>
-      <c r="G24" s="7">
-        <f t="shared" si="37"/>
-        <v>4623</v>
-      </c>
-      <c r="H24" s="7">
-        <f t="shared" si="37"/>
-        <v>8113</v>
-      </c>
-      <c r="I24" s="7">
-        <f t="shared" si="37"/>
-        <v>-454</v>
-      </c>
-      <c r="J24" s="7">
-        <f t="shared" si="37"/>
-        <v>1019</v>
-      </c>
-      <c r="K24" s="7">
-        <f t="shared" si="37"/>
-        <v>-664</v>
-      </c>
-      <c r="L24" s="7">
-        <f t="shared" si="37"/>
-        <v>-2758</v>
-      </c>
-      <c r="M24" s="7">
-        <f t="shared" si="37"/>
-        <v>1481</v>
-      </c>
-      <c r="N24" s="7">
-        <f t="shared" si="37"/>
-        <v>297</v>
-      </c>
-      <c r="O24" s="7">
-        <f t="shared" si="37"/>
-        <v>2939</v>
-      </c>
-      <c r="P24" s="7">
-        <f t="shared" si="37"/>
-        <v>-381</v>
-      </c>
-      <c r="Q24" s="7">
-        <f t="shared" si="37"/>
-        <v>-1610</v>
-      </c>
-      <c r="R24" s="7">
-        <f t="shared" si="37"/>
-        <v>-16639</v>
-      </c>
-      <c r="S24" s="7">
-        <f t="shared" si="37"/>
-        <v>-126</v>
-      </c>
-      <c r="T24" s="7">
-        <f t="shared" ref="T24:W24" si="38">T21-T22-T23</f>
-        <v>-821</v>
-      </c>
-      <c r="U24" s="7">
+        <v>-529.10231999999758</v>
+      </c>
+      <c r="Y24" s="7">
+        <f t="shared" ref="Y24:AE24" si="38">Y21-Y22-Y23</f>
+        <v>21053</v>
+      </c>
+      <c r="Z24" s="7">
         <f t="shared" si="38"/>
-        <v>-2918</v>
-      </c>
-      <c r="V24" s="7">
+        <v>21048</v>
+      </c>
+      <c r="AA24" s="7">
         <f t="shared" si="38"/>
-        <v>-874.27715999999987</v>
-      </c>
-      <c r="W24" s="7">
+        <v>20899</v>
+      </c>
+      <c r="AB24" s="7">
         <f t="shared" si="38"/>
-        <v>-92.262000000000398</v>
-      </c>
-      <c r="Y24" s="7">
-        <f t="shared" ref="Y24:AE24" si="39">Y21-Y22-Y23</f>
-        <v>21053</v>
-      </c>
-      <c r="Z24" s="7">
+        <v>19868</v>
+      </c>
+      <c r="AC24" s="7">
+        <f t="shared" si="38"/>
+        <v>8014</v>
+      </c>
+      <c r="AD24" s="7">
+        <f t="shared" si="38"/>
+        <v>1959</v>
+      </c>
+      <c r="AE24" s="7">
+        <f t="shared" si="38"/>
+        <v>-18756</v>
+      </c>
+      <c r="AF24" s="7">
+        <f t="shared" ref="AF24:AP24" si="39">AF21-AF22-AF23</f>
+        <v>-205.10232000000124</v>
+      </c>
+      <c r="AG24" s="7">
         <f t="shared" si="39"/>
-        <v>21048</v>
-      </c>
-      <c r="AA24" s="7">
+        <v>5837.4386840000025</v>
+      </c>
+      <c r="AH24" s="7">
         <f t="shared" si="39"/>
-        <v>20899</v>
-      </c>
-      <c r="AB24" s="7">
+        <v>8150.6496825600016</v>
+      </c>
+      <c r="AI24" s="7">
         <f t="shared" si="39"/>
-        <v>19868</v>
-      </c>
-      <c r="AC24" s="7">
+        <v>9141.1670344456033</v>
+      </c>
+      <c r="AJ24" s="7">
         <f t="shared" si="39"/>
-        <v>8014</v>
-      </c>
-      <c r="AD24" s="7">
+        <v>9887.5291427986958</v>
+      </c>
+      <c r="AK24" s="7">
         <f t="shared" si="39"/>
-        <v>1959</v>
-      </c>
-      <c r="AE24" s="7">
+        <v>10499.168423213947</v>
+      </c>
+      <c r="AL24" s="7">
         <f t="shared" si="39"/>
-        <v>-18756</v>
-      </c>
-      <c r="AF24" s="7">
-        <f t="shared" ref="AF24:AP24" si="40">AF21-AF22-AF23</f>
-        <v>-4705.5391600000039</v>
-      </c>
-      <c r="AG24" s="7">
-        <f t="shared" si="40"/>
-        <v>1444.5907629999997</v>
-      </c>
-      <c r="AH24" s="7">
-        <f t="shared" si="40"/>
-        <v>3879.0741934560001</v>
-      </c>
-      <c r="AI24" s="7">
-        <f t="shared" si="40"/>
-        <v>4983.7860456229982</v>
-      </c>
-      <c r="AJ24" s="7">
-        <f t="shared" si="40"/>
-        <v>5833.8127547963413</v>
-      </c>
-      <c r="AK24" s="7">
-        <f t="shared" si="40"/>
-        <v>6432.3319022442311</v>
-      </c>
-      <c r="AL24" s="7">
-        <f t="shared" si="40"/>
-        <v>7041.3580058601765</v>
+        <v>11128.12564339792</v>
       </c>
       <c r="AM24" s="7">
-        <f t="shared" si="40"/>
-        <v>7637.5764035950142</v>
+        <f t="shared" si="39"/>
+        <v>11750.110980894722</v>
       </c>
       <c r="AN24" s="7">
-        <f t="shared" si="40"/>
-        <v>8231.1426342175782</v>
+        <f t="shared" si="39"/>
+        <v>12373.787848382271</v>
       </c>
       <c r="AO24" s="7">
-        <f t="shared" si="40"/>
-        <v>8829.3531919237375</v>
+        <f t="shared" si="39"/>
+        <v>13005.407151621914</v>
       </c>
       <c r="AP24" s="7">
-        <f t="shared" si="40"/>
-        <v>9437.5095475217331</v>
+        <f t="shared" si="39"/>
+        <v>13649.537622776676</v>
       </c>
       <c r="AQ24" s="1">
         <f>AP24*(1+$AS$37)</f>
-        <v>9343.1344520465154</v>
+        <v>13513.042246548908</v>
       </c>
       <c r="AR24" s="1">
-        <f t="shared" ref="AR24:DC24" si="41">AQ24*(1+$AS$37)</f>
-        <v>9249.7031075260511</v>
+        <f t="shared" ref="AR24:DC24" si="40">AQ24*(1+$AS$37)</f>
+        <v>13377.91182408342</v>
       </c>
       <c r="AS24" s="1">
+        <f t="shared" si="40"/>
+        <v>13244.132705842585</v>
+      </c>
+      <c r="AT24" s="1">
+        <f t="shared" si="40"/>
+        <v>13111.691378784159</v>
+      </c>
+      <c r="AU24" s="1">
+        <f t="shared" si="40"/>
+        <v>12980.574464996316</v>
+      </c>
+      <c r="AV24" s="1">
+        <f t="shared" si="40"/>
+        <v>12850.768720346354</v>
+      </c>
+      <c r="AW24" s="1">
+        <f t="shared" si="40"/>
+        <v>12722.26103314289</v>
+      </c>
+      <c r="AX24" s="1">
+        <f t="shared" si="40"/>
+        <v>12595.03842281146</v>
+      </c>
+      <c r="AY24" s="1">
+        <f t="shared" si="40"/>
+        <v>12469.088038583344</v>
+      </c>
+      <c r="AZ24" s="1">
+        <f t="shared" si="40"/>
+        <v>12344.397158197511</v>
+      </c>
+      <c r="BA24" s="1">
+        <f t="shared" si="40"/>
+        <v>12220.953186615536</v>
+      </c>
+      <c r="BB24" s="1">
+        <f t="shared" si="40"/>
+        <v>12098.74365474938</v>
+      </c>
+      <c r="BC24" s="1">
+        <f t="shared" si="40"/>
+        <v>11977.756218201886</v>
+      </c>
+      <c r="BD24" s="1">
+        <f t="shared" si="40"/>
+        <v>11857.978656019868</v>
+      </c>
+      <c r="BE24" s="1">
+        <f t="shared" si="40"/>
+        <v>11739.39886945967</v>
+      </c>
+      <c r="BF24" s="1">
+        <f t="shared" si="40"/>
+        <v>11622.004880765073</v>
+      </c>
+      <c r="BG24" s="1">
+        <f t="shared" si="40"/>
+        <v>11505.784831957422</v>
+      </c>
+      <c r="BH24" s="1">
+        <f t="shared" si="40"/>
+        <v>11390.726983637847</v>
+      </c>
+      <c r="BI24" s="1">
+        <f t="shared" si="40"/>
+        <v>11276.819713801469</v>
+      </c>
+      <c r="BJ24" s="1">
+        <f t="shared" si="40"/>
+        <v>11164.051516663454</v>
+      </c>
+      <c r="BK24" s="1">
+        <f t="shared" si="40"/>
+        <v>11052.411001496819</v>
+      </c>
+      <c r="BL24" s="1">
+        <f t="shared" si="40"/>
+        <v>10941.88689148185</v>
+      </c>
+      <c r="BM24" s="1">
+        <f t="shared" si="40"/>
+        <v>10832.468022567033</v>
+      </c>
+      <c r="BN24" s="1">
+        <f t="shared" si="40"/>
+        <v>10724.143342341362</v>
+      </c>
+      <c r="BO24" s="1">
+        <f t="shared" si="40"/>
+        <v>10616.901908917947</v>
+      </c>
+      <c r="BP24" s="1">
+        <f t="shared" si="40"/>
+        <v>10510.732889828767</v>
+      </c>
+      <c r="BQ24" s="1">
+        <f t="shared" si="40"/>
+        <v>10405.625560930479</v>
+      </c>
+      <c r="BR24" s="1">
+        <f t="shared" si="40"/>
+        <v>10301.569305321174</v>
+      </c>
+      <c r="BS24" s="1">
+        <f t="shared" si="40"/>
+        <v>10198.553612267962</v>
+      </c>
+      <c r="BT24" s="1">
+        <f t="shared" si="40"/>
+        <v>10096.568076145282</v>
+      </c>
+      <c r="BU24" s="1">
+        <f t="shared" si="40"/>
+        <v>9995.6023953838285</v>
+      </c>
+      <c r="BV24" s="1">
+        <f t="shared" si="40"/>
+        <v>9895.6463714299898</v>
+      </c>
+      <c r="BW24" s="1">
+        <f t="shared" si="40"/>
+        <v>9796.6899077156904</v>
+      </c>
+      <c r="BX24" s="1">
+        <f t="shared" si="40"/>
+        <v>9698.7230086385334</v>
+      </c>
+      <c r="BY24" s="1">
+        <f t="shared" si="40"/>
+        <v>9601.7357785521472</v>
+      </c>
+      <c r="BZ24" s="1">
+        <f t="shared" si="40"/>
+        <v>9505.7184207666251</v>
+      </c>
+      <c r="CA24" s="1">
+        <f t="shared" si="40"/>
+        <v>9410.661236558959</v>
+      </c>
+      <c r="CB24" s="1">
+        <f t="shared" si="40"/>
+        <v>9316.5546241933698</v>
+      </c>
+      <c r="CC24" s="1">
+        <f t="shared" si="40"/>
+        <v>9223.3890779514368</v>
+      </c>
+      <c r="CD24" s="1">
+        <f t="shared" si="40"/>
+        <v>9131.1551871719221</v>
+      </c>
+      <c r="CE24" s="1">
+        <f t="shared" si="40"/>
+        <v>9039.8436353002035</v>
+      </c>
+      <c r="CF24" s="1">
+        <f t="shared" si="40"/>
+        <v>8949.4451989472018</v>
+      </c>
+      <c r="CG24" s="1">
+        <f t="shared" si="40"/>
+        <v>8859.9507469577293</v>
+      </c>
+      <c r="CH24" s="1">
+        <f t="shared" si="40"/>
+        <v>8771.3512394881527</v>
+      </c>
+      <c r="CI24" s="1">
+        <f t="shared" si="40"/>
+        <v>8683.6377270932717</v>
+      </c>
+      <c r="CJ24" s="1">
+        <f t="shared" si="40"/>
+        <v>8596.801349822339</v>
+      </c>
+      <c r="CK24" s="1">
+        <f t="shared" si="40"/>
+        <v>8510.8333363241163</v>
+      </c>
+      <c r="CL24" s="1">
+        <f t="shared" si="40"/>
+        <v>8425.7250029608749</v>
+      </c>
+      <c r="CM24" s="1">
+        <f t="shared" si="40"/>
+        <v>8341.4677529312667</v>
+      </c>
+      <c r="CN24" s="1">
+        <f t="shared" si="40"/>
+        <v>8258.0530754019546</v>
+      </c>
+      <c r="CO24" s="1">
+        <f t="shared" si="40"/>
+        <v>8175.4725446479351</v>
+      </c>
+      <c r="CP24" s="1">
+        <f t="shared" si="40"/>
+        <v>8093.7178192014553</v>
+      </c>
+      <c r="CQ24" s="1">
+        <f t="shared" si="40"/>
+        <v>8012.7806410094408</v>
+      </c>
+      <c r="CR24" s="1">
+        <f t="shared" si="40"/>
+        <v>7932.6528345993465</v>
+      </c>
+      <c r="CS24" s="1">
+        <f t="shared" si="40"/>
+        <v>7853.3263062533533</v>
+      </c>
+      <c r="CT24" s="1">
+        <f t="shared" si="40"/>
+        <v>7774.7930431908198</v>
+      </c>
+      <c r="CU24" s="1">
+        <f t="shared" si="40"/>
+        <v>7697.0451127589113</v>
+      </c>
+      <c r="CV24" s="1">
+        <f t="shared" si="40"/>
+        <v>7620.0746616313218</v>
+      </c>
+      <c r="CW24" s="1">
+        <f t="shared" si="40"/>
+        <v>7543.8739150150086</v>
+      </c>
+      <c r="CX24" s="1">
+        <f t="shared" si="40"/>
+        <v>7468.4351758648581</v>
+      </c>
+      <c r="CY24" s="1">
+        <f t="shared" si="40"/>
+        <v>7393.7508241062096</v>
+      </c>
+      <c r="CZ24" s="1">
+        <f t="shared" si="40"/>
+        <v>7319.8133158651472</v>
+      </c>
+      <c r="DA24" s="1">
+        <f t="shared" si="40"/>
+        <v>7246.6151827064959</v>
+      </c>
+      <c r="DB24" s="1">
+        <f t="shared" si="40"/>
+        <v>7174.1490308794309</v>
+      </c>
+      <c r="DC24" s="1">
+        <f t="shared" si="40"/>
+        <v>7102.4075405706362</v>
+      </c>
+      <c r="DD24" s="1">
+        <f t="shared" ref="DD24:EV24" si="41">DC24*(1+$AS$37)</f>
+        <v>7031.3834651649295</v>
+      </c>
+      <c r="DE24" s="1">
         <f t="shared" si="41"/>
-        <v>9157.2060764507896</v>
-      </c>
-      <c r="AT24" s="1">
+        <v>6961.0696305132806</v>
+      </c>
+      <c r="DF24" s="1">
         <f t="shared" si="41"/>
-        <v>9065.6340156862825</v>
-      </c>
-      <c r="AU24" s="1">
+        <v>6891.4589342081481</v>
+      </c>
+      <c r="DG24" s="1">
         <f t="shared" si="41"/>
-        <v>8974.9776755294188</v>
-      </c>
-      <c r="AV24" s="1">
+        <v>6822.5443448660662</v>
+      </c>
+      <c r="DH24" s="1">
         <f t="shared" si="41"/>
-        <v>8885.2278987741247</v>
-      </c>
-      <c r="AW24" s="1">
+        <v>6754.3189014174059</v>
+      </c>
+      <c r="DI24" s="1">
         <f t="shared" si="41"/>
-        <v>8796.375619786384</v>
-      </c>
-      <c r="AX24" s="1">
+        <v>6686.7757124032314</v>
+      </c>
+      <c r="DJ24" s="1">
         <f t="shared" si="41"/>
-        <v>8708.4118635885206</v>
-      </c>
-      <c r="AY24" s="1">
+        <v>6619.9079552791991</v>
+      </c>
+      <c r="DK24" s="1">
         <f t="shared" si="41"/>
-        <v>8621.3277449526358</v>
-      </c>
-      <c r="AZ24" s="1">
+        <v>6553.7088757264073</v>
+      </c>
+      <c r="DL24" s="1">
         <f t="shared" si="41"/>
-        <v>8535.1144675031101</v>
-      </c>
-      <c r="BA24" s="1">
+        <v>6488.1717869691429</v>
+      </c>
+      <c r="DM24" s="1">
         <f t="shared" si="41"/>
-        <v>8449.7633228280793</v>
-      </c>
-      <c r="BB24" s="1">
+        <v>6423.2900690994511</v>
+      </c>
+      <c r="DN24" s="1">
         <f t="shared" si="41"/>
-        <v>8365.2656895997989</v>
-      </c>
-      <c r="BC24" s="1">
+        <v>6359.0571684084562</v>
+      </c>
+      <c r="DO24" s="1">
         <f t="shared" si="41"/>
-        <v>8281.6130327038009</v>
-      </c>
-      <c r="BD24" s="1">
+        <v>6295.4665967243718</v>
+      </c>
+      <c r="DP24" s="1">
         <f t="shared" si="41"/>
-        <v>8198.7969023767619</v>
-      </c>
-      <c r="BE24" s="1">
+        <v>6232.5119307571276</v>
+      </c>
+      <c r="DQ24" s="1">
         <f t="shared" si="41"/>
-        <v>8116.8089333529942</v>
-      </c>
-      <c r="BF24" s="1">
+        <v>6170.1868114495564</v>
+      </c>
+      <c r="DR24" s="1">
         <f t="shared" si="41"/>
-        <v>8035.6408440194646</v>
-      </c>
-      <c r="BG24" s="1">
+        <v>6108.484943335061</v>
+      </c>
+      <c r="DS24" s="1">
         <f t="shared" si="41"/>
-        <v>7955.2844355792695</v>
-      </c>
-      <c r="BH24" s="1">
+        <v>6047.4000939017105</v>
+      </c>
+      <c r="DT24" s="1">
         <f t="shared" si="41"/>
-        <v>7875.7315912234772</v>
-      </c>
-      <c r="BI24" s="1">
+        <v>5986.9260929626935</v>
+      </c>
+      <c r="DU24" s="1">
         <f t="shared" si="41"/>
-        <v>7796.9742753112423</v>
-      </c>
-      <c r="BJ24" s="1">
+        <v>5927.0568320330667</v>
+      </c>
+      <c r="DV24" s="1">
         <f t="shared" si="41"/>
-        <v>7719.0045325581295</v>
-      </c>
-      <c r="BK24" s="1">
+        <v>5867.7862637127364</v>
+      </c>
+      <c r="DW24" s="1">
         <f t="shared" si="41"/>
-        <v>7641.8144872325483</v>
-      </c>
-      <c r="BL24" s="1">
+        <v>5809.1084010756094</v>
+      </c>
+      <c r="DX24" s="1">
         <f t="shared" si="41"/>
-        <v>7565.3963423602227</v>
-      </c>
-      <c r="BM24" s="1">
+        <v>5751.0173170648532</v>
+      </c>
+      <c r="DY24" s="1">
         <f t="shared" si="41"/>
-        <v>7489.7423789366203</v>
-      </c>
-      <c r="BN24" s="1">
+        <v>5693.507143894205</v>
+      </c>
+      <c r="DZ24" s="1">
         <f t="shared" si="41"/>
-        <v>7414.844955147254</v>
-      </c>
-      <c r="BO24" s="1">
+        <v>5636.572072455263</v>
+      </c>
+      <c r="EA24" s="1">
         <f t="shared" si="41"/>
-        <v>7340.6965055957817</v>
-      </c>
-      <c r="BP24" s="1">
+        <v>5580.2063517307106</v>
+      </c>
+      <c r="EB24" s="1">
         <f t="shared" si="41"/>
-        <v>7267.289540539824</v>
-      </c>
-      <c r="BQ24" s="1">
+        <v>5524.4042882134036</v>
+      </c>
+      <c r="EC24" s="1">
         <f t="shared" si="41"/>
-        <v>7194.6166451344261</v>
-      </c>
-      <c r="BR24" s="1">
+        <v>5469.1602453312698</v>
+      </c>
+      <c r="ED24" s="1">
         <f t="shared" si="41"/>
-        <v>7122.6704786830815</v>
-      </c>
-      <c r="BS24" s="1">
+        <v>5414.4686428779569</v>
+      </c>
+      <c r="EE24" s="1">
         <f t="shared" si="41"/>
-        <v>7051.4437738962506</v>
-      </c>
-      <c r="BT24" s="1">
+        <v>5360.3239564491769</v>
+      </c>
+      <c r="EF24" s="1">
         <f t="shared" si="41"/>
-        <v>6980.9293361572882</v>
-      </c>
-      <c r="BU24" s="1">
+        <v>5306.7207168846853</v>
+      </c>
+      <c r="EG24" s="1">
         <f t="shared" si="41"/>
-        <v>6911.1200427957156</v>
-      </c>
-      <c r="BV24" s="1">
+        <v>5253.6535097158385</v>
+      </c>
+      <c r="EH24" s="1">
         <f t="shared" si="41"/>
-        <v>6842.008842367758</v>
-      </c>
-      <c r="BW24" s="1">
+        <v>5201.1169746186797</v>
+      </c>
+      <c r="EI24" s="1">
         <f t="shared" si="41"/>
-        <v>6773.5887539440801</v>
-      </c>
-      <c r="BX24" s="1">
+        <v>5149.1058048724926</v>
+      </c>
+      <c r="EJ24" s="1">
         <f t="shared" si="41"/>
-        <v>6705.8528664046389</v>
-      </c>
-      <c r="BY24" s="1">
+        <v>5097.6147468237677</v>
+      </c>
+      <c r="EK24" s="1">
         <f t="shared" si="41"/>
-        <v>6638.7943377405927</v>
-      </c>
-      <c r="BZ24" s="1">
+        <v>5046.6385993555305</v>
+      </c>
+      <c r="EL24" s="1">
         <f t="shared" si="41"/>
-        <v>6572.4063943631863</v>
-      </c>
-      <c r="CA24" s="1">
+        <v>4996.1722133619751</v>
+      </c>
+      <c r="EM24" s="1">
         <f t="shared" si="41"/>
-        <v>6506.6823304195541</v>
-      </c>
-      <c r="CB24" s="1">
+        <v>4946.2104912283548</v>
+      </c>
+      <c r="EN24" s="1">
         <f t="shared" si="41"/>
-        <v>6441.6155071153589</v>
-      </c>
-      <c r="CC24" s="1">
+        <v>4896.7483863160714</v>
+      </c>
+      <c r="EO24" s="1">
         <f t="shared" si="41"/>
-        <v>6377.1993520442056</v>
-      </c>
-      <c r="CD24" s="1">
+        <v>4847.7809024529106</v>
+      </c>
+      <c r="EP24" s="1">
         <f t="shared" si="41"/>
-        <v>6313.4273585237634</v>
-      </c>
-      <c r="CE24" s="1">
+        <v>4799.3030934283815</v>
+      </c>
+      <c r="EQ24" s="1">
         <f t="shared" si="41"/>
-        <v>6250.2930849385257</v>
-      </c>
-      <c r="CF24" s="1">
+        <v>4751.310062494098</v>
+      </c>
+      <c r="ER24" s="1">
         <f t="shared" si="41"/>
-        <v>6187.7901540891407</v>
-      </c>
-      <c r="CG24" s="1">
+        <v>4703.7969618691568</v>
+      </c>
+      <c r="ES24" s="1">
         <f t="shared" si="41"/>
-        <v>6125.9122525482489</v>
-      </c>
-      <c r="CH24" s="1">
+        <v>4656.7589922504649</v>
+      </c>
+      <c r="ET24" s="1">
         <f t="shared" si="41"/>
-        <v>6064.6531300227662</v>
-      </c>
-      <c r="CI24" s="1">
+        <v>4610.1914023279605</v>
+      </c>
+      <c r="EU24" s="1">
         <f t="shared" si="41"/>
-        <v>6004.006598722538</v>
-      </c>
-      <c r="CJ24" s="1">
+        <v>4564.0894883046813</v>
+      </c>
+      <c r="EV24" s="1">
         <f t="shared" si="41"/>
-        <v>5943.9665327353123</v>
-      </c>
-      <c r="CK24" s="1">
-        <f t="shared" si="41"/>
-        <v>5884.5268674079589</v>
-      </c>
-      <c r="CL24" s="1">
-        <f t="shared" si="41"/>
-        <v>5825.6815987338796</v>
-      </c>
-      <c r="CM24" s="1">
-        <f t="shared" si="41"/>
-        <v>5767.4247827465406</v>
-      </c>
-      <c r="CN24" s="1">
-        <f t="shared" si="41"/>
-        <v>5709.7505349190751</v>
-      </c>
-      <c r="CO24" s="1">
-        <f t="shared" si="41"/>
-        <v>5652.653029569884</v>
-      </c>
-      <c r="CP24" s="1">
-        <f t="shared" si="41"/>
-        <v>5596.1264992741853</v>
-      </c>
-      <c r="CQ24" s="1">
-        <f t="shared" si="41"/>
-        <v>5540.1652342814432</v>
-      </c>
-      <c r="CR24" s="1">
-        <f t="shared" si="41"/>
-        <v>5484.7635819386287</v>
-      </c>
-      <c r="CS24" s="1">
-        <f t="shared" si="41"/>
-        <v>5429.9159461192421</v>
-      </c>
-      <c r="CT24" s="1">
-        <f t="shared" si="41"/>
-        <v>5375.6167866580499</v>
-      </c>
-      <c r="CU24" s="1">
-        <f t="shared" si="41"/>
-        <v>5321.8606187914693</v>
-      </c>
-      <c r="CV24" s="1">
-        <f t="shared" si="41"/>
-        <v>5268.6420126035546</v>
-      </c>
-      <c r="CW24" s="1">
-        <f t="shared" si="41"/>
-        <v>5215.9555924775186</v>
-      </c>
-      <c r="CX24" s="1">
-        <f t="shared" si="41"/>
-        <v>5163.7960365527433</v>
-      </c>
-      <c r="CY24" s="1">
-        <f t="shared" si="41"/>
-        <v>5112.1580761872156</v>
-      </c>
-      <c r="CZ24" s="1">
-        <f t="shared" si="41"/>
-        <v>5061.0364954253437</v>
-      </c>
-      <c r="DA24" s="1">
-        <f t="shared" si="41"/>
-        <v>5010.4261304710899</v>
-      </c>
-      <c r="DB24" s="1">
-        <f t="shared" si="41"/>
-        <v>4960.3218691663787</v>
-      </c>
-      <c r="DC24" s="1">
-        <f t="shared" si="41"/>
-        <v>4910.7186504747151</v>
-      </c>
-      <c r="DD24" s="1">
-        <f t="shared" ref="DD24:EV24" si="42">DC24*(1+$AS$37)</f>
-        <v>4861.6114639699681</v>
-      </c>
-      <c r="DE24" s="1">
-        <f t="shared" si="42"/>
-        <v>4812.9953493302683</v>
-      </c>
-      <c r="DF24" s="1">
-        <f t="shared" si="42"/>
-        <v>4764.8653958369659</v>
-      </c>
-      <c r="DG24" s="1">
-        <f t="shared" si="42"/>
-        <v>4717.2167418785966</v>
-      </c>
-      <c r="DH24" s="1">
-        <f t="shared" si="42"/>
-        <v>4670.044574459811</v>
-      </c>
-      <c r="DI24" s="1">
-        <f t="shared" si="42"/>
-        <v>4623.3441287152127</v>
-      </c>
-      <c r="DJ24" s="1">
-        <f t="shared" si="42"/>
-        <v>4577.1106874280604</v>
-      </c>
-      <c r="DK24" s="1">
-        <f t="shared" si="42"/>
-        <v>4531.3395805537793</v>
-      </c>
-      <c r="DL24" s="1">
-        <f t="shared" si="42"/>
-        <v>4486.0261847482416</v>
-      </c>
-      <c r="DM24" s="1">
-        <f t="shared" si="42"/>
-        <v>4441.1659229007591</v>
-      </c>
-      <c r="DN24" s="1">
-        <f t="shared" si="42"/>
-        <v>4396.7542636717517</v>
-      </c>
-      <c r="DO24" s="1">
-        <f t="shared" si="42"/>
-        <v>4352.7867210350341</v>
-      </c>
-      <c r="DP24" s="1">
-        <f t="shared" si="42"/>
-        <v>4309.2588538246837</v>
-      </c>
-      <c r="DQ24" s="1">
-        <f t="shared" si="42"/>
-        <v>4266.166265286437</v>
-      </c>
-      <c r="DR24" s="1">
-        <f t="shared" si="42"/>
-        <v>4223.5046026335722</v>
-      </c>
-      <c r="DS24" s="1">
-        <f t="shared" si="42"/>
-        <v>4181.2695566072362</v>
-      </c>
-      <c r="DT24" s="1">
-        <f t="shared" si="42"/>
-        <v>4139.4568610411634</v>
-      </c>
-      <c r="DU24" s="1">
-        <f t="shared" si="42"/>
-        <v>4098.0622924307518</v>
-      </c>
-      <c r="DV24" s="1">
-        <f t="shared" si="42"/>
-        <v>4057.0816695064441</v>
-      </c>
-      <c r="DW24" s="1">
-        <f t="shared" si="42"/>
-        <v>4016.5108528113797</v>
-      </c>
-      <c r="DX24" s="1">
-        <f t="shared" si="42"/>
-        <v>3976.345744283266</v>
-      </c>
-      <c r="DY24" s="1">
-        <f t="shared" si="42"/>
-        <v>3936.5822868404334</v>
-      </c>
-      <c r="DZ24" s="1">
-        <f t="shared" si="42"/>
-        <v>3897.216463972029</v>
-      </c>
-      <c r="EA24" s="1">
-        <f t="shared" si="42"/>
-        <v>3858.2442993323089</v>
-      </c>
-      <c r="EB24" s="1">
-        <f t="shared" si="42"/>
-        <v>3819.6618563389857</v>
-      </c>
-      <c r="EC24" s="1">
-        <f t="shared" si="42"/>
-        <v>3781.4652377755956</v>
-      </c>
-      <c r="ED24" s="1">
-        <f t="shared" si="42"/>
-        <v>3743.6505853978397</v>
-      </c>
-      <c r="EE24" s="1">
-        <f t="shared" si="42"/>
-        <v>3706.2140795438613</v>
-      </c>
-      <c r="EF24" s="1">
-        <f t="shared" si="42"/>
-        <v>3669.1519387484227</v>
-      </c>
-      <c r="EG24" s="1">
-        <f t="shared" si="42"/>
-        <v>3632.4604193609384</v>
-      </c>
-      <c r="EH24" s="1">
-        <f t="shared" si="42"/>
-        <v>3596.1358151673289</v>
-      </c>
-      <c r="EI24" s="1">
-        <f t="shared" si="42"/>
-        <v>3560.1744570156557</v>
-      </c>
-      <c r="EJ24" s="1">
-        <f t="shared" si="42"/>
-        <v>3524.5727124454993</v>
-      </c>
-      <c r="EK24" s="1">
-        <f t="shared" si="42"/>
-        <v>3489.326985321044</v>
-      </c>
-      <c r="EL24" s="1">
-        <f t="shared" si="42"/>
-        <v>3454.4337154678337</v>
-      </c>
-      <c r="EM24" s="1">
-        <f t="shared" si="42"/>
-        <v>3419.8893783131552</v>
-      </c>
-      <c r="EN24" s="1">
-        <f t="shared" si="42"/>
-        <v>3385.6904845300237</v>
-      </c>
-      <c r="EO24" s="1">
-        <f t="shared" si="42"/>
-        <v>3351.8335796847236</v>
-      </c>
-      <c r="EP24" s="1">
-        <f t="shared" si="42"/>
-        <v>3318.3152438878765</v>
-      </c>
-      <c r="EQ24" s="1">
-        <f t="shared" si="42"/>
-        <v>3285.1320914489975</v>
-      </c>
-      <c r="ER24" s="1">
-        <f t="shared" si="42"/>
-        <v>3252.2807705345076</v>
-      </c>
-      <c r="ES24" s="1">
-        <f t="shared" si="42"/>
-        <v>3219.7579628291624</v>
-      </c>
-      <c r="ET24" s="1">
-        <f t="shared" si="42"/>
-        <v>3187.5603832008705</v>
-      </c>
-      <c r="EU24" s="1">
-        <f t="shared" si="42"/>
-        <v>3155.6847793688617</v>
-      </c>
-      <c r="EV24" s="1">
-        <f t="shared" si="42"/>
-        <v>3124.1279315751731</v>
+        <v>4518.4485934216345</v>
       </c>
     </row>
     <row r="25" spans="2:152" x14ac:dyDescent="0.3">
@@ -4419,12 +4472,12 @@
         <v>4369</v>
       </c>
       <c r="V25" s="2">
-        <f>4369</f>
-        <v>4369</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="W25" s="2">
-        <f>4369</f>
-        <v>4369</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="Y25" s="2">
         <v>4313</v>
@@ -4448,37 +4501,48 @@
         <v>4319</v>
       </c>
       <c r="AF25" s="2">
-        <v>4343</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="AG25" s="2">
-        <v>4343</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="AH25" s="2">
-        <v>4343</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="AI25" s="2">
-        <v>4343</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="AJ25" s="2">
-        <v>4343</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="AK25" s="2">
-        <v>4343</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="AL25" s="2">
-        <v>4343</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="AM25" s="2">
-        <v>4343</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="AN25" s="2">
-        <v>4343</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="AO25" s="2">
-        <v>4343</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
       <c r="AP25" s="2">
-        <v>4343</v>
+        <f>4514</f>
+        <v>4514</v>
       </c>
     </row>
     <row r="26" spans="2:152" x14ac:dyDescent="0.3">
@@ -4486,160 +4550,160 @@
         <v>32</v>
       </c>
       <c r="C26" s="6">
-        <f t="shared" ref="C26:S26" si="43">C24/C25</f>
+        <f t="shared" ref="C26:S26" si="42">C24/C25</f>
         <v>1.3579874797124971</v>
       </c>
       <c r="D26" s="6">
+        <f t="shared" si="42"/>
+        <v>0.77927196846742408</v>
+      </c>
+      <c r="E26" s="6">
+        <f t="shared" si="42"/>
+        <v>1.1734291676327382</v>
+      </c>
+      <c r="F26" s="6">
+        <f t="shared" si="42"/>
+        <v>1.5819615117087873</v>
+      </c>
+      <c r="G26" s="6">
+        <f t="shared" si="42"/>
+        <v>1.071875724553675</v>
+      </c>
+      <c r="H26" s="6">
+        <f t="shared" si="42"/>
+        <v>1.8810572687224669</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="42"/>
+        <v>-0.10526315789473684</v>
+      </c>
+      <c r="J26" s="6">
+        <f t="shared" si="42"/>
+        <v>0.23626246232320891</v>
+      </c>
+      <c r="K26" s="6">
+        <f t="shared" si="42"/>
+        <v>-0.15395316485045213</v>
+      </c>
+      <c r="L26" s="6">
+        <f t="shared" si="42"/>
+        <v>-0.63946209135172738</v>
+      </c>
+      <c r="M26" s="6">
+        <f t="shared" si="42"/>
+        <v>0.3433804776257825</v>
+      </c>
+      <c r="N26" s="6">
+        <f t="shared" si="42"/>
+        <v>6.8861581265940178E-2</v>
+      </c>
+      <c r="O26" s="6">
+        <f t="shared" si="42"/>
+        <v>0.68142824020403436</v>
+      </c>
+      <c r="P26" s="6">
+        <f t="shared" si="42"/>
+        <v>-8.8337584048226295E-2</v>
+      </c>
+      <c r="Q26" s="6">
+        <f t="shared" si="42"/>
+        <v>-0.37329005332715048</v>
+      </c>
+      <c r="R26" s="6">
+        <f t="shared" si="42"/>
+        <v>-3.8578715511245072</v>
+      </c>
+      <c r="S26" s="6">
+        <f t="shared" si="42"/>
+        <v>-2.9173419773095625E-2</v>
+      </c>
+      <c r="T26" s="6">
+        <f t="shared" ref="T26:W26" si="43">T24/T25</f>
+        <v>-0.18903983421597972</v>
+      </c>
+      <c r="U26" s="6">
         <f t="shared" si="43"/>
-        <v>0.77927196846742408</v>
-      </c>
-      <c r="E26" s="6">
+        <v>-0.66788738841840234</v>
+      </c>
+      <c r="V26" s="6">
         <f t="shared" si="43"/>
-        <v>1.1734291676327382</v>
-      </c>
-      <c r="F26" s="6">
+        <v>0.9000886132033673</v>
+      </c>
+      <c r="W26" s="6">
         <f t="shared" si="43"/>
-        <v>1.5819615117087873</v>
-      </c>
-      <c r="G26" s="6">
-        <f t="shared" si="43"/>
-        <v>1.071875724553675</v>
-      </c>
-      <c r="H26" s="6">
-        <f t="shared" si="43"/>
-        <v>1.8810572687224669</v>
-      </c>
-      <c r="I26" s="6">
-        <f t="shared" si="43"/>
-        <v>-0.10526315789473684</v>
-      </c>
-      <c r="J26" s="6">
-        <f t="shared" si="43"/>
-        <v>0.23626246232320891</v>
-      </c>
-      <c r="K26" s="6">
-        <f t="shared" si="43"/>
-        <v>-0.15395316485045213</v>
-      </c>
-      <c r="L26" s="6">
-        <f t="shared" si="43"/>
-        <v>-0.63946209135172738</v>
-      </c>
-      <c r="M26" s="6">
-        <f t="shared" si="43"/>
-        <v>0.3433804776257825</v>
-      </c>
-      <c r="N26" s="6">
-        <f t="shared" si="43"/>
-        <v>6.8861581265940178E-2</v>
-      </c>
-      <c r="O26" s="6">
-        <f t="shared" si="43"/>
-        <v>0.68142824020403436</v>
-      </c>
-      <c r="P26" s="6">
-        <f t="shared" si="43"/>
-        <v>-8.8337584048226295E-2</v>
-      </c>
-      <c r="Q26" s="6">
-        <f t="shared" si="43"/>
-        <v>-0.37329005332715048</v>
-      </c>
-      <c r="R26" s="6">
-        <f t="shared" si="43"/>
-        <v>-3.8578715511245072</v>
-      </c>
-      <c r="S26" s="6">
-        <f t="shared" si="43"/>
-        <v>-2.9173419773095625E-2</v>
-      </c>
-      <c r="T26" s="6">
-        <f t="shared" ref="T26:W26" si="44">T24/T25</f>
-        <v>-0.18903983421597972</v>
-      </c>
-      <c r="U26" s="6">
+        <v>-0.11721362871067735</v>
+      </c>
+      <c r="Y26" s="6">
+        <f t="shared" ref="Y26:AE26" si="44">Y24/Y25</f>
+        <v>4.881289125898447</v>
+      </c>
+      <c r="Z26" s="6">
         <f t="shared" si="44"/>
-        <v>-0.66788738841840234</v>
-      </c>
-      <c r="V26" s="6">
+        <v>4.8801298400185482</v>
+      </c>
+      <c r="AA26" s="6">
         <f t="shared" si="44"/>
-        <v>-0.2001092149233234</v>
-      </c>
-      <c r="W26" s="6">
+        <v>4.8455831207975884</v>
+      </c>
+      <c r="AB26" s="6">
         <f t="shared" si="44"/>
-        <v>-2.1117418173495169E-2</v>
-      </c>
-      <c r="Y26" s="6">
-        <f t="shared" ref="Y26:AE26" si="45">Y24/Y25</f>
-        <v>4.881289125898447</v>
-      </c>
-      <c r="Z26" s="6">
+        <v>4.6065383723626248</v>
+      </c>
+      <c r="AC26" s="6">
+        <f t="shared" si="44"/>
+        <v>1.8581034083004868</v>
+      </c>
+      <c r="AD26" s="6">
+        <f t="shared" si="44"/>
+        <v>0.4542082077440297</v>
+      </c>
+      <c r="AE26" s="6">
+        <f t="shared" si="44"/>
+        <v>-4.3426719147950914</v>
+      </c>
+      <c r="AF26" s="6">
+        <f t="shared" ref="AF26:AP26" si="45">AF24/AF25</f>
+        <v>-4.5436933983163764E-2</v>
+      </c>
+      <c r="AG26" s="6">
         <f t="shared" si="45"/>
-        <v>4.8801298400185482</v>
-      </c>
-      <c r="AA26" s="6">
+        <v>1.2931853531236159</v>
+      </c>
+      <c r="AH26" s="6">
         <f t="shared" si="45"/>
-        <v>4.8455831207975884</v>
-      </c>
-      <c r="AB26" s="6">
+        <v>1.8056379447408066</v>
+      </c>
+      <c r="AI26" s="6">
         <f t="shared" si="45"/>
-        <v>4.6065383723626248</v>
-      </c>
-      <c r="AC26" s="6">
+        <v>2.0250702335945068</v>
+      </c>
+      <c r="AJ26" s="6">
         <f t="shared" si="45"/>
-        <v>1.8581034083004868</v>
-      </c>
-      <c r="AD26" s="6">
+        <v>2.1904140768273583</v>
+      </c>
+      <c r="AK26" s="6">
         <f t="shared" si="45"/>
-        <v>0.4542082077440297</v>
-      </c>
-      <c r="AE26" s="6">
+        <v>2.3259123666845252</v>
+      </c>
+      <c r="AL26" s="6">
         <f t="shared" si="45"/>
-        <v>-4.3426719147950914</v>
-      </c>
-      <c r="AF26" s="6">
-        <f t="shared" ref="AF26:AP26" si="46">AF24/AF25</f>
-        <v>-1.083476665899149</v>
-      </c>
-      <c r="AG26" s="6">
-        <f t="shared" si="46"/>
-        <v>0.3326250893391664</v>
-      </c>
-      <c r="AH26" s="6">
-        <f t="shared" si="46"/>
-        <v>0.89317849262169013</v>
-      </c>
-      <c r="AI26" s="6">
-        <f t="shared" si="46"/>
-        <v>1.1475445649603957</v>
-      </c>
-      <c r="AJ26" s="6">
-        <f t="shared" si="46"/>
-        <v>1.3432679610399128</v>
-      </c>
-      <c r="AK26" s="6">
-        <f t="shared" si="46"/>
-        <v>1.481080336689899</v>
-      </c>
-      <c r="AL26" s="6">
-        <f t="shared" si="46"/>
-        <v>1.621311997665249</v>
+        <v>2.465247151838263</v>
       </c>
       <c r="AM26" s="6">
-        <f t="shared" si="46"/>
-        <v>1.7585946128471135</v>
+        <f t="shared" si="45"/>
+        <v>2.6030374348459731</v>
       </c>
       <c r="AN26" s="6">
-        <f t="shared" si="46"/>
-        <v>1.8952665517424772</v>
+        <f t="shared" si="45"/>
+        <v>2.7412024475813626</v>
       </c>
       <c r="AO26" s="6">
-        <f t="shared" si="46"/>
-        <v>2.0330078728813579</v>
+        <f t="shared" si="45"/>
+        <v>2.8811269720030825</v>
       </c>
       <c r="AP26" s="6">
-        <f t="shared" si="46"/>
-        <v>2.1730392695191649</v>
+        <f t="shared" si="45"/>
+        <v>3.0238231330918643</v>
       </c>
     </row>
     <row r="27" spans="2:152" x14ac:dyDescent="0.3">
@@ -4650,11 +4714,11 @@
         <v>96</v>
       </c>
       <c r="P28" s="8">
-        <f t="shared" ref="P28:Q34" si="47">P3/L3-1</f>
+        <f t="shared" ref="P28:Q34" si="46">P3/L3-1</f>
         <v>0.30973922299095258</v>
       </c>
       <c r="Q28" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>6.6244725738396681E-2</v>
       </c>
       <c r="R28" s="8">
@@ -4712,19 +4776,19 @@
         <v>97</v>
       </c>
       <c r="P29" s="8">
+        <f t="shared" si="46"/>
+        <v>0.37393601408864097</v>
+      </c>
+      <c r="Q29" s="8">
+        <f t="shared" si="46"/>
+        <v>0.14989733059548249</v>
+      </c>
+      <c r="R29" s="8">
+        <f t="shared" ref="R29:S34" si="47">R4/N4-1</f>
+        <v>8.5498556517876967E-2</v>
+      </c>
+      <c r="S29" s="14" t="e">
         <f t="shared" si="47"/>
-        <v>0.37393601408864097</v>
-      </c>
-      <c r="Q29" s="8">
-        <f t="shared" si="47"/>
-        <v>0.14989733059548249</v>
-      </c>
-      <c r="R29" s="8">
-        <f t="shared" ref="R29:S34" si="48">R4/N4-1</f>
-        <v>8.5498556517876967E-2</v>
-      </c>
-      <c r="S29" s="14" t="e">
-        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T29" s="14"/>
@@ -4732,7 +4796,7 @@
       <c r="V29" s="14"/>
       <c r="W29" s="14"/>
       <c r="AE29" s="14">
-        <f t="shared" ref="AE29:AE34" si="49">AE4/AD4-1</f>
+        <f t="shared" ref="AE29:AE34" si="48">AE4/AD4-1</f>
         <v>0.18998814162290367</v>
       </c>
       <c r="AF29" s="8">
@@ -4774,27 +4838,30 @@
         <v>98</v>
       </c>
       <c r="P30" s="8">
+        <f t="shared" si="46"/>
+        <v>-0.18711018711018712</v>
+      </c>
+      <c r="Q30" s="8">
+        <f t="shared" si="46"/>
+        <v>-0.21595330739299612</v>
+      </c>
+      <c r="R30" s="8">
         <f t="shared" si="47"/>
-        <v>-0.18711018711018712</v>
-      </c>
-      <c r="Q30" s="8">
+        <v>-0.39116202945990175</v>
+      </c>
+      <c r="S30" s="14">
         <f t="shared" si="47"/>
-        <v>-0.21595330739299612</v>
-      </c>
-      <c r="R30" s="8">
-        <f t="shared" si="48"/>
-        <v>-0.39116202945990175</v>
-      </c>
-      <c r="S30" s="14">
-        <f t="shared" si="48"/>
         <v>-9.3509724106739078E-2</v>
       </c>
       <c r="T30" s="14"/>
       <c r="U30" s="14"/>
       <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
+      <c r="W30" s="14">
+        <f t="shared" ref="W30" si="49">W5/S5-1</f>
+        <v>9.7667456654608964E-2</v>
+      </c>
       <c r="AE30" s="14">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>-0.12124401913875593</v>
       </c>
       <c r="AF30" s="8">
@@ -4836,19 +4903,19 @@
         <v>99</v>
       </c>
       <c r="P31" s="8">
+        <f t="shared" si="46"/>
+        <v>4.6535677352637084E-2</v>
+      </c>
+      <c r="Q31" s="8">
+        <f t="shared" si="46"/>
+        <v>-3.4865293185419977E-2</v>
+      </c>
+      <c r="R31" s="8">
         <f t="shared" si="47"/>
-        <v>4.6535677352637084E-2</v>
-      </c>
-      <c r="Q31" s="8">
+        <v>8.8751625487646368E-2</v>
+      </c>
+      <c r="S31" s="8">
         <f t="shared" si="47"/>
-        <v>-3.4865293185419977E-2</v>
-      </c>
-      <c r="R31" s="8">
-        <f t="shared" si="48"/>
-        <v>8.8751625487646368E-2</v>
-      </c>
-      <c r="S31" s="8">
-        <f t="shared" si="48"/>
         <v>-3.3114473308592629E-2</v>
       </c>
       <c r="T31" s="8">
@@ -4861,14 +4928,14 @@
       </c>
       <c r="V31" s="8">
         <f t="shared" si="50"/>
-        <v>-1</v>
+        <v>0.22424604359510303</v>
       </c>
       <c r="W31" s="8">
         <f t="shared" si="50"/>
-        <v>-1</v>
+        <v>0.24003542958370239</v>
       </c>
       <c r="AE31" s="14">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>1.440443213296394E-2</v>
       </c>
       <c r="AF31" s="8">
@@ -4910,19 +4977,19 @@
         <v>100</v>
       </c>
       <c r="P32" s="8">
+        <f t="shared" si="46"/>
+        <v>-8.3948959032907999E-2</v>
+      </c>
+      <c r="Q32" s="8">
+        <f t="shared" si="46"/>
+        <v>-1.4662756598240456E-2</v>
+      </c>
+      <c r="R32" s="8">
         <f t="shared" si="47"/>
-        <v>-8.3948959032907999E-2</v>
-      </c>
-      <c r="Q32" s="8">
+        <v>4.2068965517241486E-2</v>
+      </c>
+      <c r="S32" s="8">
         <f t="shared" si="47"/>
-        <v>-1.4662756598240456E-2</v>
-      </c>
-      <c r="R32" s="8">
-        <f t="shared" si="48"/>
-        <v>4.2068965517241486E-2</v>
-      </c>
-      <c r="S32" s="8">
-        <f t="shared" si="48"/>
         <v>0.1033310673011556</v>
       </c>
       <c r="T32" s="8">
@@ -4942,7 +5009,7 @@
         <v>-1</v>
       </c>
       <c r="AE32" s="14">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>1.17769310703153E-2</v>
       </c>
       <c r="AF32" s="8">
@@ -4984,19 +5051,19 @@
         <v>101</v>
       </c>
       <c r="P33" s="8">
+        <f t="shared" si="46"/>
+        <v>-9.5632374249637775E-2</v>
+      </c>
+      <c r="Q33" s="8">
+        <f t="shared" si="46"/>
+        <v>3.5474592521572479E-2</v>
+      </c>
+      <c r="R33" s="8">
         <f t="shared" si="47"/>
-        <v>-9.5632374249637775E-2</v>
-      </c>
-      <c r="Q33" s="8">
+        <v>-8.0304311073541856E-2</v>
+      </c>
+      <c r="S33" s="8">
         <f t="shared" si="47"/>
-        <v>3.5474592521572479E-2</v>
-      </c>
-      <c r="R33" s="8">
-        <f t="shared" si="48"/>
-        <v>-8.0304311073541856E-2</v>
-      </c>
-      <c r="S33" s="8">
-        <f t="shared" si="48"/>
         <v>-0.13004830917874399</v>
       </c>
       <c r="T33" s="8">
@@ -5009,14 +5076,14 @@
       </c>
       <c r="V33" s="8">
         <f t="shared" si="50"/>
-        <v>-1</v>
+        <v>-3.4926470588235281E-2</v>
       </c>
       <c r="W33" s="8">
         <f t="shared" si="50"/>
-        <v>-1</v>
+        <v>-4.4868947134606874E-2</v>
       </c>
       <c r="AE33" s="14">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>-7.2289793759915399E-2</v>
       </c>
       <c r="AF33" s="8">
@@ -5058,19 +5125,19 @@
         <v>102</v>
       </c>
       <c r="P34" s="8">
+        <f t="shared" si="46"/>
+        <v>-0.46180555555555558</v>
+      </c>
+      <c r="Q34" s="8">
+        <f t="shared" si="46"/>
+        <v>-0.31782945736434109</v>
+      </c>
+      <c r="R34" s="8">
         <f t="shared" si="47"/>
-        <v>-0.46180555555555558</v>
-      </c>
-      <c r="Q34" s="8">
+        <v>-0.28443526170798894</v>
+      </c>
+      <c r="S34" s="8">
         <f t="shared" si="47"/>
-        <v>-0.31782945736434109</v>
-      </c>
-      <c r="R34" s="8">
-        <f t="shared" si="48"/>
-        <v>-0.28443526170798894</v>
-      </c>
-      <c r="S34" s="8">
-        <f t="shared" si="48"/>
         <v>-0.19660755589822665</v>
       </c>
       <c r="T34" s="8">
@@ -5083,14 +5150,14 @@
       </c>
       <c r="V34" s="8">
         <f t="shared" si="50"/>
-        <v>-1</v>
+        <v>-3.7536092396535103E-2</v>
       </c>
       <c r="W34" s="8">
         <f t="shared" si="50"/>
-        <v>-1</v>
+        <v>-4.0307101727447225E-2</v>
       </c>
       <c r="AE34" s="14">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>-0.31811697574893005</v>
       </c>
       <c r="AF34" s="8">
@@ -5193,11 +5260,11 @@
       </c>
       <c r="V35" s="10">
         <f t="shared" ref="V35" si="54">V11/R11-1</f>
-        <v>-2.0000000000000018E-2</v>
+        <v>2.7777777777777679E-2</v>
       </c>
       <c r="W35" s="10">
         <f t="shared" ref="W35" si="55">W11/S11-1</f>
-        <v>-3.0000000000000027E-2</v>
+        <v>-3.9999999999999925E-2</v>
       </c>
       <c r="Z35" s="10">
         <f>Z11/Y11-1</f>
@@ -5225,7 +5292,7 @@
       </c>
       <c r="AF35" s="10">
         <f t="shared" si="56"/>
-        <v>-1.3643434210278582E-2</v>
+        <v>-4.3765654130807352E-3</v>
       </c>
       <c r="AG35" s="10">
         <f t="shared" si="56"/>
@@ -5350,11 +5417,11 @@
       </c>
       <c r="V36" s="8">
         <f t="shared" si="59"/>
-        <v>0.34100000000000003</v>
+        <v>0.38218706511389439</v>
       </c>
       <c r="W36" s="8">
         <f t="shared" si="59"/>
-        <v>0.37</v>
+        <v>0.34499999999999992</v>
       </c>
       <c r="Y36" s="8">
         <f t="shared" ref="Y36" si="60">Y13/Y11</f>
@@ -5386,7 +5453,7 @@
       </c>
       <c r="AF36" s="8">
         <f t="shared" si="61"/>
-        <v>0.33929633202053128</v>
+        <v>0.3433968745153077</v>
       </c>
       <c r="AG36" s="8">
         <f t="shared" si="61"/>
@@ -5426,7 +5493,7 @@
       </c>
       <c r="AP36" s="8">
         <f t="shared" si="61"/>
-        <v>0.42000000000000004</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="37" spans="2:45" x14ac:dyDescent="0.3">
@@ -5499,11 +5566,11 @@
       </c>
       <c r="V37" s="8">
         <f t="shared" ref="V37:V38" si="65">V14/R14-1</f>
-        <v>-6.9999999999999951E-2</v>
+        <v>-0.2020251914052853</v>
       </c>
       <c r="W37" s="8">
         <f t="shared" ref="W37:W38" si="66">W14/S14-1</f>
-        <v>1.0000000000000009E-2</v>
+        <v>-0.15000000000000002</v>
       </c>
       <c r="Y37" s="8"/>
       <c r="Z37" s="8">
@@ -5532,7 +5599,7 @@
       </c>
       <c r="AF37" s="8">
         <f t="shared" si="67"/>
-        <v>-9.3174785446633601E-2</v>
+        <v>-0.16296385833434057</v>
       </c>
       <c r="AG37" s="8">
         <f t="shared" si="67"/>
@@ -5540,15 +5607,15 @@
       </c>
       <c r="AH37" s="8">
         <f t="shared" si="67"/>
-        <v>1.0000000000000009E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI37" s="8">
         <f t="shared" si="67"/>
-        <v>1.0000000000000009E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ37" s="8">
         <f t="shared" si="67"/>
-        <v>1.0000000000000009E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK37" s="8">
         <f t="shared" si="67"/>
@@ -5651,11 +5718,11 @@
       </c>
       <c r="V38" s="8">
         <f t="shared" si="65"/>
-        <v>-0.14000000000000012</v>
+        <v>-0.18365871294287783</v>
       </c>
       <c r="W38" s="8">
         <f t="shared" si="66"/>
-        <v>3.0000000000000027E-2</v>
+        <v>-3.9999999999999925E-2</v>
       </c>
       <c r="Y38" s="8"/>
       <c r="Z38" s="8">
@@ -5684,7 +5751,7 @@
       </c>
       <c r="AF38" s="8">
         <f t="shared" si="69"/>
-        <v>-0.13082440530234241</v>
+        <v>-0.1575376793172325</v>
       </c>
       <c r="AG38" s="8">
         <f t="shared" si="69"/>
@@ -5815,11 +5882,11 @@
       </c>
       <c r="V39" s="8">
         <f t="shared" si="72"/>
-        <v>-8.9543265183218715E-2</v>
+        <v>5.0025635391489048E-2</v>
       </c>
       <c r="W39" s="8">
         <f t="shared" si="72"/>
-        <v>-8.8934515116901539E-3</v>
+        <v>1.0144343151005097E-2</v>
       </c>
       <c r="Y39" s="8">
         <f t="shared" ref="Y39" si="73">Y18/Y11</f>
@@ -5851,54 +5918,54 @@
       </c>
       <c r="AF39" s="8">
         <f t="shared" si="74"/>
-        <v>-9.0989605265871118E-2</v>
+        <v>-5.0221265552710011E-2</v>
       </c>
       <c r="AG39" s="8">
         <f t="shared" si="74"/>
-        <v>3.0830468239654643E-2</v>
+        <v>6.1294660896844495E-2</v>
       </c>
       <c r="AH39" s="8">
         <f t="shared" si="74"/>
-        <v>8.0444422221632492E-2</v>
+        <v>0.10547705997091375</v>
       </c>
       <c r="AI39" s="8">
         <f t="shared" si="74"/>
-        <v>9.9092247335298936E-2</v>
+        <v>0.12003346087238341</v>
       </c>
       <c r="AJ39" s="8">
         <f t="shared" si="74"/>
-        <v>0.11196895197862228</v>
+        <v>0.12955110761565206</v>
       </c>
       <c r="AK39" s="8">
         <f t="shared" si="74"/>
-        <v>0.12018723018225959</v>
+        <v>0.13697682993112673</v>
       </c>
       <c r="AL39" s="8">
         <f t="shared" si="74"/>
-        <v>0.12801212004461476</v>
+        <v>0.14414989898778377</v>
       </c>
       <c r="AM39" s="8">
         <f t="shared" si="74"/>
-        <v>0.13504324186607825</v>
+        <v>0.15064624217728068</v>
       </c>
       <c r="AN39" s="8">
         <f t="shared" si="74"/>
-        <v>0.1415016429702903</v>
+        <v>0.15665119027474911</v>
       </c>
       <c r="AO39" s="8">
         <f t="shared" si="74"/>
-        <v>0.14753819564921769</v>
+        <v>0.1622913075799586</v>
       </c>
       <c r="AP39" s="8">
         <f t="shared" si="74"/>
-        <v>0.15325606788290311</v>
+        <v>0.16765320814057272</v>
       </c>
       <c r="AR39" t="s">
         <v>51</v>
       </c>
       <c r="AS39" s="2">
         <f>NPV(AS38,AF24:EV24)</f>
-        <v>146006.90887939278</v>
+        <v>228504.46224367002</v>
       </c>
     </row>
     <row r="40" spans="2:45" x14ac:dyDescent="0.3">
@@ -5983,11 +6050,11 @@
       </c>
       <c r="V40" s="8">
         <f t="shared" si="77"/>
-        <v>0.2</v>
+        <v>6.6462614779186704E-2</v>
       </c>
       <c r="W40" s="8">
         <f t="shared" si="77"/>
-        <v>0.2</v>
+        <v>4.76</v>
       </c>
       <c r="Y40" s="8">
         <f t="shared" ref="Y40" si="78">Y22/Y21</f>
@@ -6019,7 +6086,7 @@
       </c>
       <c r="AF40" s="8">
         <f t="shared" si="79"/>
-        <v>-6.4227881081380098E-2</v>
+        <v>1.1201576584538173</v>
       </c>
       <c r="AG40" s="8">
         <f t="shared" si="79"/>
@@ -6035,7 +6102,7 @@
       </c>
       <c r="AJ40" s="8">
         <f t="shared" si="79"/>
-        <v>0.2</v>
+        <v>0.20000000000000004</v>
       </c>
       <c r="AK40" s="8">
         <f t="shared" si="79"/>
@@ -6051,7 +6118,7 @@
       </c>
       <c r="AN40" s="8">
         <f t="shared" si="79"/>
-        <v>0.19999999999999998</v>
+        <v>0.2</v>
       </c>
       <c r="AO40" s="8">
         <f t="shared" si="79"/>
@@ -6059,14 +6126,14 @@
       </c>
       <c r="AP40" s="8">
         <f t="shared" si="79"/>
-        <v>0.19999999999999998</v>
+        <v>0.2</v>
       </c>
       <c r="AR40" t="s">
         <v>52</v>
       </c>
       <c r="AS40" s="2">
         <f>Main!D8</f>
-        <v>-24168</v>
+        <v>-6951</v>
       </c>
     </row>
     <row r="41" spans="2:45" x14ac:dyDescent="0.3">
@@ -6151,7 +6218,7 @@
       </c>
       <c r="V41" s="8">
         <f t="shared" si="82"/>
-        <v>0.05</v>
+        <v>4.5255793616090952E-2</v>
       </c>
       <c r="W41" s="8">
         <f t="shared" si="82"/>
@@ -6187,7 +6254,7 @@
       </c>
       <c r="AF41" s="8">
         <f t="shared" si="84"/>
-        <v>5.0915214747021861E-2</v>
+        <v>3.0889214889179614E-2</v>
       </c>
       <c r="AG41" s="8">
         <f t="shared" si="84"/>
@@ -6195,15 +6262,15 @@
       </c>
       <c r="AH41" s="8">
         <f t="shared" si="84"/>
-        <v>0.03</v>
+        <v>2.9999999999999995E-2</v>
       </c>
       <c r="AI41" s="8">
         <f t="shared" si="84"/>
-        <v>2.9999999999999995E-2</v>
+        <v>0.03</v>
       </c>
       <c r="AJ41" s="8">
         <f t="shared" si="84"/>
-        <v>2.9999999999999995E-2</v>
+        <v>0.03</v>
       </c>
       <c r="AK41" s="8">
         <f t="shared" si="84"/>
@@ -6215,7 +6282,7 @@
       </c>
       <c r="AM41" s="8">
         <f t="shared" si="84"/>
-        <v>3.0000000000000002E-2</v>
+        <v>0.03</v>
       </c>
       <c r="AN41" s="8">
         <f t="shared" si="84"/>
@@ -6227,14 +6294,14 @@
       </c>
       <c r="AP41" s="8">
         <f t="shared" si="84"/>
-        <v>0.03</v>
+        <v>2.9999999999999995E-2</v>
       </c>
       <c r="AR41" t="s">
         <v>53</v>
       </c>
       <c r="AS41" s="2">
         <f>AS39+AS40</f>
-        <v>121838.90887939278</v>
+        <v>221553.46224367002</v>
       </c>
     </row>
     <row r="42" spans="2:45" x14ac:dyDescent="0.3">
@@ -6319,11 +6386,11 @@
       </c>
       <c r="V42" s="8">
         <f t="shared" si="87"/>
-        <v>-6.715744888741404E-2</v>
+        <v>0.29759027320002929</v>
       </c>
       <c r="W42" s="8">
         <f t="shared" si="87"/>
-        <v>-6.670088633767615E-3</v>
+        <v>-3.8649947405329413E-2</v>
       </c>
       <c r="Y42" s="8">
         <f t="shared" ref="Y42" si="88">Y24/Y11</f>
@@ -6355,54 +6422,54 @@
       </c>
       <c r="AF42" s="8">
         <f t="shared" si="89"/>
-        <v>-8.9840622477400253E-2</v>
+        <v>-3.8794732601203975E-3</v>
       </c>
       <c r="AG42" s="8">
         <f t="shared" si="89"/>
-        <v>2.5073531613020485E-2</v>
+        <v>0.10037645105033993</v>
       </c>
       <c r="AH42" s="8">
         <f t="shared" si="89"/>
-        <v>6.2923806047899419E-2</v>
+        <v>0.13098391122465816</v>
       </c>
       <c r="AI42" s="8">
         <f t="shared" si="89"/>
-        <v>7.6994018695062283E-2</v>
+        <v>0.13990655819294914</v>
       </c>
       <c r="AJ42" s="8">
         <f t="shared" si="89"/>
-        <v>8.6659612907054998E-2</v>
+        <v>0.14550933811808994</v>
       </c>
       <c r="AK42" s="8">
         <f t="shared" si="89"/>
-        <v>9.2767420328162237E-2</v>
+        <v>0.15001019186075221</v>
       </c>
       <c r="AL42" s="8">
         <f t="shared" si="89"/>
-        <v>9.85930349562332E-2</v>
+        <v>0.15436564777740289</v>
       </c>
       <c r="AM42" s="8">
         <f t="shared" si="89"/>
-        <v>0.10382648533425555</v>
+        <v>0.15824623393362783</v>
       </c>
       <c r="AN42" s="8">
         <f t="shared" si="89"/>
-        <v>0.10863643058814869</v>
+        <v>0.16179192993287708</v>
       </c>
       <c r="AO42" s="8">
         <f t="shared" si="89"/>
-        <v>0.11313761658310335</v>
+        <v>0.16509766007424662</v>
       </c>
       <c r="AP42" s="8">
         <f t="shared" si="89"/>
-        <v>0.11740816891393198</v>
+        <v>0.16822776703369346</v>
       </c>
       <c r="AR42" t="s">
         <v>54</v>
       </c>
       <c r="AS42" s="9">
         <f>AS41/AP25</f>
-        <v>28.054089081140404</v>
+        <v>49.081405016320339</v>
       </c>
     </row>
     <row r="43" spans="2:45" x14ac:dyDescent="0.3">
@@ -6411,3063 +6478,3581 @@
       </c>
       <c r="AS43" s="9">
         <f>Main!D3</f>
-        <v>36.729999999999997</v>
-      </c>
-    </row>
-    <row r="44" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K44" s="7">
-        <f>K45+K46+K52-K60-K64</f>
-        <v>-7518</v>
-      </c>
-      <c r="O44" s="7">
-        <f>O45+O46+O52-O60-O64</f>
-        <v>-18403</v>
-      </c>
-      <c r="Q44" s="7">
-        <f>Q45+Q46+Q52-Q60-Q64</f>
-        <v>-15888</v>
-      </c>
-      <c r="R44" s="7">
-        <f>R45+R46+R52-R60-R64</f>
-        <v>-20654</v>
-      </c>
-      <c r="AC44" s="7">
-        <f>AC45+AC46+AC52-AC60-AC64</f>
-        <v>-7518</v>
-      </c>
-      <c r="AD44" s="7">
-        <f>AD45+AD46+AD52-AD60-AD64</f>
-        <v>-18403</v>
+        <v>38.28</v>
+      </c>
+    </row>
+    <row r="44" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>107</v>
+      </c>
+      <c r="R44" s="2">
+        <v>115000</v>
+      </c>
+      <c r="U44" s="2">
+        <v>96400</v>
+      </c>
+      <c r="V44" s="2">
+        <v>83300</v>
       </c>
       <c r="AR44" s="1" t="s">
         <v>56</v>
       </c>
       <c r="AS44" s="10">
         <f>AS42/AS43-1</f>
-        <v>-0.23620775711569819</v>
+        <v>0.28216836510763676</v>
       </c>
     </row>
     <row r="45" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>4</v>
-      </c>
-      <c r="K45" s="2">
-        <v>11144</v>
-      </c>
-      <c r="O45" s="2">
-        <v>7079</v>
-      </c>
-      <c r="Q45" s="2">
-        <v>11287</v>
+        <v>108</v>
       </c>
       <c r="R45" s="2">
-        <v>8785</v>
-      </c>
-      <c r="AC45" s="2">
-        <v>11144</v>
-      </c>
-      <c r="AD45" s="2">
-        <v>7079</v>
+        <v>5400</v>
+      </c>
+      <c r="U45" s="2">
+        <v>5000</v>
+      </c>
+      <c r="V45" s="2">
+        <v>5100</v>
       </c>
       <c r="AR45" t="s">
         <v>57</v>
       </c>
       <c r="AS45" s="13" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="R46" s="2">
+        <v>3700</v>
+      </c>
+      <c r="U46" s="2">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="R47" s="7">
+        <f>SUM(R44:R46)</f>
+        <v>124100</v>
+      </c>
+      <c r="U47" s="7">
+        <f>SUM(U44:U46)</f>
+        <v>101400</v>
+      </c>
+      <c r="V47" s="7">
+        <f>SUM(V44:V46)</f>
+        <v>88400</v>
+      </c>
+      <c r="AR47"/>
+      <c r="AS47"/>
+    </row>
+    <row r="49" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K49" s="7">
+        <f>K50+K51+K60-K68-K72</f>
+        <v>-7518</v>
+      </c>
+      <c r="O49" s="7">
+        <f>O50+O51+O60-O68-O72</f>
+        <v>-18403</v>
+      </c>
+      <c r="Q49" s="7">
+        <f>Q50+Q51+Q60-Q68-Q72</f>
+        <v>-15888</v>
+      </c>
+      <c r="R49" s="7">
+        <f>R50+R51+R60-R68-R72</f>
+        <v>-20654</v>
+      </c>
+      <c r="V49" s="7">
+        <f>V50+V51+V60-V68-V72</f>
+        <v>-6951</v>
+      </c>
+      <c r="AC49" s="7">
+        <f>AC50+AC51+AC60-AC68-AC72</f>
+        <v>-7518</v>
+      </c>
+      <c r="AD49" s="7">
+        <f>AD50+AD51+AD60-AD68-AD72</f>
+        <v>-18403</v>
+      </c>
+      <c r="AR49"/>
+      <c r="AS49"/>
+    </row>
+    <row r="50" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="K50" s="2">
+        <v>11144</v>
+      </c>
+      <c r="O50" s="2">
+        <v>7079</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>11287</v>
+      </c>
+      <c r="R50" s="2">
+        <v>8785</v>
+      </c>
+      <c r="V50" s="2">
+        <v>11141</v>
+      </c>
+      <c r="AC50" s="2">
+        <v>11144</v>
+      </c>
+      <c r="AD50" s="2">
+        <v>7079</v>
+      </c>
+    </row>
+    <row r="51" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
         <v>58</v>
       </c>
-      <c r="K46" s="2">
+      <c r="K51" s="2">
         <v>17194</v>
       </c>
-      <c r="O46" s="2">
+      <c r="O51" s="2">
         <v>17955</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q51" s="2">
         <v>17986</v>
       </c>
-      <c r="R46" s="2">
+      <c r="R51" s="2">
         <v>15301</v>
       </c>
-      <c r="AC46" s="2">
+      <c r="V51" s="2">
+        <v>19794</v>
+      </c>
+      <c r="AC51" s="2">
         <v>17194</v>
       </c>
-      <c r="AD46" s="2">
+      <c r="AD51" s="2">
         <v>17955</v>
       </c>
     </row>
-    <row r="47" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B47" t="s">
+    <row r="52" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
         <v>59</v>
       </c>
-      <c r="K47" s="2">
+      <c r="K52" s="2">
         <v>4133</v>
       </c>
-      <c r="O47" s="2">
+      <c r="O52" s="2">
         <v>3402</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="Q52" s="2">
         <v>3131</v>
       </c>
-      <c r="R47" s="2">
+      <c r="R52" s="2">
         <v>3121</v>
       </c>
-      <c r="AC47" s="2">
+      <c r="V52" s="2">
+        <v>3202</v>
+      </c>
+      <c r="AC52" s="2">
         <v>4133</v>
       </c>
-      <c r="AD47" s="2">
+      <c r="AD52" s="2">
         <v>3402</v>
       </c>
     </row>
-    <row r="48" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B48" t="s">
+    <row r="53" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>113</v>
+      </c>
+      <c r="K53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="V53" s="2">
+        <v>1135</v>
+      </c>
+      <c r="AC53" s="2"/>
+      <c r="AD53" s="2"/>
+      <c r="AR53" s="1"/>
+      <c r="AS53" s="1"/>
+    </row>
+    <row r="54" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>114</v>
+      </c>
+      <c r="K54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="V54" s="2">
+        <v>6751</v>
+      </c>
+      <c r="AC54" s="2"/>
+      <c r="AD54" s="2"/>
+    </row>
+    <row r="55" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>115</v>
+      </c>
+      <c r="K55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="V55" s="2">
+        <v>3603</v>
+      </c>
+      <c r="AC55" s="2"/>
+      <c r="AD55" s="2"/>
+    </row>
+    <row r="56" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
         <v>60</v>
       </c>
-      <c r="K48" s="2">
+      <c r="K56" s="2">
         <v>13224</v>
       </c>
-      <c r="O48" s="2">
+      <c r="O56" s="2">
         <v>11127</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="Q56" s="2">
         <v>11244</v>
       </c>
-      <c r="R48" s="2">
+      <c r="R56" s="2">
         <v>12062</v>
       </c>
-      <c r="AC48" s="2">
+      <c r="V56" s="2">
+        <f>SUM(V53:V55)</f>
+        <v>11489</v>
+      </c>
+      <c r="AC56" s="2">
         <v>13224</v>
       </c>
-      <c r="AD48" s="2">
+      <c r="AD56" s="2">
         <v>11127</v>
       </c>
     </row>
-    <row r="49" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B49" t="s">
+    <row r="57" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
         <v>61</v>
       </c>
-      <c r="K49" s="2">
+      <c r="K57" s="2">
         <v>4712</v>
       </c>
-      <c r="O49" s="2">
+      <c r="O57" s="2">
         <v>3706</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="Q57" s="2">
         <v>7181</v>
       </c>
-      <c r="R49" s="2">
+      <c r="R57" s="2">
         <v>6868</v>
       </c>
-      <c r="AC49" s="2">
+      <c r="V57" s="2">
+        <v>6105</v>
+      </c>
+      <c r="AC57" s="2">
         <v>4712</v>
       </c>
-      <c r="AD49" s="2">
+      <c r="AD57" s="2">
         <v>3706</v>
       </c>
     </row>
-    <row r="50" spans="2:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
+    <row r="58" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K50" s="7">
-        <f>SUM(K45:K49)</f>
+      <c r="K58" s="7">
+        <f>SUM(K50:K57)</f>
         <v>50407</v>
       </c>
-      <c r="O50" s="7">
-        <f>SUM(O45:O49)</f>
+      <c r="O58" s="7">
+        <f>SUM(O50:O57)</f>
         <v>43269</v>
       </c>
-      <c r="Q50" s="7">
-        <f>SUM(Q45:Q49)</f>
+      <c r="Q58" s="7">
+        <f>SUM(Q50:Q57)</f>
         <v>50829</v>
       </c>
-      <c r="R50" s="7">
-        <f>SUM(R45:R49)</f>
+      <c r="R58" s="7">
+        <f>SUM(R50:R57)</f>
         <v>46137</v>
       </c>
-      <c r="AC50" s="7">
-        <f>SUM(AC45:AC49)</f>
+      <c r="V58" s="7">
+        <f>SUM(V50:V57)-V56</f>
+        <v>51731</v>
+      </c>
+      <c r="AC58" s="7">
+        <f>SUM(AC50:AC57)</f>
         <v>50407</v>
       </c>
-      <c r="AD50" s="7">
-        <f>SUM(AD45:AD49)</f>
+      <c r="AD58" s="7">
+        <f>SUM(AD50:AD57)</f>
         <v>43269</v>
       </c>
-    </row>
-    <row r="51" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B51" t="s">
+      <c r="AR58"/>
+      <c r="AS58"/>
+    </row>
+    <row r="59" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
         <v>63</v>
       </c>
-      <c r="K51" s="2">
+      <c r="K59" s="2">
         <v>80860</v>
       </c>
-      <c r="O51" s="2">
+      <c r="O59" s="2">
         <v>96647</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="Q59" s="2">
         <v>103398</v>
       </c>
-      <c r="R51" s="2">
+      <c r="R59" s="2">
         <v>104248</v>
       </c>
-      <c r="AC51" s="2">
+      <c r="V59" s="2">
+        <v>105047</v>
+      </c>
+      <c r="AC59" s="2">
         <v>80860</v>
       </c>
-      <c r="AD51" s="2">
+      <c r="AD59" s="2">
         <v>96647</v>
       </c>
-    </row>
-    <row r="52" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B52" t="s">
+      <c r="AR59" s="1"/>
+      <c r="AS59" s="1"/>
+    </row>
+    <row r="60" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
         <v>58</v>
       </c>
-      <c r="K52" s="2">
+      <c r="K60" s="2">
         <v>5912</v>
       </c>
-      <c r="O52" s="2">
+      <c r="O60" s="2">
         <v>5829</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="Q60" s="2">
         <v>5824</v>
       </c>
-      <c r="R52" s="2">
+      <c r="R60" s="2">
         <v>5496</v>
       </c>
-      <c r="AC52" s="2">
+      <c r="V60" s="2">
+        <v>8667</v>
+      </c>
+      <c r="AC60" s="2">
         <v>5912</v>
       </c>
-      <c r="AD52" s="2">
+      <c r="AD60" s="2">
         <v>5829</v>
       </c>
-    </row>
-    <row r="53" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B53" t="s">
+      <c r="AR60" s="1"/>
+      <c r="AS60" s="1"/>
+    </row>
+    <row r="61" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
         <v>64</v>
       </c>
-      <c r="K53" s="2">
+      <c r="K61" s="2">
         <v>27591</v>
       </c>
-      <c r="O53" s="2">
+      <c r="O61" s="2">
         <v>27591</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="Q61" s="2">
         <v>27442</v>
       </c>
-      <c r="R53" s="2">
+      <c r="R61" s="2">
         <v>24680</v>
       </c>
-      <c r="AC53" s="2">
+      <c r="V61" s="2">
+        <v>23912</v>
+      </c>
+      <c r="AC61" s="2">
         <v>27591</v>
       </c>
-      <c r="AD53" s="2">
+      <c r="AD61" s="2">
         <v>27591</v>
       </c>
     </row>
-    <row r="54" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B54" t="s">
+    <row r="62" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
         <v>65</v>
       </c>
-      <c r="K54" s="2">
+      <c r="K62" s="2">
         <v>6018</v>
       </c>
-      <c r="O54" s="2">
+      <c r="O62" s="2">
         <v>4589</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="Q62" s="2">
         <v>4383</v>
       </c>
-      <c r="R54" s="2">
+      <c r="R62" s="2">
         <v>3975</v>
       </c>
-      <c r="AC54" s="2">
+      <c r="V62" s="2">
+        <v>2877</v>
+      </c>
+      <c r="AC62" s="2">
         <v>6018</v>
       </c>
-      <c r="AD54" s="2">
+      <c r="AD62" s="2">
         <v>4589</v>
       </c>
     </row>
-    <row r="55" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B55" t="s">
+    <row r="63" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
         <v>66</v>
       </c>
-      <c r="K55" s="2">
+      <c r="K63" s="2">
         <v>11315</v>
       </c>
-      <c r="O55" s="2">
+      <c r="O63" s="2">
         <v>13647</v>
       </c>
-      <c r="Q55" s="2">
+      <c r="Q63" s="2">
         <v>14329</v>
       </c>
-      <c r="R55" s="2">
+      <c r="R63" s="2">
         <v>9006</v>
       </c>
-      <c r="AC55" s="2">
+      <c r="V63" s="2">
+        <v>12280</v>
+      </c>
+      <c r="AC63" s="2">
         <v>11315</v>
       </c>
-      <c r="AD55" s="2">
+      <c r="AD63" s="2">
         <v>13647</v>
       </c>
     </row>
-    <row r="56" spans="2:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="1" t="s">
+    <row r="64" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="K56" s="7">
-        <f>SUM(K51:K55)</f>
+      <c r="K64" s="7">
+        <f>SUM(K59:K63)</f>
         <v>131696</v>
       </c>
-      <c r="O56" s="7">
-        <f>SUM(O51:O55)</f>
+      <c r="O64" s="7">
+        <f>SUM(O59:O63)</f>
         <v>148303</v>
       </c>
-      <c r="Q56" s="7">
-        <f>SUM(Q51:Q55)</f>
+      <c r="Q64" s="7">
+        <f>SUM(Q59:Q63)</f>
         <v>155376</v>
       </c>
-      <c r="R56" s="7">
-        <f>SUM(R51:R55)</f>
+      <c r="R64" s="7">
+        <f>SUM(R59:R63)</f>
         <v>147405</v>
       </c>
-      <c r="AC56" s="7">
-        <f>SUM(AC51:AC55)</f>
+      <c r="V64" s="7">
+        <f>SUM(V59:V63)</f>
+        <v>152783</v>
+      </c>
+      <c r="AC64" s="7">
+        <f>SUM(AC59:AC63)</f>
         <v>131696</v>
       </c>
-      <c r="AD56" s="7">
-        <f>SUM(AD51:AD55)</f>
+      <c r="AD64" s="7">
+        <f>SUM(AD59:AD63)</f>
         <v>148303</v>
       </c>
-    </row>
-    <row r="57" spans="2:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="1" t="s">
+      <c r="AR64"/>
+      <c r="AS64"/>
+    </row>
+    <row r="65" spans="2:45" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="K57" s="7">
-        <f>K50+K56</f>
+      <c r="K65" s="17">
+        <f>K58+K64</f>
         <v>182103</v>
       </c>
-      <c r="O57" s="7">
-        <f>O50+O56</f>
+      <c r="O65" s="17">
+        <f>O58+O64</f>
         <v>191572</v>
       </c>
-      <c r="Q57" s="7">
-        <f>Q50+Q56</f>
+      <c r="Q65" s="17">
+        <f>Q58+Q64</f>
         <v>206205</v>
       </c>
-      <c r="R57" s="7">
-        <f>R50+R56</f>
+      <c r="R65" s="17">
+        <f>R58+R64</f>
         <v>193542</v>
       </c>
-      <c r="U57" s="7"/>
-      <c r="AC57" s="7">
-        <f>AC50+AC56</f>
+      <c r="U65" s="17"/>
+      <c r="V65" s="17">
+        <f>V58+V64</f>
+        <v>204514</v>
+      </c>
+      <c r="AC65" s="17">
+        <f>AC58+AC64</f>
         <v>182103</v>
       </c>
-      <c r="AD57" s="7">
-        <f>AD50+AD56</f>
+      <c r="AD65" s="17">
+        <f>AD58+AD64</f>
         <v>191572</v>
       </c>
-      <c r="AF57" s="7">
+      <c r="AF65" s="17">
         <v>192520</v>
       </c>
-    </row>
-    <row r="58" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B58" t="s">
+      <c r="AR65" s="19"/>
+      <c r="AS65" s="19"/>
+    </row>
+    <row r="66" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
         <v>69</v>
       </c>
-      <c r="K58" s="2">
+      <c r="K66" s="2">
         <v>4367</v>
       </c>
-      <c r="O58" s="2">
+      <c r="O66" s="2">
         <v>8578</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="Q66" s="2">
         <v>4695</v>
       </c>
-      <c r="R58" s="2">
+      <c r="R66" s="2">
         <v>11074</v>
       </c>
-      <c r="AC58" s="2">
+      <c r="V66" s="2">
+        <v>10268</v>
+      </c>
+      <c r="AC66" s="2">
         <v>4367</v>
       </c>
-      <c r="AD58" s="2">
+      <c r="AD66" s="2">
         <v>8578</v>
       </c>
-    </row>
-    <row r="59" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B59" t="s">
+      <c r="AR66" s="1"/>
+      <c r="AS66" s="1"/>
+    </row>
+    <row r="67" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
         <v>70</v>
       </c>
-      <c r="K59" s="2">
+      <c r="K67" s="2">
         <v>9595</v>
       </c>
-      <c r="O59" s="2">
+      <c r="O67" s="2">
         <v>3655</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="Q67" s="2">
         <v>9618</v>
       </c>
-      <c r="R59" s="2">
+      <c r="R67" s="2">
         <v>5015</v>
       </c>
-      <c r="AC59" s="2">
+      <c r="V67" s="2">
+        <v>3756</v>
+      </c>
+      <c r="AC67" s="2">
         <v>9595</v>
       </c>
-      <c r="AD59" s="2">
+      <c r="AD67" s="2">
         <v>3655</v>
       </c>
     </row>
-    <row r="60" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B60" t="s">
+    <row r="68" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="2">
+      <c r="K68" s="2">
         <v>4084</v>
       </c>
-      <c r="O60" s="2">
+      <c r="O68" s="2">
         <v>2288</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="Q68" s="2">
         <v>2651</v>
       </c>
-      <c r="R60" s="2">
+      <c r="R68" s="2">
         <v>3765</v>
       </c>
-      <c r="AC60" s="2">
+      <c r="V68" s="2">
+        <v>2496</v>
+      </c>
+      <c r="AC68" s="2">
         <v>4084</v>
       </c>
-      <c r="AD60" s="2">
+      <c r="AD68" s="2">
         <v>2288</v>
       </c>
     </row>
-    <row r="61" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B61" t="s">
+    <row r="69" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
         <v>29</v>
       </c>
-      <c r="K61" s="2">
+      <c r="K69" s="2">
         <v>2251</v>
       </c>
-      <c r="O61" s="2">
+      <c r="O69" s="2">
         <v>1107</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="Q69" s="2">
         <v>1856</v>
       </c>
-      <c r="R61" s="2">
+      <c r="R69" s="2">
         <v>2440</v>
       </c>
-      <c r="AC61" s="2">
+      <c r="V69" s="2">
+        <v>825</v>
+      </c>
+      <c r="AC69" s="2">
         <v>2251</v>
       </c>
-      <c r="AD61" s="2">
+      <c r="AD69" s="2">
         <v>1107</v>
       </c>
-    </row>
-    <row r="62" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B62" t="s">
+      <c r="AR69" s="1"/>
+      <c r="AS69" s="1"/>
+    </row>
+    <row r="70" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
         <v>71</v>
       </c>
-      <c r="K62" s="2">
+      <c r="K70" s="2">
         <v>11858</v>
       </c>
-      <c r="O62" s="2">
+      <c r="O70" s="2">
         <v>12425</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="Q70" s="2">
         <v>13207</v>
       </c>
-      <c r="R62" s="2">
+      <c r="R70" s="2">
         <v>12865</v>
       </c>
-      <c r="AC62" s="2">
+      <c r="V70" s="2">
+        <v>14952</v>
+      </c>
+      <c r="AC70" s="2">
         <v>11858</v>
       </c>
-      <c r="AD62" s="2">
+      <c r="AD70" s="2">
         <v>12425</v>
       </c>
-    </row>
-    <row r="63" spans="2:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="1" t="s">
+      <c r="AR70" s="1"/>
+      <c r="AS70" s="1"/>
+    </row>
+    <row r="71" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K63" s="7">
-        <f>SUM(K58:K62)</f>
+      <c r="K71" s="7">
+        <f>SUM(K66:K70)</f>
         <v>32155</v>
       </c>
-      <c r="O63" s="7">
-        <f>SUM(O58:O62)</f>
+      <c r="O71" s="7">
+        <f>SUM(O66:O70)</f>
         <v>28053</v>
       </c>
-      <c r="Q63" s="7">
-        <f>SUM(Q58:Q62)</f>
+      <c r="Q71" s="7">
+        <f>SUM(Q66:Q70)</f>
         <v>32027</v>
       </c>
-      <c r="R63" s="7">
-        <f>SUM(R58:R62)</f>
+      <c r="R71" s="7">
+        <f>SUM(R66:R70)</f>
         <v>35159</v>
       </c>
-      <c r="AC63" s="7">
-        <f>SUM(AC58:AC62)</f>
+      <c r="V71" s="7">
+        <f>SUM(V66:V70)</f>
+        <v>32297</v>
+      </c>
+      <c r="AC71" s="7">
+        <f>SUM(AC66:AC70)</f>
         <v>32155</v>
       </c>
-      <c r="AD63" s="7">
-        <f>SUM(AD58:AD62)</f>
+      <c r="AD71" s="7">
+        <f>SUM(AD66:AD70)</f>
         <v>28053</v>
       </c>
     </row>
-    <row r="64" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B64" t="s">
+    <row r="72" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
         <v>5</v>
       </c>
-      <c r="K64" s="2">
+      <c r="K72" s="2">
         <v>37684</v>
       </c>
-      <c r="O64" s="2">
+      <c r="O72" s="2">
         <v>46978</v>
       </c>
-      <c r="Q64" s="2">
+      <c r="Q72" s="2">
         <v>48334</v>
       </c>
-      <c r="R64" s="2">
+      <c r="R72" s="2">
         <v>46471</v>
       </c>
-      <c r="AC64" s="2">
+      <c r="V72" s="2">
+        <v>44057</v>
+      </c>
+      <c r="AC72" s="2">
         <v>37684</v>
       </c>
-      <c r="AD64" s="2">
+      <c r="AD72" s="2">
         <v>46978</v>
       </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.3">
-      <c r="B65" t="s">
+    <row r="73" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
         <v>73</v>
       </c>
-      <c r="K65" s="2">
+      <c r="K73" s="2">
         <v>8978</v>
       </c>
-      <c r="O65" s="2">
+      <c r="O73" s="2">
         <v>6576</v>
       </c>
-      <c r="Q65" s="2">
+      <c r="Q73" s="2">
         <v>5410</v>
       </c>
-      <c r="R65" s="2">
+      <c r="R73" s="2">
         <v>7048</v>
       </c>
-      <c r="AC65" s="2">
+      <c r="V73" s="2">
+        <v>11430</v>
+      </c>
+      <c r="AC73" s="2">
         <v>8978</v>
       </c>
-      <c r="AD65" s="2">
+      <c r="AD73" s="2">
         <v>6576</v>
       </c>
-    </row>
-    <row r="66" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="1" t="s">
+      <c r="AR73" s="1"/>
+      <c r="AS73" s="1"/>
+    </row>
+    <row r="74" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K66" s="7">
-        <f>SUM(K64:K65)</f>
+      <c r="K74" s="7">
+        <f>SUM(K72:K73)</f>
         <v>46662</v>
       </c>
-      <c r="O66" s="7">
-        <f>SUM(O64:O65)</f>
+      <c r="O74" s="7">
+        <f>SUM(O72:O73)</f>
         <v>53554</v>
       </c>
-      <c r="Q66" s="7">
-        <f>SUM(Q64:Q65)</f>
+      <c r="Q74" s="7">
+        <f>SUM(Q72:Q73)</f>
         <v>53744</v>
       </c>
-      <c r="R66" s="7">
-        <f>SUM(R64:R65)</f>
+      <c r="R74" s="7">
+        <f>SUM(R72:R73)</f>
         <v>53519</v>
       </c>
-      <c r="AC66" s="7">
-        <f>SUM(AC64:AC65)</f>
+      <c r="V74" s="7">
+        <f>SUM(V72:V73)</f>
+        <v>55487</v>
+      </c>
+      <c r="AC74" s="7">
+        <f>SUM(AC72:AC73)</f>
         <v>46662</v>
       </c>
-      <c r="AD66" s="7">
-        <f>SUM(AD64:AD65)</f>
+      <c r="AD74" s="7">
+        <f>SUM(AD72:AD73)</f>
         <v>53554</v>
       </c>
-    </row>
-    <row r="67" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="1" t="s">
+      <c r="AR74"/>
+      <c r="AS74"/>
+    </row>
+    <row r="75" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K67" s="7">
+      <c r="K75" s="7">
         <f>101423+1863</f>
         <v>103286</v>
       </c>
-      <c r="O67" s="7">
+      <c r="O75" s="7">
         <f>105590+4375</f>
         <v>109965</v>
       </c>
-      <c r="Q67" s="7">
+      <c r="Q75" s="7">
         <f>115229+5205</f>
         <v>120434</v>
       </c>
-      <c r="R67" s="7">
+      <c r="R75" s="7">
         <f>99532+5332</f>
         <v>104864</v>
       </c>
-      <c r="AC67" s="7">
+      <c r="V75" s="7">
+        <v>116730</v>
+      </c>
+      <c r="AC75" s="7">
         <f>101423+1863</f>
         <v>103286</v>
       </c>
-      <c r="AD67" s="7">
+      <c r="AD75" s="7">
         <f>105590+4375</f>
         <v>109965</v>
       </c>
-    </row>
-    <row r="68" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="1" t="s">
+      <c r="AR75"/>
+      <c r="AS75"/>
+    </row>
+    <row r="76" spans="2:45" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="K68" s="7">
-        <f>K63+K66+K67</f>
+      <c r="K76" s="17">
+        <f>K71+K74+K75</f>
         <v>182103</v>
       </c>
-      <c r="O68" s="7">
-        <f>O63+O66+O67</f>
+      <c r="O76" s="17">
+        <f>O71+O74+O75</f>
         <v>191572</v>
       </c>
-      <c r="Q68" s="7">
-        <f>Q63+Q66+Q67</f>
+      <c r="Q76" s="17">
+        <f>Q71+Q74+Q75</f>
         <v>206205</v>
       </c>
-      <c r="R68" s="7">
-        <f>R63+R66+R67</f>
+      <c r="R76" s="17">
+        <f>R71+R74+R75</f>
         <v>193542</v>
       </c>
-      <c r="AC68" s="7">
-        <f>AC63+AC66+AC67</f>
+      <c r="V76" s="17">
+        <f>V71+V74+V75</f>
+        <v>204514</v>
+      </c>
+      <c r="AC76" s="17">
+        <f>AC71+AC74+AC75</f>
         <v>182103</v>
       </c>
-      <c r="AD68" s="7">
-        <f>AD63+AD66+AD67</f>
+      <c r="AD76" s="17">
+        <f>AD71+AD74+AD75</f>
         <v>191572</v>
       </c>
-    </row>
-    <row r="70" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="1" t="s">
+      <c r="AR76" s="19"/>
+      <c r="AS76" s="19"/>
+    </row>
+    <row r="78" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L70" s="7">
-        <f t="shared" ref="L70:T70" si="90">L24</f>
+      <c r="L78" s="7">
+        <f>L24</f>
         <v>-2758</v>
       </c>
-      <c r="M70" s="7">
-        <f t="shared" si="90"/>
+      <c r="M78" s="7">
+        <f>M24</f>
         <v>1481</v>
       </c>
-      <c r="N70" s="7">
-        <f t="shared" si="90"/>
+      <c r="N78" s="7">
+        <f>N24</f>
         <v>297</v>
       </c>
-      <c r="O70" s="7">
-        <f t="shared" si="90"/>
+      <c r="O78" s="7">
+        <f>O24</f>
         <v>2939</v>
       </c>
-      <c r="P70" s="7">
-        <f t="shared" si="90"/>
+      <c r="P78" s="7">
+        <f>P24</f>
         <v>-381</v>
       </c>
-      <c r="Q70" s="7">
-        <f t="shared" si="90"/>
+      <c r="Q78" s="7">
+        <f>Q24</f>
         <v>-1610</v>
       </c>
-      <c r="R70" s="7">
-        <f t="shared" si="90"/>
+      <c r="R78" s="7">
+        <f>R24</f>
         <v>-16639</v>
       </c>
-      <c r="S70" s="7">
-        <f t="shared" si="90"/>
+      <c r="S78" s="7">
+        <f>S24</f>
         <v>-126</v>
       </c>
-      <c r="T70" s="7">
-        <f t="shared" si="90"/>
+      <c r="T78" s="7">
+        <f>T24</f>
         <v>-821</v>
       </c>
-      <c r="U70" s="7">
-        <f t="shared" ref="U70" si="91">U24</f>
+      <c r="U78" s="7">
+        <f>U24</f>
         <v>-2918</v>
       </c>
-      <c r="V70" s="7"/>
-      <c r="W70" s="7"/>
-      <c r="AC70" s="7">
+      <c r="V78" s="7">
+        <f>V24</f>
+        <v>4063</v>
+      </c>
+      <c r="W78" s="7">
+        <f>W24</f>
+        <v>-529.10231999999758</v>
+      </c>
+      <c r="AC78" s="7">
         <f>AC24</f>
         <v>8014</v>
       </c>
-      <c r="AD70" s="7">
+      <c r="AD78" s="7">
         <f>AD24</f>
         <v>1959</v>
       </c>
-      <c r="AE70" s="7">
+      <c r="AE78" s="7">
         <f>AE24</f>
         <v>-18756</v>
       </c>
-      <c r="AF70" s="7">
+      <c r="AF78" s="7">
         <f>AF24</f>
-        <v>-4705.5391600000039</v>
-      </c>
-      <c r="AG70" s="7">
-        <f t="shared" ref="AG70:AP70" si="92">AG24</f>
-        <v>1444.5907629999997</v>
-      </c>
-      <c r="AH70" s="7">
+        <v>-205.10232000000124</v>
+      </c>
+      <c r="AG78" s="7">
+        <f>AG24</f>
+        <v>5837.4386840000025</v>
+      </c>
+      <c r="AH78" s="7">
+        <f>AH24</f>
+        <v>8150.6496825600016</v>
+      </c>
+      <c r="AI78" s="7">
+        <f>AI24</f>
+        <v>9141.1670344456033</v>
+      </c>
+      <c r="AJ78" s="7">
+        <f>AJ24</f>
+        <v>9887.5291427986958</v>
+      </c>
+      <c r="AK78" s="7">
+        <f>AK24</f>
+        <v>10499.168423213947</v>
+      </c>
+      <c r="AL78" s="7">
+        <f>AL24</f>
+        <v>11128.12564339792</v>
+      </c>
+      <c r="AM78" s="7">
+        <f>AM24</f>
+        <v>11750.110980894722</v>
+      </c>
+      <c r="AN78" s="7">
+        <f>AN24</f>
+        <v>12373.787848382271</v>
+      </c>
+      <c r="AO78" s="7">
+        <f>AO24</f>
+        <v>13005.407151621914</v>
+      </c>
+      <c r="AP78" s="7">
+        <f>AP24</f>
+        <v>13649.537622776676</v>
+      </c>
+      <c r="AR78"/>
+      <c r="AS78"/>
+    </row>
+    <row r="79" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>77</v>
+      </c>
+      <c r="L79" s="2">
+        <v>1901</v>
+      </c>
+      <c r="M79" s="2">
+        <f>M101-L79</f>
+        <v>1832</v>
+      </c>
+      <c r="N79" s="2">
+        <f>N101-M79-L79</f>
+        <v>2020</v>
+      </c>
+      <c r="O79" s="2">
+        <f>AD79-N79-M79-L79</f>
+        <v>2094</v>
+      </c>
+      <c r="P79" s="2">
+        <v>2200</v>
+      </c>
+      <c r="Q79" s="2">
+        <f>Q101-P79</f>
+        <v>2203</v>
+      </c>
+      <c r="R79" s="2">
+        <f>R101-Q79-P79</f>
+        <v>3248</v>
+      </c>
+      <c r="S79" s="2">
+        <f>AE79-R79-Q79-P79</f>
+        <v>2300</v>
+      </c>
+      <c r="T79" s="2">
+        <v>2425</v>
+      </c>
+      <c r="U79" s="2">
+        <f>U101-T79</f>
+        <v>2788</v>
+      </c>
+      <c r="V79" s="2">
+        <f>V101-U79-T79</f>
+        <v>2758</v>
+      </c>
+      <c r="W79" s="2">
+        <v>2850</v>
+      </c>
+      <c r="AC79" s="2">
+        <v>11128</v>
+      </c>
+      <c r="AD79" s="2">
+        <v>7847</v>
+      </c>
+      <c r="AE79" s="2">
+        <v>9951</v>
+      </c>
+      <c r="AF79" s="2">
+        <f>SUM(T79:W79)</f>
+        <v>10821</v>
+      </c>
+      <c r="AG79" s="2">
+        <f>AF79*1.01</f>
+        <v>10929.210000000001</v>
+      </c>
+      <c r="AH79" s="2">
+        <f t="shared" ref="AH79:AP79" si="90">AG79*1.01</f>
+        <v>11038.502100000002</v>
+      </c>
+      <c r="AI79" s="2">
+        <f t="shared" si="90"/>
+        <v>11148.887121000002</v>
+      </c>
+      <c r="AJ79" s="2">
+        <f t="shared" si="90"/>
+        <v>11260.375992210002</v>
+      </c>
+      <c r="AK79" s="2">
+        <f t="shared" si="90"/>
+        <v>11372.979752132102</v>
+      </c>
+      <c r="AL79" s="2">
+        <f t="shared" si="90"/>
+        <v>11486.709549653422</v>
+      </c>
+      <c r="AM79" s="2">
+        <f t="shared" si="90"/>
+        <v>11601.576645149957</v>
+      </c>
+      <c r="AN79" s="2">
+        <f t="shared" si="90"/>
+        <v>11717.592411601456</v>
+      </c>
+      <c r="AO79" s="2">
+        <f t="shared" si="90"/>
+        <v>11834.76833571747</v>
+      </c>
+      <c r="AP79" s="2">
+        <f t="shared" si="90"/>
+        <v>11953.116019074645</v>
+      </c>
+    </row>
+    <row r="80" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>78</v>
+      </c>
+      <c r="L80" s="2">
+        <v>739</v>
+      </c>
+      <c r="M80" s="2">
+        <f>M102-L80</f>
+        <v>922</v>
+      </c>
+      <c r="N80" s="2">
+        <f>N102-M80-L80</f>
+        <v>772</v>
+      </c>
+      <c r="O80" s="2">
+        <f t="shared" ref="O80:O93" si="91">AD80-N80-M80-L80</f>
+        <v>796</v>
+      </c>
+      <c r="P80" s="2">
+        <v>1179</v>
+      </c>
+      <c r="Q80" s="2">
+        <f>Q102-P80</f>
+        <v>780</v>
+      </c>
+      <c r="R80" s="2">
+        <f>R102-Q80-P80</f>
+        <v>800</v>
+      </c>
+      <c r="S80" s="2">
+        <f t="shared" ref="S80:S95" si="92">AE80-R80-Q80-P80</f>
+        <v>651</v>
+      </c>
+      <c r="T80" s="2">
+        <v>684</v>
+      </c>
+      <c r="U80" s="2">
+        <f>U102-T80</f>
+        <v>664</v>
+      </c>
+      <c r="V80" s="2">
+        <f>V102-U80-T80</f>
+        <v>548</v>
+      </c>
+      <c r="W80" s="2">
+        <v>580</v>
+      </c>
+      <c r="AC80" s="2">
+        <v>3128</v>
+      </c>
+      <c r="AD80" s="2">
+        <v>3229</v>
+      </c>
+      <c r="AE80" s="2">
+        <v>3410</v>
+      </c>
+      <c r="AF80" s="2">
+        <f t="shared" ref="AF80:AF93" si="93">SUM(T80:W80)</f>
+        <v>2476</v>
+      </c>
+      <c r="AG80" s="2">
+        <f>AF80*0.98</f>
+        <v>2426.48</v>
+      </c>
+      <c r="AH80" s="2">
+        <f t="shared" ref="AH80:AP80" si="94">AG80*0.98</f>
+        <v>2377.9504000000002</v>
+      </c>
+      <c r="AI80" s="2">
+        <f t="shared" si="94"/>
+        <v>2330.391392</v>
+      </c>
+      <c r="AJ80" s="2">
+        <f t="shared" si="94"/>
+        <v>2283.78356416</v>
+      </c>
+      <c r="AK80" s="2">
+        <f t="shared" si="94"/>
+        <v>2238.1078928767997</v>
+      </c>
+      <c r="AL80" s="2">
+        <f t="shared" si="94"/>
+        <v>2193.3457350192639</v>
+      </c>
+      <c r="AM80" s="2">
+        <f t="shared" si="94"/>
+        <v>2149.4788203188787</v>
+      </c>
+      <c r="AN80" s="2">
+        <f t="shared" si="94"/>
+        <v>2106.489243912501</v>
+      </c>
+      <c r="AO80" s="2">
+        <f t="shared" si="94"/>
+        <v>2064.3594590342509</v>
+      </c>
+      <c r="AP80" s="2">
+        <f t="shared" si="94"/>
+        <v>2023.0722698535658</v>
+      </c>
+    </row>
+    <row r="81" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
+        <v>24</v>
+      </c>
+      <c r="L81" s="2">
+        <v>55</v>
+      </c>
+      <c r="M81" s="2">
+        <f>M103-L81</f>
+        <v>200</v>
+      </c>
+      <c r="N81" s="2">
+        <f>N103-M81-L81</f>
+        <v>463</v>
+      </c>
+      <c r="O81" s="2">
+        <f t="shared" si="91"/>
+        <v>-1142</v>
+      </c>
+      <c r="P81" s="2">
+        <v>348</v>
+      </c>
+      <c r="Q81" s="2">
+        <f>Q103-P81</f>
+        <v>943</v>
+      </c>
+      <c r="R81" s="2">
+        <f>R103-Q81-P81</f>
+        <v>2335</v>
+      </c>
+      <c r="S81" s="2">
         <f t="shared" si="92"/>
-        <v>3879.0741934560001</v>
-      </c>
-      <c r="AI70" s="7">
+        <v>-135</v>
+      </c>
+      <c r="T81" s="2">
+        <v>0</v>
+      </c>
+      <c r="U81" s="2">
+        <f>U103-T81</f>
+        <v>382</v>
+      </c>
+      <c r="V81" s="2">
+        <f>V103-U81-T81</f>
+        <v>-10</v>
+      </c>
+      <c r="W81" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="2">
+        <v>1074</v>
+      </c>
+      <c r="AD81" s="2">
+        <v>-424</v>
+      </c>
+      <c r="AE81" s="2">
+        <v>3491</v>
+      </c>
+      <c r="AF81" s="2">
+        <f t="shared" si="93"/>
+        <v>372</v>
+      </c>
+      <c r="AG81" s="2">
+        <f>AG16</f>
+        <v>1624.6999999999998</v>
+      </c>
+      <c r="AH81" s="2">
+        <f>AH16</f>
+        <v>1137.2899999999997</v>
+      </c>
+      <c r="AI81" s="2">
+        <f>AI16</f>
+        <v>796.10299999999972</v>
+      </c>
+      <c r="AJ81" s="2">
+        <f>AJ16</f>
+        <v>557.2720999999998</v>
+      </c>
+      <c r="AK81" s="2">
+        <f>AK16</f>
+        <v>390.09046999999981</v>
+      </c>
+      <c r="AL81" s="2">
+        <f>AL16</f>
+        <v>273.06332899999984</v>
+      </c>
+      <c r="AM81" s="2">
+        <f>AM16</f>
+        <v>191.14433029999987</v>
+      </c>
+      <c r="AN81" s="2">
+        <f>AN16</f>
+        <v>133.80103120999991</v>
+      </c>
+      <c r="AO81" s="2">
+        <f>AO16</f>
+        <v>93.660721846999934</v>
+      </c>
+      <c r="AP81" s="2">
+        <f>AP16</f>
+        <v>65.562505292899957</v>
+      </c>
+    </row>
+    <row r="82" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>79</v>
+      </c>
+      <c r="L82" s="2">
+        <v>465</v>
+      </c>
+      <c r="M82" s="2">
+        <f>M104-L82</f>
+        <v>444</v>
+      </c>
+      <c r="N82" s="2">
+        <f>N104-M82-L82</f>
+        <v>427</v>
+      </c>
+      <c r="O82" s="2">
+        <f t="shared" si="91"/>
+        <v>419</v>
+      </c>
+      <c r="P82" s="2">
+        <v>351</v>
+      </c>
+      <c r="Q82" s="2">
+        <f>Q104-P82</f>
+        <v>366</v>
+      </c>
+      <c r="R82" s="2">
+        <f>R104-Q82-P82</f>
+        <v>364</v>
+      </c>
+      <c r="S82" s="2">
         <f t="shared" si="92"/>
-        <v>4983.7860456229982</v>
-      </c>
-      <c r="AJ70" s="7">
+        <v>347</v>
+      </c>
+      <c r="T82" s="2">
+        <v>249</v>
+      </c>
+      <c r="U82" s="2">
+        <f>U104-T82</f>
+        <v>225</v>
+      </c>
+      <c r="V82" s="2">
+        <f>V104-U82-T82</f>
+        <v>234</v>
+      </c>
+      <c r="W82" s="2">
+        <v>240</v>
+      </c>
+      <c r="AC82" s="2">
+        <v>1907</v>
+      </c>
+      <c r="AD82" s="2">
+        <v>1755</v>
+      </c>
+      <c r="AE82" s="2">
+        <v>1428</v>
+      </c>
+      <c r="AF82" s="2">
+        <f t="shared" si="93"/>
+        <v>948</v>
+      </c>
+      <c r="AG82" s="2">
+        <f t="shared" ref="AG82:AP82" si="95">AF82*1.02</f>
+        <v>966.96</v>
+      </c>
+      <c r="AH82" s="2">
+        <f t="shared" si="95"/>
+        <v>986.29920000000004</v>
+      </c>
+      <c r="AI82" s="2">
+        <f t="shared" si="95"/>
+        <v>1006.0251840000001</v>
+      </c>
+      <c r="AJ82" s="2">
+        <f t="shared" si="95"/>
+        <v>1026.14568768</v>
+      </c>
+      <c r="AK82" s="2">
+        <f t="shared" si="95"/>
+        <v>1046.6686014336001</v>
+      </c>
+      <c r="AL82" s="2">
+        <f t="shared" si="95"/>
+        <v>1067.6019734622721</v>
+      </c>
+      <c r="AM82" s="2">
+        <f t="shared" si="95"/>
+        <v>1088.9540129315176</v>
+      </c>
+      <c r="AN82" s="2">
+        <f t="shared" si="95"/>
+        <v>1110.7330931901479</v>
+      </c>
+      <c r="AO82" s="2">
+        <f t="shared" si="95"/>
+        <v>1132.9477550539509</v>
+      </c>
+      <c r="AP82" s="2">
+        <f t="shared" si="95"/>
+        <v>1155.60671015503</v>
+      </c>
+    </row>
+    <row r="83" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
+        <v>58</v>
+      </c>
+      <c r="L83" s="2">
+        <v>-167</v>
+      </c>
+      <c r="M83" s="2">
+        <f>M105-L83</f>
+        <v>21</v>
+      </c>
+      <c r="N83" s="2">
+        <f>N105-M83-L83</f>
+        <v>193</v>
+      </c>
+      <c r="O83" s="2">
+        <f t="shared" si="91"/>
+        <v>-89</v>
+      </c>
+      <c r="P83" s="2">
+        <v>-208</v>
+      </c>
+      <c r="Q83" s="2">
+        <f>Q105-P83</f>
+        <v>124</v>
+      </c>
+      <c r="R83" s="2">
+        <f>R105-Q83-P83</f>
+        <v>159</v>
+      </c>
+      <c r="S83" s="2">
         <f t="shared" si="92"/>
-        <v>5833.8127547963413</v>
-      </c>
-      <c r="AK70" s="7">
-        <f t="shared" si="92"/>
-        <v>6432.3319022442311</v>
-      </c>
-      <c r="AL70" s="7">
-        <f t="shared" si="92"/>
-        <v>7041.3580058601765</v>
-      </c>
-      <c r="AM70" s="7">
-        <f t="shared" si="92"/>
-        <v>7637.5764035950142</v>
-      </c>
-      <c r="AN70" s="7">
-        <f t="shared" si="92"/>
-        <v>8231.1426342175782</v>
-      </c>
-      <c r="AO70" s="7">
-        <f t="shared" si="92"/>
-        <v>8829.3531919237375</v>
-      </c>
-      <c r="AP70" s="7">
-        <f t="shared" si="92"/>
-        <v>9437.5095475217331</v>
-      </c>
-    </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.3">
-      <c r="B71" t="s">
-        <v>77</v>
-      </c>
-      <c r="L71" s="2">
-        <v>1901</v>
-      </c>
-      <c r="M71" s="2">
-        <f t="shared" ref="M71:M83" si="93">M91-L71</f>
-        <v>1832</v>
-      </c>
-      <c r="N71" s="2">
-        <f t="shared" ref="N71:N83" si="94">N91-M71-L71</f>
-        <v>2020</v>
-      </c>
-      <c r="O71" s="2">
-        <f>AD71-N71-M71-L71</f>
-        <v>2094</v>
-      </c>
-      <c r="P71" s="2">
-        <v>2200</v>
-      </c>
-      <c r="Q71" s="2">
-        <f t="shared" ref="Q71:Q83" si="95">Q91-P71</f>
-        <v>2203</v>
-      </c>
-      <c r="R71" s="2">
-        <f t="shared" ref="R71:R83" si="96">R91-Q71-P71</f>
-        <v>3248</v>
-      </c>
-      <c r="S71" s="2">
-        <f>AE71-R71-Q71-P71</f>
-        <v>2300</v>
-      </c>
-      <c r="T71" s="2">
-        <v>2425</v>
-      </c>
-      <c r="U71" s="2">
-        <f t="shared" ref="U71:U75" si="97">U91-T71</f>
-        <v>2788</v>
-      </c>
-      <c r="V71" s="2"/>
-      <c r="W71" s="2"/>
-      <c r="AC71" s="2">
-        <v>11128</v>
-      </c>
-      <c r="AD71" s="2">
-        <v>7847</v>
-      </c>
-      <c r="AE71" s="2">
-        <v>9951</v>
-      </c>
-      <c r="AF71" s="2">
-        <v>9500</v>
-      </c>
-      <c r="AG71" s="2">
-        <f>AF71*1.01</f>
-        <v>9595</v>
-      </c>
-      <c r="AH71" s="2">
-        <f t="shared" ref="AH71:AP71" si="98">AG71*1.01</f>
-        <v>9690.9500000000007</v>
-      </c>
-      <c r="AI71" s="2">
-        <f t="shared" si="98"/>
-        <v>9787.8595000000005</v>
-      </c>
-      <c r="AJ71" s="2">
-        <f t="shared" si="98"/>
-        <v>9885.7380950000006</v>
-      </c>
-      <c r="AK71" s="2">
-        <f t="shared" si="98"/>
-        <v>9984.59547595</v>
-      </c>
-      <c r="AL71" s="2">
-        <f t="shared" si="98"/>
-        <v>10084.441430709499</v>
-      </c>
-      <c r="AM71" s="2">
-        <f t="shared" si="98"/>
-        <v>10185.285845016595</v>
-      </c>
-      <c r="AN71" s="2">
-        <f t="shared" si="98"/>
-        <v>10287.13870346676</v>
-      </c>
-      <c r="AO71" s="2">
-        <f t="shared" si="98"/>
-        <v>10390.010090501428</v>
-      </c>
-      <c r="AP71" s="2">
-        <f t="shared" si="98"/>
-        <v>10493.910191406443</v>
-      </c>
-    </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.3">
-      <c r="B72" t="s">
-        <v>78</v>
-      </c>
-      <c r="L72" s="2">
-        <v>739</v>
-      </c>
-      <c r="M72" s="2">
-        <f t="shared" si="93"/>
-        <v>922</v>
-      </c>
-      <c r="N72" s="2">
-        <f t="shared" si="94"/>
-        <v>772</v>
-      </c>
-      <c r="O72" s="2">
-        <f t="shared" ref="O72:O83" si="99">AD72-N72-M72-L72</f>
-        <v>796</v>
-      </c>
-      <c r="P72" s="2">
-        <v>1179</v>
-      </c>
-      <c r="Q72" s="2">
-        <f t="shared" si="95"/>
-        <v>780</v>
-      </c>
-      <c r="R72" s="2">
-        <f t="shared" si="96"/>
-        <v>800</v>
-      </c>
-      <c r="S72" s="2">
-        <f t="shared" ref="S72:S85" si="100">AE72-R72-Q72-P72</f>
-        <v>651</v>
-      </c>
-      <c r="T72" s="2">
-        <v>684</v>
-      </c>
-      <c r="U72" s="2">
-        <f t="shared" si="97"/>
-        <v>664</v>
-      </c>
-      <c r="V72" s="2"/>
-      <c r="W72" s="2"/>
-      <c r="AC72" s="2">
-        <v>3128</v>
-      </c>
-      <c r="AD72" s="2">
-        <v>3229</v>
-      </c>
-      <c r="AE72" s="2">
-        <v>3410</v>
-      </c>
-      <c r="AF72" s="2">
-        <v>2800</v>
-      </c>
-      <c r="AG72" s="2">
-        <f>AF72*1.01</f>
-        <v>2828</v>
-      </c>
-      <c r="AH72" s="2">
-        <f t="shared" ref="AH72:AP72" si="101">AG72*1.01</f>
-        <v>2856.28</v>
-      </c>
-      <c r="AI72" s="2">
-        <f t="shared" si="101"/>
-        <v>2884.8428000000004</v>
-      </c>
-      <c r="AJ72" s="2">
-        <f t="shared" si="101"/>
-        <v>2913.6912280000006</v>
-      </c>
-      <c r="AK72" s="2">
-        <f t="shared" si="101"/>
-        <v>2942.8281402800008</v>
-      </c>
-      <c r="AL72" s="2">
-        <f t="shared" si="101"/>
-        <v>2972.2564216828009</v>
-      </c>
-      <c r="AM72" s="2">
-        <f t="shared" si="101"/>
-        <v>3001.9789858996292</v>
-      </c>
-      <c r="AN72" s="2">
-        <f t="shared" si="101"/>
-        <v>3031.9987757586255</v>
-      </c>
-      <c r="AO72" s="2">
-        <f t="shared" si="101"/>
-        <v>3062.3187635162117</v>
-      </c>
-      <c r="AP72" s="2">
-        <f t="shared" si="101"/>
-        <v>3092.9419511513738</v>
-      </c>
-    </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.3">
-      <c r="B73" t="s">
-        <v>24</v>
-      </c>
-      <c r="L73" s="2">
-        <v>55</v>
-      </c>
-      <c r="M73" s="2">
-        <f t="shared" si="93"/>
-        <v>200</v>
-      </c>
-      <c r="N73" s="2">
-        <f t="shared" si="94"/>
-        <v>463</v>
-      </c>
-      <c r="O73" s="2">
-        <f t="shared" si="99"/>
-        <v>-1142</v>
-      </c>
-      <c r="P73" s="2">
-        <v>348</v>
-      </c>
-      <c r="Q73" s="2">
-        <f t="shared" si="95"/>
-        <v>943</v>
-      </c>
-      <c r="R73" s="2">
-        <f t="shared" si="96"/>
-        <v>2335</v>
-      </c>
-      <c r="S73" s="2">
-        <f t="shared" si="100"/>
-        <v>-135</v>
-      </c>
-      <c r="T73" s="2">
-        <v>0</v>
-      </c>
-      <c r="U73" s="2">
-        <f t="shared" si="97"/>
-        <v>382</v>
-      </c>
-      <c r="V73" s="2"/>
-      <c r="W73" s="2"/>
-      <c r="AC73" s="2">
-        <v>1074</v>
-      </c>
-      <c r="AD73" s="2">
-        <v>-424</v>
-      </c>
-      <c r="AE73" s="2">
-        <v>3491</v>
-      </c>
-      <c r="AF73" s="2">
-        <f>AF16</f>
-        <v>2746</v>
-      </c>
-      <c r="AG73" s="2">
-        <f t="shared" ref="AG73:AP73" si="102">AG16</f>
-        <v>1922.1999999999998</v>
-      </c>
-      <c r="AH73" s="2">
-        <f t="shared" si="102"/>
-        <v>1345.5399999999997</v>
-      </c>
-      <c r="AI73" s="2">
-        <f t="shared" si="102"/>
-        <v>941.8779999999997</v>
-      </c>
-      <c r="AJ73" s="2">
-        <f t="shared" si="102"/>
-        <v>659.3145999999997</v>
-      </c>
-      <c r="AK73" s="2">
-        <f t="shared" si="102"/>
-        <v>461.52021999999977</v>
-      </c>
-      <c r="AL73" s="2">
-        <f t="shared" si="102"/>
-        <v>323.0641539999998</v>
-      </c>
-      <c r="AM73" s="2">
-        <f t="shared" si="102"/>
-        <v>226.14490779999986</v>
-      </c>
-      <c r="AN73" s="2">
-        <f t="shared" si="102"/>
-        <v>158.30143545999988</v>
-      </c>
-      <c r="AO73" s="2">
-        <f t="shared" si="102"/>
-        <v>110.81100482199992</v>
-      </c>
-      <c r="AP73" s="2">
-        <f t="shared" si="102"/>
-        <v>77.56770337539993</v>
-      </c>
-    </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.3">
-      <c r="B74" t="s">
-        <v>79</v>
-      </c>
-      <c r="L74" s="2">
-        <v>465</v>
-      </c>
-      <c r="M74" s="2">
-        <f t="shared" si="93"/>
-        <v>444</v>
-      </c>
-      <c r="N74" s="2">
-        <f t="shared" si="94"/>
-        <v>427</v>
-      </c>
-      <c r="O74" s="2">
-        <f t="shared" si="99"/>
-        <v>419</v>
-      </c>
-      <c r="P74" s="2">
-        <v>351</v>
-      </c>
-      <c r="Q74" s="2">
-        <f t="shared" si="95"/>
-        <v>366</v>
-      </c>
-      <c r="R74" s="2">
-        <f t="shared" si="96"/>
-        <v>364</v>
-      </c>
-      <c r="S74" s="2">
-        <f t="shared" si="100"/>
-        <v>347</v>
-      </c>
-      <c r="T74" s="2">
-        <v>249</v>
-      </c>
-      <c r="U74" s="2">
-        <f t="shared" si="97"/>
-        <v>225</v>
-      </c>
-      <c r="V74" s="2"/>
-      <c r="W74" s="2"/>
-      <c r="AC74" s="2">
-        <v>1907</v>
-      </c>
-      <c r="AD74" s="2">
-        <v>1755</v>
-      </c>
-      <c r="AE74" s="2">
-        <v>1428</v>
-      </c>
-      <c r="AF74" s="2">
-        <f>AE74*1.02</f>
-        <v>1456.56</v>
-      </c>
-      <c r="AG74" s="2">
-        <f t="shared" ref="AG74:AP74" si="103">AF74*1.02</f>
-        <v>1485.6912</v>
-      </c>
-      <c r="AH74" s="2">
-        <f t="shared" si="103"/>
-        <v>1515.4050239999999</v>
-      </c>
-      <c r="AI74" s="2">
-        <f t="shared" si="103"/>
-        <v>1545.71312448</v>
-      </c>
-      <c r="AJ74" s="2">
-        <f t="shared" si="103"/>
-        <v>1576.6273869696001</v>
-      </c>
-      <c r="AK74" s="2">
-        <f t="shared" si="103"/>
-        <v>1608.1599347089921</v>
-      </c>
-      <c r="AL74" s="2">
-        <f t="shared" si="103"/>
-        <v>1640.3231334031721</v>
-      </c>
-      <c r="AM74" s="2">
-        <f t="shared" si="103"/>
-        <v>1673.1295960712355</v>
-      </c>
-      <c r="AN74" s="2">
-        <f t="shared" si="103"/>
-        <v>1706.5921879926602</v>
-      </c>
-      <c r="AO74" s="2">
-        <f t="shared" si="103"/>
-        <v>1740.7240317525134</v>
-      </c>
-      <c r="AP74" s="2">
-        <f t="shared" si="103"/>
-        <v>1775.5385123875637</v>
-      </c>
-    </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.3">
-      <c r="B75" t="s">
-        <v>58</v>
-      </c>
-      <c r="L75" s="2">
-        <v>-167</v>
-      </c>
-      <c r="M75" s="2">
-        <f t="shared" si="93"/>
-        <v>21</v>
-      </c>
-      <c r="N75" s="2">
-        <f t="shared" si="94"/>
-        <v>193</v>
-      </c>
-      <c r="O75" s="2">
-        <f t="shared" si="99"/>
-        <v>-89</v>
-      </c>
-      <c r="P75" s="2">
-        <v>-208</v>
-      </c>
-      <c r="Q75" s="2">
-        <f t="shared" si="95"/>
-        <v>124</v>
-      </c>
-      <c r="R75" s="2">
-        <f t="shared" si="96"/>
-        <v>159</v>
-      </c>
-      <c r="S75" s="2">
-        <f t="shared" si="100"/>
         <v>-321</v>
       </c>
-      <c r="T75" s="2">
+      <c r="T83" s="2">
         <v>112</v>
       </c>
-      <c r="U75" s="2">
-        <f t="shared" si="97"/>
+      <c r="U83" s="2">
+        <f>U105-T83</f>
         <v>-502</v>
       </c>
-      <c r="V75" s="2"/>
-      <c r="W75" s="2"/>
-      <c r="AC75" s="2">
+      <c r="V83" s="2">
+        <f>V105-U83-T83</f>
+        <v>-221</v>
+      </c>
+      <c r="W83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="2">
         <f>-4254-1059</f>
         <v>-5313</v>
       </c>
-      <c r="AD75" s="2">
+      <c r="AD83" s="2">
         <v>-42</v>
       </c>
-      <c r="AE75" s="2">
+      <c r="AE83" s="2">
         <v>-246</v>
       </c>
-      <c r="AF75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP75" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.3">
-      <c r="B76" t="s">
+      <c r="AF83" s="2">
+        <f t="shared" si="93"/>
+        <v>-611</v>
+      </c>
+      <c r="AG83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP83" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
+        <v>111</v>
+      </c>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2"/>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" s="2"/>
+      <c r="Q84" s="2"/>
+      <c r="R84" s="2"/>
+      <c r="S84" s="2"/>
+      <c r="T84" s="2"/>
+      <c r="U84" s="2"/>
+      <c r="V84" s="2">
+        <f t="shared" ref="V84:V85" si="96">V106-U84-T84</f>
+        <v>1687</v>
+      </c>
+      <c r="W84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="2"/>
+      <c r="AD84" s="2"/>
+      <c r="AE84" s="2"/>
+      <c r="AF84" s="2">
+        <f t="shared" si="93"/>
+        <v>1687</v>
+      </c>
+      <c r="AG84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>112</v>
+      </c>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2"/>
+      <c r="R85" s="2"/>
+      <c r="S85" s="2"/>
+      <c r="T85" s="2"/>
+      <c r="U85" s="2"/>
+      <c r="V85" s="2">
+        <f t="shared" si="96"/>
+        <v>-5355</v>
+      </c>
+      <c r="W85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="2"/>
+      <c r="AD85" s="2"/>
+      <c r="AE85" s="2"/>
+      <c r="AF85" s="2">
+        <f t="shared" si="93"/>
+        <v>-5355</v>
+      </c>
+      <c r="AG85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
         <v>80</v>
       </c>
-      <c r="L76" s="2">
-        <f t="shared" ref="L76" si="104">L96-K76</f>
-        <v>0</v>
-      </c>
-      <c r="M76" s="2">
+      <c r="L86" s="2">
+        <f t="shared" ref="L86" si="97">L108-K86</f>
+        <v>0</v>
+      </c>
+      <c r="M86" s="2">
+        <f>M108-L86</f>
+        <v>0</v>
+      </c>
+      <c r="N86" s="2">
+        <f>N108-M86-L86</f>
+        <v>-1376</v>
+      </c>
+      <c r="O86" s="2">
+        <f t="shared" si="91"/>
+        <v>1376</v>
+      </c>
+      <c r="P86" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="2">
+        <f>Q108-P86</f>
+        <v>0</v>
+      </c>
+      <c r="R86" s="2">
+        <f>R108-Q86-P86</f>
+        <v>6368</v>
+      </c>
+      <c r="S86" s="2">
+        <f t="shared" si="92"/>
+        <v>-236</v>
+      </c>
+      <c r="T86" s="2">
+        <v>19</v>
+      </c>
+      <c r="U86" s="2">
+        <f>U108-T86</f>
+        <v>87</v>
+      </c>
+      <c r="V86" s="2">
+        <f>V108-U86-T86</f>
+        <v>17</v>
+      </c>
+      <c r="W86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="2">
+        <v>6132</v>
+      </c>
+      <c r="AF86" s="2">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="N76" s="2">
-        <f t="shared" si="94"/>
-        <v>-1376</v>
-      </c>
-      <c r="O76" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>81</v>
+      </c>
+      <c r="L87" s="2">
+        <f t="shared" ref="L87" si="98">L109-K87</f>
+        <v>0</v>
+      </c>
+      <c r="M87" s="2">
+        <f>M109-L87</f>
+        <v>0</v>
+      </c>
+      <c r="N87" s="2">
+        <f>N109-M87-L87</f>
+        <v>-87</v>
+      </c>
+      <c r="O87" s="2">
+        <f t="shared" si="91"/>
+        <v>87</v>
+      </c>
+      <c r="P87" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="2">
+        <f>Q109-P87</f>
+        <v>0</v>
+      </c>
+      <c r="R87" s="2">
+        <f>R109-Q87-P87</f>
+        <v>2290</v>
+      </c>
+      <c r="S87" s="2">
+        <f t="shared" si="92"/>
+        <v>-38</v>
+      </c>
+      <c r="T87" s="2">
+        <v>0</v>
+      </c>
+      <c r="U87" s="2">
+        <f>U109-T87</f>
+        <v>482</v>
+      </c>
+      <c r="V87" s="2">
+        <f>V109-U87-T87</f>
+        <v>-17</v>
+      </c>
+      <c r="W87" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="2">
+        <v>2252</v>
+      </c>
+      <c r="AF87" s="2">
+        <f t="shared" si="93"/>
+        <v>465</v>
+      </c>
+      <c r="AG87" s="2">
+        <f>AF87*0.8</f>
+        <v>372</v>
+      </c>
+      <c r="AH87" s="2">
+        <f t="shared" ref="AH87:AP87" si="99">AG87*0.8</f>
+        <v>297.60000000000002</v>
+      </c>
+      <c r="AI87" s="2">
         <f t="shared" si="99"/>
-        <v>1376</v>
-      </c>
-      <c r="P76" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="2">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-      <c r="R76" s="2">
-        <f t="shared" si="96"/>
-        <v>6368</v>
-      </c>
-      <c r="S76" s="2">
-        <f t="shared" si="100"/>
-        <v>-236</v>
-      </c>
-      <c r="T76" s="2">
-        <v>19</v>
-      </c>
-      <c r="U76" s="2">
-        <f t="shared" ref="U76:U83" si="105">U96-T76</f>
-        <v>87</v>
-      </c>
-      <c r="V76" s="2"/>
-      <c r="W76" s="2"/>
-      <c r="AC76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE76" s="2">
-        <v>6132</v>
-      </c>
-      <c r="AF76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP76" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.3">
-      <c r="B77" t="s">
-        <v>81</v>
-      </c>
-      <c r="L77" s="2">
-        <f t="shared" ref="L77" si="106">L97-K77</f>
-        <v>0</v>
-      </c>
-      <c r="M77" s="2">
+        <v>238.08000000000004</v>
+      </c>
+      <c r="AJ87" s="2">
+        <f t="shared" si="99"/>
+        <v>190.46400000000006</v>
+      </c>
+      <c r="AK87" s="2">
+        <f t="shared" si="99"/>
+        <v>152.37120000000004</v>
+      </c>
+      <c r="AL87" s="2">
+        <f t="shared" si="99"/>
+        <v>121.89696000000004</v>
+      </c>
+      <c r="AM87" s="2">
+        <f t="shared" si="99"/>
+        <v>97.51756800000004</v>
+      </c>
+      <c r="AN87" s="2">
+        <f t="shared" si="99"/>
+        <v>78.014054400000035</v>
+      </c>
+      <c r="AO87" s="2">
+        <f t="shared" si="99"/>
+        <v>62.411243520000028</v>
+      </c>
+      <c r="AP87" s="2">
+        <f t="shared" si="99"/>
+        <v>49.928994816000028</v>
+      </c>
+    </row>
+    <row r="88" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>59</v>
+      </c>
+      <c r="L88" s="2">
+        <v>286</v>
+      </c>
+      <c r="M88" s="2">
+        <f>M110-L88</f>
+        <v>851</v>
+      </c>
+      <c r="N88" s="2">
+        <f>N110-M88-L88</f>
+        <v>153</v>
+      </c>
+      <c r="O88" s="2">
+        <f t="shared" si="91"/>
+        <v>-559</v>
+      </c>
+      <c r="P88" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q88" s="2">
+        <f>Q110-P88</f>
+        <v>192</v>
+      </c>
+      <c r="R88" s="2">
+        <f>R110-Q88-P88</f>
+        <v>10</v>
+      </c>
+      <c r="S88" s="2">
+        <f t="shared" si="92"/>
+        <v>-357</v>
+      </c>
+      <c r="T88" s="2">
+        <v>414</v>
+      </c>
+      <c r="U88" s="2">
+        <f>U110-T88</f>
+        <v>590</v>
+      </c>
+      <c r="V88" s="2">
+        <f>V110-U88-T88</f>
+        <v>-842</v>
+      </c>
+      <c r="W88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="2">
+        <v>5327</v>
+      </c>
+      <c r="AD88" s="2">
+        <v>731</v>
+      </c>
+      <c r="AE88" s="2">
+        <v>-75</v>
+      </c>
+      <c r="AF88" s="2">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="2">
-        <f t="shared" si="94"/>
-        <v>-87</v>
-      </c>
-      <c r="O77" s="2">
-        <f t="shared" si="99"/>
-        <v>87</v>
-      </c>
-      <c r="P77" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="2">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-      <c r="R77" s="2">
-        <f t="shared" si="96"/>
-        <v>2290</v>
-      </c>
-      <c r="S77" s="2">
-        <f t="shared" si="100"/>
-        <v>-38</v>
-      </c>
-      <c r="T77" s="2">
-        <v>0</v>
-      </c>
-      <c r="U77" s="2">
-        <f t="shared" si="105"/>
-        <v>482</v>
-      </c>
-      <c r="V77" s="2"/>
-      <c r="W77" s="2"/>
-      <c r="AC77" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD77" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="2">
-        <v>2252</v>
-      </c>
-      <c r="AF77" s="2">
-        <f>AE77*0.5</f>
-        <v>1126</v>
-      </c>
-      <c r="AG77" s="2">
-        <f t="shared" ref="AG77:AP77" si="107">AF77*0.5</f>
-        <v>563</v>
-      </c>
-      <c r="AH77" s="2">
-        <f t="shared" si="107"/>
-        <v>281.5</v>
-      </c>
-      <c r="AI77" s="2">
-        <f t="shared" si="107"/>
-        <v>140.75</v>
-      </c>
-      <c r="AJ77" s="2">
-        <f t="shared" si="107"/>
-        <v>70.375</v>
-      </c>
-      <c r="AK77" s="2">
-        <f t="shared" si="107"/>
-        <v>35.1875</v>
-      </c>
-      <c r="AL77" s="2">
-        <f t="shared" si="107"/>
-        <v>17.59375</v>
-      </c>
-      <c r="AM77" s="2">
-        <f t="shared" si="107"/>
-        <v>8.796875</v>
-      </c>
-      <c r="AN77" s="2">
-        <f t="shared" si="107"/>
-        <v>4.3984375</v>
-      </c>
-      <c r="AO77" s="2">
-        <f t="shared" si="107"/>
-        <v>2.19921875</v>
-      </c>
-      <c r="AP77" s="2">
-        <f t="shared" si="107"/>
-        <v>1.099609375</v>
-      </c>
-    </row>
-    <row r="78" spans="2:42" x14ac:dyDescent="0.3">
-      <c r="B78" t="s">
-        <v>59</v>
-      </c>
-      <c r="L78" s="2">
-        <v>286</v>
-      </c>
-      <c r="M78" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
+        <v>60</v>
+      </c>
+      <c r="L89" s="2">
+        <v>231</v>
+      </c>
+      <c r="M89" s="2">
+        <f>M111-L89</f>
+        <v>1009</v>
+      </c>
+      <c r="N89" s="2">
+        <f>N111-M89-L89</f>
+        <v>518</v>
+      </c>
+      <c r="O89" s="2">
+        <f t="shared" si="91"/>
+        <v>339</v>
+      </c>
+      <c r="P89" s="2">
+        <v>-366</v>
+      </c>
+      <c r="Q89" s="2">
+        <f>Q111-P89</f>
+        <v>250</v>
+      </c>
+      <c r="R89" s="2">
+        <f>R111-Q89-P89</f>
+        <v>-853</v>
+      </c>
+      <c r="S89" s="2">
+        <f t="shared" si="92"/>
+        <v>-136</v>
+      </c>
+      <c r="T89" s="2">
+        <v>-83</v>
+      </c>
+      <c r="U89" s="2">
+        <f>U111-T89</f>
+        <v>182</v>
+      </c>
+      <c r="V89" s="2">
+        <f>V111-U89-T89</f>
+        <v>-108</v>
+      </c>
+      <c r="W89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="2">
+        <v>-2436</v>
+      </c>
+      <c r="AD89" s="2">
+        <v>2097</v>
+      </c>
+      <c r="AE89" s="2">
+        <v>-1105</v>
+      </c>
+      <c r="AF89" s="2">
         <f t="shared" si="93"/>
-        <v>851</v>
-      </c>
-      <c r="N78" s="2">
-        <f t="shared" si="94"/>
-        <v>153</v>
-      </c>
-      <c r="O78" s="2">
-        <f t="shared" si="99"/>
-        <v>-559</v>
-      </c>
-      <c r="P78" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q78" s="2">
-        <f t="shared" si="95"/>
-        <v>192</v>
-      </c>
-      <c r="R78" s="2">
-        <f t="shared" si="96"/>
-        <v>10</v>
-      </c>
-      <c r="S78" s="2">
-        <f t="shared" si="100"/>
-        <v>-357</v>
-      </c>
-      <c r="T78" s="2">
-        <v>414</v>
-      </c>
-      <c r="U78" s="2">
-        <f t="shared" si="105"/>
-        <v>590</v>
-      </c>
-      <c r="V78" s="2"/>
-      <c r="W78" s="2"/>
-      <c r="AC78" s="2">
-        <v>5327</v>
-      </c>
-      <c r="AD78" s="2">
-        <v>731</v>
-      </c>
-      <c r="AE78" s="2">
-        <v>-75</v>
-      </c>
-      <c r="AF78" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG78" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH78" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI78" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ78" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK78" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL78" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM78" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN78" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO78" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP78" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.3">
-      <c r="B79" t="s">
-        <v>60</v>
-      </c>
-      <c r="L79" s="2">
-        <v>231</v>
-      </c>
-      <c r="M79" s="2">
+        <v>-9</v>
+      </c>
+      <c r="AG89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR89" s="1"/>
+      <c r="AS89" s="1"/>
+    </row>
+    <row r="90" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>69</v>
+      </c>
+      <c r="L90" s="2">
+        <v>-771</v>
+      </c>
+      <c r="M90" s="2">
+        <f>M112-L90</f>
+        <v>-331</v>
+      </c>
+      <c r="N90" s="2">
+        <f>N112-M90-L90</f>
+        <v>20</v>
+      </c>
+      <c r="O90" s="2">
+        <f t="shared" si="91"/>
+        <v>281</v>
+      </c>
+      <c r="P90" s="2">
+        <v>-386</v>
+      </c>
+      <c r="Q90" s="2">
+        <f>Q112-P90</f>
+        <v>570</v>
+      </c>
+      <c r="R90" s="2">
+        <f>R112-Q90-P90</f>
+        <v>382</v>
+      </c>
+      <c r="S90" s="2">
+        <f t="shared" si="92"/>
+        <v>68</v>
+      </c>
+      <c r="T90" s="2">
+        <v>-240</v>
+      </c>
+      <c r="U90" s="2">
+        <f>U112-T90</f>
+        <v>354</v>
+      </c>
+      <c r="V90" s="2">
+        <f>V112-U90-T90</f>
+        <v>-395</v>
+      </c>
+      <c r="W90" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="2">
+        <v>-29</v>
+      </c>
+      <c r="AD90" s="2">
+        <v>-801</v>
+      </c>
+      <c r="AE90" s="2">
+        <v>634</v>
+      </c>
+      <c r="AF90" s="2">
         <f t="shared" si="93"/>
-        <v>1009</v>
-      </c>
-      <c r="N79" s="2">
-        <f t="shared" si="94"/>
-        <v>518</v>
-      </c>
-      <c r="O79" s="2">
-        <f t="shared" si="99"/>
-        <v>339</v>
-      </c>
-      <c r="P79" s="2">
-        <v>-366</v>
-      </c>
-      <c r="Q79" s="2">
-        <f t="shared" si="95"/>
-        <v>250</v>
-      </c>
-      <c r="R79" s="2">
-        <f t="shared" si="96"/>
-        <v>-853</v>
-      </c>
-      <c r="S79" s="2">
-        <f t="shared" si="100"/>
-        <v>-136</v>
-      </c>
-      <c r="T79" s="2">
-        <v>-83</v>
-      </c>
-      <c r="U79" s="2">
-        <f t="shared" si="105"/>
-        <v>182</v>
-      </c>
-      <c r="V79" s="2"/>
-      <c r="W79" s="2"/>
-      <c r="AC79" s="2">
-        <v>-2436</v>
-      </c>
-      <c r="AD79" s="2">
-        <v>2097</v>
-      </c>
-      <c r="AE79" s="2">
-        <v>-1105</v>
-      </c>
-      <c r="AF79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP79" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.3">
-      <c r="B80" t="s">
-        <v>69</v>
-      </c>
-      <c r="L80" s="2">
-        <v>-771</v>
-      </c>
-      <c r="M80" s="2">
+        <v>-281</v>
+      </c>
+      <c r="AG90" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI90" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK90" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM90" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN90" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO90" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP90" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B91" t="s">
+        <v>70</v>
+      </c>
+      <c r="L91" s="2">
+        <v>-1560</v>
+      </c>
+      <c r="M91" s="2">
+        <f>M113-L91</f>
+        <v>220</v>
+      </c>
+      <c r="N91" s="2">
+        <f>N113-M91-L91</f>
+        <v>169</v>
+      </c>
+      <c r="O91" s="2">
+        <f t="shared" si="91"/>
+        <v>557</v>
+      </c>
+      <c r="P91" s="2">
+        <v>-1289</v>
+      </c>
+      <c r="Q91" s="2">
+        <f>Q113-P91</f>
+        <v>-20</v>
+      </c>
+      <c r="R91" s="2">
+        <f>R113-Q91-P91</f>
+        <v>2693</v>
+      </c>
+      <c r="S91" s="2">
+        <f t="shared" si="92"/>
+        <v>-1602</v>
+      </c>
+      <c r="T91" s="2">
+        <v>-741</v>
+      </c>
+      <c r="U91" s="2">
+        <f>U113-T91</f>
+        <v>1763</v>
+      </c>
+      <c r="V91" s="2">
+        <f>V113-U91-T91</f>
+        <v>-481</v>
+      </c>
+      <c r="W91" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="2">
+        <v>-1533</v>
+      </c>
+      <c r="AD91" s="2">
+        <v>-614</v>
+      </c>
+      <c r="AE91" s="2">
+        <v>-218</v>
+      </c>
+      <c r="AF91" s="2">
         <f t="shared" si="93"/>
-        <v>-331</v>
-      </c>
-      <c r="N80" s="2">
-        <f t="shared" si="94"/>
-        <v>20</v>
-      </c>
-      <c r="O80" s="2">
-        <f t="shared" si="99"/>
-        <v>281</v>
-      </c>
-      <c r="P80" s="2">
-        <v>-386</v>
-      </c>
-      <c r="Q80" s="2">
-        <f t="shared" si="95"/>
-        <v>570</v>
-      </c>
-      <c r="R80" s="2">
-        <f t="shared" si="96"/>
-        <v>382</v>
-      </c>
-      <c r="S80" s="2">
-        <f t="shared" si="100"/>
-        <v>68</v>
-      </c>
-      <c r="T80" s="2">
-        <v>-240</v>
-      </c>
-      <c r="U80" s="2">
-        <f t="shared" si="105"/>
-        <v>354</v>
-      </c>
-      <c r="V80" s="2"/>
-      <c r="W80" s="2"/>
-      <c r="AC80" s="2">
-        <v>-29</v>
-      </c>
-      <c r="AD80" s="2">
-        <v>-801</v>
-      </c>
-      <c r="AE80" s="2">
-        <v>634</v>
-      </c>
-      <c r="AF80" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG80" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH80" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI80" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ80" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK80" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL80" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM80" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN80" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO80" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP80" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="B81" t="s">
-        <v>70</v>
-      </c>
-      <c r="L81" s="2">
-        <v>-1560</v>
-      </c>
-      <c r="M81" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG91" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO91" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP91" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR91" s="1"/>
+      <c r="AS91" s="1"/>
+    </row>
+    <row r="92" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>29</v>
+      </c>
+      <c r="L92" s="2">
+        <v>1344</v>
+      </c>
+      <c r="M92" s="2">
+        <f>M114-L92</f>
+        <v>-3530</v>
+      </c>
+      <c r="N92" s="2">
+        <f>N114-M92-L92</f>
+        <v>886</v>
+      </c>
+      <c r="O92" s="2">
+        <f t="shared" si="91"/>
+        <v>-2231</v>
+      </c>
+      <c r="P92" s="2">
+        <v>-591</v>
+      </c>
+      <c r="Q92" s="2">
+        <f>Q114-P92</f>
+        <v>-1583</v>
+      </c>
+      <c r="R92" s="2">
+        <f>R114-Q92-P92</f>
+        <v>1244</v>
+      </c>
+      <c r="S92" s="2">
+        <f t="shared" si="92"/>
+        <v>574</v>
+      </c>
+      <c r="T92" s="2">
+        <v>67</v>
+      </c>
+      <c r="U92" s="2">
+        <f>U114-T92</f>
+        <v>-1405</v>
+      </c>
+      <c r="V92" s="2">
+        <f>V114-U92-T92</f>
+        <v>142</v>
+      </c>
+      <c r="W92" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="2">
+        <v>-4535</v>
+      </c>
+      <c r="AD92" s="2">
+        <v>-3531</v>
+      </c>
+      <c r="AE92" s="2">
+        <v>-356</v>
+      </c>
+      <c r="AF92" s="2">
         <f t="shared" si="93"/>
-        <v>220</v>
-      </c>
-      <c r="N81" s="2">
-        <f t="shared" si="94"/>
-        <v>169</v>
-      </c>
-      <c r="O81" s="2">
-        <f t="shared" si="99"/>
-        <v>557</v>
-      </c>
-      <c r="P81" s="2">
-        <v>-1289</v>
-      </c>
-      <c r="Q81" s="2">
-        <f t="shared" si="95"/>
-        <v>-20</v>
-      </c>
-      <c r="R81" s="2">
-        <f t="shared" si="96"/>
-        <v>2693</v>
-      </c>
-      <c r="S81" s="2">
-        <f t="shared" si="100"/>
-        <v>-1602</v>
-      </c>
-      <c r="T81" s="2">
-        <v>-741</v>
-      </c>
-      <c r="U81" s="2">
-        <f t="shared" si="105"/>
-        <v>1763</v>
-      </c>
-      <c r="V81" s="2"/>
-      <c r="W81" s="2"/>
-      <c r="AC81" s="2">
-        <v>-1533</v>
-      </c>
-      <c r="AD81" s="2">
-        <v>-614</v>
-      </c>
-      <c r="AE81" s="2">
-        <v>-218</v>
-      </c>
-      <c r="AF81" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG81" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH81" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI81" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ81" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK81" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL81" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM81" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN81" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO81" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP81" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="B82" t="s">
-        <v>29</v>
-      </c>
-      <c r="L82" s="2">
-        <v>1344</v>
-      </c>
-      <c r="M82" s="2">
-        <f t="shared" si="93"/>
-        <v>-3530</v>
-      </c>
-      <c r="N82" s="2">
-        <f t="shared" si="94"/>
-        <v>886</v>
-      </c>
-      <c r="O82" s="2">
-        <f t="shared" si="99"/>
-        <v>-2231</v>
-      </c>
-      <c r="P82" s="2">
-        <v>-591</v>
-      </c>
-      <c r="Q82" s="2">
-        <f t="shared" si="95"/>
-        <v>-1583</v>
-      </c>
-      <c r="R82" s="2">
-        <f t="shared" si="96"/>
-        <v>1244</v>
-      </c>
-      <c r="S82" s="2">
-        <f t="shared" si="100"/>
-        <v>574</v>
-      </c>
-      <c r="T82" s="2">
-        <v>67</v>
-      </c>
-      <c r="U82" s="2">
-        <f t="shared" si="105"/>
-        <v>-1405</v>
-      </c>
-      <c r="V82" s="2"/>
-      <c r="W82" s="2"/>
-      <c r="AC82" s="2">
-        <v>-4535</v>
-      </c>
-      <c r="AD82" s="2">
-        <v>-3531</v>
-      </c>
-      <c r="AE82" s="2">
-        <v>-356</v>
-      </c>
-      <c r="AF82" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG82" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH82" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI82" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ82" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK82" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL82" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM82" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN82" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO82" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP82" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="B83" t="s">
+        <v>-1196</v>
+      </c>
+      <c r="AG92" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR92" s="1"/>
+      <c r="AS92" s="1"/>
+    </row>
+    <row r="93" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B93" t="s">
         <v>82</v>
       </c>
-      <c r="L83" s="2">
+      <c r="L93" s="2">
         <v>-1540</v>
       </c>
-      <c r="M83" s="2">
-        <f t="shared" si="93"/>
+      <c r="M93" s="2">
+        <f>M115-L93</f>
         <v>-303</v>
       </c>
-      <c r="N83" s="2">
-        <f t="shared" si="94"/>
+      <c r="N93" s="2">
+        <f>N115-M93-L93</f>
         <v>1356</v>
       </c>
-      <c r="O83" s="2">
-        <f t="shared" si="99"/>
+      <c r="O93" s="2">
+        <f t="shared" si="91"/>
         <v>36</v>
       </c>
-      <c r="P83" s="2">
+      <c r="P93" s="2">
         <v>-2104</v>
       </c>
-      <c r="Q83" s="2">
-        <f t="shared" si="95"/>
+      <c r="Q93" s="2">
+        <f>Q115-P93</f>
         <v>121</v>
       </c>
-      <c r="R83" s="2">
-        <f t="shared" si="96"/>
+      <c r="R93" s="2">
+        <f>R115-Q93-P93</f>
         <v>2003</v>
       </c>
-      <c r="S83" s="2">
-        <f t="shared" si="100"/>
+      <c r="S93" s="2">
+        <f t="shared" si="92"/>
         <v>2203</v>
       </c>
-      <c r="T83" s="2">
+      <c r="T93" s="2">
         <v>-1206</v>
       </c>
-      <c r="U83" s="2">
-        <f t="shared" si="105"/>
+      <c r="U93" s="2">
+        <f>U115-T93</f>
         <v>-536</v>
       </c>
-      <c r="V83" s="2"/>
-      <c r="W83" s="2"/>
-      <c r="AC83" s="2">
+      <c r="V93" s="2">
+        <f>V115-U93-T93</f>
+        <v>319</v>
+      </c>
+      <c r="W93" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="2">
         <f>-1278-24</f>
         <v>-1302</v>
       </c>
-      <c r="AD83" s="2">
+      <c r="AD93" s="2">
         <v>-451</v>
       </c>
-      <c r="AE83" s="2">
+      <c r="AE93" s="2">
         <v>2223</v>
       </c>
-      <c r="AF83" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG83" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH83" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI83" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ83" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK83" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL83" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM83" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN83" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO83" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP83" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="1" t="s">
+      <c r="AF93" s="2">
+        <f t="shared" si="93"/>
+        <v>-1423</v>
+      </c>
+      <c r="AG93" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L84" s="7">
-        <f t="shared" ref="L84:S84" si="108">L70+SUM(L71:L83)</f>
+      <c r="L94" s="7">
+        <f t="shared" ref="L94:S94" si="100">L78+SUM(L79:L93)</f>
         <v>-1775</v>
       </c>
-      <c r="M84" s="7">
+      <c r="M94" s="7">
+        <f t="shared" si="100"/>
+        <v>2816</v>
+      </c>
+      <c r="N94" s="7">
+        <f t="shared" si="100"/>
+        <v>5811</v>
+      </c>
+      <c r="O94" s="7">
+        <f t="shared" si="100"/>
+        <v>4903</v>
+      </c>
+      <c r="P94" s="7">
+        <f t="shared" si="100"/>
+        <v>-1167</v>
+      </c>
+      <c r="Q94" s="7">
+        <f t="shared" si="100"/>
+        <v>2336</v>
+      </c>
+      <c r="R94" s="7">
+        <f t="shared" si="100"/>
+        <v>4404</v>
+      </c>
+      <c r="S94" s="7">
+        <f t="shared" si="100"/>
+        <v>3192</v>
+      </c>
+      <c r="T94" s="7">
+        <f t="shared" ref="T94" si="101">T78+SUM(T79:T93)</f>
+        <v>879</v>
+      </c>
+      <c r="U94" s="7">
+        <f t="shared" ref="U94" si="102">U78+SUM(U79:U93)</f>
+        <v>2156</v>
+      </c>
+      <c r="V94" s="7">
+        <f t="shared" ref="V94:W94" si="103">V78+SUM(V79:V93)</f>
+        <v>2339</v>
+      </c>
+      <c r="W94" s="7">
+        <f t="shared" si="103"/>
+        <v>3140.8976800000023</v>
+      </c>
+      <c r="AC94" s="7">
+        <f>AC78+SUM(AC79:AC93)</f>
+        <v>15430</v>
+      </c>
+      <c r="AD94" s="7">
+        <f>AD78+SUM(AD79:AD93)</f>
+        <v>11755</v>
+      </c>
+      <c r="AE94" s="7">
+        <f>AE78+SUM(AE79:AE93)</f>
+        <v>8765</v>
+      </c>
+      <c r="AF94" s="7">
+        <f>AF78+SUM(AF79:AF93)</f>
+        <v>8514.8976799999982</v>
+      </c>
+      <c r="AG94" s="7">
+        <f t="shared" ref="AG94:AP94" si="104">AG78+SUM(AG79:AG93)</f>
+        <v>22156.788683999999</v>
+      </c>
+      <c r="AH94" s="7">
+        <f t="shared" si="104"/>
+        <v>23988.291382560001</v>
+      </c>
+      <c r="AI94" s="7">
+        <f t="shared" si="104"/>
+        <v>24660.653731445604</v>
+      </c>
+      <c r="AJ94" s="7">
+        <f t="shared" si="104"/>
+        <v>25205.570486848697</v>
+      </c>
+      <c r="AK94" s="7">
+        <f t="shared" si="104"/>
+        <v>25699.386339656448</v>
+      </c>
+      <c r="AL94" s="7">
+        <f t="shared" si="104"/>
+        <v>26270.743190532878</v>
+      </c>
+      <c r="AM94" s="7">
+        <f t="shared" si="104"/>
+        <v>26878.782357595075</v>
+      </c>
+      <c r="AN94" s="7">
+        <f t="shared" si="104"/>
+        <v>27520.417682696374</v>
+      </c>
+      <c r="AO94" s="7">
+        <f t="shared" si="104"/>
+        <v>28193.554666794586</v>
+      </c>
+      <c r="AP94" s="7">
+        <f t="shared" si="104"/>
+        <v>28896.824121968821</v>
+      </c>
+    </row>
+    <row r="95" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B95" t="s">
+        <v>63</v>
+      </c>
+      <c r="L95" s="2">
+        <v>7413</v>
+      </c>
+      <c r="M95" s="2">
+        <f>M117-L95</f>
+        <v>5888</v>
+      </c>
+      <c r="N95" s="2">
+        <f>N117-M95-L95</f>
+        <v>5753</v>
+      </c>
+      <c r="O95" s="2">
+        <f>AD95-N95-M95-L95</f>
+        <v>6696</v>
+      </c>
+      <c r="P95" s="2">
+        <v>5970</v>
+      </c>
+      <c r="Q95" s="2">
+        <f>Q117-P95</f>
+        <v>5682</v>
+      </c>
+      <c r="R95" s="2">
+        <f>R117-Q95-P95</f>
+        <v>6458</v>
+      </c>
+      <c r="S95" s="2">
+        <f t="shared" si="92"/>
+        <v>5834</v>
+      </c>
+      <c r="T95" s="2">
+        <v>5183</v>
+      </c>
+      <c r="U95" s="2">
+        <f>U117-T95</f>
+        <v>3550</v>
+      </c>
+      <c r="V95" s="2">
+        <f>V117-U95-T95</f>
+        <v>2785</v>
+      </c>
+      <c r="W95" s="2">
+        <v>3000</v>
+      </c>
+      <c r="AC95" s="2">
+        <v>24844</v>
+      </c>
+      <c r="AD95" s="2">
+        <v>25750</v>
+      </c>
+      <c r="AE95" s="2">
+        <v>23944</v>
+      </c>
+      <c r="AF95" s="2">
+        <f>SUM(T95:W95)</f>
+        <v>14518</v>
+      </c>
+      <c r="AG95" s="2">
+        <f>AF95*1.05</f>
+        <v>15243.900000000001</v>
+      </c>
+      <c r="AH95" s="2">
+        <f>AG95*1.03</f>
+        <v>15701.217000000002</v>
+      </c>
+      <c r="AI95" s="2">
+        <f t="shared" ref="AI95:AP95" si="105">AH95*1.03</f>
+        <v>16172.253510000002</v>
+      </c>
+      <c r="AJ95" s="2">
+        <f t="shared" si="105"/>
+        <v>16657.421115300003</v>
+      </c>
+      <c r="AK95" s="2">
+        <f>AJ95*1.02</f>
+        <v>16990.569537606003</v>
+      </c>
+      <c r="AL95" s="2">
+        <f t="shared" ref="AL95:AP95" si="106">AK95*1.02</f>
+        <v>17330.380928358125</v>
+      </c>
+      <c r="AM95" s="2">
+        <f t="shared" si="106"/>
+        <v>17676.988546925288</v>
+      </c>
+      <c r="AN95" s="2">
+        <f t="shared" si="106"/>
+        <v>18030.528317863795</v>
+      </c>
+      <c r="AO95" s="2">
+        <f t="shared" si="106"/>
+        <v>18391.138884221073</v>
+      </c>
+      <c r="AP95" s="2">
+        <f t="shared" si="106"/>
+        <v>18758.961661905494</v>
+      </c>
+    </row>
+    <row r="96" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B96" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L96" s="7">
+        <f>L94-L95</f>
+        <v>-9188</v>
+      </c>
+      <c r="M96" s="7">
+        <f t="shared" ref="M96:S96" si="107">M94-M95</f>
+        <v>-3072</v>
+      </c>
+      <c r="N96" s="7">
+        <f t="shared" si="107"/>
+        <v>58</v>
+      </c>
+      <c r="O96" s="7">
+        <f t="shared" si="107"/>
+        <v>-1793</v>
+      </c>
+      <c r="P96" s="7">
+        <f t="shared" si="107"/>
+        <v>-7137</v>
+      </c>
+      <c r="Q96" s="7">
+        <f t="shared" si="107"/>
+        <v>-3346</v>
+      </c>
+      <c r="R96" s="7">
+        <f t="shared" si="107"/>
+        <v>-2054</v>
+      </c>
+      <c r="S96" s="7">
+        <f t="shared" si="107"/>
+        <v>-2642</v>
+      </c>
+      <c r="T96" s="7">
+        <f t="shared" ref="T96:W96" si="108">T94-T95</f>
+        <v>-4304</v>
+      </c>
+      <c r="U96" s="7">
         <f t="shared" si="108"/>
-        <v>2816</v>
-      </c>
-      <c r="N84" s="7">
+        <v>-1394</v>
+      </c>
+      <c r="V96" s="7">
         <f t="shared" si="108"/>
-        <v>5811</v>
-      </c>
-      <c r="O84" s="7">
+        <v>-446</v>
+      </c>
+      <c r="W96" s="7">
         <f t="shared" si="108"/>
-        <v>4903</v>
-      </c>
-      <c r="P84" s="7">
-        <f t="shared" si="108"/>
-        <v>-1167</v>
-      </c>
-      <c r="Q84" s="7">
-        <f t="shared" si="108"/>
-        <v>2336</v>
-      </c>
-      <c r="R84" s="7">
-        <f t="shared" si="108"/>
-        <v>4404</v>
-      </c>
-      <c r="S84" s="7">
-        <f t="shared" si="108"/>
-        <v>3192</v>
-      </c>
-      <c r="T84" s="7">
-        <f t="shared" ref="T84" si="109">T70+SUM(T71:T83)</f>
-        <v>879</v>
-      </c>
-      <c r="U84" s="7">
-        <f t="shared" ref="U84" si="110">U70+SUM(U71:U83)</f>
-        <v>2156</v>
-      </c>
-      <c r="V84" s="7"/>
-      <c r="W84" s="7"/>
-      <c r="AC84" s="7">
-        <f>AC70+SUM(AC71:AC83)</f>
-        <v>15430</v>
-      </c>
-      <c r="AD84" s="7">
-        <f>AD70+SUM(AD71:AD83)</f>
-        <v>11755</v>
-      </c>
-      <c r="AE84" s="7">
-        <f>AE70+SUM(AE71:AE83)</f>
-        <v>8765</v>
-      </c>
-      <c r="AF84" s="7">
-        <f>AF70+SUM(AF71:AF83)</f>
-        <v>12923.020839999997</v>
-      </c>
-      <c r="AG84" s="7">
-        <f t="shared" ref="AG84:AP84" si="111">AG70+SUM(AG71:AG83)</f>
-        <v>17838.481962999998</v>
-      </c>
-      <c r="AH84" s="7">
-        <f t="shared" si="111"/>
-        <v>19568.749217455999</v>
-      </c>
-      <c r="AI84" s="7">
-        <f t="shared" si="111"/>
-        <v>20284.829470102999</v>
-      </c>
-      <c r="AJ84" s="7">
-        <f t="shared" si="111"/>
-        <v>20939.559064765941</v>
-      </c>
-      <c r="AK84" s="7">
-        <f t="shared" si="111"/>
-        <v>21464.623173183223</v>
-      </c>
-      <c r="AL84" s="7">
-        <f t="shared" si="111"/>
-        <v>22079.036895655649</v>
-      </c>
-      <c r="AM84" s="7">
-        <f t="shared" si="111"/>
-        <v>22732.912613382476</v>
-      </c>
-      <c r="AN84" s="7">
-        <f t="shared" si="111"/>
-        <v>23419.572174395624</v>
-      </c>
-      <c r="AO84" s="7">
-        <f t="shared" si="111"/>
-        <v>24135.41630126589</v>
-      </c>
-      <c r="AP84" s="7">
-        <f t="shared" si="111"/>
-        <v>24878.567515217514</v>
-      </c>
-    </row>
-    <row r="85" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="B85" t="s">
-        <v>63</v>
-      </c>
-      <c r="L85" s="2">
-        <v>7413</v>
-      </c>
-      <c r="M85" s="2">
-        <f>M105-L85</f>
-        <v>5888</v>
-      </c>
-      <c r="N85" s="2">
-        <f>N105-M85-L85</f>
-        <v>5753</v>
-      </c>
-      <c r="O85" s="2">
-        <f>AD85-N85-M85-L85</f>
-        <v>6696</v>
-      </c>
-      <c r="P85" s="2">
-        <v>5970</v>
-      </c>
-      <c r="Q85" s="2">
-        <f>Q105-P85</f>
-        <v>5682</v>
-      </c>
-      <c r="R85" s="2">
-        <f>R105-Q85-P85</f>
-        <v>6458</v>
-      </c>
-      <c r="S85" s="2">
-        <f t="shared" si="100"/>
-        <v>5834</v>
-      </c>
-      <c r="T85" s="2">
-        <v>5183</v>
-      </c>
-      <c r="U85" s="2">
-        <f>U105-T85</f>
-        <v>3550</v>
-      </c>
-      <c r="V85" s="2"/>
-      <c r="W85" s="2"/>
-      <c r="AC85" s="2">
-        <v>24844</v>
-      </c>
-      <c r="AD85" s="2">
-        <v>25750</v>
-      </c>
-      <c r="AE85" s="2">
-        <v>23944</v>
-      </c>
-      <c r="AF85" s="2">
-        <v>18000</v>
-      </c>
-      <c r="AG85" s="2">
-        <f>AF85*0.98</f>
-        <v>17640</v>
-      </c>
-      <c r="AH85" s="2">
-        <f t="shared" ref="AH85:AI85" si="112">AG85*0.98</f>
-        <v>17287.2</v>
-      </c>
-      <c r="AI85" s="2">
-        <f t="shared" si="112"/>
-        <v>16941.456000000002</v>
-      </c>
-      <c r="AJ85" s="2">
-        <f t="shared" ref="AJ85:AP85" si="113">AI85*0.99</f>
-        <v>16772.041440000001</v>
-      </c>
-      <c r="AK85" s="2">
-        <f t="shared" si="113"/>
-        <v>16604.321025600002</v>
-      </c>
-      <c r="AL85" s="2">
-        <f t="shared" si="113"/>
-        <v>16438.277815344001</v>
-      </c>
-      <c r="AM85" s="2">
-        <f t="shared" si="113"/>
-        <v>16273.895037190561</v>
-      </c>
-      <c r="AN85" s="2">
-        <f t="shared" si="113"/>
-        <v>16111.156086818655</v>
-      </c>
-      <c r="AO85" s="2">
-        <f t="shared" si="113"/>
-        <v>15950.044525950469</v>
-      </c>
-      <c r="AP85" s="2">
-        <f t="shared" si="113"/>
-        <v>15790.544080690965</v>
-      </c>
-    </row>
-    <row r="86" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L86" s="7">
-        <f>L84-L85</f>
-        <v>-9188</v>
-      </c>
-      <c r="M86" s="7">
-        <f t="shared" ref="M86:S86" si="114">M84-M85</f>
-        <v>-3072</v>
-      </c>
-      <c r="N86" s="7">
-        <f t="shared" si="114"/>
-        <v>58</v>
-      </c>
-      <c r="O86" s="7">
-        <f t="shared" si="114"/>
-        <v>-1793</v>
-      </c>
-      <c r="P86" s="7">
-        <f t="shared" si="114"/>
-        <v>-7137</v>
-      </c>
-      <c r="Q86" s="7">
-        <f t="shared" si="114"/>
-        <v>-3346</v>
-      </c>
-      <c r="R86" s="7">
-        <f t="shared" si="114"/>
-        <v>-2054</v>
-      </c>
-      <c r="S86" s="7">
-        <f t="shared" si="114"/>
-        <v>-2642</v>
-      </c>
-      <c r="T86" s="7">
-        <f t="shared" ref="T86:U86" si="115">T84-T85</f>
-        <v>-4304</v>
-      </c>
-      <c r="U86" s="7">
-        <f t="shared" si="115"/>
-        <v>-1394</v>
-      </c>
-      <c r="V86" s="7"/>
-      <c r="W86" s="7"/>
-      <c r="AC86" s="7">
-        <f t="shared" ref="AC86" si="116">AC84-AC85</f>
+        <v>140.89768000000231</v>
+      </c>
+      <c r="AC96" s="7">
+        <f t="shared" ref="AC96" si="109">AC94-AC95</f>
         <v>-9414</v>
       </c>
-      <c r="AD86" s="7">
-        <f t="shared" ref="AD86" si="117">AD84-AD85</f>
+      <c r="AD96" s="7">
+        <f t="shared" ref="AD96" si="110">AD94-AD95</f>
         <v>-13995</v>
       </c>
-      <c r="AE86" s="7">
-        <f t="shared" ref="AE86" si="118">AE84-AE85</f>
+      <c r="AE96" s="7">
+        <f t="shared" ref="AE96" si="111">AE94-AE95</f>
         <v>-15179</v>
       </c>
-      <c r="AF86" s="7">
-        <f t="shared" ref="AF86" si="119">AF84-AF85</f>
-        <v>-5076.9791600000026</v>
-      </c>
-      <c r="AG86" s="7">
-        <f t="shared" ref="AG86" si="120">AG84-AG85</f>
-        <v>198.48196299999836</v>
-      </c>
-      <c r="AH86" s="7">
-        <f t="shared" ref="AH86" si="121">AH84-AH85</f>
-        <v>2281.5492174559986</v>
-      </c>
-      <c r="AI86" s="7">
-        <f t="shared" ref="AI86" si="122">AI84-AI85</f>
-        <v>3343.3734701029971</v>
-      </c>
-      <c r="AJ86" s="7">
-        <f t="shared" ref="AJ86" si="123">AJ84-AJ85</f>
-        <v>4167.5176247659401</v>
-      </c>
-      <c r="AK86" s="7">
-        <f t="shared" ref="AK86" si="124">AK84-AK85</f>
-        <v>4860.3021475832211</v>
-      </c>
-      <c r="AL86" s="7">
-        <f t="shared" ref="AL86" si="125">AL84-AL85</f>
-        <v>5640.7590803116473</v>
-      </c>
-      <c r="AM86" s="7">
-        <f t="shared" ref="AM86" si="126">AM84-AM85</f>
-        <v>6459.0175761919145</v>
-      </c>
-      <c r="AN86" s="7">
-        <f t="shared" ref="AN86" si="127">AN84-AN85</f>
-        <v>7308.4160875769685</v>
-      </c>
-      <c r="AO86" s="7">
-        <f t="shared" ref="AO86" si="128">AO84-AO85</f>
-        <v>8185.3717753154215</v>
-      </c>
-      <c r="AP86" s="7">
-        <f t="shared" ref="AP86" si="129">AP84-AP85</f>
-        <v>9088.023434526549</v>
-      </c>
-      <c r="AQ86" s="1">
-        <f>AP86*(1+$AS$88)</f>
-        <v>8997.1432001812827</v>
-      </c>
-      <c r="AR86" s="1">
-        <f t="shared" ref="AR86:DC86" si="130">AQ86*(1+$AS$88)</f>
-        <v>8907.1717681794689</v>
-      </c>
-      <c r="AS86" s="1">
-        <f t="shared" si="130"/>
-        <v>8818.1000504976746</v>
-      </c>
-      <c r="AT86" s="1">
-        <f t="shared" si="130"/>
-        <v>8729.9190499926972</v>
-      </c>
-      <c r="AU86" s="1">
-        <f t="shared" si="130"/>
-        <v>8642.61985949277</v>
-      </c>
-      <c r="AV86" s="1">
-        <f t="shared" si="130"/>
-        <v>8556.1936608978431</v>
-      </c>
-      <c r="AW86" s="1">
-        <f t="shared" si="130"/>
-        <v>8470.6317242888654</v>
-      </c>
-      <c r="AX86" s="1">
-        <f t="shared" si="130"/>
-        <v>8385.9254070459774</v>
-      </c>
-      <c r="AY86" s="1">
-        <f t="shared" si="130"/>
-        <v>8302.066152975518</v>
-      </c>
-      <c r="AZ86" s="1">
-        <f t="shared" si="130"/>
-        <v>8219.0454914457623</v>
-      </c>
-      <c r="BA86" s="1">
-        <f t="shared" si="130"/>
-        <v>8136.8550365313049</v>
-      </c>
-      <c r="BB86" s="1">
-        <f t="shared" si="130"/>
-        <v>8055.4864861659917</v>
-      </c>
-      <c r="BC86" s="1">
-        <f t="shared" si="130"/>
-        <v>7974.9316213043321</v>
-      </c>
-      <c r="BD86" s="1">
-        <f t="shared" si="130"/>
-        <v>7895.182305091289</v>
-      </c>
-      <c r="BE86" s="1">
-        <f t="shared" si="130"/>
-        <v>7816.230482040376</v>
-      </c>
-      <c r="BF86" s="1">
-        <f t="shared" si="130"/>
-        <v>7738.0681772199723</v>
-      </c>
-      <c r="BG86" s="1">
-        <f t="shared" si="130"/>
-        <v>7660.6874954477726</v>
-      </c>
-      <c r="BH86" s="1">
-        <f t="shared" si="130"/>
-        <v>7584.0806204932951</v>
-      </c>
-      <c r="BI86" s="1">
-        <f t="shared" si="130"/>
-        <v>7508.2398142883621</v>
-      </c>
-      <c r="BJ86" s="1">
-        <f t="shared" si="130"/>
-        <v>7433.1574161454782</v>
-      </c>
-      <c r="BK86" s="1">
-        <f t="shared" si="130"/>
-        <v>7358.8258419840231</v>
-      </c>
-      <c r="BL86" s="1">
-        <f t="shared" si="130"/>
-        <v>7285.2375835641824</v>
-      </c>
-      <c r="BM86" s="1">
-        <f t="shared" si="130"/>
-        <v>7212.3852077285401</v>
-      </c>
-      <c r="BN86" s="1">
-        <f t="shared" si="130"/>
-        <v>7140.2613556512542</v>
-      </c>
-      <c r="BO86" s="1">
-        <f t="shared" si="130"/>
-        <v>7068.8587420947415</v>
-      </c>
-      <c r="BP86" s="1">
-        <f t="shared" si="130"/>
-        <v>6998.1701546737941</v>
-      </c>
-      <c r="BQ86" s="1">
-        <f t="shared" si="130"/>
-        <v>6928.1884531270562</v>
-      </c>
-      <c r="BR86" s="1">
-        <f t="shared" si="130"/>
-        <v>6858.9065685957858</v>
-      </c>
-      <c r="BS86" s="1">
-        <f t="shared" si="130"/>
-        <v>6790.3175029098275</v>
-      </c>
-      <c r="BT86" s="1">
-        <f t="shared" si="130"/>
-        <v>6722.4143278807287</v>
-      </c>
-      <c r="BU86" s="1">
-        <f t="shared" si="130"/>
-        <v>6655.1901846019209</v>
-      </c>
-      <c r="BV86" s="1">
-        <f t="shared" si="130"/>
-        <v>6588.6382827559019</v>
-      </c>
-      <c r="BW86" s="1">
-        <f t="shared" si="130"/>
-        <v>6522.7518999283429</v>
-      </c>
-      <c r="BX86" s="1">
-        <f t="shared" si="130"/>
-        <v>6457.5243809290596</v>
-      </c>
-      <c r="BY86" s="1">
-        <f t="shared" si="130"/>
-        <v>6392.9491371197691</v>
-      </c>
-      <c r="BZ86" s="1">
-        <f t="shared" si="130"/>
-        <v>6329.0196457485717</v>
-      </c>
-      <c r="CA86" s="1">
-        <f t="shared" si="130"/>
-        <v>6265.729449291086</v>
-      </c>
-      <c r="CB86" s="1">
-        <f t="shared" si="130"/>
-        <v>6203.0721547981748</v>
-      </c>
-      <c r="CC86" s="1">
-        <f t="shared" si="130"/>
-        <v>6141.0414332501932</v>
-      </c>
-      <c r="CD86" s="1">
-        <f t="shared" si="130"/>
-        <v>6079.6310189176911</v>
-      </c>
-      <c r="CE86" s="1">
-        <f t="shared" si="130"/>
-        <v>6018.8347087285138</v>
-      </c>
-      <c r="CF86" s="1">
-        <f t="shared" si="130"/>
-        <v>5958.6463616412284</v>
-      </c>
-      <c r="CG86" s="1">
-        <f t="shared" si="130"/>
-        <v>5899.059898024816</v>
-      </c>
-      <c r="CH86" s="1">
-        <f t="shared" si="130"/>
-        <v>5840.0692990445677</v>
-      </c>
-      <c r="CI86" s="1">
-        <f t="shared" si="130"/>
-        <v>5781.6686060541224</v>
-      </c>
-      <c r="CJ86" s="1">
-        <f t="shared" si="130"/>
-        <v>5723.8519199935809</v>
-      </c>
-      <c r="CK86" s="1">
-        <f t="shared" si="130"/>
-        <v>5666.6134007936453</v>
-      </c>
-      <c r="CL86" s="1">
-        <f t="shared" si="130"/>
-        <v>5609.947266785709</v>
-      </c>
-      <c r="CM86" s="1">
-        <f t="shared" si="130"/>
-        <v>5553.8477941178517</v>
-      </c>
-      <c r="CN86" s="1">
-        <f t="shared" si="130"/>
-        <v>5498.3093161766728</v>
-      </c>
-      <c r="CO86" s="1">
-        <f t="shared" si="130"/>
-        <v>5443.3262230149057</v>
-      </c>
-      <c r="CP86" s="1">
-        <f t="shared" si="130"/>
-        <v>5388.8929607847567</v>
-      </c>
-      <c r="CQ86" s="1">
-        <f t="shared" si="130"/>
-        <v>5335.0040311769089</v>
-      </c>
-      <c r="CR86" s="1">
-        <f t="shared" si="130"/>
-        <v>5281.6539908651393</v>
-      </c>
-      <c r="CS86" s="1">
-        <f t="shared" si="130"/>
-        <v>5228.8374509564883</v>
-      </c>
-      <c r="CT86" s="1">
-        <f t="shared" si="130"/>
-        <v>5176.5490764469232</v>
-      </c>
-      <c r="CU86" s="1">
-        <f t="shared" si="130"/>
-        <v>5124.783585682454</v>
-      </c>
-      <c r="CV86" s="1">
-        <f t="shared" si="130"/>
-        <v>5073.5357498256299</v>
-      </c>
-      <c r="CW86" s="1">
-        <f t="shared" si="130"/>
-        <v>5022.8003923273736</v>
-      </c>
-      <c r="CX86" s="1">
-        <f t="shared" si="130"/>
-        <v>4972.5723884040999</v>
-      </c>
-      <c r="CY86" s="1">
-        <f t="shared" si="130"/>
-        <v>4922.8466645200588</v>
-      </c>
-      <c r="CZ86" s="1">
-        <f t="shared" si="130"/>
-        <v>4873.6181978748582</v>
-      </c>
-      <c r="DA86" s="1">
-        <f t="shared" si="130"/>
-        <v>4824.8820158961098</v>
-      </c>
-      <c r="DB86" s="1">
-        <f t="shared" si="130"/>
-        <v>4776.6331957371485</v>
-      </c>
-      <c r="DC86" s="1">
-        <f t="shared" si="130"/>
-        <v>4728.8668637797773</v>
-      </c>
-      <c r="DD86" s="1">
-        <f t="shared" ref="DD86:EN86" si="131">DC86*(1+$AS$88)</f>
-        <v>4681.5781951419794</v>
-      </c>
-      <c r="DE86" s="1">
-        <f t="shared" si="131"/>
-        <v>4634.7624131905595</v>
-      </c>
-      <c r="DF86" s="1">
-        <f t="shared" si="131"/>
-        <v>4588.4147890586537</v>
-      </c>
-      <c r="DG86" s="1">
-        <f t="shared" si="131"/>
-        <v>4542.5306411680667</v>
-      </c>
-      <c r="DH86" s="1">
-        <f t="shared" si="131"/>
-        <v>4497.1053347563857</v>
-      </c>
-      <c r="DI86" s="1">
-        <f t="shared" si="131"/>
-        <v>4452.1342814088221</v>
-      </c>
-      <c r="DJ86" s="1">
-        <f t="shared" si="131"/>
-        <v>4407.6129385947334</v>
-      </c>
-      <c r="DK86" s="1">
-        <f t="shared" si="131"/>
-        <v>4363.5368092087856</v>
-      </c>
-      <c r="DL86" s="1">
-        <f t="shared" si="131"/>
-        <v>4319.9014411166982</v>
-      </c>
-      <c r="DM86" s="1">
-        <f t="shared" si="131"/>
-        <v>4276.7024267055313</v>
-      </c>
-      <c r="DN86" s="1">
-        <f t="shared" si="131"/>
-        <v>4233.9354024384756</v>
-      </c>
-      <c r="DO86" s="1">
-        <f t="shared" si="131"/>
-        <v>4191.5960484140905</v>
-      </c>
-      <c r="DP86" s="1">
-        <f t="shared" si="131"/>
-        <v>4149.6800879299499</v>
-      </c>
-      <c r="DQ86" s="1">
-        <f t="shared" si="131"/>
-        <v>4108.1832870506505</v>
-      </c>
-      <c r="DR86" s="1">
-        <f t="shared" si="131"/>
-        <v>4067.1014541801442</v>
-      </c>
-      <c r="DS86" s="1">
-        <f t="shared" si="131"/>
-        <v>4026.4304396383427</v>
-      </c>
-      <c r="DT86" s="1">
-        <f t="shared" si="131"/>
-        <v>3986.1661352419592</v>
-      </c>
-      <c r="DU86" s="1">
-        <f t="shared" si="131"/>
-        <v>3946.3044738895396</v>
-      </c>
-      <c r="DV86" s="1">
-        <f t="shared" si="131"/>
-        <v>3906.8414291506442</v>
-      </c>
-      <c r="DW86" s="1">
-        <f t="shared" si="131"/>
-        <v>3867.7730148591377</v>
-      </c>
-      <c r="DX86" s="1">
-        <f t="shared" si="131"/>
-        <v>3829.0952847105464</v>
-      </c>
-      <c r="DY86" s="1">
-        <f t="shared" si="131"/>
-        <v>3790.8043318634409</v>
-      </c>
-      <c r="DZ86" s="1">
-        <f t="shared" si="131"/>
-        <v>3752.8962885448063</v>
-      </c>
-      <c r="EA86" s="1">
-        <f t="shared" si="131"/>
-        <v>3715.3673256593584</v>
-      </c>
-      <c r="EB86" s="1">
-        <f t="shared" si="131"/>
-        <v>3678.2136524027646</v>
-      </c>
-      <c r="EC86" s="1">
-        <f t="shared" si="131"/>
-        <v>3641.4315158787372</v>
-      </c>
-      <c r="ED86" s="1">
-        <f t="shared" si="131"/>
-        <v>3605.0172007199499</v>
-      </c>
-      <c r="EE86" s="1">
-        <f t="shared" si="131"/>
-        <v>3568.9670287127506</v>
-      </c>
-      <c r="EF86" s="1">
-        <f t="shared" si="131"/>
-        <v>3533.2773584256229</v>
-      </c>
-      <c r="EG86" s="1">
-        <f t="shared" si="131"/>
-        <v>3497.9445848413666</v>
-      </c>
-      <c r="EH86" s="1">
-        <f t="shared" si="131"/>
-        <v>3462.9651389929527</v>
-      </c>
-      <c r="EI86" s="1">
-        <f t="shared" si="131"/>
-        <v>3428.335487603023</v>
-      </c>
-      <c r="EJ86" s="1">
-        <f t="shared" si="131"/>
-        <v>3394.0521327269926</v>
-      </c>
-      <c r="EK86" s="1">
-        <f t="shared" si="131"/>
-        <v>3360.1116113997227</v>
-      </c>
-      <c r="EL86" s="1">
-        <f t="shared" si="131"/>
-        <v>3326.5104952857255</v>
-      </c>
-      <c r="EM86" s="1">
-        <f t="shared" si="131"/>
-        <v>3293.2453903328683</v>
-      </c>
-      <c r="EN86" s="1">
-        <f t="shared" si="131"/>
-        <v>3260.3129364295396</v>
-      </c>
-    </row>
-    <row r="87" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L87" s="7"/>
-      <c r="M87" s="7"/>
-      <c r="N87" s="7"/>
-      <c r="O87" s="7"/>
-      <c r="P87" s="7"/>
-      <c r="Q87" s="7"/>
-      <c r="R87" s="7"/>
-      <c r="S87" s="7"/>
-      <c r="T87" s="7"/>
-      <c r="U87" s="7"/>
-      <c r="V87" s="7"/>
-      <c r="W87" s="7"/>
-      <c r="AC87" s="7"/>
-      <c r="AD87" s="7"/>
-      <c r="AE87" s="7"/>
-    </row>
-    <row r="88" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B88" t="s">
+      <c r="AF96" s="7">
+        <f t="shared" ref="AF96" si="112">AF94-AF95</f>
+        <v>-6003.1023200000018</v>
+      </c>
+      <c r="AG96" s="7">
+        <f t="shared" ref="AG96" si="113">AG94-AG95</f>
+        <v>6912.8886839999977</v>
+      </c>
+      <c r="AH96" s="7">
+        <f t="shared" ref="AH96" si="114">AH94-AH95</f>
+        <v>8287.0743825599984</v>
+      </c>
+      <c r="AI96" s="7">
+        <f t="shared" ref="AI96" si="115">AI94-AI95</f>
+        <v>8488.4002214456013</v>
+      </c>
+      <c r="AJ96" s="7">
+        <f t="shared" ref="AJ96" si="116">AJ94-AJ95</f>
+        <v>8548.149371548694</v>
+      </c>
+      <c r="AK96" s="7">
+        <f t="shared" ref="AK96" si="117">AK94-AK95</f>
+        <v>8708.8168020504454</v>
+      </c>
+      <c r="AL96" s="7">
+        <f t="shared" ref="AL96" si="118">AL94-AL95</f>
+        <v>8940.3622621747527</v>
+      </c>
+      <c r="AM96" s="7">
+        <f t="shared" ref="AM96" si="119">AM94-AM95</f>
+        <v>9201.7938106697875</v>
+      </c>
+      <c r="AN96" s="7">
+        <f t="shared" ref="AN96" si="120">AN94-AN95</f>
+        <v>9489.8893648325793</v>
+      </c>
+      <c r="AO96" s="7">
+        <f t="shared" ref="AO96" si="121">AO94-AO95</f>
+        <v>9802.4157825735128</v>
+      </c>
+      <c r="AP96" s="7">
+        <f t="shared" ref="AP96" si="122">AP94-AP95</f>
+        <v>10137.862460063327</v>
+      </c>
+      <c r="AQ96" s="1">
+        <f>AP96*(1+$AS$100)</f>
+        <v>10036.483835462694</v>
+      </c>
+      <c r="AR96" s="1">
+        <f t="shared" ref="AR96:DC96" si="123">AQ96*(1+$AS$100)</f>
+        <v>9936.1189971080657</v>
+      </c>
+      <c r="AS96" s="1">
+        <f t="shared" si="123"/>
+        <v>9836.7578071369844</v>
+      </c>
+      <c r="AT96" s="1">
+        <f t="shared" si="123"/>
+        <v>9738.3902290656151</v>
+      </c>
+      <c r="AU96" s="1">
+        <f t="shared" si="123"/>
+        <v>9641.0063267749592</v>
+      </c>
+      <c r="AV96" s="1">
+        <f t="shared" si="123"/>
+        <v>9544.5962635072101</v>
+      </c>
+      <c r="AW96" s="1">
+        <f t="shared" si="123"/>
+        <v>9449.1503008721374</v>
+      </c>
+      <c r="AX96" s="1">
+        <f t="shared" si="123"/>
+        <v>9354.6587978634161</v>
+      </c>
+      <c r="AY96" s="1">
+        <f t="shared" si="123"/>
+        <v>9261.1122098847827</v>
+      </c>
+      <c r="AZ96" s="1">
+        <f t="shared" si="123"/>
+        <v>9168.5010877859349</v>
+      </c>
+      <c r="BA96" s="1">
+        <f t="shared" si="123"/>
+        <v>9076.816076908075</v>
+      </c>
+      <c r="BB96" s="1">
+        <f t="shared" si="123"/>
+        <v>8986.047916138994</v>
+      </c>
+      <c r="BC96" s="1">
+        <f t="shared" si="123"/>
+        <v>8896.1874369776033</v>
+      </c>
+      <c r="BD96" s="1">
+        <f t="shared" si="123"/>
+        <v>8807.2255626078277</v>
+      </c>
+      <c r="BE96" s="1">
+        <f t="shared" si="123"/>
+        <v>8719.1533069817488</v>
+      </c>
+      <c r="BF96" s="1">
+        <f t="shared" si="123"/>
+        <v>8631.9617739119312</v>
+      </c>
+      <c r="BG96" s="1">
+        <f t="shared" si="123"/>
+        <v>8545.6421561728112</v>
+      </c>
+      <c r="BH96" s="1">
+        <f t="shared" si="123"/>
+        <v>8460.1857346110828</v>
+      </c>
+      <c r="BI96" s="1">
+        <f t="shared" si="123"/>
+        <v>8375.5838772649713</v>
+      </c>
+      <c r="BJ96" s="1">
+        <f t="shared" si="123"/>
+        <v>8291.8280384923219</v>
+      </c>
+      <c r="BK96" s="1">
+        <f t="shared" si="123"/>
+        <v>8208.9097581073984</v>
+      </c>
+      <c r="BL96" s="1">
+        <f t="shared" si="123"/>
+        <v>8126.820660526324</v>
+      </c>
+      <c r="BM96" s="1">
+        <f t="shared" si="123"/>
+        <v>8045.552453921061</v>
+      </c>
+      <c r="BN96" s="1">
+        <f t="shared" si="123"/>
+        <v>7965.0969293818507</v>
+      </c>
+      <c r="BO96" s="1">
+        <f t="shared" si="123"/>
+        <v>7885.4459600880318</v>
+      </c>
+      <c r="BP96" s="1">
+        <f t="shared" si="123"/>
+        <v>7806.5915004871513</v>
+      </c>
+      <c r="BQ96" s="1">
+        <f t="shared" si="123"/>
+        <v>7728.5255854822799</v>
+      </c>
+      <c r="BR96" s="1">
+        <f t="shared" si="123"/>
+        <v>7651.240329627457</v>
+      </c>
+      <c r="BS96" s="1">
+        <f t="shared" si="123"/>
+        <v>7574.7279263311821</v>
+      </c>
+      <c r="BT96" s="1">
+        <f t="shared" si="123"/>
+        <v>7498.9806470678704</v>
+      </c>
+      <c r="BU96" s="1">
+        <f t="shared" si="123"/>
+        <v>7423.9908405971919</v>
+      </c>
+      <c r="BV96" s="1">
+        <f t="shared" si="123"/>
+        <v>7349.7509321912203</v>
+      </c>
+      <c r="BW96" s="1">
+        <f t="shared" si="123"/>
+        <v>7276.2534228693085</v>
+      </c>
+      <c r="BX96" s="1">
+        <f t="shared" si="123"/>
+        <v>7203.4908886406156</v>
+      </c>
+      <c r="BY96" s="1">
+        <f t="shared" si="123"/>
+        <v>7131.4559797542097</v>
+      </c>
+      <c r="BZ96" s="1">
+        <f t="shared" si="123"/>
+        <v>7060.141419956668</v>
+      </c>
+      <c r="CA96" s="1">
+        <f t="shared" si="123"/>
+        <v>6989.5400057571014</v>
+      </c>
+      <c r="CB96" s="1">
+        <f t="shared" si="123"/>
+        <v>6919.6446056995301</v>
+      </c>
+      <c r="CC96" s="1">
+        <f t="shared" si="123"/>
+        <v>6850.4481596425348</v>
+      </c>
+      <c r="CD96" s="1">
+        <f t="shared" si="123"/>
+        <v>6781.9436780461092</v>
+      </c>
+      <c r="CE96" s="1">
+        <f t="shared" si="123"/>
+        <v>6714.1242412656484</v>
+      </c>
+      <c r="CF96" s="1">
+        <f t="shared" si="123"/>
+        <v>6646.9829988529918</v>
+      </c>
+      <c r="CG96" s="1">
+        <f t="shared" si="123"/>
+        <v>6580.5131688644615</v>
+      </c>
+      <c r="CH96" s="1">
+        <f t="shared" si="123"/>
+        <v>6514.7080371758166</v>
+      </c>
+      <c r="CI96" s="1">
+        <f t="shared" si="123"/>
+        <v>6449.5609568040582</v>
+      </c>
+      <c r="CJ96" s="1">
+        <f t="shared" si="123"/>
+        <v>6385.0653472360173</v>
+      </c>
+      <c r="CK96" s="1">
+        <f t="shared" si="123"/>
+        <v>6321.2146937636571</v>
+      </c>
+      <c r="CL96" s="1">
+        <f t="shared" si="123"/>
+        <v>6258.0025468260201</v>
+      </c>
+      <c r="CM96" s="1">
+        <f t="shared" si="123"/>
+        <v>6195.4225213577602</v>
+      </c>
+      <c r="CN96" s="1">
+        <f t="shared" si="123"/>
+        <v>6133.4682961441822</v>
+      </c>
+      <c r="CO96" s="1">
+        <f t="shared" si="123"/>
+        <v>6072.1336131827402</v>
+      </c>
+      <c r="CP96" s="1">
+        <f t="shared" si="123"/>
+        <v>6011.412277050913</v>
+      </c>
+      <c r="CQ96" s="1">
+        <f t="shared" si="123"/>
+        <v>5951.2981542804037</v>
+      </c>
+      <c r="CR96" s="1">
+        <f t="shared" si="123"/>
+        <v>5891.7851727375992</v>
+      </c>
+      <c r="CS96" s="1">
+        <f t="shared" si="123"/>
+        <v>5832.8673210102233</v>
+      </c>
+      <c r="CT96" s="1">
+        <f t="shared" si="123"/>
+        <v>5774.538647800121</v>
+      </c>
+      <c r="CU96" s="1">
+        <f t="shared" si="123"/>
+        <v>5716.7932613221201</v>
+      </c>
+      <c r="CV96" s="1">
+        <f t="shared" si="123"/>
+        <v>5659.6253287088985</v>
+      </c>
+      <c r="CW96" s="1">
+        <f t="shared" si="123"/>
+        <v>5603.0290754218095</v>
+      </c>
+      <c r="CX96" s="1">
+        <f t="shared" si="123"/>
+        <v>5546.9987846675913</v>
+      </c>
+      <c r="CY96" s="1">
+        <f t="shared" si="123"/>
+        <v>5491.528796820915</v>
+      </c>
+      <c r="CZ96" s="1">
+        <f t="shared" si="123"/>
+        <v>5436.6135088527062</v>
+      </c>
+      <c r="DA96" s="1">
+        <f t="shared" si="123"/>
+        <v>5382.2473737641794</v>
+      </c>
+      <c r="DB96" s="1">
+        <f t="shared" si="123"/>
+        <v>5328.4249000265372</v>
+      </c>
+      <c r="DC96" s="1">
+        <f t="shared" si="123"/>
+        <v>5275.1406510262714</v>
+      </c>
+      <c r="DD96" s="1">
+        <f t="shared" ref="DD96:EN96" si="124">DC96*(1+$AS$100)</f>
+        <v>5222.3892445160091</v>
+      </c>
+      <c r="DE96" s="1">
+        <f t="shared" si="124"/>
+        <v>5170.1653520708487</v>
+      </c>
+      <c r="DF96" s="1">
+        <f t="shared" si="124"/>
+        <v>5118.4636985501402</v>
+      </c>
+      <c r="DG96" s="1">
+        <f t="shared" si="124"/>
+        <v>5067.2790615646391</v>
+      </c>
+      <c r="DH96" s="1">
+        <f t="shared" si="124"/>
+        <v>5016.6062709489925</v>
+      </c>
+      <c r="DI96" s="1">
+        <f t="shared" si="124"/>
+        <v>4966.4402082395027</v>
+      </c>
+      <c r="DJ96" s="1">
+        <f t="shared" si="124"/>
+        <v>4916.7758061571076</v>
+      </c>
+      <c r="DK96" s="1">
+        <f t="shared" si="124"/>
+        <v>4867.6080480955361</v>
+      </c>
+      <c r="DL96" s="1">
+        <f t="shared" si="124"/>
+        <v>4818.9319676145806</v>
+      </c>
+      <c r="DM96" s="1">
+        <f t="shared" si="124"/>
+        <v>4770.7426479384349</v>
+      </c>
+      <c r="DN96" s="1">
+        <f t="shared" si="124"/>
+        <v>4723.0352214590503</v>
+      </c>
+      <c r="DO96" s="1">
+        <f t="shared" si="124"/>
+        <v>4675.80486924446</v>
+      </c>
+      <c r="DP96" s="1">
+        <f t="shared" si="124"/>
+        <v>4629.0468205520156</v>
+      </c>
+      <c r="DQ96" s="1">
+        <f t="shared" si="124"/>
+        <v>4582.7563523464951</v>
+      </c>
+      <c r="DR96" s="1">
+        <f t="shared" si="124"/>
+        <v>4536.9287888230301</v>
+      </c>
+      <c r="DS96" s="1">
+        <f t="shared" si="124"/>
+        <v>4491.5595009347999</v>
+      </c>
+      <c r="DT96" s="1">
+        <f t="shared" si="124"/>
+        <v>4446.6439059254517</v>
+      </c>
+      <c r="DU96" s="1">
+        <f t="shared" si="124"/>
+        <v>4402.1774668661974</v>
+      </c>
+      <c r="DV96" s="1">
+        <f t="shared" si="124"/>
+        <v>4358.1556921975352</v>
+      </c>
+      <c r="DW96" s="1">
+        <f t="shared" si="124"/>
+        <v>4314.5741352755595</v>
+      </c>
+      <c r="DX96" s="1">
+        <f t="shared" si="124"/>
+        <v>4271.4283939228035</v>
+      </c>
+      <c r="DY96" s="1">
+        <f t="shared" si="124"/>
+        <v>4228.7141099835753</v>
+      </c>
+      <c r="DZ96" s="1">
+        <f t="shared" si="124"/>
+        <v>4186.4269688837394</v>
+      </c>
+      <c r="EA96" s="1">
+        <f t="shared" si="124"/>
+        <v>4144.5626991949021</v>
+      </c>
+      <c r="EB96" s="1">
+        <f t="shared" si="124"/>
+        <v>4103.1170722029528</v>
+      </c>
+      <c r="EC96" s="1">
+        <f t="shared" si="124"/>
+        <v>4062.0859014809234</v>
+      </c>
+      <c r="ED96" s="1">
+        <f t="shared" si="124"/>
+        <v>4021.465042466114</v>
+      </c>
+      <c r="EE96" s="1">
+        <f t="shared" si="124"/>
+        <v>3981.2503920414529</v>
+      </c>
+      <c r="EF96" s="1">
+        <f t="shared" si="124"/>
+        <v>3941.4378881210382</v>
+      </c>
+      <c r="EG96" s="1">
+        <f t="shared" si="124"/>
+        <v>3902.0235092398279</v>
+      </c>
+      <c r="EH96" s="1">
+        <f t="shared" si="124"/>
+        <v>3863.0032741474297</v>
+      </c>
+      <c r="EI96" s="1">
+        <f t="shared" si="124"/>
+        <v>3824.3732414059555</v>
+      </c>
+      <c r="EJ96" s="1">
+        <f t="shared" si="124"/>
+        <v>3786.1295089918958</v>
+      </c>
+      <c r="EK96" s="1">
+        <f t="shared" si="124"/>
+        <v>3748.2682139019767</v>
+      </c>
+      <c r="EL96" s="1">
+        <f t="shared" si="124"/>
+        <v>3710.7855317629569</v>
+      </c>
+      <c r="EM96" s="1">
+        <f t="shared" si="124"/>
+        <v>3673.6776764453275</v>
+      </c>
+      <c r="EN96" s="1">
+        <f t="shared" si="124"/>
+        <v>3636.9408996808743</v>
+      </c>
+    </row>
+    <row r="97" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="L97" s="7"/>
+      <c r="M97" s="7"/>
+      <c r="N97" s="7"/>
+      <c r="O97" s="7"/>
+      <c r="P97" s="7"/>
+      <c r="Q97" s="7"/>
+      <c r="R97" s="7"/>
+      <c r="S97" s="7"/>
+      <c r="T97" s="7"/>
+      <c r="U97" s="7"/>
+      <c r="V97" s="7"/>
+      <c r="W97" s="7"/>
+      <c r="AC97" s="7"/>
+      <c r="AD97" s="7"/>
+      <c r="AE97" s="7"/>
+    </row>
+    <row r="98" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
         <v>94</v>
       </c>
-      <c r="L88" s="7"/>
-      <c r="M88" s="7"/>
-      <c r="N88" s="7"/>
-      <c r="O88" s="7"/>
-      <c r="P88" s="8">
-        <f t="shared" ref="P88:R88" si="132">P85/L85-1</f>
+      <c r="L98" s="7"/>
+      <c r="M98" s="7"/>
+      <c r="N98" s="7"/>
+      <c r="O98" s="7"/>
+      <c r="P98" s="8">
+        <f t="shared" ref="P98:R98" si="125">P95/L95-1</f>
         <v>-0.19465803318494534</v>
       </c>
-      <c r="Q88" s="8">
-        <f t="shared" si="132"/>
+      <c r="Q98" s="8">
+        <f t="shared" si="125"/>
         <v>-3.4986413043478271E-2</v>
       </c>
-      <c r="R88" s="8">
-        <f t="shared" si="132"/>
+      <c r="R98" s="8">
+        <f t="shared" si="125"/>
         <v>0.12254475925604025</v>
       </c>
-      <c r="S88" s="8">
-        <f>S85/O85-1</f>
+      <c r="S98" s="8">
+        <f>S95/O95-1</f>
         <v>-0.12873357228195936</v>
       </c>
-      <c r="T88" s="8">
-        <f t="shared" ref="T88:U88" si="133">T85/P85-1</f>
+      <c r="T98" s="8">
+        <f t="shared" ref="T98:W98" si="126">T95/P95-1</f>
         <v>-0.13182579564489116</v>
       </c>
-      <c r="U88" s="8">
-        <f t="shared" si="133"/>
+      <c r="U98" s="8">
+        <f t="shared" si="126"/>
         <v>-0.37521999296022523</v>
       </c>
-      <c r="V88" s="8"/>
-      <c r="W88" s="8"/>
-      <c r="AC88" s="7"/>
-      <c r="AD88" s="8">
-        <f t="shared" ref="AD88" si="134">AD85/AC85-1</f>
+      <c r="V98" s="8">
+        <f t="shared" si="126"/>
+        <v>-0.56875193558377202</v>
+      </c>
+      <c r="W98" s="8">
+        <f t="shared" si="126"/>
+        <v>-0.48577305450805619</v>
+      </c>
+      <c r="AC98" s="7"/>
+      <c r="AD98" s="8">
+        <f t="shared" ref="AD98" si="127">AD95/AC95-1</f>
         <v>3.6467557559169306E-2</v>
       </c>
-      <c r="AE88" s="8">
-        <f>AE85/AD85-1</f>
+      <c r="AE98" s="8">
+        <f>AE95/AD95-1</f>
         <v>-7.0135922330097134E-2</v>
       </c>
-      <c r="AR88" t="s">
-        <v>49</v>
-      </c>
-      <c r="AS88" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="89" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="AR89" t="s">
-        <v>50</v>
-      </c>
-      <c r="AS89" s="8">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="90" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="B90" t="s">
+      <c r="AF98" s="8">
+        <f>AF95/AE95-1</f>
+        <v>-0.39366855997327099</v>
+      </c>
+      <c r="AG98" s="8">
+        <f>AG95/AF95-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="100" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B100" t="s">
         <v>85</v>
       </c>
-      <c r="M90" s="2">
+      <c r="M100" s="2">
         <f>M24+L24</f>
         <v>-1277</v>
       </c>
-      <c r="N90" s="2">
+      <c r="N100" s="2">
         <f>N24+M24+L24</f>
         <v>-980</v>
       </c>
-      <c r="Q90" s="2">
+      <c r="Q100" s="2">
         <f>Q24+P24</f>
         <v>-1991</v>
       </c>
-      <c r="R90" s="2">
+      <c r="R100" s="2">
         <f>R24+Q24+P24</f>
         <v>-18630</v>
       </c>
-      <c r="U90" s="2">
+      <c r="U100" s="2">
         <f>U24+T24</f>
         <v>-3739</v>
       </c>
-      <c r="AR90" t="s">
+      <c r="V100" s="2">
+        <f>V24+U24+T24</f>
+        <v>324</v>
+      </c>
+      <c r="AR100" t="s">
+        <v>49</v>
+      </c>
+      <c r="AS100" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="101" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B101" t="s">
+        <v>77</v>
+      </c>
+      <c r="M101">
+        <v>3733</v>
+      </c>
+      <c r="N101">
+        <v>5753</v>
+      </c>
+      <c r="Q101">
+        <v>4403</v>
+      </c>
+      <c r="R101">
+        <v>7651</v>
+      </c>
+      <c r="U101">
+        <v>5213</v>
+      </c>
+      <c r="V101">
+        <v>7971</v>
+      </c>
+      <c r="AR101" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS101" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="102" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B102" t="s">
+        <v>78</v>
+      </c>
+      <c r="M102">
+        <v>1661</v>
+      </c>
+      <c r="N102">
+        <v>2433</v>
+      </c>
+      <c r="Q102">
+        <v>1959</v>
+      </c>
+      <c r="R102">
+        <v>2759</v>
+      </c>
+      <c r="U102">
+        <v>1348</v>
+      </c>
+      <c r="V102">
+        <v>1896</v>
+      </c>
+      <c r="AR102" t="s">
         <v>95</v>
       </c>
-      <c r="AS90" s="2">
-        <f>NPV(AS89,AF86:EN86)</f>
-        <v>117845.85718643072</v>
-      </c>
-    </row>
-    <row r="91" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="B91" t="s">
-        <v>77</v>
-      </c>
-      <c r="M91">
-        <v>3733</v>
-      </c>
-      <c r="N91">
-        <v>5753</v>
-      </c>
-      <c r="Q91">
-        <v>4403</v>
-      </c>
-      <c r="R91">
-        <v>7651</v>
-      </c>
-      <c r="U91">
-        <v>5213</v>
-      </c>
-      <c r="AR91" t="s">
+      <c r="AS102" s="2">
+        <f>NPV(AS101,AF96:EN96)</f>
+        <v>156095.86573176115</v>
+      </c>
+    </row>
+    <row r="103" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B103" t="s">
+        <v>24</v>
+      </c>
+      <c r="M103">
+        <v>255</v>
+      </c>
+      <c r="N103">
+        <v>718</v>
+      </c>
+      <c r="Q103">
+        <v>1291</v>
+      </c>
+      <c r="R103">
+        <v>3626</v>
+      </c>
+      <c r="U103">
+        <v>382</v>
+      </c>
+      <c r="V103">
+        <v>372</v>
+      </c>
+      <c r="AR103" t="s">
         <v>52</v>
       </c>
-      <c r="AS91" s="2">
+      <c r="AS103" s="2">
         <f>Main!D8</f>
-        <v>-24168</v>
-      </c>
-    </row>
-    <row r="92" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="B92" t="s">
-        <v>78</v>
-      </c>
-      <c r="M92">
-        <v>1661</v>
-      </c>
-      <c r="N92">
-        <v>2433</v>
-      </c>
-      <c r="Q92">
-        <v>1959</v>
-      </c>
-      <c r="R92">
-        <v>2759</v>
-      </c>
-      <c r="U92">
-        <v>1348</v>
-      </c>
-      <c r="AR92" t="s">
+        <v>-6951</v>
+      </c>
+    </row>
+    <row r="104" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B104" t="s">
+        <v>79</v>
+      </c>
+      <c r="M104">
+        <v>909</v>
+      </c>
+      <c r="N104">
+        <v>1336</v>
+      </c>
+      <c r="Q104">
+        <v>717</v>
+      </c>
+      <c r="R104">
+        <v>1081</v>
+      </c>
+      <c r="U104">
+        <v>474</v>
+      </c>
+      <c r="V104">
+        <v>708</v>
+      </c>
+      <c r="AR104" t="s">
         <v>53</v>
       </c>
-      <c r="AS92" s="2">
-        <f>AS90+AS91</f>
-        <v>93677.857186430716</v>
-      </c>
-    </row>
-    <row r="93" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="B93" t="s">
-        <v>24</v>
-      </c>
-      <c r="M93">
-        <v>255</v>
-      </c>
-      <c r="N93">
-        <v>718</v>
-      </c>
-      <c r="Q93">
-        <v>1291</v>
-      </c>
-      <c r="R93">
-        <v>3626</v>
-      </c>
-      <c r="U93">
-        <v>382</v>
-      </c>
-      <c r="AR93" t="s">
+      <c r="AS104" s="2">
+        <f>AS102+AS103</f>
+        <v>149144.86573176115</v>
+      </c>
+    </row>
+    <row r="105" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B105" t="s">
+        <v>58</v>
+      </c>
+      <c r="M105">
+        <v>-146</v>
+      </c>
+      <c r="N105">
+        <v>47</v>
+      </c>
+      <c r="Q105">
+        <v>-84</v>
+      </c>
+      <c r="R105">
+        <v>75</v>
+      </c>
+      <c r="U105">
+        <v>-390</v>
+      </c>
+      <c r="V105">
+        <v>-611</v>
+      </c>
+      <c r="AR105" t="s">
         <v>54</v>
       </c>
-      <c r="AS93" s="9">
-        <f>AS92/AP25</f>
-        <v>21.569849686030558</v>
-      </c>
-    </row>
-    <row r="94" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="B94" t="s">
-        <v>79</v>
-      </c>
-      <c r="M94">
-        <v>909</v>
-      </c>
-      <c r="N94">
-        <v>1336</v>
-      </c>
-      <c r="Q94">
-        <v>717</v>
-      </c>
-      <c r="R94">
-        <v>1081</v>
-      </c>
-      <c r="U94">
-        <v>474</v>
-      </c>
-      <c r="AR94" t="s">
+      <c r="AS105" s="9">
+        <f>AS104/AP25</f>
+        <v>33.040510795693656</v>
+      </c>
+    </row>
+    <row r="106" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B106" t="s">
+        <v>111</v>
+      </c>
+      <c r="V106">
+        <v>1687</v>
+      </c>
+      <c r="AR106" t="s">
         <v>55</v>
       </c>
-      <c r="AS94" s="9">
+      <c r="AS106" s="9">
         <f>Main!D3</f>
-        <v>36.729999999999997</v>
-      </c>
-    </row>
-    <row r="95" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="B95" t="s">
-        <v>58</v>
-      </c>
-      <c r="M95">
-        <v>-146</v>
-      </c>
-      <c r="N95">
-        <v>47</v>
-      </c>
-      <c r="Q95">
-        <v>-84</v>
-      </c>
-      <c r="R95">
-        <v>75</v>
-      </c>
-      <c r="U95">
-        <v>-390</v>
-      </c>
-    </row>
-    <row r="96" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="B96" t="s">
+        <v>38.28</v>
+      </c>
+    </row>
+    <row r="107" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B107" t="s">
+        <v>112</v>
+      </c>
+      <c r="V107">
+        <v>-5355</v>
+      </c>
+    </row>
+    <row r="108" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B108" t="s">
         <v>80</v>
       </c>
-      <c r="N96">
+      <c r="N108">
         <v>-1376</v>
       </c>
-      <c r="R96">
+      <c r="R108">
         <v>6368</v>
       </c>
-      <c r="U96">
+      <c r="U108">
         <v>106</v>
       </c>
-    </row>
-    <row r="97" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B97" t="s">
+      <c r="V108">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="109" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B109" t="s">
         <v>81</v>
       </c>
-      <c r="N97">
+      <c r="N109">
         <v>-87</v>
       </c>
-      <c r="R97">
+      <c r="R109">
         <v>2290</v>
       </c>
-      <c r="U97">
+      <c r="U109">
         <v>482</v>
       </c>
-    </row>
-    <row r="98" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B98" t="s">
+      <c r="V109">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="110" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B110" t="s">
         <v>59</v>
       </c>
-      <c r="M98">
+      <c r="M110">
         <v>1137</v>
       </c>
-      <c r="N98">
+      <c r="N110">
         <v>1290</v>
       </c>
-      <c r="Q98">
+      <c r="Q110">
         <v>272</v>
       </c>
-      <c r="R98">
+      <c r="R110">
         <v>282</v>
       </c>
-      <c r="U98">
+      <c r="U110">
         <v>1004</v>
       </c>
-    </row>
-    <row r="99" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B99" t="s">
+      <c r="V110">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="111" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B111" t="s">
         <v>60</v>
       </c>
-      <c r="M99">
+      <c r="M111">
         <v>1240</v>
       </c>
-      <c r="N99">
+      <c r="N111">
         <v>1758</v>
       </c>
-      <c r="Q99">
+      <c r="Q111">
         <v>-116</v>
       </c>
-      <c r="R99">
+      <c r="R111">
         <v>-969</v>
       </c>
-      <c r="U99">
+      <c r="U111">
         <v>99</v>
       </c>
-    </row>
-    <row r="100" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B100" t="s">
+      <c r="V111">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="112" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B112" t="s">
         <v>69</v>
       </c>
-      <c r="M100">
+      <c r="M112">
         <v>-1102</v>
       </c>
-      <c r="N100">
+      <c r="N112">
         <v>-1082</v>
       </c>
-      <c r="Q100">
+      <c r="Q112">
         <v>184</v>
       </c>
-      <c r="R100">
+      <c r="R112">
         <v>566</v>
       </c>
-      <c r="U100">
+      <c r="U112">
         <v>114</v>
       </c>
-    </row>
-    <row r="101" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B101" t="s">
+      <c r="V112">
+        <v>-281</v>
+      </c>
+    </row>
+    <row r="113" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B113" t="s">
         <v>70</v>
       </c>
-      <c r="M101">
+      <c r="M113">
         <v>-1340</v>
       </c>
-      <c r="N101">
+      <c r="N113">
         <v>-1171</v>
       </c>
-      <c r="Q101">
+      <c r="Q113">
         <v>-1309</v>
       </c>
-      <c r="R101">
+      <c r="R113">
         <v>1384</v>
       </c>
-      <c r="U101">
+      <c r="U113">
         <v>1022</v>
       </c>
-    </row>
-    <row r="102" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B102" t="s">
+      <c r="V113">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="114" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B114" t="s">
         <v>29</v>
       </c>
-      <c r="M102">
+      <c r="M114">
         <v>-2186</v>
       </c>
-      <c r="N102">
+      <c r="N114">
         <v>-1300</v>
       </c>
-      <c r="Q102">
+      <c r="Q114">
         <v>-2174</v>
       </c>
-      <c r="R102">
+      <c r="R114">
         <v>-930</v>
       </c>
-      <c r="U102">
+      <c r="U114">
         <v>-1338</v>
       </c>
-    </row>
-    <row r="103" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B103" t="s">
+      <c r="V114">
+        <v>-1196</v>
+      </c>
+    </row>
+    <row r="115" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B115" t="s">
         <v>82</v>
       </c>
-      <c r="M103">
+      <c r="M115">
         <v>-1843</v>
       </c>
-      <c r="N103">
+      <c r="N115">
         <v>-487</v>
       </c>
-      <c r="Q103">
+      <c r="Q115">
         <v>-1983</v>
       </c>
-      <c r="R103">
+      <c r="R115">
         <v>20</v>
       </c>
-      <c r="U103">
+      <c r="U115">
         <v>-1742</v>
       </c>
-    </row>
-    <row r="104" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B104" t="s">
+      <c r="V115">
+        <v>-1423</v>
+      </c>
+    </row>
+    <row r="116" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B116" t="s">
         <v>83</v>
       </c>
-      <c r="M104" s="2">
-        <f>M90+SUM(M91:M103)</f>
+      <c r="M116" s="2">
+        <f>M100+SUM(M101:M115)</f>
         <v>1041</v>
       </c>
-      <c r="N104" s="2">
-        <f>N90+SUM(N91:N103)</f>
+      <c r="N116" s="2">
+        <f>N100+SUM(N101:N115)</f>
         <v>6852</v>
       </c>
-      <c r="Q104" s="2">
-        <f>Q90+SUM(Q91:Q103)</f>
+      <c r="Q116" s="2">
+        <f>Q100+SUM(Q101:Q115)</f>
         <v>1169</v>
       </c>
-      <c r="R104" s="2">
-        <f>R90+SUM(R91:R103)</f>
+      <c r="R116" s="2">
+        <f>R100+SUM(R101:R115)</f>
         <v>5573</v>
       </c>
-      <c r="U104" s="2">
-        <f>U90+SUM(U91:U103)</f>
+      <c r="U116" s="2">
+        <f>U100+SUM(U101:U115)</f>
         <v>3035</v>
       </c>
-    </row>
-    <row r="105" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B105" t="s">
+      <c r="V116" s="2">
+        <f>V100+SUM(V101:V115)</f>
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="117" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B117" t="s">
         <v>63</v>
       </c>
-      <c r="M105">
+      <c r="M117">
         <v>13301</v>
       </c>
-      <c r="N105">
+      <c r="N117">
         <v>19054</v>
       </c>
-      <c r="Q105">
+      <c r="Q117">
         <v>11652</v>
       </c>
-      <c r="R105">
+      <c r="R117">
         <v>18110</v>
       </c>
-      <c r="U105">
+      <c r="U117">
         <v>8733</v>
+      </c>
+      <c r="V117">
+        <v>11518</v>
       </c>
     </row>
   </sheetData>
